--- a/Översikt GÖTENE.xlsx
+++ b/Översikt GÖTENE.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44642</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45352</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45847</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>45846</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>46234</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>44827</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>44490</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 5086-2024</t>
+          <t>A 41724-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45330</v>
+        <v>44827</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1815,17 +1815,17 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1839,7 +1839,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1848,49 +1848,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 5086-2024 artfynd.xlsx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 41724-2022 artfynd.xlsx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 5086-2024 karta.png", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 41724-2022 karta.png", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 5086-2024 georefererad karta.tif", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 41724-2022 georefererad karta.tif", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 5086-2024 FSC-klagomål.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 41724-2022 FSC-klagomål.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 5086-2024 FSC-klagomål mail.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 41724-2022 FSC-klagomål mail.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 5086-2024 tillsynsbegäran.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 41724-2022 tillsynsbegäran.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 5086-2024 tillsynsbegäran mail.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 41724-2022 tillsynsbegäran mail.docx", "A 41724-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 28273-2023</t>
+          <t>A 32909-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45099</v>
+        <v>45839</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1920,17 +1920,17 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1944,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1960,42 +1960,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 28273-2023 artfynd.xlsx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32909-2025 artfynd.xlsx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 28273-2023 karta.png", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32909-2025 karta.png", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 28273-2023 georefererad karta.tif", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32909-2025 georefererad karta.tif", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 28273-2023 FSC-klagomål.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32909-2025 FSC-klagomål.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 28273-2023 FSC-klagomål mail.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32909-2025 FSC-klagomål mail.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 28273-2023 tillsynsbegäran.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32909-2025 tillsynsbegäran.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 28273-2023 tillsynsbegäran mail.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32909-2025 tillsynsbegäran mail.docx", "A 32909-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32909-2025</t>
+          <t>A 47393-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45839</v>
+        <v>45930</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2065,42 +2065,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Korallticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32909-2025 artfynd.xlsx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 47393-2025 artfynd.xlsx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32909-2025 karta.png", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 47393-2025 karta.png", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32909-2025 georefererad karta.tif", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 47393-2025 georefererad karta.tif", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32909-2025 FSC-klagomål.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 47393-2025 FSC-klagomål.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32909-2025 FSC-klagomål mail.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 47393-2025 FSC-klagomål mail.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32909-2025 tillsynsbegäran.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 47393-2025 tillsynsbegäran.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32909-2025 tillsynsbegäran mail.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 47393-2025 tillsynsbegäran mail.docx", "A 47393-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 41724-2022</t>
+          <t>A 50366-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44827</v>
+        <v>45944</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2170,42 +2170,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Korallticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 41724-2022 artfynd.xlsx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 50366-2025 artfynd.xlsx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 41724-2022 karta.png", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 50366-2025 karta.png", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 41724-2022 georefererad karta.tif", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 50366-2025 georefererad karta.tif", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 41724-2022 FSC-klagomål.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 50366-2025 FSC-klagomål.docx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 41724-2022 FSC-klagomål mail.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 50366-2025 FSC-klagomål mail.docx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 41724-2022 tillsynsbegäran.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 50366-2025 tillsynsbegäran.docx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 41724-2022 tillsynsbegäran mail.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 50366-2025 tillsynsbegäran mail.docx", "A 50366-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 47393-2025</t>
+          <t>A 45211-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45930</v>
+        <v>44844</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2235,16 +2235,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2259,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2271,46 +2271,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Korallticka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 47393-2025 artfynd.xlsx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 45211-2022 artfynd.xlsx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 47393-2025 karta.png", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 45211-2022 karta.png", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 47393-2025 georefererad karta.tif", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 45211-2022 georefererad karta.tif", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 47393-2025 FSC-klagomål.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 45211-2022 FSC-klagomål.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 47393-2025 FSC-klagomål mail.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 45211-2022 FSC-klagomål mail.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 47393-2025 tillsynsbegäran.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 45211-2022 tillsynsbegäran.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 47393-2025 tillsynsbegäran mail.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 45211-2022 tillsynsbegäran mail.docx", "A 45211-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 50366-2025</t>
+          <t>A 18647-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45944</v>
+        <v>45763</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2339,17 +2339,22 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2364,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2380,42 +2385,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Korallticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 50366-2025 artfynd.xlsx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 18647-2025 artfynd.xlsx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 50366-2025 karta.png", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 18647-2025 karta.png", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 50366-2025 georefererad karta.tif", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 18647-2025 georefererad karta.tif", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 50366-2025 FSC-klagomål.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 18647-2025 FSC-klagomål.docx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 50366-2025 FSC-klagomål mail.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 18647-2025 FSC-klagomål mail.docx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 50366-2025 tillsynsbegäran.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 18647-2025 tillsynsbegäran.docx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 50366-2025 tillsynsbegäran mail.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 18647-2025 tillsynsbegäran mail.docx", "A 18647-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 18647-2025</t>
+          <t>A 33478-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2429,10 +2434,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45763</v>
+        <v>46247</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2444,13 +2449,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2490,42 +2490,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 18647-2025 artfynd.xlsx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 33478-2026 artfynd.xlsx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 18647-2025 karta.png", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 33478-2026 karta.png", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 18647-2025 georefererad karta.tif", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 33478-2026 georefererad karta.tif", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 18647-2025 FSC-klagomål.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 33478-2026 FSC-klagomål.docx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 18647-2025 FSC-klagomål mail.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 33478-2026 FSC-klagomål mail.docx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 18647-2025 tillsynsbegäran.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 33478-2026 tillsynsbegäran.docx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 18647-2025 tillsynsbegäran mail.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 33478-2026 tillsynsbegäran mail.docx", "A 33478-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 14296-2023</t>
+          <t>A 31326-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45011</v>
+        <v>46219</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2564,10 +2564,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2582,7 +2582,7 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2591,50 +2591,50 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Pilgrimsfalk</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 14296-2023 artfynd.xlsx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 31326-2026 artfynd.xlsx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 14296-2023 karta.png", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 31326-2026 karta.png", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 14296-2023 georefererad karta.tif", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 31326-2026 georefererad karta.tif", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 14296-2023 FSC-klagomål.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 31326-2026 FSC-klagomål.docx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 14296-2023 FSC-klagomål mail.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 31326-2026 FSC-klagomål mail.docx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 14296-2023 tillsynsbegäran.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 31326-2026 tillsynsbegäran.docx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 14296-2023 tillsynsbegäran mail.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 31326-2026 tillsynsbegäran mail.docx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 14296-2023 prioriterade fågelarter.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 31326-2026 prioriterade fågelarter.docx", "A 31326-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 19083-2022</t>
+          <t>A 32224-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44691</v>
+        <v>46237</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2664,19 +2664,19 @@
         </is>
       </c>
       <c r="I21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2700,46 +2700,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Läderbagge</t>
+          <t>Backmåra</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 19083-2022 artfynd.xlsx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32224-2026 artfynd.xlsx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 19083-2022 karta.png", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32224-2026 karta.png", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 19083-2022 georefererad karta.tif", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32224-2026 georefererad karta.tif", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 19083-2022 FSC-klagomål.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32224-2026 FSC-klagomål.docx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 19083-2022 FSC-klagomål mail.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32224-2026 FSC-klagomål mail.docx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 19083-2022 tillsynsbegäran.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32224-2026 tillsynsbegäran.docx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 19083-2022 tillsynsbegäran mail.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32224-2026 tillsynsbegäran mail.docx", "A 32224-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 45211-2022</t>
+          <t>A 19083-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44844</v>
+        <v>44691</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2769,20 +2769,20 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>1</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
@@ -2793,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2809,42 +2809,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Läderbagge</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 45211-2022 artfynd.xlsx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 19083-2022 artfynd.xlsx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 45211-2022 karta.png", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 19083-2022 karta.png", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 45211-2022 georefererad karta.tif", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 19083-2022 georefererad karta.tif", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 45211-2022 FSC-klagomål.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 19083-2022 FSC-klagomål.docx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 45211-2022 FSC-klagomål mail.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 19083-2022 FSC-klagomål mail.docx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 45211-2022 tillsynsbegäran.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 19083-2022 tillsynsbegäran.docx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 45211-2022 tillsynsbegäran mail.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 19083-2022 tillsynsbegäran mail.docx", "A 19083-2022")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32224-2026</t>
+          <t>A 14296-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46237</v>
+        <v>45011</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2874,19 +2874,19 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2901,7 +2901,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2910,46 +2910,50 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Backmåra</t>
+          <t>Pilgrimsfalk</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32224-2026 artfynd.xlsx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 14296-2023 artfynd.xlsx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32224-2026 karta.png", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 14296-2023 karta.png", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32224-2026 georefererad karta.tif", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 14296-2023 georefererad karta.tif", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32224-2026 FSC-klagomål.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 14296-2023 FSC-klagomål.docx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32224-2026 FSC-klagomål mail.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 14296-2023 FSC-klagomål mail.docx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32224-2026 tillsynsbegäran.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 14296-2023 tillsynsbegäran.docx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32224-2026 tillsynsbegäran mail.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 14296-2023 tillsynsbegäran mail.docx", "A 14296-2023")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 14296-2023 prioriterade fågelarter.docx", "A 14296-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 33478-2026</t>
+          <t>A 5086-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2963,10 +2967,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46247</v>
+        <v>45330</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2979,7 +2983,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3012,49 +3016,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
         <v>1</v>
       </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 33478-2026 artfynd.xlsx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 5086-2024 artfynd.xlsx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 33478-2026 karta.png", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 5086-2024 karta.png", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 33478-2026 georefererad karta.tif", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 5086-2024 georefererad karta.tif", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 33478-2026 FSC-klagomål.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 5086-2024 FSC-klagomål.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 33478-2026 FSC-klagomål mail.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 5086-2024 FSC-klagomål mail.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 33478-2026 tillsynsbegäran.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 5086-2024 tillsynsbegäran.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 33478-2026 tillsynsbegäran mail.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 5086-2024 tillsynsbegäran mail.docx", "A 5086-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 31326-2026</t>
+          <t>A 28273-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3068,10 +3072,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46219</v>
+        <v>45099</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3084,7 +3088,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>5.1</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3093,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3108,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3124,39 +3128,35 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 31326-2026 artfynd.xlsx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 28273-2023 artfynd.xlsx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 31326-2026 karta.png", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 28273-2023 karta.png", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 31326-2026 georefererad karta.tif", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 28273-2023 georefererad karta.tif", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 31326-2026 FSC-klagomål.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 28273-2023 FSC-klagomål.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 31326-2026 FSC-klagomål mail.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 28273-2023 FSC-klagomål mail.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 31326-2026 tillsynsbegäran.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 28273-2023 tillsynsbegäran.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 31326-2026 tillsynsbegäran mail.docx", "A 31326-2026")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 31326-2026 prioriterade fågelarter.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 28273-2023 tillsynsbegäran mail.docx", "A 28273-2023")</f>
         <v/>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
         <v>45372</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>44490</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>44645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>44490</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>44490</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>44507</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>44614</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>44859</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>44840</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>44566</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>44684</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>44477</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>44507</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>44581</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>44761</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>44757</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>44869</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>44812</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>44848</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>44865</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>44490</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>44603</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>44475</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>44803</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 61148-2021</t>
+          <t>A 38945-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44498</v>
+        <v>44816</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5327,7 +5327,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38945-2022</t>
+          <t>A 61148-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44816</v>
+        <v>44498</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5400,7 +5400,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 9607-2024</t>
+          <t>A 58418-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45361</v>
+        <v>45634</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 58650-2023</t>
+          <t>A 36381-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45251</v>
+        <v>45152</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5546,7 +5546,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 45239-2022</t>
+          <t>A 8330-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5560,10 +5560,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44844</v>
+        <v>45352</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5575,13 +5575,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5624,7 +5619,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 49536-2021</t>
+          <t>A 13276-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5638,10 +5633,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44455</v>
+        <v>45386</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5653,13 +5648,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5702,7 +5692,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 52352-2023</t>
+          <t>A 49700-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5716,10 +5706,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45224</v>
+        <v>44455</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5732,7 +5722,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5775,7 +5765,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 28264-2023</t>
+          <t>A 849-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5789,10 +5779,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45099</v>
+        <v>44931</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5805,7 +5795,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5848,7 +5838,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28268-2023</t>
+          <t>A 25434-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5862,10 +5852,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45099</v>
+        <v>45800</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5878,7 +5868,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5921,7 +5911,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 49700-2021</t>
+          <t>A 25435-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5935,10 +5925,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44455</v>
+        <v>45800</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5951,7 +5941,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5994,7 +5984,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 13276-2024</t>
+          <t>A 25436-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6008,10 +5998,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45386</v>
+        <v>45800</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6024,7 +6014,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6067,7 +6057,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 1352-2023</t>
+          <t>A 26105-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6077,14 +6067,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44931</v>
+        <v>45805</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6097,7 +6087,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.8</v>
+        <v>5.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6140,7 +6130,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 72879-2021</t>
+          <t>A 10703-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6154,10 +6144,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44547</v>
+        <v>45722</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6170,7 +6160,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6213,7 +6203,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 28267-2023</t>
+          <t>A 44608-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6227,10 +6217,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45099</v>
+        <v>45189</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6243,7 +6233,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6286,7 +6276,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 62499-2022</t>
+          <t>A 61194-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6300,10 +6290,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44924</v>
+        <v>45645</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6317,11 +6307,11 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6364,7 +6354,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3932-2022</t>
+          <t>A 41721-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6378,10 +6368,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44587</v>
+        <v>44827</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6394,7 +6384,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6437,7 +6427,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 28390-2025</t>
+          <t>A 31917-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6451,10 +6441,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45819</v>
+        <v>44777</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6466,13 +6456,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6515,7 +6500,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 58418-2024</t>
+          <t>A 39998-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6529,10 +6514,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45634</v>
+        <v>45894</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6545,7 +6530,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.4</v>
+        <v>4.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6588,7 +6573,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 13170-2024</t>
+          <t>A 28390-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6602,10 +6587,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45386</v>
+        <v>45819</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6617,8 +6602,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6661,7 +6651,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 45180-2024</t>
+          <t>A 11889-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6675,10 +6665,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45575</v>
+        <v>45376</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6691,7 +6681,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>14.7</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6734,7 +6724,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 36304-2023</t>
+          <t>A 11772-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6748,10 +6738,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45152</v>
+        <v>45373</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6764,7 +6754,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6807,7 +6797,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 31258-2025</t>
+          <t>A 11773-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6821,10 +6811,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45833</v>
+        <v>45373</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6837,7 +6827,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5.2</v>
+        <v>1.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6880,7 +6870,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 49256-2023</t>
+          <t>A 3960-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6894,10 +6884,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45210</v>
+        <v>46044</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6909,8 +6899,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6953,7 +6948,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 61194-2024</t>
+          <t>A 31258-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6967,10 +6962,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45645</v>
+        <v>45833</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6982,13 +6977,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7031,7 +7021,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 32967-2025</t>
+          <t>A 5044-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7045,10 +7035,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45839</v>
+        <v>46049</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7061,7 +7051,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>5.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7104,7 +7094,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 10596-2024</t>
+          <t>A 32967-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7118,10 +7108,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45366</v>
+        <v>45839</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7134,7 +7124,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7177,7 +7167,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 39998-2025</t>
+          <t>A 45007-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7191,10 +7181,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45894</v>
+        <v>45918</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7207,7 +7197,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7250,7 +7240,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 21285-2024</t>
+          <t>A 17010-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7264,10 +7254,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45440</v>
+        <v>44676</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7280,7 +7270,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7323,7 +7313,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 6925-2023</t>
+          <t>A 61021-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7333,14 +7323,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44967</v>
+        <v>44914</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7352,13 +7342,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7401,7 +7386,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 58236-2024</t>
+          <t>A 6925-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7415,10 +7400,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45632</v>
+        <v>44967</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7436,7 +7421,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7479,7 +7464,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 58691-2024</t>
+          <t>A 47175-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7493,10 +7478,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45635</v>
+        <v>45930</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7508,13 +7493,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7557,7 +7537,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 41721-2022</t>
+          <t>A 47383-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7571,10 +7551,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44827</v>
+        <v>45930</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7587,7 +7567,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7630,7 +7610,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 55764-2024</t>
+          <t>A 47385-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7644,10 +7624,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45623</v>
+        <v>45930</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7660,7 +7640,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7703,7 +7683,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 13450-2025</t>
+          <t>A 30205-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7717,10 +7697,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45736</v>
+        <v>45110</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7733,7 +7713,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.7</v>
+        <v>6.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7776,7 +7756,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 56169-2024</t>
+          <t>A 47389-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7790,10 +7770,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45624</v>
+        <v>45930</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7806,7 +7786,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>19.7</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7849,7 +7829,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 850-2023</t>
+          <t>A 58236-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7863,10 +7843,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44931</v>
+        <v>45632</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7878,8 +7858,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7922,7 +7907,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 45007-2025</t>
+          <t>A 58691-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7936,10 +7921,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45918</v>
+        <v>45635</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7951,8 +7936,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7995,7 +7985,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 47385-2025</t>
+          <t>A 13450-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8009,10 +7999,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45930</v>
+        <v>45736</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8025,7 +8015,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8068,7 +8058,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 47175-2025</t>
+          <t>A 22278-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8082,10 +8072,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45930</v>
+        <v>45446</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8098,7 +8088,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8141,7 +8131,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 47389-2025</t>
+          <t>A 10630-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8155,10 +8145,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45930</v>
+        <v>46078</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8214,7 +8204,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 10630-2026</t>
+          <t>A 11459-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8228,10 +8218,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46078</v>
+        <v>46083</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8244,7 +8234,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8287,7 +8277,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 47383-2025</t>
+          <t>A 11460-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8301,10 +8291,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45930</v>
+        <v>46083</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8317,7 +8307,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8360,7 +8350,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 11459-2026</t>
+          <t>A 11630-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8374,10 +8364,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8389,8 +8379,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8433,7 +8428,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 61294-2024</t>
+          <t>A 17069-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8447,10 +8442,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45645</v>
+        <v>45034</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8463,7 +8458,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8506,7 +8501,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 11460-2026</t>
+          <t>A 1379-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8520,10 +8515,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46083</v>
+        <v>45667</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8536,7 +8531,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8579,7 +8574,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 12660-2023</t>
+          <t>A 52141-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8589,14 +8584,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45000</v>
+        <v>45953</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8609,7 +8604,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8652,7 +8647,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 11630-2026</t>
+          <t>A 45180-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8666,10 +8661,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46084</v>
+        <v>45575</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8681,13 +8676,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>1.7</v>
+        <v>14.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8730,7 +8720,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 62390-2023</t>
+          <t>A 14502-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8744,10 +8734,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45268</v>
+        <v>45012</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8760,7 +8750,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8803,7 +8793,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 62402-2023</t>
+          <t>A 13340-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8817,10 +8807,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45268</v>
+        <v>44645</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8833,7 +8823,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8876,7 +8866,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 11771-2024</t>
+          <t>A 13348-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8890,10 +8880,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45373</v>
+        <v>44645</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8906,7 +8896,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8949,7 +8939,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 31981-2023</t>
+          <t>A 13366-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8963,10 +8953,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45119</v>
+        <v>44645</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8979,7 +8969,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9022,7 +9012,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 52141-2025</t>
+          <t>A 15646-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9036,10 +9026,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45953</v>
+        <v>45021</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9052,7 +9042,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9095,7 +9085,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 15646-2023</t>
+          <t>A 18776-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9109,10 +9099,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45021</v>
+        <v>46128</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9125,7 +9115,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9168,7 +9158,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 56365-2025</t>
+          <t>A 9607-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9182,10 +9172,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45974</v>
+        <v>45361</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9198,7 +9188,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9241,7 +9231,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 56347-2025</t>
+          <t>A 56365-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9258,7 +9248,7 @@
         <v>45974</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9271,7 +9261,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>10.9</v>
+        <v>1.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9314,7 +9304,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 56352-2025</t>
+          <t>A 56347-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9331,7 +9321,7 @@
         <v>45974</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9344,7 +9334,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>5.9</v>
+        <v>10.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9387,7 +9377,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 56346-2025</t>
+          <t>A 56352-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9404,7 +9394,7 @@
         <v>45974</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9417,7 +9407,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>18.8</v>
+        <v>5.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9460,7 +9450,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 56340-2025</t>
+          <t>A 56414-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9474,10 +9464,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9490,7 +9480,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9533,7 +9523,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 56417-2025</t>
+          <t>A 56340-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9547,10 +9537,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45975</v>
+        <v>45974</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9563,7 +9553,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9606,7 +9596,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 56414-2025</t>
+          <t>A 56417-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9623,7 +9613,7 @@
         <v>45975</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9636,7 +9626,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9679,7 +9669,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 62510-2022</t>
+          <t>A 56346-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9693,10 +9683,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44924</v>
+        <v>45974</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9708,13 +9698,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>0.6</v>
+        <v>18.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9757,7 +9742,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 61021-2022</t>
+          <t>A 45013-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9767,14 +9752,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44914</v>
+        <v>45918</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9787,7 +9772,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9830,7 +9815,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 849-2023</t>
+          <t>A 58517-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9844,10 +9829,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44931</v>
+        <v>45985</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9860,7 +9845,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9903,7 +9888,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 58766-2025</t>
+          <t>A 58520-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9917,10 +9902,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45986</v>
+        <v>45985</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9933,7 +9918,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9976,7 +9961,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 58767-2025</t>
+          <t>A 1662-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9990,10 +9975,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45986</v>
+        <v>45670</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10006,7 +9991,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10049,7 +10034,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 58517-2025</t>
+          <t>A 58766-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10063,10 +10048,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10079,7 +10064,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10122,7 +10107,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 58520-2025</t>
+          <t>A 9145-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10136,10 +10121,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45985</v>
+        <v>44974</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10152,7 +10137,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10195,7 +10180,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 18776-2026</t>
+          <t>A 58767-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10209,10 +10194,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46128</v>
+        <v>45986</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10225,7 +10210,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10268,7 +10253,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 60559-2025</t>
+          <t>A 30174-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10282,10 +10267,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45995</v>
+        <v>44757</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10298,7 +10283,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.5</v>
+        <v>5.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10341,7 +10326,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 31969-2023</t>
+          <t>A 34161-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10355,10 +10340,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45119</v>
+        <v>45845</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10371,7 +10356,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10414,7 +10399,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 31978-2023</t>
+          <t>A 60559-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10428,10 +10413,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45119</v>
+        <v>45995</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10444,7 +10429,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10487,7 +10472,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 28258-2023</t>
+          <t>A 13268-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10501,10 +10486,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45099</v>
+        <v>45386</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10517,7 +10502,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.7</v>
+        <v>6.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10560,7 +10545,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 22278-2024</t>
+          <t>A 10451-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10574,10 +10559,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45446</v>
+        <v>45366</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10589,8 +10574,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10633,7 +10623,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 17069-2023</t>
+          <t>A 25594-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10643,14 +10633,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45034</v>
+        <v>45803</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10663,7 +10653,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10706,7 +10696,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 30174-2022</t>
+          <t>A 20710-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10720,10 +10710,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44757</v>
+        <v>46141</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10736,7 +10726,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>5.1</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10779,7 +10769,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 59074-2023</t>
+          <t>A 12660-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10789,14 +10779,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45252</v>
+        <v>45000</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10809,7 +10799,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10852,7 +10842,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 11772-2024</t>
+          <t>A 22055-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10866,10 +10856,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45373</v>
+        <v>45069</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10882,7 +10872,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10925,7 +10915,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 11773-2024</t>
+          <t>A 10596-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10939,10 +10929,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45373</v>
+        <v>45366</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10955,7 +10945,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10998,7 +10988,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 8765-2022</t>
+          <t>A 20811-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11012,10 +11002,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44614</v>
+        <v>46141</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11027,13 +11017,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11076,7 +11061,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 3960-2026</t>
+          <t>A 33162-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11090,10 +11075,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46044</v>
+        <v>45518</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11105,13 +11090,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11154,7 +11134,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 5044-2026</t>
+          <t>A 20812-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11168,10 +11148,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46049</v>
+        <v>46141</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11184,7 +11164,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11227,7 +11207,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 30205-2023</t>
+          <t>A 20700-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11241,10 +11221,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45110</v>
+        <v>46141</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11257,7 +11237,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>6.8</v>
+        <v>1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11300,7 +11280,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 45013-2025</t>
+          <t>A 21369-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11314,10 +11294,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45918</v>
+        <v>46147</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11373,7 +11353,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 34161-2025</t>
+          <t>A 28268-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11387,10 +11367,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45845</v>
+        <v>45099</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11403,7 +11383,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>4.7</v>
+        <v>0.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11446,7 +11426,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 1662-2025</t>
+          <t>A 21376-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11460,10 +11440,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45670</v>
+        <v>46147</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11476,7 +11456,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.8</v>
+        <v>7.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11519,7 +11499,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 20710-2026</t>
+          <t>A 850-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11533,10 +11513,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46141</v>
+        <v>44931</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11549,7 +11529,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11592,7 +11572,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 20812-2026</t>
+          <t>A 55764-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11606,10 +11586,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46141</v>
+        <v>45623</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11622,7 +11602,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11665,7 +11645,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 33162-2024</t>
+          <t>A 19674-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11679,10 +11659,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45518</v>
+        <v>45051</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11695,7 +11675,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11738,7 +11718,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 20700-2026</t>
+          <t>A 19683-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11752,10 +11732,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46141</v>
+        <v>45051</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11768,7 +11748,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11811,7 +11791,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 25594-2025</t>
+          <t>A 22916-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11821,14 +11801,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45803</v>
+        <v>46160</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11841,7 +11821,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11884,7 +11864,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 20811-2026</t>
+          <t>A 22906-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11898,10 +11878,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46141</v>
+        <v>46160</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11914,7 +11894,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11957,7 +11937,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 21376-2026</t>
+          <t>A 22912-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11971,10 +11951,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46147</v>
+        <v>46160</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11987,7 +11967,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>7.2</v>
+        <v>2.2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12030,7 +12010,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 1379-2025</t>
+          <t>A 8765-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12044,10 +12024,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45667</v>
+        <v>44614</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12059,8 +12039,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12103,7 +12088,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 21369-2026</t>
+          <t>A 52352-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12117,10 +12102,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46147</v>
+        <v>45224</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12133,7 +12118,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12176,7 +12161,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 44608-2023</t>
+          <t>A 25777-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12186,14 +12171,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45189</v>
+        <v>46178</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12206,7 +12191,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12249,7 +12234,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 44033-2024</t>
+          <t>A 26336-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12263,10 +12248,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45572</v>
+        <v>46182</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12279,7 +12264,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12322,7 +12307,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 13366-2022</t>
+          <t>A 26338-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12336,10 +12321,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44645</v>
+        <v>46182</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12352,7 +12337,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12395,7 +12380,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 15428-2025</t>
+          <t>A 10636-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12409,10 +12394,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45747</v>
+        <v>46078</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12425,7 +12410,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12468,7 +12453,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 15434-2025</t>
+          <t>A 32363-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12482,10 +12467,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45747</v>
+        <v>46238</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12498,7 +12483,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.1</v>
+        <v>6.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12541,7 +12526,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 22906-2026</t>
+          <t>A 32364-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12555,10 +12540,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46160</v>
+        <v>46238</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12571,7 +12556,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12614,7 +12599,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 17010-2022</t>
+          <t>A 28467-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12628,10 +12613,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44676</v>
+        <v>46197</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12644,7 +12629,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12687,7 +12672,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 22916-2026</t>
+          <t>A 62510-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12701,10 +12686,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46160</v>
+        <v>44924</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12716,8 +12701,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12760,7 +12750,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 22912-2026</t>
+          <t>A 28647-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12774,10 +12764,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46160</v>
+        <v>46198</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12790,7 +12780,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12833,7 +12823,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 19674-2023</t>
+          <t>A 20507-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12847,10 +12837,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45051</v>
+        <v>46140</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12863,7 +12853,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12906,7 +12896,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 13345-2022</t>
+          <t>A 30191-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12920,10 +12910,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44645</v>
+        <v>46206</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12935,8 +12925,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12979,7 +12974,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 21429-2022</t>
+          <t>A 34008-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12993,10 +12988,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44706</v>
+        <v>46252</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13009,7 +13004,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13052,7 +13047,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 35408-2023</t>
+          <t>A 5690-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13066,10 +13061,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45146</v>
+        <v>46051</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13082,7 +13077,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13125,7 +13120,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 55511-2023</t>
+          <t>A 17876-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13139,10 +13134,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45238</v>
+        <v>45758</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13155,7 +13150,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13198,7 +13193,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 36472-2023</t>
+          <t>A 31329-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13212,10 +13207,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45152</v>
+        <v>46219</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13228,7 +13223,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13271,7 +13266,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 25777-2026</t>
+          <t>A 31446-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13281,14 +13276,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46178</v>
+        <v>46220</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13301,7 +13296,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13344,7 +13339,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 49252-2023</t>
+          <t>A 31452-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13358,10 +13353,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45210</v>
+        <v>46220</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13374,7 +13369,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.4</v>
+        <v>3.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13417,7 +13412,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 31917-2022</t>
+          <t>A 31324-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13431,10 +13426,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44777</v>
+        <v>46219</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13447,7 +13442,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13490,7 +13485,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 17876-2025</t>
+          <t>A 13170-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13504,10 +13499,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45758</v>
+        <v>45386</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13520,7 +13515,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13563,7 +13558,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 26338-2026</t>
+          <t>A 35869-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13577,10 +13572,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46182</v>
+        <v>46266</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13593,7 +13588,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13636,7 +13631,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 26336-2026</t>
+          <t>A 35871-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13650,10 +13645,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46182</v>
+        <v>46266</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13666,7 +13661,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13709,7 +13704,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 12450-2022</t>
+          <t>A 62390-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13723,10 +13718,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44638</v>
+        <v>45268</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13739,7 +13734,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13782,7 +13777,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 64712-2023</t>
+          <t>A 62499-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13796,10 +13791,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45281</v>
+        <v>44924</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13811,8 +13806,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13855,7 +13855,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 39081-2022</t>
+          <t>A 10958-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13869,10 +13869,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44817</v>
+        <v>44628</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13928,7 +13928,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 36381-2023</t>
+          <t>A 45239-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13942,10 +13942,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45152</v>
+        <v>44844</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13957,8 +13957,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14001,7 +14006,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 32364-2026</t>
+          <t>A 37557-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14015,10 +14020,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46238</v>
+        <v>46276</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14031,7 +14036,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14074,7 +14079,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 10636-2026</t>
+          <t>A 15426-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14088,10 +14093,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46078</v>
+        <v>45747</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14104,7 +14109,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14147,7 +14152,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 32363-2026</t>
+          <t>A 15442-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14161,10 +14166,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46238</v>
+        <v>45747</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14177,7 +14182,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>6.2</v>
+        <v>0.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14237,7 +14242,7 @@
         <v>46237</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14298,7 +14303,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 13268-2024</t>
+          <t>A 12450-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14312,10 +14317,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45386</v>
+        <v>44638</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14328,7 +14333,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>6.7</v>
+        <v>1.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14371,7 +14376,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 13281-2024</t>
+          <t>A 21429-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14385,10 +14390,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45386</v>
+        <v>44706</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14401,7 +14406,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14444,7 +14449,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 19683-2023</t>
+          <t>A 56169-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14458,10 +14463,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45051</v>
+        <v>45624</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14474,7 +14479,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.3</v>
+        <v>19.7</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14517,7 +14522,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 58417-2024</t>
+          <t>A 13279-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14531,10 +14536,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45634</v>
+        <v>45386</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14546,13 +14551,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14595,7 +14595,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 28647-2026</t>
+          <t>A 49256-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14609,10 +14609,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46198</v>
+        <v>45210</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14668,7 +14668,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 28467-2026</t>
+          <t>A 31969-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14682,10 +14682,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46197</v>
+        <v>45119</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14741,7 +14741,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 39150-2022</t>
+          <t>A 31978-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14755,10 +14755,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44817</v>
+        <v>45119</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14814,7 +14814,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 14502-2023</t>
+          <t>A 39150-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14828,10 +14828,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45012</v>
+        <v>44817</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14887,7 +14887,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 20507-2026</t>
+          <t>A 36472-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14901,10 +14901,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46140</v>
+        <v>45152</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14960,7 +14960,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 30191-2026</t>
+          <t>A 3932-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14974,10 +14974,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46206</v>
+        <v>44587</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14989,13 +14989,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>6.5</v>
+        <v>1.7</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15038,7 +15033,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 34008-2026</t>
+          <t>A 7225-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15052,10 +15047,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46252</v>
+        <v>44970</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15068,7 +15063,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15111,7 +15106,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 5690-2026</t>
+          <t>A 35408-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15125,10 +15120,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46051</v>
+        <v>45146</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15141,7 +15136,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15184,7 +15179,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 10958-2022</t>
+          <t>A 13280-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15198,10 +15193,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44628</v>
+        <v>45386</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15214,7 +15209,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15257,7 +15252,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 9145-2023</t>
+          <t>A 31981-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15271,10 +15266,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44974</v>
+        <v>45119</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15287,7 +15282,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15330,7 +15325,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 7225-2023</t>
+          <t>A 55511-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15344,10 +15339,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44970</v>
+        <v>45238</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15360,7 +15355,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15403,7 +15398,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 31329-2026</t>
+          <t>A 28258-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15417,10 +15412,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46219</v>
+        <v>45099</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15433,7 +15428,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>7.5</v>
+        <v>2.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15476,7 +15471,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 10451-2024</t>
+          <t>A 28264-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15490,10 +15485,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45366</v>
+        <v>45099</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15505,13 +15500,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15554,7 +15544,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 31324-2026</t>
+          <t>A 49252-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15568,10 +15558,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46219</v>
+        <v>45210</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15584,7 +15574,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15627,7 +15617,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 35869-2026</t>
+          <t>A 28335-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15641,10 +15631,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46266</v>
+        <v>45099</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15657,7 +15647,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15700,7 +15690,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 35871-2026</t>
+          <t>A 13281-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15714,10 +15704,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46266</v>
+        <v>45386</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15730,7 +15720,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15773,7 +15763,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 31446-2026</t>
+          <t>A 58650-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15787,10 +15777,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46220</v>
+        <v>45251</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15803,7 +15793,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15846,7 +15836,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 31452-2026</t>
+          <t>A 36304-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15860,10 +15850,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46220</v>
+        <v>45152</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15876,7 +15866,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15919,7 +15909,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 28332-2023</t>
+          <t>A 49536-2021</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15933,10 +15923,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45099</v>
+        <v>44455</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15948,8 +15938,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15992,7 +15987,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 8330-2024</t>
+          <t>A 59074-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16006,10 +16001,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45352</v>
+        <v>45252</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16022,7 +16017,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16065,7 +16060,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 13279-2024</t>
+          <t>A 15428-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16079,10 +16074,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45386</v>
+        <v>45747</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16095,7 +16090,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16138,7 +16133,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 11889-2024</t>
+          <t>A 15434-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16152,10 +16147,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45376</v>
+        <v>45747</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16168,7 +16163,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16211,7 +16206,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 15426-2025</t>
+          <t>A 11771-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16225,10 +16220,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45747</v>
+        <v>45373</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16241,7 +16236,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16284,7 +16279,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 15442-2025</t>
+          <t>A 58417-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16298,10 +16293,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45747</v>
+        <v>45634</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16313,8 +16308,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16357,7 +16357,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 13340-2022</t>
+          <t>A 13345-2022</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16374,7 +16374,7 @@
         <v>44645</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16430,7 +16430,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 13348-2022</t>
+          <t>A 64712-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16444,10 +16444,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44645</v>
+        <v>45281</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16503,7 +16503,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 22055-2023</t>
+          <t>A 39081-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16517,10 +16517,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45069</v>
+        <v>44817</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16576,7 +16576,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 13280-2024</t>
+          <t>A 61294-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16590,10 +16590,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45386</v>
+        <v>45645</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16649,7 +16649,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 37557-2026</t>
+          <t>A 62402-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16663,10 +16663,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46276</v>
+        <v>45268</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16722,7 +16722,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 28335-2023</t>
+          <t>A 1352-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16736,10 +16736,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45099</v>
+        <v>44931</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16795,7 +16795,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 12664-2023</t>
+          <t>A 28332-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16809,10 +16809,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45000</v>
+        <v>45099</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16868,7 +16868,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 21269-2024</t>
+          <t>A 44033-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16882,10 +16882,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45440</v>
+        <v>45572</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16941,7 +16941,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 28316-2024</t>
+          <t>A 72879-2021</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16955,10 +16955,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45477</v>
+        <v>44547</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17014,7 +17014,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 16341-2025</t>
+          <t>A 28267-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17024,14 +17024,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45751</v>
+        <v>45099</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17087,7 +17087,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 10668-2025</t>
+          <t>A 21285-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17101,10 +17101,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45721</v>
+        <v>45440</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17160,7 +17160,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 25434-2025</t>
+          <t>A 28316-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17174,10 +17174,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45800</v>
+        <v>45477</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17233,7 +17233,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 25435-2025</t>
+          <t>A 21269-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17247,10 +17247,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45800</v>
+        <v>45440</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17306,7 +17306,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 25436-2025</t>
+          <t>A 12664-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17320,10 +17320,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45800</v>
+        <v>45000</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17379,7 +17379,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 26105-2025</t>
+          <t>A 16341-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17393,10 +17393,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45805</v>
+        <v>45751</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17452,7 +17452,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 10703-2025</t>
+          <t>A 10668-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17466,10 +17466,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17542,7 +17542,7 @@
         <v>44862</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>45352</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>45352</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>

--- a/Översikt GÖTENE.xlsx
+++ b/Översikt GÖTENE.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44642</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45352</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45847</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>45846</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>46234</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>44827</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>44490</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41724-2022</t>
+          <t>A 5086-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44827</v>
+        <v>45330</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1815,16 +1815,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1839,7 +1839,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1848,49 +1848,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
         <v>1</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 41724-2022 artfynd.xlsx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 5086-2024 artfynd.xlsx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 41724-2022 karta.png", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 5086-2024 karta.png", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 41724-2022 georefererad karta.tif", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 5086-2024 georefererad karta.tif", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 41724-2022 FSC-klagomål.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 5086-2024 FSC-klagomål.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 41724-2022 FSC-klagomål mail.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 5086-2024 FSC-klagomål mail.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 41724-2022 tillsynsbegäran.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 5086-2024 tillsynsbegäran.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 41724-2022 tillsynsbegäran mail.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 5086-2024 tillsynsbegäran mail.docx", "A 5086-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32909-2025</t>
+          <t>A 45211-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45839</v>
+        <v>44844</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1944,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1956,46 +1956,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32909-2025 artfynd.xlsx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 45211-2022 artfynd.xlsx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32909-2025 karta.png", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 45211-2022 karta.png", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32909-2025 georefererad karta.tif", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 45211-2022 georefererad karta.tif", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32909-2025 FSC-klagomål.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 45211-2022 FSC-klagomål.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32909-2025 FSC-klagomål mail.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 45211-2022 FSC-klagomål mail.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32909-2025 tillsynsbegäran.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 45211-2022 tillsynsbegäran.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32909-2025 tillsynsbegäran mail.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 45211-2022 tillsynsbegäran mail.docx", "A 45211-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 47393-2025</t>
+          <t>A 28273-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45930</v>
+        <v>45099</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2025,16 +2025,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2049,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2065,42 +2065,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Korallticka</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 47393-2025 artfynd.xlsx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 28273-2023 artfynd.xlsx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 47393-2025 karta.png", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 28273-2023 karta.png", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 47393-2025 georefererad karta.tif", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 28273-2023 georefererad karta.tif", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 47393-2025 FSC-klagomål.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 28273-2023 FSC-klagomål.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 47393-2025 FSC-klagomål mail.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 28273-2023 FSC-klagomål mail.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 47393-2025 tillsynsbegäran.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 28273-2023 tillsynsbegäran.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 47393-2025 tillsynsbegäran mail.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 28273-2023 tillsynsbegäran mail.docx", "A 28273-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 50366-2025</t>
+          <t>A 47393-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45944</v>
+        <v>45930</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2174,38 +2174,38 @@
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 50366-2025 artfynd.xlsx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 47393-2025 artfynd.xlsx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 50366-2025 karta.png", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 47393-2025 karta.png", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 50366-2025 georefererad karta.tif", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 47393-2025 georefererad karta.tif", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 50366-2025 FSC-klagomål.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 47393-2025 FSC-klagomål.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 50366-2025 FSC-klagomål mail.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 47393-2025 FSC-klagomål mail.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 50366-2025 tillsynsbegäran.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 47393-2025 tillsynsbegäran.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 50366-2025 tillsynsbegäran mail.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 47393-2025 tillsynsbegäran mail.docx", "A 47393-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 45211-2022</t>
+          <t>A 50366-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44844</v>
+        <v>45944</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2235,17 +2235,17 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
@@ -2259,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2271,46 +2271,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Korallticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 45211-2022 artfynd.xlsx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 50366-2025 artfynd.xlsx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 45211-2022 karta.png", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 50366-2025 karta.png", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 45211-2022 georefererad karta.tif", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 50366-2025 georefererad karta.tif", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 45211-2022 FSC-klagomål.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 50366-2025 FSC-klagomål.docx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 45211-2022 FSC-klagomål mail.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 50366-2025 FSC-klagomål mail.docx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 45211-2022 tillsynsbegäran.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 50366-2025 tillsynsbegäran.docx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 45211-2022 tillsynsbegäran mail.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 50366-2025 tillsynsbegäran mail.docx", "A 50366-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 18647-2025</t>
+          <t>A 41724-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45763</v>
+        <v>44827</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2339,23 +2339,18 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -2369,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2385,42 +2380,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 18647-2025 artfynd.xlsx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 41724-2022 artfynd.xlsx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 18647-2025 karta.png", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 41724-2022 karta.png", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 18647-2025 georefererad karta.tif", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 41724-2022 georefererad karta.tif", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 18647-2025 FSC-klagomål.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 41724-2022 FSC-klagomål.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 18647-2025 FSC-klagomål mail.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 41724-2022 FSC-klagomål mail.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 18647-2025 tillsynsbegäran.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 41724-2022 tillsynsbegäran.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 18647-2025 tillsynsbegäran mail.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 41724-2022 tillsynsbegäran mail.docx", "A 41724-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33478-2026</t>
+          <t>A 18647-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2434,10 +2429,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46247</v>
+        <v>45763</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2449,8 +2444,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2490,42 +2490,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 33478-2026 artfynd.xlsx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 18647-2025 artfynd.xlsx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 33478-2026 karta.png", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 18647-2025 karta.png", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 33478-2026 georefererad karta.tif", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 18647-2025 georefererad karta.tif", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 33478-2026 FSC-klagomål.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 18647-2025 FSC-klagomål.docx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 33478-2026 FSC-klagomål mail.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 18647-2025 FSC-klagomål mail.docx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 33478-2026 tillsynsbegäran.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 18647-2025 tillsynsbegäran.docx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 33478-2026 tillsynsbegäran mail.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 18647-2025 tillsynsbegäran mail.docx", "A 18647-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 31326-2026</t>
+          <t>A 14296-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46219</v>
+        <v>45011</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2564,10 +2564,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2582,7 +2582,7 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2591,50 +2591,50 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Pilgrimsfalk</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 31326-2026 artfynd.xlsx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 14296-2023 artfynd.xlsx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 31326-2026 karta.png", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 14296-2023 karta.png", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 31326-2026 georefererad karta.tif", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 14296-2023 georefererad karta.tif", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 31326-2026 FSC-klagomål.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 14296-2023 FSC-klagomål.docx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 31326-2026 FSC-klagomål mail.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 14296-2023 FSC-klagomål mail.docx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 31326-2026 tillsynsbegäran.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 14296-2023 tillsynsbegäran.docx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 31326-2026 tillsynsbegäran mail.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 14296-2023 tillsynsbegäran mail.docx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 31326-2026 prioriterade fågelarter.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 14296-2023 prioriterade fågelarter.docx", "A 14296-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 32224-2026</t>
+          <t>A 33478-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46237</v>
+        <v>46247</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2664,16 +2664,16 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2688,7 +2688,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2704,35 +2704,35 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Backmåra</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32224-2026 artfynd.xlsx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 33478-2026 artfynd.xlsx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32224-2026 karta.png", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 33478-2026 karta.png", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32224-2026 georefererad karta.tif", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 33478-2026 georefererad karta.tif", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32224-2026 FSC-klagomål.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 33478-2026 FSC-klagomål.docx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32224-2026 FSC-klagomål mail.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 33478-2026 FSC-klagomål mail.docx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32224-2026 tillsynsbegäran.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 33478-2026 tillsynsbegäran.docx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32224-2026 tillsynsbegäran mail.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 33478-2026 tillsynsbegäran mail.docx", "A 33478-2026")</f>
         <v/>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
         <v>44691</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 14296-2023</t>
+          <t>A 31326-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45011</v>
+        <v>46219</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2883,10 +2883,10 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2901,7 +2901,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2910,50 +2910,50 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Pilgrimsfalk</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 14296-2023 artfynd.xlsx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 31326-2026 artfynd.xlsx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 14296-2023 karta.png", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 31326-2026 karta.png", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 14296-2023 georefererad karta.tif", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 31326-2026 georefererad karta.tif", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 14296-2023 FSC-klagomål.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 31326-2026 FSC-klagomål.docx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 14296-2023 FSC-klagomål mail.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 31326-2026 FSC-klagomål mail.docx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 14296-2023 tillsynsbegäran.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 31326-2026 tillsynsbegäran.docx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 14296-2023 tillsynsbegäran mail.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 31326-2026 tillsynsbegäran mail.docx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 14296-2023 prioriterade fågelarter.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 31326-2026 prioriterade fågelarter.docx", "A 31326-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 5086-2024</t>
+          <t>A 32224-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45330</v>
+        <v>46237</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2983,17 +2983,17 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3007,7 +3007,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3016,49 +3016,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Backmåra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 5086-2024 artfynd.xlsx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32224-2026 artfynd.xlsx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 5086-2024 karta.png", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32224-2026 karta.png", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 5086-2024 georefererad karta.tif", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32224-2026 georefererad karta.tif", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 5086-2024 FSC-klagomål.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32224-2026 FSC-klagomål.docx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 5086-2024 FSC-klagomål mail.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32224-2026 FSC-klagomål mail.docx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 5086-2024 tillsynsbegäran.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32224-2026 tillsynsbegäran.docx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 5086-2024 tillsynsbegäran mail.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32224-2026 tillsynsbegäran mail.docx", "A 32224-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 28273-2023</t>
+          <t>A 32909-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45099</v>
+        <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3088,17 +3088,17 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
@@ -3112,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3128,35 +3128,35 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 28273-2023 artfynd.xlsx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32909-2025 artfynd.xlsx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 28273-2023 karta.png", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32909-2025 karta.png", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 28273-2023 georefererad karta.tif", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32909-2025 georefererad karta.tif", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 28273-2023 FSC-klagomål.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32909-2025 FSC-klagomål.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 28273-2023 FSC-klagomål mail.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32909-2025 FSC-klagomål mail.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 28273-2023 tillsynsbegäran.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32909-2025 tillsynsbegäran.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 28273-2023 tillsynsbegäran mail.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32909-2025 tillsynsbegäran mail.docx", "A 32909-2025")</f>
         <v/>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
         <v>45372</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>44490</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>44645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>44490</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>44490</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>44507</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>44614</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>44859</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>44840</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>44566</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>44684</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>44477</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>44507</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>44581</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>44761</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>44757</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>44869</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 38195-2022</t>
+          <t>A 9607-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44812</v>
+        <v>45361</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4762,13 +4762,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4811,7 +4806,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 46381-2022</t>
+          <t>A 58650-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4825,10 +4820,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44848</v>
+        <v>45251</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4838,11 +4833,6 @@
       <c r="G48" t="inlineStr">
         <is>
           <t>GÖTENE</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -4889,7 +4879,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 49968-2022</t>
+          <t>A 38195-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4903,10 +4893,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44865</v>
+        <v>44812</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4918,8 +4908,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4962,7 +4957,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 59114-2021</t>
+          <t>A 6969-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4976,10 +4971,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44490</v>
+        <v>44603</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4992,7 +4987,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5035,7 +5030,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 6969-2022</t>
+          <t>A 55496-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5049,10 +5044,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44603</v>
+        <v>44475</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5065,7 +5060,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5108,7 +5103,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 55496-2021</t>
+          <t>A 45239-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5122,10 +5117,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44475</v>
+        <v>44844</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5137,8 +5132,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 36244-2022</t>
+          <t>A 49536-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5195,10 +5195,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44803</v>
+        <v>44455</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5210,8 +5210,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5254,7 +5259,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 38945-2022</t>
+          <t>A 36472-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5268,10 +5273,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44816</v>
+        <v>45152</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5284,7 +5289,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5327,7 +5332,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 61148-2021</t>
+          <t>A 46381-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5341,10 +5346,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44498</v>
+        <v>44848</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5356,8 +5361,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5400,7 +5410,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 58418-2024</t>
+          <t>A 36244-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5414,10 +5424,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45634</v>
+        <v>44803</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5430,7 +5440,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5473,7 +5483,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 36381-2023</t>
+          <t>A 49968-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5487,10 +5497,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45152</v>
+        <v>44865</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5503,7 +5513,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5546,7 +5556,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8330-2024</t>
+          <t>A 61148-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5560,10 +5570,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45352</v>
+        <v>44498</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5576,7 +5586,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5619,7 +5629,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 13276-2024</t>
+          <t>A 38945-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5633,10 +5643,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45386</v>
+        <v>44816</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5649,7 +5659,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5692,7 +5702,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 49700-2021</t>
+          <t>A 59114-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5706,10 +5716,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44455</v>
+        <v>44490</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5722,7 +5732,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5765,7 +5775,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 849-2023</t>
+          <t>A 28264-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5779,10 +5789,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44931</v>
+        <v>45099</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5795,7 +5805,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5838,7 +5848,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25434-2025</t>
+          <t>A 28268-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5852,10 +5862,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45800</v>
+        <v>45099</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5868,7 +5878,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5911,7 +5921,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 25435-2025</t>
+          <t>A 52352-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5925,10 +5935,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45800</v>
+        <v>45224</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5941,7 +5951,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5984,7 +5994,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 25436-2025</t>
+          <t>A 49252-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5998,10 +6008,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45800</v>
+        <v>45210</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6014,7 +6024,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6057,7 +6067,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 26105-2025</t>
+          <t>A 31917-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6067,14 +6077,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45805</v>
+        <v>44777</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6087,7 +6097,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5.3</v>
+        <v>1.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6130,7 +6140,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 10703-2025</t>
+          <t>A 17876-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6144,10 +6154,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45722</v>
+        <v>45758</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6160,7 +6170,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6203,7 +6213,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 44608-2023</t>
+          <t>A 49700-2021</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6217,10 +6227,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45189</v>
+        <v>44455</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6233,7 +6243,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6276,7 +6286,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 61194-2024</t>
+          <t>A 13276-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6290,10 +6300,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45645</v>
+        <v>45386</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6305,13 +6315,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6354,7 +6359,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 41721-2022</t>
+          <t>A 12450-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6368,10 +6373,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44827</v>
+        <v>44638</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6384,7 +6389,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6427,7 +6432,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 31917-2022</t>
+          <t>A 10630-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6441,10 +6446,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44777</v>
+        <v>46078</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6457,7 +6462,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6500,7 +6505,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 39998-2025</t>
+          <t>A 11459-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6514,10 +6519,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45894</v>
+        <v>46083</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6530,7 +6535,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6573,7 +6578,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 28390-2025</t>
+          <t>A 11460-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6587,10 +6592,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45819</v>
+        <v>46083</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6600,11 +6605,6 @@
       <c r="G72" t="inlineStr">
         <is>
           <t>GÖTENE</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -6651,7 +6651,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 11889-2024</t>
+          <t>A 11630-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6665,10 +6665,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45376</v>
+        <v>46084</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6680,8 +6680,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6724,7 +6729,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 11772-2024</t>
+          <t>A 61194-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6738,10 +6743,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45373</v>
+        <v>45645</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6753,8 +6758,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6797,7 +6807,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 11773-2024</t>
+          <t>A 64712-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6811,10 +6821,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45373</v>
+        <v>45281</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6827,7 +6837,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6870,7 +6880,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 3960-2026</t>
+          <t>A 39998-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6884,10 +6894,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46044</v>
+        <v>45894</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6899,13 +6909,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6948,7 +6953,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 31258-2025</t>
+          <t>A 1352-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6962,10 +6967,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45833</v>
+        <v>44931</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6978,7 +6983,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5.2</v>
+        <v>1.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7021,7 +7026,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 5044-2026</t>
+          <t>A 28267-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7035,10 +7040,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46049</v>
+        <v>45099</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7051,7 +7056,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5.4</v>
+        <v>0.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7094,7 +7099,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 32967-2025</t>
+          <t>A 72879-2021</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7108,10 +7113,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45839</v>
+        <v>44547</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7124,7 +7129,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7167,7 +7172,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 45007-2025</t>
+          <t>A 39081-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7181,10 +7186,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45918</v>
+        <v>44817</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7197,7 +7202,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7240,7 +7245,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 17010-2022</t>
+          <t>A 36381-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7254,10 +7259,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44676</v>
+        <v>45152</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7270,7 +7275,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7313,7 +7318,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 61021-2022</t>
+          <t>A 62499-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7323,14 +7328,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44914</v>
+        <v>44924</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7342,8 +7347,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7386,7 +7396,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 6925-2023</t>
+          <t>A 45007-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7400,10 +7410,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44967</v>
+        <v>45918</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7415,13 +7425,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7464,7 +7469,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 47175-2025</t>
+          <t>A 3932-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7478,10 +7483,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45930</v>
+        <v>44587</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7494,7 +7499,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7537,7 +7542,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 47383-2025</t>
+          <t>A 13268-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7551,10 +7556,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45930</v>
+        <v>45386</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7567,7 +7572,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.4</v>
+        <v>6.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7610,7 +7615,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 47385-2025</t>
+          <t>A 13281-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7624,10 +7629,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45930</v>
+        <v>45386</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7640,7 +7645,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7683,7 +7688,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 30205-2023</t>
+          <t>A 47385-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7697,10 +7702,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45110</v>
+        <v>45930</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7713,7 +7718,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>6.8</v>
+        <v>1.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7756,7 +7761,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 47389-2025</t>
+          <t>A 47175-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7773,7 +7778,7 @@
         <v>45930</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7786,7 +7791,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7829,7 +7834,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 58236-2024</t>
+          <t>A 47389-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7843,10 +7848,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45632</v>
+        <v>45930</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7858,13 +7863,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7907,7 +7907,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 58691-2024</t>
+          <t>A 47383-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45635</v>
+        <v>45930</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7936,13 +7936,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7985,7 +7980,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 13450-2025</t>
+          <t>A 58418-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7999,10 +7994,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45736</v>
+        <v>45634</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8015,7 +8010,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8058,7 +8053,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 22278-2024</t>
+          <t>A 13170-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8072,10 +8067,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45446</v>
+        <v>45386</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8088,7 +8083,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8131,7 +8126,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 10630-2026</t>
+          <t>A 19683-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8145,10 +8140,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46078</v>
+        <v>45051</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8161,7 +8156,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8204,7 +8199,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 11459-2026</t>
+          <t>A 58417-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8218,10 +8213,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46083</v>
+        <v>45634</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8233,8 +8228,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8277,7 +8277,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 11460-2026</t>
+          <t>A 18776-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8291,10 +8291,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46083</v>
+        <v>46128</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8350,7 +8350,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 11630-2026</t>
+          <t>A 45180-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8364,10 +8364,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46084</v>
+        <v>45575</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8379,13 +8379,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>1.7</v>
+        <v>14.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8428,7 +8423,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 17069-2023</t>
+          <t>A 36304-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8442,10 +8437,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45034</v>
+        <v>45152</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8458,7 +8453,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8501,7 +8496,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 1379-2025</t>
+          <t>A 49256-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8515,10 +8510,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45667</v>
+        <v>45210</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8531,7 +8526,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8574,7 +8569,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 52141-2025</t>
+          <t>A 10596-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8588,10 +8583,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45953</v>
+        <v>45366</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8604,7 +8599,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8647,7 +8642,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 45180-2024</t>
+          <t>A 21285-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8661,10 +8656,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45575</v>
+        <v>45440</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8677,7 +8672,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>14.7</v>
+        <v>1.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8720,7 +8715,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 14502-2023</t>
+          <t>A 52141-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8734,10 +8729,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45012</v>
+        <v>45953</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8750,7 +8745,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8793,7 +8788,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 13340-2022</t>
+          <t>A 30174-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8807,10 +8802,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44645</v>
+        <v>44757</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8823,7 +8818,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8866,7 +8861,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 13348-2022</t>
+          <t>A 41721-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8880,10 +8875,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44645</v>
+        <v>44827</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8896,7 +8891,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8939,7 +8934,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 13366-2022</t>
+          <t>A 55764-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8953,10 +8948,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44645</v>
+        <v>45623</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8969,7 +8964,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9012,7 +9007,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 15646-2023</t>
+          <t>A 56169-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9026,10 +9021,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45021</v>
+        <v>45624</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9042,7 +9037,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3</v>
+        <v>19.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9085,7 +9080,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 18776-2026</t>
+          <t>A 850-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9099,10 +9094,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46128</v>
+        <v>44931</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9115,7 +9110,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9158,7 +9153,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 9607-2024</t>
+          <t>A 56365-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9172,10 +9167,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45361</v>
+        <v>45974</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9188,7 +9183,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9231,7 +9226,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 56365-2025</t>
+          <t>A 56347-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9248,7 +9243,7 @@
         <v>45974</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9261,7 +9256,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.8</v>
+        <v>10.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9304,7 +9299,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 56347-2025</t>
+          <t>A 56352-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9321,7 +9316,7 @@
         <v>45974</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9334,7 +9329,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>10.9</v>
+        <v>5.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9377,7 +9372,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 56352-2025</t>
+          <t>A 56346-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9394,7 +9389,7 @@
         <v>45974</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9407,7 +9402,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>5.9</v>
+        <v>18.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9450,7 +9445,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 56414-2025</t>
+          <t>A 56340-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9464,10 +9459,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45975</v>
+        <v>45974</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9480,7 +9475,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9523,7 +9518,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 56340-2025</t>
+          <t>A 56417-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9537,10 +9532,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9553,7 +9548,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9596,7 +9591,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 56417-2025</t>
+          <t>A 56414-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9613,7 +9608,7 @@
         <v>45975</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9626,7 +9621,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9669,7 +9664,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 56346-2025</t>
+          <t>A 45013-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9683,10 +9678,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45974</v>
+        <v>45918</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9699,7 +9694,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>18.8</v>
+        <v>1.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9742,7 +9737,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 45013-2025</t>
+          <t>A 34161-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9756,10 +9751,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45918</v>
+        <v>45845</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9772,7 +9767,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9815,7 +9810,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 58517-2025</t>
+          <t>A 39150-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9829,10 +9824,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45985</v>
+        <v>44817</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9888,7 +9883,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 58520-2025</t>
+          <t>A 61294-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9902,10 +9897,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45985</v>
+        <v>45645</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9918,7 +9913,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9961,7 +9956,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 1662-2025</t>
+          <t>A 12660-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9971,14 +9966,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45670</v>
+        <v>45000</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9991,7 +9986,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10034,7 +10029,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 58766-2025</t>
+          <t>A 1662-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10048,10 +10043,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45986</v>
+        <v>45670</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10064,7 +10059,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10107,7 +10102,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 9145-2023</t>
+          <t>A 20710-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10121,10 +10116,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44974</v>
+        <v>46141</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10137,7 +10132,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10180,7 +10175,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 58767-2025</t>
+          <t>A 20812-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10194,10 +10189,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45986</v>
+        <v>46141</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10210,7 +10205,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10253,7 +10248,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 30174-2022</t>
+          <t>A 33162-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10267,10 +10262,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44757</v>
+        <v>45518</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10283,7 +10278,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10326,7 +10321,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 34161-2025</t>
+          <t>A 20700-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10340,10 +10335,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45845</v>
+        <v>46141</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10356,7 +10351,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10399,7 +10394,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 60559-2025</t>
+          <t>A 58766-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10413,10 +10408,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45995</v>
+        <v>45986</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10429,7 +10424,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10472,7 +10467,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 13268-2024</t>
+          <t>A 58767-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10486,10 +10481,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45386</v>
+        <v>45986</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10502,7 +10497,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>6.7</v>
+        <v>3.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10545,7 +10540,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 10451-2024</t>
+          <t>A 58517-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10559,10 +10554,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45366</v>
+        <v>45985</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10574,13 +10569,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10623,7 +10613,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 25594-2025</t>
+          <t>A 58520-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10633,14 +10623,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45803</v>
+        <v>45985</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10653,7 +10643,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10696,7 +10686,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 20710-2026</t>
+          <t>A 62390-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10710,10 +10700,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46141</v>
+        <v>45268</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10726,7 +10716,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10769,7 +10759,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 12660-2023</t>
+          <t>A 62402-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10779,14 +10769,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45000</v>
+        <v>45268</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10842,7 +10832,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 22055-2023</t>
+          <t>A 11771-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10856,10 +10846,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45069</v>
+        <v>45373</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10872,7 +10862,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10915,7 +10905,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 10596-2024</t>
+          <t>A 25594-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10925,14 +10915,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45366</v>
+        <v>45803</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10945,7 +10935,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11005,7 +10995,7 @@
         <v>46141</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11061,7 +11051,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 33162-2024</t>
+          <t>A 31981-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11075,10 +11065,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45518</v>
+        <v>45119</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11091,7 +11081,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11134,7 +11124,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 20812-2026</t>
+          <t>A 21376-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11148,10 +11138,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46141</v>
+        <v>46147</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11164,7 +11154,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.2</v>
+        <v>7.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11207,7 +11197,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 20700-2026</t>
+          <t>A 60559-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11221,10 +11211,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46141</v>
+        <v>45995</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11237,7 +11227,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11297,7 +11287,7 @@
         <v>46147</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11353,7 +11343,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 28268-2023</t>
+          <t>A 15646-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11367,10 +11357,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45099</v>
+        <v>45021</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11383,7 +11373,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11426,7 +11416,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 21376-2026</t>
+          <t>A 14502-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11440,10 +11430,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46147</v>
+        <v>45012</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11456,7 +11446,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>7.2</v>
+        <v>3.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11499,7 +11489,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 850-2023</t>
+          <t>A 22906-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11513,10 +11503,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44931</v>
+        <v>46160</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11529,7 +11519,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11572,7 +11562,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 55764-2024</t>
+          <t>A 22916-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11586,10 +11576,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45623</v>
+        <v>46160</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11602,7 +11592,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11645,7 +11635,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 19674-2023</t>
+          <t>A 22912-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11659,10 +11649,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45051</v>
+        <v>46160</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11675,7 +11665,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11718,7 +11708,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 19683-2023</t>
+          <t>A 62510-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11732,10 +11722,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45051</v>
+        <v>44924</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11747,8 +11737,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11791,7 +11786,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 22916-2026</t>
+          <t>A 61021-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11801,14 +11796,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46160</v>
+        <v>44914</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11864,7 +11859,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 22906-2026</t>
+          <t>A 849-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11878,10 +11873,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46160</v>
+        <v>44931</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11894,7 +11889,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11937,7 +11932,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 22912-2026</t>
+          <t>A 3960-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11951,10 +11946,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46160</v>
+        <v>46044</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11966,8 +11961,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12010,7 +12010,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 8765-2022</t>
+          <t>A 31969-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12024,10 +12024,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44614</v>
+        <v>45119</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12039,13 +12039,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12088,7 +12083,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 52352-2023</t>
+          <t>A 31978-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12102,10 +12097,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45224</v>
+        <v>45119</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12118,7 +12113,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12161,7 +12156,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 25777-2026</t>
+          <t>A 5044-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12171,14 +12166,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46178</v>
+        <v>46049</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12191,7 +12186,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12234,7 +12229,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 26336-2026</t>
+          <t>A 28258-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12248,10 +12243,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46182</v>
+        <v>45099</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12264,7 +12259,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12307,7 +12302,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 26338-2026</t>
+          <t>A 25777-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12317,14 +12312,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12337,7 +12332,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12380,7 +12375,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 10636-2026</t>
+          <t>A 22278-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12394,10 +12389,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46078</v>
+        <v>45446</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12410,7 +12405,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12453,7 +12448,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 32363-2026</t>
+          <t>A 17069-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12467,10 +12462,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46238</v>
+        <v>45034</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12483,7 +12478,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>6.2</v>
+        <v>0.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12526,7 +12521,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 32364-2026</t>
+          <t>A 10958-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12540,10 +12535,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46238</v>
+        <v>44628</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12556,7 +12551,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12599,7 +12594,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 28467-2026</t>
+          <t>A 26338-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12613,10 +12608,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46197</v>
+        <v>46182</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12629,7 +12624,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12672,7 +12667,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 62510-2022</t>
+          <t>A 26336-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12686,10 +12681,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44924</v>
+        <v>46182</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12701,13 +12696,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12750,7 +12740,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 28647-2026</t>
+          <t>A 59074-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12764,10 +12754,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46198</v>
+        <v>45252</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12780,7 +12770,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12823,7 +12813,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 20507-2026</t>
+          <t>A 11772-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12837,10 +12827,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46140</v>
+        <v>45373</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12853,7 +12843,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12896,7 +12886,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 30191-2026</t>
+          <t>A 11773-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12910,10 +12900,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46206</v>
+        <v>45373</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12925,13 +12915,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>6.5</v>
+        <v>1.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12974,7 +12959,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 34008-2026</t>
+          <t>A 8765-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12988,10 +12973,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46252</v>
+        <v>44614</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13003,8 +12988,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13047,7 +13037,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 5690-2026</t>
+          <t>A 9145-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13061,10 +13051,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46051</v>
+        <v>44974</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13077,7 +13067,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13120,7 +13110,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 17876-2025</t>
+          <t>A 30205-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13134,10 +13124,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45758</v>
+        <v>45110</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13150,7 +13140,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13193,7 +13183,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 31329-2026</t>
+          <t>A 10636-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13207,10 +13197,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46219</v>
+        <v>46078</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13223,7 +13213,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>7.5</v>
+        <v>1.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13266,7 +13256,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 31446-2026</t>
+          <t>A 28647-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13280,10 +13270,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46220</v>
+        <v>46198</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13296,7 +13286,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13339,7 +13329,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 31452-2026</t>
+          <t>A 7225-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13353,10 +13343,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46220</v>
+        <v>44970</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13369,7 +13359,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13412,7 +13402,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 31324-2026</t>
+          <t>A 28467-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13426,10 +13416,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46219</v>
+        <v>46197</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13442,7 +13432,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13485,7 +13475,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 13170-2024</t>
+          <t>A 10451-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13499,10 +13489,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45386</v>
+        <v>45366</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13514,8 +13504,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13558,7 +13553,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 35869-2026</t>
+          <t>A 1379-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13572,10 +13567,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46266</v>
+        <v>45667</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13588,7 +13583,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13631,7 +13626,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 35871-2026</t>
+          <t>A 20507-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13645,10 +13640,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46266</v>
+        <v>46140</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13661,7 +13656,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13704,7 +13699,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 62390-2023</t>
+          <t>A 44608-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13718,10 +13713,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45268</v>
+        <v>45189</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13734,7 +13729,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13777,7 +13772,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 62499-2022</t>
+          <t>A 30191-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13791,10 +13786,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44924</v>
+        <v>46206</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13808,11 +13803,11 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.6</v>
+        <v>6.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13855,7 +13850,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 10958-2022</t>
+          <t>A 44033-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13869,10 +13864,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44628</v>
+        <v>45572</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13928,7 +13923,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 45239-2022</t>
+          <t>A 34008-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13942,10 +13937,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44844</v>
+        <v>46252</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13957,13 +13952,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14006,7 +13996,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 37557-2026</t>
+          <t>A 13366-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14020,10 +14010,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46276</v>
+        <v>44645</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14036,7 +14026,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14079,7 +14069,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 15426-2025</t>
+          <t>A 5690-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14093,10 +14083,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45747</v>
+        <v>46051</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14109,7 +14099,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14152,7 +14142,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 15442-2025</t>
+          <t>A 15428-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14169,7 +14159,7 @@
         <v>45747</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14182,7 +14172,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14225,7 +14215,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 32298-2026</t>
+          <t>A 15434-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14239,10 +14229,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46237</v>
+        <v>45747</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14254,13 +14244,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>3.8</v>
+        <v>0.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14303,7 +14288,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 12450-2022</t>
+          <t>A 17010-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14317,10 +14302,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44638</v>
+        <v>44676</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14333,7 +14318,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14376,7 +14361,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 21429-2022</t>
+          <t>A 19674-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14390,10 +14375,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44706</v>
+        <v>45051</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14406,7 +14391,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14449,7 +14434,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 56169-2024</t>
+          <t>A 13345-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14463,10 +14448,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45624</v>
+        <v>44645</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14479,7 +14464,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>19.7</v>
+        <v>3.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14522,7 +14507,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 13279-2024</t>
+          <t>A 28332-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14536,10 +14521,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45386</v>
+        <v>45099</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14552,7 +14537,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14595,7 +14580,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 49256-2023</t>
+          <t>A 21429-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14609,10 +14594,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45210</v>
+        <v>44706</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14625,7 +14610,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14668,7 +14653,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 31969-2023</t>
+          <t>A 35408-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14682,10 +14667,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45119</v>
+        <v>45146</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14698,7 +14683,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14741,7 +14726,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 31978-2023</t>
+          <t>A 31329-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14755,10 +14740,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45119</v>
+        <v>46219</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14771,7 +14756,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.2</v>
+        <v>7.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14814,7 +14799,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 39150-2022</t>
+          <t>A 8330-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14828,10 +14813,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44817</v>
+        <v>45352</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14844,7 +14829,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14887,7 +14872,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 36472-2023</t>
+          <t>A 55511-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14901,10 +14886,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45152</v>
+        <v>45238</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14917,7 +14902,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14960,7 +14945,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 3932-2022</t>
+          <t>A 31324-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14974,10 +14959,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44587</v>
+        <v>46219</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14990,7 +14975,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15033,7 +15018,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 7225-2023</t>
+          <t>A 35869-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15047,10 +15032,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44970</v>
+        <v>46266</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15106,7 +15091,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 35408-2023</t>
+          <t>A 35871-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15120,10 +15105,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45146</v>
+        <v>46266</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15136,7 +15121,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15179,7 +15164,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 13280-2024</t>
+          <t>A 13279-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15196,7 +15181,7 @@
         <v>45386</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15209,7 +15194,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15252,7 +15237,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 31981-2023</t>
+          <t>A 31446-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15266,10 +15251,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45119</v>
+        <v>46220</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15282,7 +15267,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15325,7 +15310,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 55511-2023</t>
+          <t>A 11889-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15339,10 +15324,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45238</v>
+        <v>45376</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15355,7 +15340,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15398,7 +15383,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 28258-2023</t>
+          <t>A 15426-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15412,10 +15397,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45099</v>
+        <v>45747</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15428,7 +15413,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15471,7 +15456,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 28264-2023</t>
+          <t>A 15442-2025</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15485,10 +15470,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45099</v>
+        <v>45747</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15501,7 +15486,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15544,7 +15529,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 49252-2023</t>
+          <t>A 31452-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15558,10 +15543,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45210</v>
+        <v>46220</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15574,7 +15559,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.4</v>
+        <v>3.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15617,7 +15602,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 28335-2023</t>
+          <t>A 13340-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15631,10 +15616,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45099</v>
+        <v>44645</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15647,7 +15632,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15690,7 +15675,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 13281-2024</t>
+          <t>A 13348-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15704,10 +15689,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45386</v>
+        <v>44645</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15720,7 +15705,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15763,7 +15748,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 58650-2023</t>
+          <t>A 22055-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15777,10 +15762,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45251</v>
+        <v>45069</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15793,7 +15778,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15836,7 +15821,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 36304-2023</t>
+          <t>A 13280-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15850,10 +15835,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45152</v>
+        <v>45386</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15866,7 +15851,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15909,7 +15894,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 49536-2021</t>
+          <t>A 37557-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15923,10 +15908,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44455</v>
+        <v>46276</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15938,13 +15923,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15987,7 +15967,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 59074-2023</t>
+          <t>A 28335-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16001,10 +15981,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45252</v>
+        <v>45099</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16017,7 +15997,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16060,7 +16040,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 15428-2025</t>
+          <t>A 32364-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16074,10 +16054,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45747</v>
+        <v>46238</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16090,7 +16070,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16133,7 +16113,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 15434-2025</t>
+          <t>A 32298-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16147,10 +16127,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45747</v>
+        <v>46237</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16162,8 +16142,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>0.1</v>
+        <v>3.8</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16206,7 +16191,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 11771-2024</t>
+          <t>A 12664-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16220,10 +16205,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45373</v>
+        <v>45000</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16236,7 +16221,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16279,7 +16264,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 58417-2024</t>
+          <t>A 32363-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16293,10 +16278,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45634</v>
+        <v>46238</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16308,13 +16293,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I204" t="n">
-        <v>0.5</v>
+        <v>6.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16357,7 +16337,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 13345-2022</t>
+          <t>A 21269-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16371,10 +16351,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44645</v>
+        <v>45440</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16387,7 +16367,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16430,7 +16410,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 64712-2023</t>
+          <t>A 28316-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16444,10 +16424,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45281</v>
+        <v>45477</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16460,7 +16440,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16503,7 +16483,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 39081-2022</t>
+          <t>A 16341-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16513,14 +16493,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44817</v>
+        <v>45751</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16533,7 +16513,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16576,7 +16556,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 61294-2024</t>
+          <t>A 10668-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16590,10 +16570,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45645</v>
+        <v>45721</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16606,7 +16586,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16649,7 +16629,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 62402-2023</t>
+          <t>A 25434-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16663,10 +16643,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45268</v>
+        <v>45800</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16679,7 +16659,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16722,7 +16702,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 1352-2023</t>
+          <t>A 25435-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16736,10 +16716,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44931</v>
+        <v>45800</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16752,7 +16732,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16795,7 +16775,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 28332-2023</t>
+          <t>A 25436-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16809,10 +16789,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45099</v>
+        <v>45800</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16825,7 +16805,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16868,7 +16848,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 44033-2024</t>
+          <t>A 26105-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16878,14 +16858,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45572</v>
+        <v>45805</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16898,7 +16878,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16941,7 +16921,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 72879-2021</t>
+          <t>A 10703-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16955,10 +16935,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44547</v>
+        <v>45722</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16971,7 +16951,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17014,7 +16994,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 28267-2023</t>
+          <t>A 28390-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17028,10 +17008,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45099</v>
+        <v>45819</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17043,8 +17023,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I214" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17087,7 +17072,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 21285-2024</t>
+          <t>A 31258-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17101,10 +17086,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45440</v>
+        <v>45833</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17117,7 +17102,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.3</v>
+        <v>5.2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17160,7 +17145,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 28316-2024</t>
+          <t>A 32967-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17174,10 +17159,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45477</v>
+        <v>45839</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17190,7 +17175,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17233,7 +17218,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 21269-2024</t>
+          <t>A 6925-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17247,10 +17232,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45440</v>
+        <v>44967</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17262,8 +17247,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17306,7 +17296,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 12664-2023</t>
+          <t>A 58236-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17320,10 +17310,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45000</v>
+        <v>45632</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17335,8 +17325,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17379,7 +17374,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 16341-2025</t>
+          <t>A 58691-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17389,14 +17384,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45751</v>
+        <v>45635</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17408,8 +17403,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I219" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17452,7 +17452,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 10668-2025</t>
+          <t>A 13450-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17466,10 +17466,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45721</v>
+        <v>45736</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17542,7 +17542,7 @@
         <v>44862</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>45352</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>45352</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>

--- a/Översikt GÖTENE.xlsx
+++ b/Översikt GÖTENE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE223"/>
+  <dimension ref="A1:AE221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44642</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45352</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45847</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>45846</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>46234</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>44827</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>44490</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 5086-2024</t>
+          <t>A 41724-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45330</v>
+        <v>44827</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1815,17 +1815,17 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1839,7 +1839,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1848,49 +1848,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 5086-2024 artfynd.xlsx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 41724-2022 artfynd.xlsx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 5086-2024 karta.png", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 41724-2022 karta.png", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 5086-2024 georefererad karta.tif", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 41724-2022 georefererad karta.tif", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 5086-2024 FSC-klagomål.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 41724-2022 FSC-klagomål.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 5086-2024 FSC-klagomål mail.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 41724-2022 FSC-klagomål mail.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 5086-2024 tillsynsbegäran.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 41724-2022 tillsynsbegäran.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 5086-2024 tillsynsbegäran mail.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 41724-2022 tillsynsbegäran mail.docx", "A 41724-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 45211-2022</t>
+          <t>A 32909-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44844</v>
+        <v>45839</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1920,17 +1920,17 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1944,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1956,46 +1956,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 45211-2022 artfynd.xlsx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32909-2025 artfynd.xlsx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 45211-2022 karta.png", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32909-2025 karta.png", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 45211-2022 georefererad karta.tif", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32909-2025 georefererad karta.tif", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 45211-2022 FSC-klagomål.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32909-2025 FSC-klagomål.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 45211-2022 FSC-klagomål mail.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32909-2025 FSC-klagomål mail.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 45211-2022 tillsynsbegäran.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32909-2025 tillsynsbegäran.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 45211-2022 tillsynsbegäran mail.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32909-2025 tillsynsbegäran mail.docx", "A 32909-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 28273-2023</t>
+          <t>A 47393-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45099</v>
+        <v>45930</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2025,17 +2025,17 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
@@ -2049,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2065,42 +2065,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Korallticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 28273-2023 artfynd.xlsx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 47393-2025 artfynd.xlsx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 28273-2023 karta.png", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 47393-2025 karta.png", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 28273-2023 georefererad karta.tif", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 47393-2025 georefererad karta.tif", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 28273-2023 FSC-klagomål.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 47393-2025 FSC-klagomål.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 28273-2023 FSC-klagomål mail.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 47393-2025 FSC-klagomål mail.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 28273-2023 tillsynsbegäran.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 47393-2025 tillsynsbegäran.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 28273-2023 tillsynsbegäran mail.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 47393-2025 tillsynsbegäran mail.docx", "A 47393-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 47393-2025</t>
+          <t>A 50366-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45930</v>
+        <v>45944</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2174,38 +2174,38 @@
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 47393-2025 artfynd.xlsx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 50366-2025 artfynd.xlsx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 47393-2025 karta.png", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 50366-2025 karta.png", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 47393-2025 georefererad karta.tif", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 50366-2025 georefererad karta.tif", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 47393-2025 FSC-klagomål.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 50366-2025 FSC-klagomål.docx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 47393-2025 FSC-klagomål mail.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 50366-2025 FSC-klagomål mail.docx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 47393-2025 tillsynsbegäran.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 50366-2025 tillsynsbegäran.docx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 47393-2025 tillsynsbegäran mail.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 50366-2025 tillsynsbegäran mail.docx", "A 50366-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 50366-2025</t>
+          <t>A 45211-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45944</v>
+        <v>44844</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2235,16 +2235,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2259,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2271,46 +2271,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Korallticka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 50366-2025 artfynd.xlsx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 45211-2022 artfynd.xlsx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 50366-2025 karta.png", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 45211-2022 karta.png", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 50366-2025 georefererad karta.tif", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 45211-2022 georefererad karta.tif", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 50366-2025 FSC-klagomål.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 45211-2022 FSC-klagomål.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 50366-2025 FSC-klagomål mail.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 45211-2022 FSC-klagomål mail.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 50366-2025 tillsynsbegäran.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 45211-2022 tillsynsbegäran.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 50366-2025 tillsynsbegäran mail.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 45211-2022 tillsynsbegäran mail.docx", "A 45211-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 41724-2022</t>
+          <t>A 18647-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44827</v>
+        <v>45763</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2339,17 +2339,22 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2364,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2380,42 +2385,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 41724-2022 artfynd.xlsx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 18647-2025 artfynd.xlsx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 41724-2022 karta.png", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 18647-2025 karta.png", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 41724-2022 georefererad karta.tif", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 18647-2025 georefererad karta.tif", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 41724-2022 FSC-klagomål.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 18647-2025 FSC-klagomål.docx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 41724-2022 FSC-klagomål mail.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 18647-2025 FSC-klagomål mail.docx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 41724-2022 tillsynsbegäran.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 18647-2025 tillsynsbegäran.docx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 41724-2022 tillsynsbegäran mail.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 18647-2025 tillsynsbegäran mail.docx", "A 18647-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 18647-2025</t>
+          <t>A 19083-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2429,10 +2434,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45763</v>
+        <v>44691</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2444,26 +2449,21 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
@@ -2474,10 +2474,10 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2486,39 +2486,39 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Läderbagge</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 18647-2025 artfynd.xlsx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 19083-2022 artfynd.xlsx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 18647-2025 karta.png", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 19083-2022 karta.png", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 18647-2025 georefererad karta.tif", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 19083-2022 georefererad karta.tif", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 18647-2025 FSC-klagomål.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 19083-2022 FSC-klagomål.docx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 18647-2025 FSC-klagomål mail.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 19083-2022 FSC-klagomål mail.docx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 18647-2025 tillsynsbegäran.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 19083-2022 tillsynsbegäran.docx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 18647-2025 tillsynsbegäran mail.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 19083-2022 tillsynsbegäran mail.docx", "A 19083-2022")</f>
         <v/>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
         <v>45011</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>46247</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 19083-2022</t>
+          <t>A 5086-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44691</v>
+        <v>45330</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2769,19 +2769,19 @@
         </is>
       </c>
       <c r="I22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>1</v>
       </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2793,51 +2793,51 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
         <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Läderbagge</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 19083-2022 artfynd.xlsx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 5086-2024 artfynd.xlsx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 19083-2022 karta.png", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 5086-2024 karta.png", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 19083-2022 georefererad karta.tif", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 5086-2024 georefererad karta.tif", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 19083-2022 FSC-klagomål.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 5086-2024 FSC-klagomål.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 19083-2022 FSC-klagomål mail.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 5086-2024 FSC-klagomål mail.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 19083-2022 tillsynsbegäran.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 5086-2024 tillsynsbegäran.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 19083-2022 tillsynsbegäran mail.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 5086-2024 tillsynsbegäran mail.docx", "A 5086-2024")</f>
         <v/>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
         <v>46219</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32224-2026</t>
+          <t>A 28273-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46237</v>
+        <v>45099</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2983,16 +2983,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3007,7 +3007,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3023,42 +3023,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Backmåra</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32224-2026 artfynd.xlsx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 28273-2023 artfynd.xlsx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32224-2026 karta.png", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 28273-2023 karta.png", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32224-2026 georefererad karta.tif", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 28273-2023 georefererad karta.tif", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32224-2026 FSC-klagomål.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 28273-2023 FSC-klagomål.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32224-2026 FSC-klagomål mail.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 28273-2023 FSC-klagomål mail.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32224-2026 tillsynsbegäran.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 28273-2023 tillsynsbegäran.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32224-2026 tillsynsbegäran mail.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 28273-2023 tillsynsbegäran mail.docx", "A 28273-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32909-2025</t>
+          <t>A 32224-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45839</v>
+        <v>46237</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3128,35 +3128,35 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Backmåra</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32909-2025 artfynd.xlsx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32224-2026 artfynd.xlsx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32909-2025 karta.png", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32224-2026 karta.png", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32909-2025 georefererad karta.tif", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32224-2026 georefererad karta.tif", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32909-2025 FSC-klagomål.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32224-2026 FSC-klagomål.docx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32909-2025 FSC-klagomål mail.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32224-2026 FSC-klagomål mail.docx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32909-2025 tillsynsbegäran.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32224-2026 tillsynsbegäran.docx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32909-2025 tillsynsbegäran mail.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32224-2026 tillsynsbegäran mail.docx", "A 32224-2026")</f>
         <v/>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
         <v>45372</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>44490</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>44645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>44490</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>44490</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>44507</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>44614</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 48733-2022</t>
+          <t>A 44507-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44859</v>
+        <v>44840</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4076,7 +4076,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 44507-2022</t>
+          <t>A 48733-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44840</v>
+        <v>44859</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4166,7 +4166,7 @@
         <v>44566</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>44684</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>44477</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>44507</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>44581</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30432-2022</t>
+          <t>A 30128-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44761</v>
+        <v>44757</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30128-2022</t>
+          <t>A 30432-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44757</v>
+        <v>44761</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>44869</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 9607-2024</t>
+          <t>A 38195-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45361</v>
+        <v>44812</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4762,8 +4762,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4806,7 +4811,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 58650-2023</t>
+          <t>A 46381-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4820,10 +4825,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45251</v>
+        <v>44848</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4833,6 +4838,11 @@
       <c r="G48" t="inlineStr">
         <is>
           <t>GÖTENE</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -4879,7 +4889,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38195-2022</t>
+          <t>A 49968-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4893,10 +4903,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44812</v>
+        <v>44865</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4908,13 +4918,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4957,7 +4962,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 6969-2022</t>
+          <t>A 59114-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4971,10 +4976,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44603</v>
+        <v>44490</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4987,7 +4992,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5030,7 +5035,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 55496-2021</t>
+          <t>A 6969-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5044,10 +5049,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44475</v>
+        <v>44603</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5060,7 +5065,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5103,7 +5108,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 45239-2022</t>
+          <t>A 55496-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5117,10 +5122,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44844</v>
+        <v>44475</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5132,13 +5137,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 49536-2021</t>
+          <t>A 36244-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5195,10 +5195,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44455</v>
+        <v>44803</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5210,13 +5210,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5259,7 +5254,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 36472-2023</t>
+          <t>A 61148-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5273,10 +5268,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45152</v>
+        <v>44498</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5289,7 +5284,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5332,7 +5327,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 46381-2022</t>
+          <t>A 38945-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5346,10 +5341,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44848</v>
+        <v>44816</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5361,13 +5356,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5410,7 +5400,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 36244-2022</t>
+          <t>A 58418-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5424,10 +5414,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44803</v>
+        <v>45634</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5440,7 +5430,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5483,7 +5473,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 49968-2022</t>
+          <t>A 36381-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5497,10 +5487,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44865</v>
+        <v>45152</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5513,7 +5503,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5556,7 +5546,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 61148-2021</t>
+          <t>A 8330-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5570,10 +5560,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44498</v>
+        <v>45352</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5586,7 +5576,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5629,7 +5619,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 38945-2022</t>
+          <t>A 13276-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5643,10 +5633,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44816</v>
+        <v>45386</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5659,7 +5649,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5702,7 +5692,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59114-2021</t>
+          <t>A 849-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5716,10 +5706,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44490</v>
+        <v>44931</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5732,7 +5722,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.4</v>
+        <v>3.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5775,7 +5765,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 28264-2023</t>
+          <t>A 41721-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5789,10 +5779,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45099</v>
+        <v>44827</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5805,7 +5795,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5848,7 +5838,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28268-2023</t>
+          <t>A 44608-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5862,10 +5852,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45099</v>
+        <v>45189</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5878,7 +5868,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5921,7 +5911,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 52352-2023</t>
+          <t>A 31917-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5935,10 +5925,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45224</v>
+        <v>44777</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5951,7 +5941,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5994,7 +5984,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 49252-2023</t>
+          <t>A 25434-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6008,10 +5998,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45210</v>
+        <v>45800</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6024,7 +6014,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6067,7 +6057,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 31917-2022</t>
+          <t>A 25435-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6081,10 +6071,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44777</v>
+        <v>45800</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6097,7 +6087,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6140,7 +6130,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 17876-2025</t>
+          <t>A 11889-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6154,10 +6144,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45758</v>
+        <v>45376</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6170,7 +6160,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6213,7 +6203,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 49700-2021</t>
+          <t>A 11772-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6227,10 +6217,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44455</v>
+        <v>45373</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6243,7 +6233,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6286,7 +6276,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 13276-2024</t>
+          <t>A 25436-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6300,10 +6290,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45386</v>
+        <v>45800</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6316,7 +6306,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6359,7 +6349,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 12450-2022</t>
+          <t>A 11773-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6373,10 +6363,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44638</v>
+        <v>45373</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6389,7 +6379,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6432,7 +6422,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 10630-2026</t>
+          <t>A 26105-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6442,14 +6432,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46078</v>
+        <v>45805</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6462,7 +6452,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6505,7 +6495,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11459-2026</t>
+          <t>A 10703-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6519,10 +6509,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46083</v>
+        <v>45722</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6535,7 +6525,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6578,7 +6568,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 11460-2026</t>
+          <t>A 61194-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6592,10 +6582,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46083</v>
+        <v>45645</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6607,8 +6597,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6651,7 +6646,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 11630-2026</t>
+          <t>A 28390-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6665,10 +6660,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46084</v>
+        <v>45819</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6686,7 +6681,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6729,7 +6724,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 61194-2024</t>
+          <t>A 39998-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6743,10 +6738,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45645</v>
+        <v>45894</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6758,13 +6753,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6807,7 +6797,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 64712-2023</t>
+          <t>A 17010-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6821,10 +6811,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45281</v>
+        <v>44676</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6837,7 +6827,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6880,7 +6870,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 39998-2025</t>
+          <t>A 61021-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6890,14 +6880,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45894</v>
+        <v>44914</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6910,7 +6900,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6953,7 +6943,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 1352-2023</t>
+          <t>A 31258-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6967,10 +6957,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44931</v>
+        <v>45833</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6983,7 +6973,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7026,7 +7016,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 28267-2023</t>
+          <t>A 30205-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7040,10 +7030,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45099</v>
+        <v>45110</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7056,7 +7046,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.4</v>
+        <v>6.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7099,7 +7089,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 72879-2021</t>
+          <t>A 32967-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7113,10 +7103,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44547</v>
+        <v>45839</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7129,7 +7119,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7172,7 +7162,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 39081-2022</t>
+          <t>A 45007-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7186,10 +7176,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44817</v>
+        <v>45918</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7202,7 +7192,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7245,7 +7235,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 36381-2023</t>
+          <t>A 22278-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7259,10 +7249,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45152</v>
+        <v>45446</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7275,7 +7265,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7318,7 +7308,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 62499-2022</t>
+          <t>A 6925-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7332,10 +7322,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44924</v>
+        <v>44967</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7349,11 +7339,11 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7396,7 +7386,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 45007-2025</t>
+          <t>A 58236-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7410,10 +7400,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45918</v>
+        <v>45632</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7425,8 +7415,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7469,7 +7464,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 3932-2022</t>
+          <t>A 58691-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7483,10 +7478,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44587</v>
+        <v>45635</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7498,8 +7493,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7542,7 +7542,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 13268-2024</t>
+          <t>A 47175-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7556,10 +7556,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45386</v>
+        <v>45930</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>6.7</v>
+        <v>2.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7615,7 +7615,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 13281-2024</t>
+          <t>A 47383-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45386</v>
+        <v>45930</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7705,7 +7705,7 @@
         <v>45930</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 47175-2025</t>
+          <t>A 47389-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7778,7 +7778,7 @@
         <v>45930</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7834,7 +7834,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 47389-2025</t>
+          <t>A 17069-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7848,10 +7848,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45930</v>
+        <v>45034</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7907,7 +7907,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 47383-2025</t>
+          <t>A 1379-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45930</v>
+        <v>45667</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7980,7 +7980,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 58418-2024</t>
+          <t>A 13450-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7994,10 +7994,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45634</v>
+        <v>45736</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8053,7 +8053,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 13170-2024</t>
+          <t>A 3960-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8067,10 +8067,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45386</v>
+        <v>46044</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8082,8 +8082,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8126,7 +8131,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 19683-2023</t>
+          <t>A 5044-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8140,10 +8145,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45051</v>
+        <v>46049</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8156,7 +8161,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.3</v>
+        <v>5.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8199,7 +8204,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 58417-2024</t>
+          <t>A 52141-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8213,10 +8218,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45634</v>
+        <v>45953</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8228,13 +8233,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8277,7 +8277,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 18776-2026</t>
+          <t>A 45180-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8291,10 +8291,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46128</v>
+        <v>45575</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.3</v>
+        <v>14.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8350,7 +8350,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 45180-2024</t>
+          <t>A 14502-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8364,10 +8364,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45575</v>
+        <v>45012</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>14.7</v>
+        <v>3.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8423,7 +8423,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 36304-2023</t>
+          <t>A 13340-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8437,10 +8437,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45152</v>
+        <v>44645</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8496,7 +8496,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 49256-2023</t>
+          <t>A 13348-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8510,10 +8510,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45210</v>
+        <v>44645</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8569,7 +8569,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 10596-2024</t>
+          <t>A 13366-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8583,10 +8583,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45366</v>
+        <v>44645</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8642,7 +8642,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 21285-2024</t>
+          <t>A 15646-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8656,10 +8656,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45440</v>
+        <v>45021</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 52141-2025</t>
+          <t>A 9607-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8729,10 +8729,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45953</v>
+        <v>45361</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8788,7 +8788,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 30174-2022</t>
+          <t>A 56365-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8802,10 +8802,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44757</v>
+        <v>45974</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5.1</v>
+        <v>1.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8861,7 +8861,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 41721-2022</t>
+          <t>A 56347-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8875,10 +8875,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44827</v>
+        <v>45974</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4.1</v>
+        <v>10.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8934,7 +8934,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 55764-2024</t>
+          <t>A 56352-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45623</v>
+        <v>45974</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.7</v>
+        <v>5.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9007,7 +9007,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 56169-2024</t>
+          <t>A 56414-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9021,10 +9021,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45624</v>
+        <v>45975</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>19.7</v>
+        <v>3.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9080,7 +9080,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 850-2023</t>
+          <t>A 56340-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9094,10 +9094,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44931</v>
+        <v>45974</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9153,7 +9153,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 56365-2025</t>
+          <t>A 56417-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9167,10 +9167,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9226,7 +9226,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 56347-2025</t>
+          <t>A 56346-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9243,7 +9243,7 @@
         <v>45974</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>10.9</v>
+        <v>18.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9299,7 +9299,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 56352-2025</t>
+          <t>A 9145-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9313,10 +9313,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45974</v>
+        <v>44974</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>5.9</v>
+        <v>1.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9372,7 +9372,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 56346-2025</t>
+          <t>A 58517-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45974</v>
+        <v>45985</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>18.8</v>
+        <v>1.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9445,7 +9445,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 56340-2025</t>
+          <t>A 58520-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9459,10 +9459,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45974</v>
+        <v>45985</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9518,7 +9518,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 56417-2025</t>
+          <t>A 58766-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45975</v>
+        <v>45986</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 56414-2025</t>
+          <t>A 58767-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9605,10 +9605,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45975</v>
+        <v>45986</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9664,7 +9664,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 45013-2025</t>
+          <t>A 10630-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45918</v>
+        <v>46078</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9737,7 +9737,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 34161-2025</t>
+          <t>A 11459-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45845</v>
+        <v>46083</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9810,7 +9810,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 39150-2022</t>
+          <t>A 13268-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9824,10 +9824,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44817</v>
+        <v>45386</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.1</v>
+        <v>6.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9883,7 +9883,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 61294-2024</t>
+          <t>A 11460-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9897,10 +9897,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45645</v>
+        <v>46083</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9956,7 +9956,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 12660-2023</t>
+          <t>A 11630-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9966,14 +9966,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45000</v>
+        <v>46084</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9985,8 +9985,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10029,7 +10034,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 1662-2025</t>
+          <t>A 10451-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10043,10 +10048,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45670</v>
+        <v>45366</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10058,8 +10063,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10102,7 +10112,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 20710-2026</t>
+          <t>A 60559-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10116,10 +10126,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46141</v>
+        <v>45995</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10132,7 +10142,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10175,7 +10185,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 20812-2026</t>
+          <t>A 12660-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10185,14 +10195,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46141</v>
+        <v>45000</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10205,7 +10215,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10248,7 +10258,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 33162-2024</t>
+          <t>A 22055-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10262,10 +10272,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45518</v>
+        <v>45069</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10278,7 +10288,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10321,7 +10331,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 20700-2026</t>
+          <t>A 10596-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10335,10 +10345,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46141</v>
+        <v>45366</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10351,7 +10361,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10394,7 +10404,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 58766-2025</t>
+          <t>A 28268-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10408,10 +10418,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45986</v>
+        <v>45099</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10424,7 +10434,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10467,7 +10477,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 58767-2025</t>
+          <t>A 850-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10481,10 +10491,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45986</v>
+        <v>44931</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10497,7 +10507,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10540,7 +10550,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 58517-2025</t>
+          <t>A 55764-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10554,10 +10564,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45985</v>
+        <v>45623</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10570,7 +10580,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10613,7 +10623,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 58520-2025</t>
+          <t>A 19674-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10627,10 +10637,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45985</v>
+        <v>45051</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10643,7 +10653,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10686,7 +10696,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 62390-2023</t>
+          <t>A 19683-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10700,10 +10710,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45268</v>
+        <v>45051</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10716,7 +10726,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10759,7 +10769,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 62402-2023</t>
+          <t>A 8765-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10773,10 +10783,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45268</v>
+        <v>44614</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10788,8 +10798,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10832,7 +10847,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 11771-2024</t>
+          <t>A 52352-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10846,10 +10861,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45373</v>
+        <v>45224</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10862,7 +10877,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10905,7 +10920,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 25594-2025</t>
+          <t>A 18776-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10915,14 +10930,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45803</v>
+        <v>46128</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10935,7 +10950,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10978,7 +10993,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 20811-2026</t>
+          <t>A 62510-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10992,10 +11007,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46141</v>
+        <v>44924</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11007,8 +11022,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11051,7 +11071,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 31981-2023</t>
+          <t>A 45013-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11065,10 +11085,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45119</v>
+        <v>45918</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11081,7 +11101,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11124,7 +11144,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 21376-2026</t>
+          <t>A 1662-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11138,10 +11158,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46147</v>
+        <v>45670</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11154,7 +11174,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>7.2</v>
+        <v>1.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11197,7 +11217,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 60559-2025</t>
+          <t>A 17876-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11211,10 +11231,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45995</v>
+        <v>45758</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11227,7 +11247,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11270,7 +11290,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 21369-2026</t>
+          <t>A 30174-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11284,10 +11304,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46147</v>
+        <v>44757</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11300,7 +11320,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11343,7 +11363,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 15646-2023</t>
+          <t>A 34161-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11357,10 +11377,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45021</v>
+        <v>45845</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11373,7 +11393,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11416,7 +11436,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 14502-2023</t>
+          <t>A 13170-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11430,10 +11450,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45012</v>
+        <v>45386</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11446,7 +11466,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11489,7 +11509,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 22906-2026</t>
+          <t>A 62390-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11503,10 +11523,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46160</v>
+        <v>45268</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11519,7 +11539,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11562,7 +11582,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 22916-2026</t>
+          <t>A 25594-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11572,14 +11592,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46160</v>
+        <v>45803</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11592,7 +11612,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11635,7 +11655,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 22912-2026</t>
+          <t>A 20710-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11649,10 +11669,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46160</v>
+        <v>46141</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11665,7 +11685,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11708,7 +11728,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 62510-2022</t>
+          <t>A 20811-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11722,10 +11742,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44924</v>
+        <v>46141</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11737,13 +11757,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11786,7 +11801,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 61021-2022</t>
+          <t>A 33162-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11796,14 +11811,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44914</v>
+        <v>45518</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11816,7 +11831,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11859,7 +11874,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 849-2023</t>
+          <t>A 62499-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11873,10 +11888,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44931</v>
+        <v>44924</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11888,8 +11903,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11932,7 +11952,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 3960-2026</t>
+          <t>A 20812-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11946,10 +11966,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46044</v>
+        <v>46141</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11961,13 +11981,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12010,7 +12025,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 31969-2023</t>
+          <t>A 20700-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12024,10 +12039,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45119</v>
+        <v>46141</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12040,7 +12055,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12083,7 +12098,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 31978-2023</t>
+          <t>A 10958-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12097,10 +12112,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45119</v>
+        <v>44628</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12156,7 +12171,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 5044-2026</t>
+          <t>A 45239-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12170,10 +12185,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46049</v>
+        <v>44844</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12185,8 +12200,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>5.4</v>
+        <v>1.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12229,7 +12249,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 28258-2023</t>
+          <t>A 21369-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12243,10 +12263,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45099</v>
+        <v>46147</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12259,7 +12279,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12302,7 +12322,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 25777-2026</t>
+          <t>A 15426-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12312,14 +12332,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46178</v>
+        <v>45747</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12332,7 +12352,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12375,7 +12395,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 22278-2024</t>
+          <t>A 15442-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12389,10 +12409,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45446</v>
+        <v>45747</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12405,7 +12425,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12448,7 +12468,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 17069-2023</t>
+          <t>A 21376-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12462,10 +12482,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45034</v>
+        <v>46147</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12478,7 +12498,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.8</v>
+        <v>7.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12521,7 +12541,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 10958-2022</t>
+          <t>A 22916-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12535,10 +12555,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44628</v>
+        <v>46160</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12551,7 +12571,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12594,7 +12614,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 26338-2026</t>
+          <t>A 22906-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12608,10 +12628,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46182</v>
+        <v>46160</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12624,7 +12644,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12667,7 +12687,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 26336-2026</t>
+          <t>A 22912-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12681,10 +12701,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46182</v>
+        <v>46160</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12697,7 +12717,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12740,7 +12760,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 59074-2023</t>
+          <t>A 12450-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12754,10 +12774,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45252</v>
+        <v>44638</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12770,7 +12790,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12813,7 +12833,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 11772-2024</t>
+          <t>A 21429-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12827,10 +12847,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45373</v>
+        <v>44706</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12843,7 +12863,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12886,7 +12906,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 11773-2024</t>
+          <t>A 56169-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12900,10 +12920,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45373</v>
+        <v>45624</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12916,7 +12936,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.9</v>
+        <v>19.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12959,7 +12979,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 8765-2022</t>
+          <t>A 13279-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12973,10 +12993,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44614</v>
+        <v>45386</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12988,13 +13008,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13037,7 +13052,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 9145-2023</t>
+          <t>A 49256-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13051,10 +13066,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44974</v>
+        <v>45210</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13067,7 +13082,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13110,7 +13125,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 30205-2023</t>
+          <t>A 31969-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13124,10 +13139,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45110</v>
+        <v>45119</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13140,7 +13155,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>6.8</v>
+        <v>1.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13183,7 +13198,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 10636-2026</t>
+          <t>A 31978-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13197,10 +13212,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46078</v>
+        <v>45119</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13213,7 +13228,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13256,7 +13271,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 28647-2026</t>
+          <t>A 39150-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13270,10 +13285,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46198</v>
+        <v>44817</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13286,7 +13301,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13329,7 +13344,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 7225-2023</t>
+          <t>A 25777-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13339,14 +13354,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44970</v>
+        <v>46178</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13359,7 +13374,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13402,7 +13417,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 28467-2026</t>
+          <t>A 36472-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13416,10 +13431,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46197</v>
+        <v>45152</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13432,7 +13447,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13475,7 +13490,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 10451-2024</t>
+          <t>A 26336-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13489,10 +13504,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45366</v>
+        <v>46182</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13504,13 +13519,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13553,7 +13563,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 1379-2025</t>
+          <t>A 26338-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13567,10 +13577,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45667</v>
+        <v>46182</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13583,7 +13593,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13626,7 +13636,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 20507-2026</t>
+          <t>A 3932-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13640,10 +13650,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46140</v>
+        <v>44587</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13656,7 +13666,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13699,7 +13709,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 44608-2023</t>
+          <t>A 7225-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13713,10 +13723,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45189</v>
+        <v>44970</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13729,7 +13739,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13772,7 +13782,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 30191-2026</t>
+          <t>A 35408-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13786,10 +13796,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46206</v>
+        <v>45146</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13801,13 +13811,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>6.5</v>
+        <v>3.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13850,7 +13855,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 44033-2024</t>
+          <t>A 13280-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13864,10 +13869,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45572</v>
+        <v>45386</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13880,7 +13885,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13923,7 +13928,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 34008-2026</t>
+          <t>A 31981-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13937,10 +13942,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46252</v>
+        <v>45119</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13953,7 +13958,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13996,7 +14001,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 13366-2022</t>
+          <t>A 55511-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14010,10 +14015,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44645</v>
+        <v>45238</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14026,7 +14031,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14069,7 +14074,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 5690-2026</t>
+          <t>A 28258-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14083,10 +14088,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46051</v>
+        <v>45099</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14099,7 +14104,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14142,7 +14147,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 15428-2025</t>
+          <t>A 28264-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14156,10 +14161,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45747</v>
+        <v>45099</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14172,7 +14177,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14215,7 +14220,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 15434-2025</t>
+          <t>A 49252-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14229,10 +14234,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45747</v>
+        <v>45210</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14245,7 +14250,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14288,7 +14293,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 17010-2022</t>
+          <t>A 10636-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14302,10 +14307,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44676</v>
+        <v>46078</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14318,7 +14323,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14361,7 +14366,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 19674-2023</t>
+          <t>A 28467-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14375,10 +14380,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45051</v>
+        <v>46197</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14391,7 +14396,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14434,7 +14439,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 13345-2022</t>
+          <t>A 28647-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14448,10 +14453,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44645</v>
+        <v>46198</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14464,7 +14469,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14507,7 +14512,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 28332-2023</t>
+          <t>A 20507-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14521,10 +14526,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45099</v>
+        <v>46140</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14537,7 +14542,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14580,7 +14585,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 21429-2022</t>
+          <t>A 28335-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14594,10 +14599,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44706</v>
+        <v>45099</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14610,7 +14615,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14653,7 +14658,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 35408-2023</t>
+          <t>A 13281-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14667,10 +14672,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45146</v>
+        <v>45386</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14683,7 +14688,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14726,7 +14731,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 31329-2026</t>
+          <t>A 58650-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14740,10 +14745,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46219</v>
+        <v>45251</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14756,7 +14761,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>7.5</v>
+        <v>1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14799,7 +14804,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 8330-2024</t>
+          <t>A 36304-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14813,10 +14818,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45352</v>
+        <v>45152</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14829,7 +14834,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14872,7 +14877,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 55511-2023</t>
+          <t>A 59074-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14886,10 +14891,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45238</v>
+        <v>45252</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14902,7 +14907,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>3.6</v>
+        <v>0.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14945,7 +14950,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 31324-2026</t>
+          <t>A 30191-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14959,10 +14964,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46219</v>
+        <v>46206</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14974,8 +14979,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>2.3</v>
+        <v>6.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15018,7 +15028,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 35869-2026</t>
+          <t>A 34008-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15032,10 +15042,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46266</v>
+        <v>46252</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15048,7 +15058,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15091,7 +15101,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 35871-2026</t>
+          <t>A 5690-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15105,10 +15115,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46266</v>
+        <v>46051</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15121,7 +15131,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15164,7 +15174,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 13279-2024</t>
+          <t>A 15428-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15178,10 +15188,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45386</v>
+        <v>45747</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15194,7 +15204,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15237,7 +15247,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 31446-2026</t>
+          <t>A 15434-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15251,10 +15261,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46220</v>
+        <v>45747</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15267,7 +15277,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15310,7 +15320,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 11889-2024</t>
+          <t>A 11771-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15324,10 +15334,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45376</v>
+        <v>45373</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15340,7 +15350,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15383,7 +15393,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 15426-2025</t>
+          <t>A 58417-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15397,10 +15407,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45747</v>
+        <v>45634</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15412,8 +15422,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15456,7 +15471,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 15442-2025</t>
+          <t>A 13345-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15470,10 +15485,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45747</v>
+        <v>44645</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15486,7 +15501,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.2</v>
+        <v>3.4</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15529,7 +15544,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 31452-2026</t>
+          <t>A 31329-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15543,10 +15558,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46220</v>
+        <v>46219</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15559,7 +15574,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15602,7 +15617,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 13340-2022</t>
+          <t>A 31446-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15616,10 +15631,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44645</v>
+        <v>46220</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15632,7 +15647,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15675,7 +15690,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 13348-2022</t>
+          <t>A 31452-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15689,10 +15704,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44645</v>
+        <v>46220</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15705,7 +15720,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15748,7 +15763,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 22055-2023</t>
+          <t>A 64712-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15762,10 +15777,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45069</v>
+        <v>45281</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15778,7 +15793,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15821,7 +15836,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 13280-2024</t>
+          <t>A 31324-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15835,10 +15850,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45386</v>
+        <v>46219</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15851,7 +15866,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15894,7 +15909,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 37557-2026</t>
+          <t>A 39081-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15908,10 +15923,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46276</v>
+        <v>44817</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15924,7 +15939,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15967,7 +15982,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 28335-2023</t>
+          <t>A 61294-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15981,10 +15996,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45099</v>
+        <v>45645</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15997,7 +16012,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16040,7 +16055,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 32364-2026</t>
+          <t>A 35869-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16054,10 +16069,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46238</v>
+        <v>46266</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16070,7 +16085,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16113,7 +16128,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 32298-2026</t>
+          <t>A 35871-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16127,10 +16142,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46237</v>
+        <v>46266</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16142,13 +16157,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16191,7 +16201,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 12664-2023</t>
+          <t>A 62402-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16205,10 +16215,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45000</v>
+        <v>45268</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16221,7 +16231,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16264,7 +16274,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 32363-2026</t>
+          <t>A 1352-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16278,10 +16288,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46238</v>
+        <v>44931</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16294,7 +16304,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>6.2</v>
+        <v>1.8</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16337,7 +16347,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 21269-2024</t>
+          <t>A 28332-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16351,10 +16361,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45440</v>
+        <v>45099</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16367,7 +16377,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16410,7 +16420,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 28316-2024</t>
+          <t>A 44033-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16424,10 +16434,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45477</v>
+        <v>45572</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16440,7 +16450,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16483,7 +16493,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 16341-2025</t>
+          <t>A 72879-2021</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16493,14 +16503,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45751</v>
+        <v>44547</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16513,7 +16523,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16556,7 +16566,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 10668-2025</t>
+          <t>A 28267-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16570,10 +16580,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45721</v>
+        <v>45099</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16586,7 +16596,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16629,7 +16639,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 25434-2025</t>
+          <t>A 21285-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16643,10 +16653,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45800</v>
+        <v>45440</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16659,7 +16669,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16702,7 +16712,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 25435-2025</t>
+          <t>A 37557-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16716,10 +16726,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45800</v>
+        <v>46276</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16732,7 +16742,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16775,7 +16785,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 25436-2025</t>
+          <t>A 32298-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16789,10 +16799,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45800</v>
+        <v>46237</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16804,8 +16814,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16848,7 +16863,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 26105-2025</t>
+          <t>A 32363-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16858,14 +16873,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45805</v>
+        <v>46238</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16878,7 +16893,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16921,7 +16936,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 10703-2025</t>
+          <t>A 32364-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16935,10 +16950,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45722</v>
+        <v>46238</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16951,7 +16966,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16994,7 +17009,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 28390-2025</t>
+          <t>A 28316-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17008,10 +17023,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45819</v>
+        <v>45477</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17023,13 +17038,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17072,7 +17082,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 31258-2025</t>
+          <t>A 21269-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17086,10 +17096,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45833</v>
+        <v>45440</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17102,7 +17112,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17145,7 +17155,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 32967-2025</t>
+          <t>A 12664-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17159,10 +17169,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45839</v>
+        <v>45000</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17175,7 +17185,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17218,7 +17228,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 6925-2023</t>
+          <t>A 16341-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17228,14 +17238,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44967</v>
+        <v>45751</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17247,13 +17257,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17296,7 +17301,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 58236-2024</t>
+          <t>A 10668-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17310,10 +17315,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45632</v>
+        <v>45721</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17325,13 +17330,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I218" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17374,24 +17374,24 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 58691-2024</t>
+          <t>S 6120-2022</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45635</v>
+        <v>44862</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17403,13 +17403,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I219" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17452,24 +17447,24 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 13450-2025</t>
+          <t>S 615-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45736</v>
+        <v>45352</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17482,7 +17477,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.7</v>
+        <v>19.1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17522,10 +17517,10 @@
       </c>
       <c r="V220" s="2" t="inlineStr"/>
     </row>
-    <row r="221" ht="15" customHeight="1">
+    <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>S 6120-2022</t>
+          <t>S 614-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17535,14 +17530,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44862</v>
+        <v>45352</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17555,7 +17550,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>2.1</v>
+        <v>11.4</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17594,152 +17589,6 @@
         <v>0</v>
       </c>
       <c r="V221" s="2" t="inlineStr"/>
-    </row>
-    <row r="222" ht="15" customHeight="1">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>S 615-2024</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D222" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="E222" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>GÖTENE</t>
-        </is>
-      </c>
-      <c r="I222" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="J222" t="n">
-        <v>0</v>
-      </c>
-      <c r="K222" t="n">
-        <v>0</v>
-      </c>
-      <c r="L222" t="n">
-        <v>0</v>
-      </c>
-      <c r="M222" t="n">
-        <v>0</v>
-      </c>
-      <c r="N222" t="n">
-        <v>0</v>
-      </c>
-      <c r="O222" t="n">
-        <v>0</v>
-      </c>
-      <c r="P222" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
-      <c r="R222" t="n">
-        <v>0</v>
-      </c>
-      <c r="S222" t="n">
-        <v>0</v>
-      </c>
-      <c r="T222" t="n">
-        <v>0</v>
-      </c>
-      <c r="U222" t="n">
-        <v>0</v>
-      </c>
-      <c r="V222" s="2" t="inlineStr"/>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>S 614-2024</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D223" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="E223" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>GÖTENE</t>
-        </is>
-      </c>
-      <c r="I223" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J223" t="n">
-        <v>0</v>
-      </c>
-      <c r="K223" t="n">
-        <v>0</v>
-      </c>
-      <c r="L223" t="n">
-        <v>0</v>
-      </c>
-      <c r="M223" t="n">
-        <v>0</v>
-      </c>
-      <c r="N223" t="n">
-        <v>0</v>
-      </c>
-      <c r="O223" t="n">
-        <v>0</v>
-      </c>
-      <c r="P223" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
-      <c r="R223" t="n">
-        <v>0</v>
-      </c>
-      <c r="S223" t="n">
-        <v>0</v>
-      </c>
-      <c r="T223" t="n">
-        <v>0</v>
-      </c>
-      <c r="U223" t="n">
-        <v>0</v>
-      </c>
-      <c r="V223" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt GÖTENE.xlsx
+++ b/Översikt GÖTENE.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44642</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45352</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45847</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>45846</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>46234</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>44827</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>44490</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41724-2022</t>
+          <t>A 5086-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44827</v>
+        <v>45330</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1815,16 +1815,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1839,7 +1839,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1848,49 +1848,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
         <v>1</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 41724-2022 artfynd.xlsx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 5086-2024 artfynd.xlsx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 41724-2022 karta.png", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 5086-2024 karta.png", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 41724-2022 georefererad karta.tif", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 5086-2024 georefererad karta.tif", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 41724-2022 FSC-klagomål.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 5086-2024 FSC-klagomål.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 41724-2022 FSC-klagomål mail.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 5086-2024 FSC-klagomål mail.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 41724-2022 tillsynsbegäran.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 5086-2024 tillsynsbegäran.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 41724-2022 tillsynsbegäran mail.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 5086-2024 tillsynsbegäran mail.docx", "A 5086-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32909-2025</t>
+          <t>A 28273-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45839</v>
+        <v>45099</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1944,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1960,42 +1960,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32909-2025 artfynd.xlsx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 28273-2023 artfynd.xlsx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32909-2025 karta.png", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 28273-2023 karta.png", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32909-2025 georefererad karta.tif", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 28273-2023 georefererad karta.tif", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32909-2025 FSC-klagomål.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 28273-2023 FSC-klagomål.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32909-2025 FSC-klagomål mail.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 28273-2023 FSC-klagomål mail.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32909-2025 tillsynsbegäran.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 28273-2023 tillsynsbegäran.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32909-2025 tillsynsbegäran mail.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 28273-2023 tillsynsbegäran mail.docx", "A 28273-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 47393-2025</t>
+          <t>A 32909-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45930</v>
+        <v>45839</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2065,42 +2065,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Korallticka</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 47393-2025 artfynd.xlsx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32909-2025 artfynd.xlsx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 47393-2025 karta.png", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32909-2025 karta.png", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 47393-2025 georefererad karta.tif", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32909-2025 georefererad karta.tif", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 47393-2025 FSC-klagomål.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32909-2025 FSC-klagomål.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 47393-2025 FSC-klagomål mail.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32909-2025 FSC-klagomål mail.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 47393-2025 tillsynsbegäran.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32909-2025 tillsynsbegäran.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 47393-2025 tillsynsbegäran mail.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32909-2025 tillsynsbegäran mail.docx", "A 32909-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 50366-2025</t>
+          <t>A 41724-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45944</v>
+        <v>44827</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2170,42 +2170,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Korallticka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 50366-2025 artfynd.xlsx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 41724-2022 artfynd.xlsx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 50366-2025 karta.png", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 41724-2022 karta.png", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 50366-2025 georefererad karta.tif", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 41724-2022 georefererad karta.tif", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 50366-2025 FSC-klagomål.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 41724-2022 FSC-klagomål.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 50366-2025 FSC-klagomål mail.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 41724-2022 FSC-klagomål mail.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 50366-2025 tillsynsbegäran.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 41724-2022 tillsynsbegäran.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 50366-2025 tillsynsbegäran mail.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 41724-2022 tillsynsbegäran mail.docx", "A 41724-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 45211-2022</t>
+          <t>A 18647-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44844</v>
+        <v>45763</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2234,8 +2234,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2271,46 +2276,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 45211-2022 artfynd.xlsx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 18647-2025 artfynd.xlsx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 45211-2022 karta.png", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 18647-2025 karta.png", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 45211-2022 georefererad karta.tif", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 18647-2025 georefererad karta.tif", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 45211-2022 FSC-klagomål.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 18647-2025 FSC-klagomål.docx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 45211-2022 FSC-klagomål mail.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 18647-2025 FSC-klagomål mail.docx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 45211-2022 tillsynsbegäran.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 18647-2025 tillsynsbegäran.docx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 45211-2022 tillsynsbegäran mail.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 18647-2025 tillsynsbegäran mail.docx", "A 18647-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 18647-2025</t>
+          <t>A 47393-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2324,10 +2329,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45763</v>
+        <v>45930</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2339,23 +2344,18 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2385,42 +2385,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Korallticka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 18647-2025 artfynd.xlsx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 47393-2025 artfynd.xlsx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 18647-2025 karta.png", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 47393-2025 karta.png", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 18647-2025 georefererad karta.tif", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 47393-2025 georefererad karta.tif", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 18647-2025 FSC-klagomål.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 47393-2025 FSC-klagomål.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 18647-2025 FSC-klagomål mail.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 47393-2025 FSC-klagomål mail.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 18647-2025 tillsynsbegäran.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 47393-2025 tillsynsbegäran.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 18647-2025 tillsynsbegäran mail.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 47393-2025 tillsynsbegäran mail.docx", "A 47393-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 19083-2022</t>
+          <t>A 50366-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44691</v>
+        <v>45944</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2450,19 +2450,19 @@
         </is>
       </c>
       <c r="I19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2477,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2486,39 +2486,39 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Läderbagge</t>
+          <t>Korallticka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 19083-2022 artfynd.xlsx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 50366-2025 artfynd.xlsx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 19083-2022 karta.png", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 50366-2025 karta.png", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 19083-2022 georefererad karta.tif", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 50366-2025 georefererad karta.tif", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 19083-2022 FSC-klagomål.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 50366-2025 FSC-klagomål.docx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 19083-2022 FSC-klagomål mail.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 50366-2025 FSC-klagomål mail.docx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 19083-2022 tillsynsbegäran.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 50366-2025 tillsynsbegäran.docx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 19083-2022 tillsynsbegäran mail.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 50366-2025 tillsynsbegäran mail.docx", "A 50366-2025")</f>
         <v/>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
         <v>45011</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 33478-2026</t>
+          <t>A 19083-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46247</v>
+        <v>44691</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2664,20 +2664,20 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
@@ -2688,10 +2688,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2700,46 +2700,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Läderbagge</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 33478-2026 artfynd.xlsx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 19083-2022 artfynd.xlsx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 33478-2026 karta.png", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 19083-2022 karta.png", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 33478-2026 georefererad karta.tif", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 19083-2022 georefererad karta.tif", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 33478-2026 FSC-klagomål.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 19083-2022 FSC-klagomål.docx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 33478-2026 FSC-klagomål mail.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 19083-2022 FSC-klagomål mail.docx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 33478-2026 tillsynsbegäran.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 19083-2022 tillsynsbegäran.docx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 33478-2026 tillsynsbegäran mail.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 19083-2022 tillsynsbegäran mail.docx", "A 19083-2022")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 5086-2024</t>
+          <t>A 33478-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45330</v>
+        <v>46247</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2802,42 +2802,42 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 5086-2024 artfynd.xlsx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 33478-2026 artfynd.xlsx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 5086-2024 karta.png", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 33478-2026 karta.png", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 5086-2024 georefererad karta.tif", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 33478-2026 georefererad karta.tif", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 5086-2024 FSC-klagomål.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 33478-2026 FSC-klagomål.docx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 5086-2024 FSC-klagomål mail.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 33478-2026 FSC-klagomål mail.docx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 5086-2024 tillsynsbegäran.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 33478-2026 tillsynsbegäran.docx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 5086-2024 tillsynsbegäran mail.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 33478-2026 tillsynsbegäran mail.docx", "A 33478-2026")</f>
         <v/>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
         <v>46219</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 28273-2023</t>
+          <t>A 45211-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45099</v>
+        <v>44844</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2983,13 +2983,13 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5.1</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3019,39 +3019,39 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 28273-2023 artfynd.xlsx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 45211-2022 artfynd.xlsx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 28273-2023 karta.png", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 45211-2022 karta.png", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 28273-2023 georefererad karta.tif", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 45211-2022 georefererad karta.tif", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 28273-2023 FSC-klagomål.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 45211-2022 FSC-klagomål.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 28273-2023 FSC-klagomål mail.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 45211-2022 FSC-klagomål mail.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 28273-2023 tillsynsbegäran.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 45211-2022 tillsynsbegäran.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 28273-2023 tillsynsbegäran mail.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 45211-2022 tillsynsbegäran mail.docx", "A 45211-2022")</f>
         <v/>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
         <v>46237</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>45372</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>44490</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>44645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>44490</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>44490</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>44507</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>44614</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>44840</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>44859</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>44566</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>44684</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>44477</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>44507</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>44581</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30128-2022</t>
+          <t>A 30432-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44757</v>
+        <v>44761</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30432-2022</t>
+          <t>A 30128-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44761</v>
+        <v>44757</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>44869</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>44812</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>44848</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>44865</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>44490</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>44603</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>44475</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>44803</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>44498</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>44816</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 58418-2024</t>
+          <t>A 9607-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45634</v>
+        <v>45361</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 36381-2023</t>
+          <t>A 58650-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45152</v>
+        <v>45251</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5546,7 +5546,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8330-2024</t>
+          <t>A 45239-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5560,10 +5560,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45352</v>
+        <v>44844</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5575,8 +5575,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5619,7 +5624,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 13276-2024</t>
+          <t>A 52352-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5633,10 +5638,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45386</v>
+        <v>45224</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5649,7 +5654,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5692,7 +5697,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 849-2023</t>
+          <t>A 28264-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5706,10 +5711,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44931</v>
+        <v>45099</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5722,7 +5727,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5765,7 +5770,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 41721-2022</t>
+          <t>A 28268-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5779,10 +5784,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44827</v>
+        <v>45099</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5795,7 +5800,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5838,7 +5843,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 44608-2023</t>
+          <t>A 13276-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5852,10 +5857,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45189</v>
+        <v>45386</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5868,7 +5873,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5911,7 +5916,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 31917-2022</t>
+          <t>A 1352-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5925,10 +5930,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44777</v>
+        <v>44931</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5941,7 +5946,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5984,7 +5989,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 25434-2025</t>
+          <t>A 72879-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5998,10 +6003,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45800</v>
+        <v>44547</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6014,7 +6019,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6057,7 +6062,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 25435-2025</t>
+          <t>A 28267-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6071,10 +6076,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45800</v>
+        <v>45099</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6087,7 +6092,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6130,7 +6135,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 11889-2024</t>
+          <t>A 62499-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6144,10 +6149,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45376</v>
+        <v>44924</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6159,8 +6164,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6203,7 +6213,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 11772-2024</t>
+          <t>A 3932-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6217,10 +6227,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45373</v>
+        <v>44587</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6233,7 +6243,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6276,7 +6286,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 25436-2025</t>
+          <t>A 28390-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6290,10 +6300,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45800</v>
+        <v>45819</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6305,8 +6315,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6349,7 +6364,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 11773-2024</t>
+          <t>A 58418-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6363,10 +6378,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45373</v>
+        <v>45634</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6379,7 +6394,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6422,7 +6437,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 26105-2025</t>
+          <t>A 13170-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6432,14 +6447,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45805</v>
+        <v>45386</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6452,7 +6467,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6495,7 +6510,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 10703-2025</t>
+          <t>A 45180-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6509,10 +6524,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45722</v>
+        <v>45575</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6525,7 +6540,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>14.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6568,7 +6583,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 61194-2024</t>
+          <t>A 36304-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6582,10 +6597,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45645</v>
+        <v>45152</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6597,13 +6612,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6646,7 +6656,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 28390-2025</t>
+          <t>A 49256-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6660,10 +6670,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45819</v>
+        <v>45210</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6675,13 +6685,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6724,7 +6729,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 39998-2025</t>
+          <t>A 10630-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6738,10 +6743,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45894</v>
+        <v>46078</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6754,7 +6759,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6797,7 +6802,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 17010-2022</t>
+          <t>A 31258-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6811,10 +6816,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44676</v>
+        <v>45833</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6827,7 +6832,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>5.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6870,7 +6875,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 61021-2022</t>
+          <t>A 11459-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6880,14 +6885,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44914</v>
+        <v>46083</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6900,7 +6905,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6943,7 +6948,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 31258-2025</t>
+          <t>A 11460-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6957,10 +6962,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45833</v>
+        <v>46083</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6973,7 +6978,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7016,7 +7021,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 30205-2023</t>
+          <t>A 11630-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7030,10 +7035,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45110</v>
+        <v>46084</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7045,8 +7050,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>6.8</v>
+        <v>1.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7089,7 +7099,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 32967-2025</t>
+          <t>A 10596-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7103,10 +7113,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45839</v>
+        <v>45366</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7119,7 +7129,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7162,7 +7172,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 45007-2025</t>
+          <t>A 61194-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7176,10 +7186,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45918</v>
+        <v>45645</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7191,8 +7201,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7235,7 +7250,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 22278-2024</t>
+          <t>A 32967-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7249,10 +7264,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45446</v>
+        <v>45839</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7265,7 +7280,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7308,7 +7323,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 6925-2023</t>
+          <t>A 21285-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7322,10 +7337,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44967</v>
+        <v>45440</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7337,13 +7352,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7386,7 +7396,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 58236-2024</t>
+          <t>A 41721-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7400,10 +7410,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45632</v>
+        <v>44827</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7415,13 +7425,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7464,7 +7469,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 58691-2024</t>
+          <t>A 6925-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7478,10 +7483,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45635</v>
+        <v>44967</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7499,7 +7504,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7542,7 +7547,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 47175-2025</t>
+          <t>A 58236-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7556,10 +7561,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45930</v>
+        <v>45632</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7571,8 +7576,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7615,7 +7625,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 47383-2025</t>
+          <t>A 58691-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7629,10 +7639,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45930</v>
+        <v>45635</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7644,8 +7654,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7688,7 +7703,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 47385-2025</t>
+          <t>A 55764-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7702,10 +7717,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45930</v>
+        <v>45623</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7718,7 +7733,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7761,7 +7776,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 47389-2025</t>
+          <t>A 56169-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7775,10 +7790,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45930</v>
+        <v>45624</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7791,7 +7806,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>19.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7834,7 +7849,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 17069-2023</t>
+          <t>A 850-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7848,10 +7863,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45034</v>
+        <v>44931</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7864,7 +7879,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7907,7 +7922,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 1379-2025</t>
+          <t>A 13450-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7921,10 +7936,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45667</v>
+        <v>45736</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7937,7 +7952,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7980,7 +7995,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 13450-2025</t>
+          <t>A 39998-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7994,10 +8009,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45736</v>
+        <v>45894</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8010,7 +8025,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8053,7 +8068,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 3960-2026</t>
+          <t>A 61294-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8067,10 +8082,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46044</v>
+        <v>45645</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8082,13 +8097,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>3.7</v>
+        <v>0.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8131,7 +8141,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 5044-2026</t>
+          <t>A 12660-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8141,14 +8151,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46049</v>
+        <v>45000</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8161,7 +8171,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>5.4</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8204,7 +8214,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 52141-2025</t>
+          <t>A 62390-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8218,10 +8228,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45953</v>
+        <v>45268</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8234,7 +8244,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8277,7 +8287,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 45180-2024</t>
+          <t>A 62402-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8291,10 +8301,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45575</v>
+        <v>45268</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8307,7 +8317,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>14.7</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8350,7 +8360,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 14502-2023</t>
+          <t>A 18776-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8364,10 +8374,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45012</v>
+        <v>46128</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8380,7 +8390,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8423,7 +8433,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 13340-2022</t>
+          <t>A 11771-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8437,10 +8447,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44645</v>
+        <v>45373</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8453,7 +8463,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8496,7 +8506,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 13348-2022</t>
+          <t>A 31981-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8510,10 +8520,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44645</v>
+        <v>45119</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8526,7 +8536,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8569,7 +8579,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 13366-2022</t>
+          <t>A 45007-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8583,10 +8593,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44645</v>
+        <v>45918</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8599,7 +8609,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8659,7 +8669,7 @@
         <v>45021</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8715,7 +8725,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 9607-2024</t>
+          <t>A 30174-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8729,10 +8739,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45361</v>
+        <v>44757</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8745,7 +8755,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8788,7 +8798,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 56365-2025</t>
+          <t>A 62510-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8802,10 +8812,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45974</v>
+        <v>44924</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8817,8 +8827,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8861,7 +8876,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 56347-2025</t>
+          <t>A 61021-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8871,14 +8886,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45974</v>
+        <v>44914</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8891,7 +8906,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>10.9</v>
+        <v>1.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8934,7 +8949,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 56352-2025</t>
+          <t>A 849-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8948,10 +8963,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45974</v>
+        <v>44931</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8964,7 +8979,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5.9</v>
+        <v>3.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9007,7 +9022,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 56414-2025</t>
+          <t>A 45013-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9021,10 +9036,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45975</v>
+        <v>45918</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9037,7 +9052,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9080,7 +9095,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 56340-2025</t>
+          <t>A 34161-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9094,10 +9109,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45974</v>
+        <v>45845</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9110,7 +9125,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9153,7 +9168,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 56417-2025</t>
+          <t>A 1662-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9167,10 +9182,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45975</v>
+        <v>45670</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9183,7 +9198,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9226,7 +9241,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 56346-2025</t>
+          <t>A 20710-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9240,10 +9255,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45974</v>
+        <v>46141</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9256,7 +9271,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>18.8</v>
+        <v>1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9299,7 +9314,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 9145-2023</t>
+          <t>A 20812-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9313,10 +9328,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44974</v>
+        <v>46141</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9329,7 +9344,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9372,7 +9387,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 58517-2025</t>
+          <t>A 33162-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9386,10 +9401,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45985</v>
+        <v>45518</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9402,7 +9417,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9445,7 +9460,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 58520-2025</t>
+          <t>A 47385-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9459,10 +9474,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45985</v>
+        <v>45930</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9475,7 +9490,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9518,7 +9533,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 58766-2025</t>
+          <t>A 20700-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9532,10 +9547,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45986</v>
+        <v>46141</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9591,7 +9606,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 58767-2025</t>
+          <t>A 47175-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9605,10 +9620,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45986</v>
+        <v>45930</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9621,7 +9636,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9664,7 +9679,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 10630-2026</t>
+          <t>A 47389-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9678,10 +9693,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46078</v>
+        <v>45930</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9737,7 +9752,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 11459-2026</t>
+          <t>A 25594-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9747,14 +9762,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46083</v>
+        <v>45803</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9767,7 +9782,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9810,7 +9825,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 13268-2024</t>
+          <t>A 47383-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9824,10 +9839,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45386</v>
+        <v>45930</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9840,7 +9855,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>6.7</v>
+        <v>1.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9883,7 +9898,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 11460-2026</t>
+          <t>A 20811-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9897,10 +9912,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46083</v>
+        <v>46141</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9913,7 +9928,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9956,7 +9971,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 11630-2026</t>
+          <t>A 31969-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9970,10 +9985,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46084</v>
+        <v>45119</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9985,13 +10000,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10034,7 +10044,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 10451-2024</t>
+          <t>A 31978-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10048,10 +10058,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45366</v>
+        <v>45119</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10061,11 +10071,6 @@
       <c r="G119" t="inlineStr">
         <is>
           <t>GÖTENE</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I119" t="n">
@@ -10112,7 +10117,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 60559-2025</t>
+          <t>A 21376-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10126,10 +10131,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45995</v>
+        <v>46147</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10142,7 +10147,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.5</v>
+        <v>7.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10185,7 +10190,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 12660-2023</t>
+          <t>A 21369-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10195,14 +10200,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45000</v>
+        <v>46147</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10215,7 +10220,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10258,7 +10263,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 22055-2023</t>
+          <t>A 28258-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10272,10 +10277,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45069</v>
+        <v>45099</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10288,7 +10293,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10331,7 +10336,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 10596-2024</t>
+          <t>A 22278-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10345,10 +10350,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45366</v>
+        <v>45446</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10361,7 +10366,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10404,7 +10409,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 28268-2023</t>
+          <t>A 17069-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10418,10 +10423,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45099</v>
+        <v>45034</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10434,7 +10439,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10477,7 +10482,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 850-2023</t>
+          <t>A 22906-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10491,10 +10496,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44931</v>
+        <v>46160</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10507,7 +10512,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10550,7 +10555,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 55764-2024</t>
+          <t>A 22916-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10564,10 +10569,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45623</v>
+        <v>46160</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10580,7 +10585,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10623,7 +10628,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 19674-2023</t>
+          <t>A 22912-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10637,10 +10642,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45051</v>
+        <v>46160</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10653,7 +10658,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10696,7 +10701,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 19683-2023</t>
+          <t>A 59074-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10710,10 +10715,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45051</v>
+        <v>45252</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10726,7 +10731,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10769,7 +10774,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 8765-2022</t>
+          <t>A 11772-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10783,10 +10788,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44614</v>
+        <v>45373</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10798,13 +10803,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10847,7 +10847,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 52352-2023</t>
+          <t>A 11773-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10861,10 +10861,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45224</v>
+        <v>45373</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10920,7 +10920,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 18776-2026</t>
+          <t>A 8765-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10934,10 +10934,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46128</v>
+        <v>44614</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10949,8 +10949,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10993,7 +10998,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 62510-2022</t>
+          <t>A 30205-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11007,10 +11012,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44924</v>
+        <v>45110</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11022,13 +11027,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>0.6</v>
+        <v>6.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11071,7 +11071,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 45013-2025</t>
+          <t>A 25777-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11081,14 +11081,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45918</v>
+        <v>46178</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11144,7 +11144,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 1662-2025</t>
+          <t>A 26338-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11158,10 +11158,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45670</v>
+        <v>46182</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11217,7 +11217,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 17876-2025</t>
+          <t>A 52141-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11231,10 +11231,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45758</v>
+        <v>45953</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11290,7 +11290,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 30174-2022</t>
+          <t>A 26336-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11304,10 +11304,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44757</v>
+        <v>46182</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>5.1</v>
+        <v>1.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11363,7 +11363,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 34161-2025</t>
+          <t>A 1379-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11377,10 +11377,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45845</v>
+        <v>45667</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11436,7 +11436,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 13170-2024</t>
+          <t>A 44608-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11450,10 +11450,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45386</v>
+        <v>45189</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11509,7 +11509,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 62390-2023</t>
+          <t>A 44033-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11523,10 +11523,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45268</v>
+        <v>45572</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11582,7 +11582,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 25594-2025</t>
+          <t>A 10636-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11592,14 +11592,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45803</v>
+        <v>46078</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11655,7 +11655,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 20710-2026</t>
+          <t>A 13366-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11669,10 +11669,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46141</v>
+        <v>44645</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11728,7 +11728,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 20811-2026</t>
+          <t>A 15428-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11742,10 +11742,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46141</v>
+        <v>45747</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11801,7 +11801,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 33162-2024</t>
+          <t>A 15434-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11815,10 +11815,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45518</v>
+        <v>45747</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11874,7 +11874,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 62499-2022</t>
+          <t>A 28647-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11888,10 +11888,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44924</v>
+        <v>46198</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11901,11 +11901,6 @@
       <c r="G144" t="inlineStr">
         <is>
           <t>GÖTENE</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I144" t="n">
@@ -11952,7 +11947,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 20812-2026</t>
+          <t>A 28467-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11966,10 +11961,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46141</v>
+        <v>46197</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11982,7 +11977,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12025,7 +12020,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 20700-2026</t>
+          <t>A 17010-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12039,10 +12034,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46141</v>
+        <v>44676</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12055,7 +12050,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12098,7 +12093,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 10958-2022</t>
+          <t>A 56365-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12112,10 +12107,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44628</v>
+        <v>45974</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12128,7 +12123,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12171,7 +12166,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 45239-2022</t>
+          <t>A 56347-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12185,10 +12180,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44844</v>
+        <v>45974</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12200,13 +12195,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>1.7</v>
+        <v>10.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12249,7 +12239,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 21369-2026</t>
+          <t>A 56352-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12263,10 +12253,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46147</v>
+        <v>45974</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12279,7 +12269,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12322,7 +12312,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 15426-2025</t>
+          <t>A 56346-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12336,10 +12326,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45747</v>
+        <v>45974</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12352,7 +12342,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.1</v>
+        <v>18.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12395,7 +12385,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 15442-2025</t>
+          <t>A 56340-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12409,10 +12399,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45747</v>
+        <v>45974</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12425,7 +12415,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.2</v>
+        <v>4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12468,7 +12458,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 21376-2026</t>
+          <t>A 19674-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12482,10 +12472,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46147</v>
+        <v>45051</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12498,7 +12488,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>7.2</v>
+        <v>0.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12541,7 +12531,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 22916-2026</t>
+          <t>A 56417-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12555,10 +12545,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46160</v>
+        <v>45975</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12571,7 +12561,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12614,7 +12604,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 22906-2026</t>
+          <t>A 13345-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12628,10 +12618,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46160</v>
+        <v>44645</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12644,7 +12634,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12687,7 +12677,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 22912-2026</t>
+          <t>A 56414-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12701,10 +12691,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46160</v>
+        <v>45975</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12717,7 +12707,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12760,7 +12750,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 12450-2022</t>
+          <t>A 21429-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12774,10 +12764,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44638</v>
+        <v>44706</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12790,7 +12780,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12833,7 +12823,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 21429-2022</t>
+          <t>A 35408-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12847,10 +12837,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44706</v>
+        <v>45146</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12863,7 +12853,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12906,7 +12896,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 56169-2024</t>
+          <t>A 58766-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12920,10 +12910,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45624</v>
+        <v>45986</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12936,7 +12926,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>19.7</v>
+        <v>1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12979,7 +12969,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 13279-2024</t>
+          <t>A 20507-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12993,10 +12983,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45386</v>
+        <v>46140</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13009,7 +12999,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13052,7 +13042,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 49256-2023</t>
+          <t>A 58767-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13066,10 +13056,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45210</v>
+        <v>45986</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13082,7 +13072,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13125,7 +13115,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 31969-2023</t>
+          <t>A 58517-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13139,10 +13129,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45119</v>
+        <v>45985</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13198,7 +13188,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 31978-2023</t>
+          <t>A 58520-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13212,10 +13202,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45119</v>
+        <v>45985</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13228,7 +13218,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13271,7 +13261,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 39150-2022</t>
+          <t>A 55511-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13285,10 +13275,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44817</v>
+        <v>45238</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13301,7 +13291,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13344,7 +13334,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 25777-2026</t>
+          <t>A 30191-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13354,14 +13344,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46178</v>
+        <v>46206</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13373,8 +13363,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13417,7 +13412,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 36472-2023</t>
+          <t>A 34008-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13431,10 +13426,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45152</v>
+        <v>46252</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13447,7 +13442,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13490,7 +13485,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 26336-2026</t>
+          <t>A 5690-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13504,10 +13499,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46182</v>
+        <v>46051</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13520,7 +13515,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13563,7 +13558,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 26338-2026</t>
+          <t>A 36472-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13577,10 +13572,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46182</v>
+        <v>45152</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13636,7 +13631,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 3932-2022</t>
+          <t>A 49252-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13650,10 +13645,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44587</v>
+        <v>45210</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13666,7 +13661,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13709,7 +13704,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 7225-2023</t>
+          <t>A 31917-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13723,10 +13718,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44970</v>
+        <v>44777</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13739,7 +13734,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13782,7 +13777,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 35408-2023</t>
+          <t>A 17876-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13796,10 +13791,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45146</v>
+        <v>45758</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13812,7 +13807,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13855,7 +13850,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 13280-2024</t>
+          <t>A 60559-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13869,10 +13864,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45386</v>
+        <v>45995</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13885,7 +13880,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13928,7 +13923,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 31981-2023</t>
+          <t>A 12450-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13942,10 +13937,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45119</v>
+        <v>44638</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13958,7 +13953,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14001,7 +13996,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 55511-2023</t>
+          <t>A 31329-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14015,10 +14010,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45238</v>
+        <v>46219</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14031,7 +14026,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14074,7 +14069,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 28258-2023</t>
+          <t>A 31324-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14088,10 +14083,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45099</v>
+        <v>46219</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14104,7 +14099,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14147,7 +14142,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 28264-2023</t>
+          <t>A 35869-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14161,10 +14156,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45099</v>
+        <v>46266</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14177,7 +14172,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14220,7 +14215,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 49252-2023</t>
+          <t>A 35871-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14234,10 +14229,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45210</v>
+        <v>46266</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14250,7 +14245,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14293,7 +14288,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 10636-2026</t>
+          <t>A 31446-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14307,10 +14302,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46078</v>
+        <v>46220</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14323,7 +14318,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14366,7 +14361,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 28467-2026</t>
+          <t>A 31452-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14380,10 +14375,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46197</v>
+        <v>46220</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14396,7 +14391,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14439,7 +14434,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 28647-2026</t>
+          <t>A 64712-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14453,10 +14448,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46198</v>
+        <v>45281</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14469,7 +14464,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14512,7 +14507,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 20507-2026</t>
+          <t>A 39081-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14526,10 +14521,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46140</v>
+        <v>44817</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14542,7 +14537,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14585,7 +14580,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 28335-2023</t>
+          <t>A 36381-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14599,10 +14594,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45099</v>
+        <v>45152</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14615,7 +14610,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14658,7 +14653,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 13281-2024</t>
+          <t>A 13268-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14675,7 +14670,7 @@
         <v>45386</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14688,7 +14683,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.1</v>
+        <v>6.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14731,7 +14726,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 58650-2023</t>
+          <t>A 13281-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14745,10 +14740,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45251</v>
+        <v>45386</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14761,7 +14756,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14804,7 +14799,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 36304-2023</t>
+          <t>A 19683-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14818,10 +14813,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45152</v>
+        <v>45051</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14834,7 +14829,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14877,7 +14872,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 59074-2023</t>
+          <t>A 58417-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14891,10 +14886,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45252</v>
+        <v>45634</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14906,8 +14901,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14950,7 +14950,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 30191-2026</t>
+          <t>A 37557-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14964,10 +14964,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46206</v>
+        <v>46276</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14979,13 +14979,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15028,7 +15023,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 34008-2026</t>
+          <t>A 39150-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15042,10 +15037,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46252</v>
+        <v>44817</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15058,7 +15053,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15101,7 +15096,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 5690-2026</t>
+          <t>A 32298-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15115,10 +15110,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46051</v>
+        <v>46237</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15130,8 +15125,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15174,7 +15174,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 15428-2025</t>
+          <t>A 32363-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15188,10 +15188,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45747</v>
+        <v>46238</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.1</v>
+        <v>6.2</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15247,7 +15247,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 15434-2025</t>
+          <t>A 32364-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15261,10 +15261,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45747</v>
+        <v>46238</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15320,7 +15320,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 11771-2024</t>
+          <t>A 14502-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15334,10 +15334,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45373</v>
+        <v>45012</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15393,7 +15393,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 58417-2024</t>
+          <t>A 3960-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15407,10 +15407,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45634</v>
+        <v>46044</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15424,11 +15424,11 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15471,7 +15471,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 13345-2022</t>
+          <t>A 10958-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15485,10 +15485,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44645</v>
+        <v>44628</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15544,7 +15544,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 31329-2026</t>
+          <t>A 5044-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15558,10 +15558,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46219</v>
+        <v>46049</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>7.5</v>
+        <v>5.4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 31446-2026</t>
+          <t>A 9145-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15631,10 +15631,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46220</v>
+        <v>44974</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 31452-2026</t>
+          <t>A 7225-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15704,10 +15704,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46220</v>
+        <v>44970</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15763,7 +15763,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 64712-2023</t>
+          <t>A 10451-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15777,10 +15777,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45281</v>
+        <v>45366</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15792,8 +15792,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15836,7 +15841,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 31324-2026</t>
+          <t>A 28332-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15850,10 +15855,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46219</v>
+        <v>45099</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15866,7 +15871,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15909,7 +15914,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 39081-2022</t>
+          <t>A 8330-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15923,10 +15928,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44817</v>
+        <v>45352</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15939,7 +15944,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15982,7 +15987,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 61294-2024</t>
+          <t>A 13279-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15996,10 +16001,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45645</v>
+        <v>45386</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16012,7 +16017,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16055,7 +16060,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 35869-2026</t>
+          <t>A 11889-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16069,10 +16074,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46266</v>
+        <v>45376</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16085,7 +16090,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16128,7 +16133,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 35871-2026</t>
+          <t>A 15426-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16142,10 +16147,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46266</v>
+        <v>45747</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16158,7 +16163,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16201,7 +16206,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 62402-2023</t>
+          <t>A 15442-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16215,10 +16220,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45268</v>
+        <v>45747</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16231,7 +16236,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16274,7 +16279,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 1352-2023</t>
+          <t>A 13340-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16288,10 +16293,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44931</v>
+        <v>44645</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16304,7 +16309,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16347,7 +16352,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 28332-2023</t>
+          <t>A 13348-2022</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16361,10 +16366,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45099</v>
+        <v>44645</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16377,7 +16382,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16420,7 +16425,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 44033-2024</t>
+          <t>A 22055-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16434,10 +16439,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45572</v>
+        <v>45069</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16450,7 +16455,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16493,7 +16498,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 72879-2021</t>
+          <t>A 13280-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16507,10 +16512,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44547</v>
+        <v>45386</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16523,7 +16528,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16566,7 +16571,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 28267-2023</t>
+          <t>A 28335-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16583,7 +16588,7 @@
         <v>45099</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16596,7 +16601,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16639,7 +16644,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 21285-2024</t>
+          <t>A 12664-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16653,10 +16658,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45440</v>
+        <v>45000</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16669,7 +16674,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16712,7 +16717,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 37557-2026</t>
+          <t>A 21269-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16726,10 +16731,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46276</v>
+        <v>45440</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16742,7 +16747,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16785,7 +16790,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 32298-2026</t>
+          <t>A 28316-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16799,10 +16804,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46237</v>
+        <v>45477</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16814,13 +16819,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16863,7 +16863,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 32363-2026</t>
+          <t>A 16341-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16873,14 +16873,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46238</v>
+        <v>45751</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>6.2</v>
+        <v>1.4</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16936,7 +16936,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 32364-2026</t>
+          <t>A 10668-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16950,10 +16950,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46238</v>
+        <v>45721</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17009,7 +17009,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 28316-2024</t>
+          <t>A 25434-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17023,10 +17023,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45477</v>
+        <v>45800</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17082,7 +17082,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 21269-2024</t>
+          <t>A 25435-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17096,10 +17096,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45440</v>
+        <v>45800</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17155,7 +17155,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 12664-2023</t>
+          <t>A 25436-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17169,10 +17169,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45000</v>
+        <v>45800</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17228,7 +17228,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 16341-2025</t>
+          <t>A 26105-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17242,10 +17242,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45751</v>
+        <v>45805</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 10668-2025</t>
+          <t>A 10703-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17315,10 +17315,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17391,7 +17391,7 @@
         <v>44862</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45352</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>45352</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>

--- a/Översikt GÖTENE.xlsx
+++ b/Översikt GÖTENE.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44642</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45352</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45847</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>45846</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>46234</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>44827</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>44490</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 5086-2024</t>
+          <t>A 41724-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45330</v>
+        <v>44827</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1815,17 +1815,17 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1839,7 +1839,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1848,49 +1848,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 5086-2024 artfynd.xlsx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 41724-2022 artfynd.xlsx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 5086-2024 karta.png", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 41724-2022 karta.png", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 5086-2024 georefererad karta.tif", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 41724-2022 georefererad karta.tif", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 5086-2024 FSC-klagomål.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 41724-2022 FSC-klagomål.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 5086-2024 FSC-klagomål mail.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 41724-2022 FSC-klagomål mail.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 5086-2024 tillsynsbegäran.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 41724-2022 tillsynsbegäran.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 5086-2024 tillsynsbegäran mail.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 41724-2022 tillsynsbegäran mail.docx", "A 41724-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 28273-2023</t>
+          <t>A 45211-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45099</v>
+        <v>44844</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1920,13 +1920,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>2.3</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1956,46 +1956,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 28273-2023 artfynd.xlsx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 45211-2022 artfynd.xlsx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 28273-2023 karta.png", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 45211-2022 karta.png", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 28273-2023 georefererad karta.tif", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 45211-2022 georefererad karta.tif", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 28273-2023 FSC-klagomål.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 45211-2022 FSC-klagomål.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 28273-2023 FSC-klagomål mail.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 45211-2022 FSC-klagomål mail.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 28273-2023 tillsynsbegäran.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 45211-2022 tillsynsbegäran.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 28273-2023 tillsynsbegäran mail.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 45211-2022 tillsynsbegäran mail.docx", "A 45211-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32909-2025</t>
+          <t>A 18647-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45839</v>
+        <v>45763</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2024,17 +2024,22 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2049,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2065,42 +2070,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32909-2025 artfynd.xlsx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 18647-2025 artfynd.xlsx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32909-2025 karta.png", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 18647-2025 karta.png", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32909-2025 georefererad karta.tif", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 18647-2025 georefererad karta.tif", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32909-2025 FSC-klagomål.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 18647-2025 FSC-klagomål.docx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32909-2025 FSC-klagomål mail.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 18647-2025 FSC-klagomål mail.docx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32909-2025 tillsynsbegäran.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 18647-2025 tillsynsbegäran.docx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32909-2025 tillsynsbegäran mail.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 18647-2025 tillsynsbegäran mail.docx", "A 18647-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 41724-2022</t>
+          <t>A 47393-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2114,10 +2119,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44827</v>
+        <v>45930</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2130,7 +2135,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2170,42 +2175,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Korallticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 41724-2022 artfynd.xlsx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 47393-2025 artfynd.xlsx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 41724-2022 karta.png", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 47393-2025 karta.png", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 41724-2022 georefererad karta.tif", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 47393-2025 georefererad karta.tif", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 41724-2022 FSC-klagomål.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 47393-2025 FSC-klagomål.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 41724-2022 FSC-klagomål mail.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 47393-2025 FSC-klagomål mail.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 41724-2022 tillsynsbegäran.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 47393-2025 tillsynsbegäran.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 41724-2022 tillsynsbegäran mail.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 47393-2025 tillsynsbegäran mail.docx", "A 47393-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 18647-2025</t>
+          <t>A 50366-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2219,10 +2224,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45763</v>
+        <v>45944</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2234,23 +2239,18 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2280,42 +2280,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Korallticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 18647-2025 artfynd.xlsx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 50366-2025 artfynd.xlsx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 18647-2025 karta.png", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 50366-2025 karta.png", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 18647-2025 georefererad karta.tif", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 50366-2025 georefererad karta.tif", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 18647-2025 FSC-klagomål.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 50366-2025 FSC-klagomål.docx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 18647-2025 FSC-klagomål mail.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 50366-2025 FSC-klagomål mail.docx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 18647-2025 tillsynsbegäran.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 50366-2025 tillsynsbegäran.docx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 18647-2025 tillsynsbegäran mail.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 50366-2025 tillsynsbegäran mail.docx", "A 50366-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 47393-2025</t>
+          <t>A 19083-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45930</v>
+        <v>44691</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2345,19 +2345,19 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2372,7 +2372,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2381,46 +2381,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Korallticka</t>
+          <t>Läderbagge</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 47393-2025 artfynd.xlsx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 19083-2022 artfynd.xlsx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 47393-2025 karta.png", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 19083-2022 karta.png", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 47393-2025 georefererad karta.tif", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 19083-2022 georefererad karta.tif", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 47393-2025 FSC-klagomål.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 19083-2022 FSC-klagomål.docx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 47393-2025 FSC-klagomål mail.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 19083-2022 FSC-klagomål mail.docx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 47393-2025 tillsynsbegäran.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 19083-2022 tillsynsbegäran.docx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 47393-2025 tillsynsbegäran mail.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 19083-2022 tillsynsbegäran mail.docx", "A 19083-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 50366-2025</t>
+          <t>A 14296-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45944</v>
+        <v>45011</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2450,19 +2450,19 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2477,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2486,46 +2486,50 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Korallticka</t>
+          <t>Pilgrimsfalk</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 50366-2025 artfynd.xlsx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 14296-2023 artfynd.xlsx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 50366-2025 karta.png", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 14296-2023 karta.png", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 50366-2025 georefererad karta.tif", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 14296-2023 georefererad karta.tif", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 50366-2025 FSC-klagomål.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 14296-2023 FSC-klagomål.docx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 50366-2025 FSC-klagomål mail.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 14296-2023 FSC-klagomål mail.docx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 50366-2025 tillsynsbegäran.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 14296-2023 tillsynsbegäran.docx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 50366-2025 tillsynsbegäran mail.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 14296-2023 tillsynsbegäran mail.docx", "A 14296-2023")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 14296-2023 prioriterade fågelarter.docx", "A 14296-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 14296-2023</t>
+          <t>A 33478-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2539,10 +2543,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45011</v>
+        <v>46247</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2555,19 +2559,19 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2579,10 +2583,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2591,50 +2595,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Pilgrimsfalk</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 14296-2023 artfynd.xlsx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 33478-2026 artfynd.xlsx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 14296-2023 karta.png", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 33478-2026 karta.png", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 14296-2023 georefererad karta.tif", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 33478-2026 georefererad karta.tif", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 14296-2023 FSC-klagomål.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 33478-2026 FSC-klagomål.docx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 14296-2023 FSC-klagomål mail.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 33478-2026 FSC-klagomål mail.docx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 14296-2023 tillsynsbegäran.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 33478-2026 tillsynsbegäran.docx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 14296-2023 tillsynsbegäran mail.docx", "A 14296-2023")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 14296-2023 prioriterade fågelarter.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 33478-2026 tillsynsbegäran mail.docx", "A 33478-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 19083-2022</t>
+          <t>A 5086-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44691</v>
+        <v>45330</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2664,19 +2664,19 @@
         </is>
       </c>
       <c r="I21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2688,58 +2688,58 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Läderbagge</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 19083-2022 artfynd.xlsx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 5086-2024 artfynd.xlsx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 19083-2022 karta.png", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 5086-2024 karta.png", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 19083-2022 georefererad karta.tif", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 5086-2024 georefererad karta.tif", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 19083-2022 FSC-klagomål.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 5086-2024 FSC-klagomål.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 19083-2022 FSC-klagomål mail.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 5086-2024 FSC-klagomål mail.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 19083-2022 tillsynsbegäran.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 5086-2024 tillsynsbegäran.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 19083-2022 tillsynsbegäran mail.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 5086-2024 tillsynsbegäran mail.docx", "A 5086-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 33478-2026</t>
+          <t>A 28273-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46247</v>
+        <v>45099</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2769,13 +2769,13 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>5.1</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2809,35 +2809,35 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 33478-2026 artfynd.xlsx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 28273-2023 artfynd.xlsx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 33478-2026 karta.png", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 28273-2023 karta.png", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 33478-2026 georefererad karta.tif", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 28273-2023 georefererad karta.tif", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 33478-2026 FSC-klagomål.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 28273-2023 FSC-klagomål.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 33478-2026 FSC-klagomål mail.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 28273-2023 FSC-klagomål mail.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 33478-2026 tillsynsbegäran.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 28273-2023 tillsynsbegäran.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 33478-2026 tillsynsbegäran mail.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 28273-2023 tillsynsbegäran mail.docx", "A 28273-2023")</f>
         <v/>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
         <v>46219</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 45211-2022</t>
+          <t>A 32224-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44844</v>
+        <v>46237</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2983,17 +2983,17 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3007,7 +3007,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3019,46 +3019,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Backmåra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 45211-2022 artfynd.xlsx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32224-2026 artfynd.xlsx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 45211-2022 karta.png", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32224-2026 karta.png", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 45211-2022 georefererad karta.tif", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32224-2026 georefererad karta.tif", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 45211-2022 FSC-klagomål.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32224-2026 FSC-klagomål.docx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 45211-2022 FSC-klagomål mail.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32224-2026 FSC-klagomål mail.docx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 45211-2022 tillsynsbegäran.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32224-2026 tillsynsbegäran.docx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 45211-2022 tillsynsbegäran mail.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32224-2026 tillsynsbegäran mail.docx", "A 32224-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32224-2026</t>
+          <t>A 32909-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46237</v>
+        <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3128,35 +3128,35 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Backmåra</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32224-2026 artfynd.xlsx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32909-2025 artfynd.xlsx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32224-2026 karta.png", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32909-2025 karta.png", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32224-2026 georefererad karta.tif", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32909-2025 georefererad karta.tif", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32224-2026 FSC-klagomål.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32909-2025 FSC-klagomål.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32224-2026 FSC-klagomål mail.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32909-2025 FSC-klagomål mail.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32224-2026 tillsynsbegäran.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32909-2025 tillsynsbegäran.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32224-2026 tillsynsbegäran mail.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32909-2025 tillsynsbegäran mail.docx", "A 32909-2025")</f>
         <v/>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
         <v>45372</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>44490</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>44645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>44490</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>44490</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>44507</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>44614</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 44507-2022</t>
+          <t>A 48733-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44840</v>
+        <v>44859</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4076,7 +4076,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 48733-2022</t>
+          <t>A 44507-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44859</v>
+        <v>44840</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4166,7 +4166,7 @@
         <v>44566</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>44684</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>44477</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>44507</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>44581</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>44761</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>44757</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>44869</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>44812</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>44848</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>44865</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>44490</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>44603</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>44475</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>44803</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>44498</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>44816</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 9607-2024</t>
+          <t>A 58418-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45361</v>
+        <v>45634</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 58650-2023</t>
+          <t>A 36381-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45251</v>
+        <v>45152</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5546,7 +5546,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 45239-2022</t>
+          <t>A 8330-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5560,10 +5560,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44844</v>
+        <v>45352</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5575,13 +5575,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5624,7 +5619,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 52352-2023</t>
+          <t>A 13276-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5638,10 +5633,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45224</v>
+        <v>45386</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5654,7 +5649,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5697,7 +5692,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 28264-2023</t>
+          <t>A 849-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5711,10 +5706,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45099</v>
+        <v>44931</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5727,7 +5722,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5770,7 +5765,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 28268-2023</t>
+          <t>A 44608-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5784,10 +5779,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45099</v>
+        <v>45189</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5800,7 +5795,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5843,7 +5838,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 13276-2024</t>
+          <t>A 41721-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5857,10 +5852,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45386</v>
+        <v>44827</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5873,7 +5868,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5916,7 +5911,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 1352-2023</t>
+          <t>A 31917-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5930,10 +5925,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44931</v>
+        <v>44777</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5946,7 +5941,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5989,7 +5984,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 72879-2021</t>
+          <t>A 11889-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6003,10 +5998,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44547</v>
+        <v>45376</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6019,7 +6014,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6062,7 +6057,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 28267-2023</t>
+          <t>A 11772-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6076,10 +6071,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45099</v>
+        <v>45373</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6092,7 +6087,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6135,7 +6130,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 62499-2022</t>
+          <t>A 11773-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6149,10 +6144,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44924</v>
+        <v>45373</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6164,13 +6159,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6213,7 +6203,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 3932-2022</t>
+          <t>A 17010-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6227,10 +6217,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44587</v>
+        <v>44676</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6286,7 +6276,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 28390-2025</t>
+          <t>A 61021-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6296,14 +6286,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45819</v>
+        <v>44914</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6315,13 +6305,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6364,7 +6349,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 58418-2024</t>
+          <t>A 30205-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6378,10 +6363,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45634</v>
+        <v>45110</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6394,7 +6379,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.4</v>
+        <v>6.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6437,7 +6422,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 13170-2024</t>
+          <t>A 22278-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6451,10 +6436,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45386</v>
+        <v>45446</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6467,7 +6452,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6510,7 +6495,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 45180-2024</t>
+          <t>A 1379-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6524,10 +6509,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45575</v>
+        <v>45667</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6540,7 +6525,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>14.7</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6583,7 +6568,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 36304-2023</t>
+          <t>A 17069-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6597,10 +6582,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45152</v>
+        <v>45034</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6613,7 +6598,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6656,7 +6641,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 49256-2023</t>
+          <t>A 45180-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6670,10 +6655,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45210</v>
+        <v>45575</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6686,7 +6671,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.1</v>
+        <v>14.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6729,7 +6714,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 10630-2026</t>
+          <t>A 14502-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6743,10 +6728,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46078</v>
+        <v>45012</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6759,7 +6744,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6802,7 +6787,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 31258-2025</t>
+          <t>A 13340-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6816,10 +6801,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45833</v>
+        <v>44645</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6832,7 +6817,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6875,7 +6860,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 11459-2026</t>
+          <t>A 13348-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6889,10 +6874,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46083</v>
+        <v>44645</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6905,7 +6890,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6948,7 +6933,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 11460-2026</t>
+          <t>A 13366-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6962,10 +6947,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46083</v>
+        <v>44645</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6978,7 +6963,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7021,7 +7006,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 11630-2026</t>
+          <t>A 9607-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7035,10 +7020,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46084</v>
+        <v>45361</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7050,13 +7035,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7099,7 +7079,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 10596-2024</t>
+          <t>A 15646-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7113,10 +7093,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45366</v>
+        <v>45021</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7129,7 +7109,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7172,7 +7152,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 61194-2024</t>
+          <t>A 30174-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7186,10 +7166,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45645</v>
+        <v>44757</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7201,13 +7181,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>5.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7250,7 +7225,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 32967-2025</t>
+          <t>A 9145-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7264,10 +7239,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45839</v>
+        <v>44974</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7280,7 +7255,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7323,7 +7298,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 21285-2024</t>
+          <t>A 61194-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7337,10 +7312,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45440</v>
+        <v>45645</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7352,8 +7327,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7396,7 +7376,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 41721-2022</t>
+          <t>A 34161-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7410,10 +7390,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44827</v>
+        <v>45845</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7426,7 +7406,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7469,7 +7449,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 6925-2023</t>
+          <t>A 39998-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7483,10 +7463,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44967</v>
+        <v>45894</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7498,13 +7478,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7547,7 +7522,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 58236-2024</t>
+          <t>A 13268-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7561,10 +7536,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45632</v>
+        <v>45386</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7576,13 +7551,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>2.3</v>
+        <v>6.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7625,7 +7595,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 58691-2024</t>
+          <t>A 10451-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7639,10 +7609,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45635</v>
+        <v>45366</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7656,11 +7626,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7703,7 +7673,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 55764-2024</t>
+          <t>A 12660-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7713,14 +7683,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45623</v>
+        <v>45000</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7733,7 +7703,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7776,7 +7746,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 56169-2024</t>
+          <t>A 25594-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7786,14 +7756,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45624</v>
+        <v>45803</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7806,7 +7776,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>19.7</v>
+        <v>3.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7849,7 +7819,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 850-2023</t>
+          <t>A 22055-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7863,10 +7833,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44931</v>
+        <v>45069</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7879,7 +7849,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7922,7 +7892,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 13450-2025</t>
+          <t>A 20710-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7936,10 +7906,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45736</v>
+        <v>46141</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7952,7 +7922,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7995,7 +7965,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 39998-2025</t>
+          <t>A 20811-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8009,10 +7979,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45894</v>
+        <v>46141</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8025,7 +7995,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8068,7 +8038,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 61294-2024</t>
+          <t>A 10596-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8082,10 +8052,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45645</v>
+        <v>45366</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8098,7 +8068,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8141,7 +8111,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 12660-2023</t>
+          <t>A 33162-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8151,14 +8121,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45000</v>
+        <v>45518</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8171,7 +8141,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8214,7 +8184,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 62390-2023</t>
+          <t>A 45007-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8228,10 +8198,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45268</v>
+        <v>45918</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8244,7 +8214,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8287,7 +8257,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 62402-2023</t>
+          <t>A 20812-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8301,10 +8271,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45268</v>
+        <v>46141</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8317,7 +8287,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8360,7 +8330,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 18776-2026</t>
+          <t>A 20700-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8374,10 +8344,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46128</v>
+        <v>46141</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8390,7 +8360,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8433,7 +8403,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 11771-2024</t>
+          <t>A 28268-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8447,10 +8417,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45373</v>
+        <v>45099</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8463,7 +8433,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8506,7 +8476,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 31981-2023</t>
+          <t>A 850-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8520,10 +8490,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45119</v>
+        <v>44931</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8536,7 +8506,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8579,7 +8549,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 45007-2025</t>
+          <t>A 47175-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8593,10 +8563,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45918</v>
+        <v>45930</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8609,7 +8579,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8652,7 +8622,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 15646-2023</t>
+          <t>A 47383-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8666,10 +8636,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45021</v>
+        <v>45930</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8682,7 +8652,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8725,7 +8695,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 30174-2022</t>
+          <t>A 47385-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8739,10 +8709,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44757</v>
+        <v>45930</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8755,7 +8725,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8798,7 +8768,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 62510-2022</t>
+          <t>A 47389-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8812,10 +8782,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44924</v>
+        <v>45930</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8827,13 +8797,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8876,7 +8841,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 61021-2022</t>
+          <t>A 55764-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8886,14 +8851,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44914</v>
+        <v>45623</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8906,7 +8871,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8949,7 +8914,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 849-2023</t>
+          <t>A 21369-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8963,10 +8928,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44931</v>
+        <v>46147</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8979,7 +8944,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9022,7 +8987,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 45013-2025</t>
+          <t>A 19674-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9036,10 +9001,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45918</v>
+        <v>45051</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9052,7 +9017,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9095,7 +9060,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 34161-2025</t>
+          <t>A 19683-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9109,10 +9074,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45845</v>
+        <v>45051</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9125,7 +9090,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9168,7 +9133,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 1662-2025</t>
+          <t>A 21376-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9182,10 +9147,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45670</v>
+        <v>46147</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9198,7 +9163,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.8</v>
+        <v>7.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9241,7 +9206,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 20710-2026</t>
+          <t>A 8765-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9255,10 +9220,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46141</v>
+        <v>44614</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9270,8 +9235,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9314,7 +9284,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 20812-2026</t>
+          <t>A 52352-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9328,10 +9298,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46141</v>
+        <v>45224</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9344,7 +9314,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9387,7 +9357,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 33162-2024</t>
+          <t>A 52141-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9401,10 +9371,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45518</v>
+        <v>45953</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9417,7 +9387,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9460,7 +9430,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 47385-2025</t>
+          <t>A 62510-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9474,10 +9444,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45930</v>
+        <v>44924</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9489,8 +9459,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9533,7 +9508,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 20700-2026</t>
+          <t>A 17876-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9547,10 +9522,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46141</v>
+        <v>45758</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9563,7 +9538,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9606,7 +9581,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 47175-2025</t>
+          <t>A 56365-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9620,10 +9595,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45930</v>
+        <v>45974</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9636,7 +9611,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9679,7 +9654,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 47389-2025</t>
+          <t>A 56347-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9693,10 +9668,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45930</v>
+        <v>45974</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9709,7 +9684,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.5</v>
+        <v>10.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9752,7 +9727,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 25594-2025</t>
+          <t>A 56352-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9762,14 +9737,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45803</v>
+        <v>45974</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9782,7 +9757,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.2</v>
+        <v>5.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9825,7 +9800,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 47383-2025</t>
+          <t>A 56414-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9839,10 +9814,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45930</v>
+        <v>45975</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9855,7 +9830,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9898,7 +9873,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 20811-2026</t>
+          <t>A 56340-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9912,10 +9887,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46141</v>
+        <v>45974</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9928,7 +9903,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9971,7 +9946,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 31969-2023</t>
+          <t>A 56417-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9985,10 +9960,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45119</v>
+        <v>45975</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10001,7 +9976,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10044,7 +10019,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 31978-2023</t>
+          <t>A 56346-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10058,10 +10033,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45119</v>
+        <v>45974</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10074,7 +10049,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.2</v>
+        <v>18.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10117,7 +10092,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 21376-2026</t>
+          <t>A 13170-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10131,10 +10106,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46147</v>
+        <v>45386</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10147,7 +10122,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>7.2</v>
+        <v>0.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10190,7 +10165,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 21369-2026</t>
+          <t>A 58517-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10204,10 +10179,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46147</v>
+        <v>45985</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10220,7 +10195,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10263,7 +10238,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 28258-2023</t>
+          <t>A 58520-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10277,10 +10252,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45099</v>
+        <v>45985</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10293,7 +10268,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10336,7 +10311,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 22278-2024</t>
+          <t>A 58766-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10350,10 +10325,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45446</v>
+        <v>45986</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10366,7 +10341,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10409,7 +10384,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 17069-2023</t>
+          <t>A 58767-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10423,10 +10398,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45034</v>
+        <v>45986</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10439,7 +10414,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10482,7 +10457,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 22906-2026</t>
+          <t>A 22916-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10499,7 +10474,7 @@
         <v>46160</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10512,7 +10487,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10555,7 +10530,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 22916-2026</t>
+          <t>A 62390-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10569,10 +10544,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46160</v>
+        <v>45268</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10628,7 +10603,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 22912-2026</t>
+          <t>A 22906-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10645,7 +10620,7 @@
         <v>46160</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10658,7 +10633,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10701,7 +10676,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 59074-2023</t>
+          <t>A 22912-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10715,10 +10690,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45252</v>
+        <v>46160</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10731,7 +10706,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10774,7 +10749,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 11772-2024</t>
+          <t>A 62499-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10788,10 +10763,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45373</v>
+        <v>44924</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10803,8 +10778,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10847,7 +10827,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 11773-2024</t>
+          <t>A 10958-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10861,10 +10841,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45373</v>
+        <v>44628</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10877,7 +10857,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10920,7 +10900,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 8765-2022</t>
+          <t>A 60559-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10934,10 +10914,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44614</v>
+        <v>45995</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10947,11 +10927,6 @@
       <c r="G131" t="inlineStr">
         <is>
           <t>GÖTENE</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I131" t="n">
@@ -10998,7 +10973,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 30205-2023</t>
+          <t>A 45239-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11012,10 +10987,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45110</v>
+        <v>44844</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11027,8 +11002,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>6.8</v>
+        <v>1.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11071,7 +11051,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 25777-2026</t>
+          <t>A 15426-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11081,14 +11061,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46178</v>
+        <v>45747</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11101,7 +11081,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11144,7 +11124,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 26338-2026</t>
+          <t>A 15442-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11158,10 +11138,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46182</v>
+        <v>45747</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11174,7 +11154,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11217,7 +11197,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 52141-2025</t>
+          <t>A 12450-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11231,10 +11211,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45953</v>
+        <v>44638</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11247,7 +11227,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11290,7 +11270,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 26336-2026</t>
+          <t>A 21429-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11304,10 +11284,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46182</v>
+        <v>44706</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11320,7 +11300,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11363,7 +11343,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 1379-2025</t>
+          <t>A 56169-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11377,10 +11357,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45667</v>
+        <v>45624</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11393,7 +11373,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.6</v>
+        <v>19.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11436,7 +11416,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 44608-2023</t>
+          <t>A 13279-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11450,10 +11430,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45189</v>
+        <v>45386</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11466,7 +11446,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11509,7 +11489,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 44033-2024</t>
+          <t>A 49256-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11523,10 +11503,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45572</v>
+        <v>45210</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11539,7 +11519,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11582,7 +11562,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 10636-2026</t>
+          <t>A 3960-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11596,10 +11576,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46078</v>
+        <v>46044</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11611,8 +11591,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11655,7 +11640,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 13366-2022</t>
+          <t>A 5044-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11669,10 +11654,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44645</v>
+        <v>46049</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11685,7 +11670,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.7</v>
+        <v>5.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11728,7 +11713,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 15428-2025</t>
+          <t>A 31969-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11742,10 +11727,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45747</v>
+        <v>45119</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11758,7 +11743,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11801,7 +11786,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 15434-2025</t>
+          <t>A 31978-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11815,10 +11800,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45747</v>
+        <v>45119</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11831,7 +11816,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11874,7 +11859,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 28647-2026</t>
+          <t>A 25777-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11884,14 +11869,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46198</v>
+        <v>46178</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11904,7 +11889,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11947,7 +11932,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 28467-2026</t>
+          <t>A 39150-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11961,10 +11946,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46197</v>
+        <v>44817</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11977,7 +11962,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12020,7 +12005,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 17010-2022</t>
+          <t>A 26336-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12034,10 +12019,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44676</v>
+        <v>46182</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12050,7 +12035,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12093,7 +12078,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 56365-2025</t>
+          <t>A 26338-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12107,10 +12092,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45974</v>
+        <v>46182</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12123,7 +12108,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12166,7 +12151,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 56347-2025</t>
+          <t>A 36472-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12180,10 +12165,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45974</v>
+        <v>45152</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12196,7 +12181,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>10.9</v>
+        <v>1.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12239,7 +12224,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 56352-2025</t>
+          <t>A 10630-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12253,10 +12238,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45974</v>
+        <v>46078</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12269,7 +12254,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>5.9</v>
+        <v>0.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12312,7 +12297,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 56346-2025</t>
+          <t>A 3932-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12326,10 +12311,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45974</v>
+        <v>44587</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12342,7 +12327,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>18.8</v>
+        <v>1.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12385,7 +12370,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 56340-2025</t>
+          <t>A 7225-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12399,10 +12384,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45974</v>
+        <v>44970</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12415,7 +12400,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12458,7 +12443,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 19674-2023</t>
+          <t>A 11459-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12472,10 +12457,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45051</v>
+        <v>46083</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12488,7 +12473,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12531,7 +12516,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 56417-2025</t>
+          <t>A 11460-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12545,10 +12530,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45975</v>
+        <v>46083</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12561,7 +12546,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12604,7 +12589,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 13345-2022</t>
+          <t>A 11630-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12618,10 +12603,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44645</v>
+        <v>46084</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12633,8 +12618,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12677,7 +12667,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 56414-2025</t>
+          <t>A 35408-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12691,10 +12681,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45975</v>
+        <v>45146</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12707,7 +12697,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12750,7 +12740,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 21429-2022</t>
+          <t>A 13280-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12764,10 +12754,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44706</v>
+        <v>45386</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12780,7 +12770,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12823,7 +12813,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 35408-2023</t>
+          <t>A 31981-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12837,10 +12827,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45146</v>
+        <v>45119</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12853,7 +12843,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12896,7 +12886,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 58766-2025</t>
+          <t>A 55511-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12910,10 +12900,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45986</v>
+        <v>45238</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12926,7 +12916,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12969,7 +12959,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 20507-2026</t>
+          <t>A 28258-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12983,10 +12973,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46140</v>
+        <v>45099</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12999,7 +12989,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13042,7 +13032,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 58767-2025</t>
+          <t>A 28264-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13056,10 +13046,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45986</v>
+        <v>45099</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13072,7 +13062,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13115,7 +13105,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 58517-2025</t>
+          <t>A 49252-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13129,10 +13119,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45985</v>
+        <v>45210</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13145,7 +13135,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13188,7 +13178,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 58520-2025</t>
+          <t>A 10636-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13202,10 +13192,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45985</v>
+        <v>46078</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13218,7 +13208,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13261,7 +13251,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 55511-2023</t>
+          <t>A 28467-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13275,10 +13265,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45238</v>
+        <v>46197</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13291,7 +13281,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13334,7 +13324,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 30191-2026</t>
+          <t>A 28647-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13348,10 +13338,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46206</v>
+        <v>46198</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13363,13 +13353,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>6.5</v>
+        <v>1.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13412,7 +13397,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 34008-2026</t>
+          <t>A 28335-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13426,10 +13411,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46252</v>
+        <v>45099</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13442,7 +13427,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13485,7 +13470,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 5690-2026</t>
+          <t>A 13281-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13499,10 +13484,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46051</v>
+        <v>45386</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13515,7 +13500,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13558,7 +13543,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 36472-2023</t>
+          <t>A 58650-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13572,10 +13557,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45152</v>
+        <v>45251</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13588,7 +13573,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13631,7 +13616,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 49252-2023</t>
+          <t>A 36304-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13645,10 +13630,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45210</v>
+        <v>45152</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13661,7 +13646,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13704,7 +13689,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 31917-2022</t>
+          <t>A 18776-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13718,10 +13703,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44777</v>
+        <v>46128</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13734,7 +13719,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13777,7 +13762,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 17876-2025</t>
+          <t>A 59074-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13791,10 +13776,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45758</v>
+        <v>45252</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13807,7 +13792,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>4.2</v>
+        <v>0.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13850,7 +13835,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 60559-2025</t>
+          <t>A 20507-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13864,10 +13849,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45995</v>
+        <v>46140</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13880,7 +13865,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13923,7 +13908,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 12450-2022</t>
+          <t>A 45013-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13937,10 +13922,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44638</v>
+        <v>45918</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13953,7 +13938,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13996,7 +13981,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 31329-2026</t>
+          <t>A 1662-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14010,10 +13995,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46219</v>
+        <v>45670</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14026,7 +14011,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>7.5</v>
+        <v>1.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14069,7 +14054,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 31324-2026</t>
+          <t>A 15428-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14083,10 +14068,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46219</v>
+        <v>45747</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14099,7 +14084,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14142,7 +14127,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 35869-2026</t>
+          <t>A 15434-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14156,10 +14141,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46266</v>
+        <v>45747</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14172,7 +14157,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14215,7 +14200,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 35871-2026</t>
+          <t>A 11771-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14229,10 +14214,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46266</v>
+        <v>45373</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14245,7 +14230,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14288,7 +14273,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 31446-2026</t>
+          <t>A 58417-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14302,10 +14287,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46220</v>
+        <v>45634</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14317,8 +14302,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14361,7 +14351,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 31452-2026</t>
+          <t>A 30191-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14375,10 +14365,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46220</v>
+        <v>46206</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14390,8 +14380,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14434,7 +14429,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 64712-2023</t>
+          <t>A 13345-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14448,10 +14443,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45281</v>
+        <v>44645</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14464,7 +14459,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14507,7 +14502,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 39081-2022</t>
+          <t>A 34008-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14521,10 +14516,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44817</v>
+        <v>46252</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14537,7 +14532,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14580,7 +14575,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 36381-2023</t>
+          <t>A 64712-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14594,10 +14589,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45152</v>
+        <v>45281</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14610,7 +14605,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14653,7 +14648,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 13268-2024</t>
+          <t>A 5690-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14667,10 +14662,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45386</v>
+        <v>46051</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14683,7 +14678,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>6.7</v>
+        <v>0.8</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14726,7 +14721,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 13281-2024</t>
+          <t>A 39081-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14740,10 +14735,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45386</v>
+        <v>44817</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14756,7 +14751,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14799,7 +14794,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 19683-2023</t>
+          <t>A 61294-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14813,10 +14808,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45051</v>
+        <v>45645</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14829,7 +14824,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14872,7 +14867,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 58417-2024</t>
+          <t>A 62402-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14886,10 +14881,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45634</v>
+        <v>45268</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14899,11 +14894,6 @@
       <c r="G185" t="inlineStr">
         <is>
           <t>GÖTENE</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I185" t="n">
@@ -14950,7 +14940,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 37557-2026</t>
+          <t>A 1352-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14964,10 +14954,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46276</v>
+        <v>44931</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14980,7 +14970,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15023,7 +15013,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 39150-2022</t>
+          <t>A 28332-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15037,10 +15027,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44817</v>
+        <v>45099</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15053,7 +15043,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15096,7 +15086,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 32298-2026</t>
+          <t>A 44033-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15110,10 +15100,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46237</v>
+        <v>45572</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15125,13 +15115,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15174,7 +15159,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 32363-2026</t>
+          <t>A 31329-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15188,10 +15173,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46238</v>
+        <v>46219</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15204,7 +15189,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15247,7 +15232,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 32364-2026</t>
+          <t>A 72879-2021</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15261,10 +15246,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46238</v>
+        <v>44547</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15320,7 +15305,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 14502-2023</t>
+          <t>A 31446-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15334,10 +15319,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45012</v>
+        <v>46220</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15350,7 +15335,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15393,7 +15378,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 3960-2026</t>
+          <t>A 31452-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15407,10 +15392,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46044</v>
+        <v>46220</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15422,13 +15407,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15471,7 +15451,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 10958-2022</t>
+          <t>A 28267-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15485,10 +15465,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44628</v>
+        <v>45099</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15501,7 +15481,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15544,7 +15524,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 5044-2026</t>
+          <t>A 31324-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15558,10 +15538,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46049</v>
+        <v>46219</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15574,7 +15554,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>5.4</v>
+        <v>2.3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15617,7 +15597,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 9145-2023</t>
+          <t>A 35869-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15631,10 +15611,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44974</v>
+        <v>46266</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15647,7 +15627,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15690,7 +15670,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 7225-2023</t>
+          <t>A 35871-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15704,10 +15684,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44970</v>
+        <v>46266</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15720,7 +15700,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15763,7 +15743,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 10451-2024</t>
+          <t>A 21285-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15777,10 +15757,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45366</v>
+        <v>45440</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15792,13 +15772,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15841,7 +15816,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 28332-2023</t>
+          <t>A 28316-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15855,10 +15830,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45099</v>
+        <v>45477</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15871,7 +15846,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15914,7 +15889,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 8330-2024</t>
+          <t>A 37557-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15928,10 +15903,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45352</v>
+        <v>46276</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15944,7 +15919,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15987,7 +15962,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 13279-2024</t>
+          <t>A 32298-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16001,10 +15976,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45386</v>
+        <v>46237</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16016,8 +15991,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16060,7 +16040,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 11889-2024</t>
+          <t>A 21269-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16074,10 +16054,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45376</v>
+        <v>45440</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16090,7 +16070,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16133,7 +16113,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 15426-2025</t>
+          <t>A 12664-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16147,10 +16127,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45747</v>
+        <v>45000</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16163,7 +16143,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16206,7 +16186,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 15442-2025</t>
+          <t>A 32363-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16220,10 +16200,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45747</v>
+        <v>46238</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16236,7 +16216,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.2</v>
+        <v>6.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16279,7 +16259,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 13340-2022</t>
+          <t>A 16341-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16289,14 +16269,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44645</v>
+        <v>45751</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16309,7 +16289,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16352,7 +16332,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 13348-2022</t>
+          <t>A 32364-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16366,10 +16346,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44645</v>
+        <v>46238</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16382,7 +16362,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16425,7 +16405,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 22055-2023</t>
+          <t>A 10668-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16439,10 +16419,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45069</v>
+        <v>45721</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16455,7 +16435,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16498,7 +16478,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 13280-2024</t>
+          <t>A 25434-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16512,10 +16492,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45386</v>
+        <v>45800</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16571,7 +16551,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 28335-2023</t>
+          <t>A 25435-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16585,10 +16565,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45099</v>
+        <v>45800</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16601,7 +16581,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16644,7 +16624,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 12664-2023</t>
+          <t>A 25436-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16658,10 +16638,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45000</v>
+        <v>45800</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16674,7 +16654,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16717,7 +16697,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 21269-2024</t>
+          <t>A 26105-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16727,14 +16707,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45440</v>
+        <v>45805</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16747,7 +16727,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.3</v>
+        <v>5.3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16790,7 +16770,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 28316-2024</t>
+          <t>A 10703-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16804,10 +16784,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45477</v>
+        <v>45722</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16820,7 +16800,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16863,7 +16843,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 16341-2025</t>
+          <t>A 28390-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16873,14 +16853,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45751</v>
+        <v>45819</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16892,8 +16872,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I212" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16936,7 +16921,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 10668-2025</t>
+          <t>A 31258-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16950,10 +16935,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45721</v>
+        <v>45833</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16966,7 +16951,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.3</v>
+        <v>5.2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17009,7 +16994,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 25434-2025</t>
+          <t>A 32967-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17023,10 +17008,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45800</v>
+        <v>45839</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17039,7 +17024,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17082,7 +17067,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 25435-2025</t>
+          <t>A 6925-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17096,10 +17081,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45800</v>
+        <v>44967</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17111,8 +17096,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I215" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17155,7 +17145,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 25436-2025</t>
+          <t>A 58236-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17169,10 +17159,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45800</v>
+        <v>45632</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17184,8 +17174,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I216" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17228,7 +17223,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 26105-2025</t>
+          <t>A 58691-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17238,14 +17233,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45805</v>
+        <v>45635</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17257,8 +17252,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>5.3</v>
+        <v>2.3</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 10703-2025</t>
+          <t>A 13450-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17315,10 +17315,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45722</v>
+        <v>45736</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17391,7 +17391,7 @@
         <v>44862</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45352</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>45352</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>

--- a/Översikt GÖTENE.xlsx
+++ b/Översikt GÖTENE.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44642</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45352</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45847</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>45846</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>46234</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>44827</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>44490</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>44827</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>44844</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>45763</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>45930</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>45944</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>44691</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>45011</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>46247</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>45330</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>45099</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>46219</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>46237</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>45372</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>44490</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>44645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>44490</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>44490</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>44507</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>44614</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>44859</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>44840</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>44566</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>44684</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>44477</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>44507</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>44581</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>44761</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>44757</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>44869</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>44812</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>44848</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>44865</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>44490</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>44603</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>44475</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>44803</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>44498</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>44816</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>45634</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>45152</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>45352</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>45386</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>44931</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>45189</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>44827</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>44777</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>45376</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>45373</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>45373</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>44676</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44914</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>45110</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>45446</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>45667</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>45034</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>45575</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>45012</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>44645</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>44645</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>44645</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>45361</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>45021</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>44757</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>44974</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>45645</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45845</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>45894</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45386</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45366</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>45000</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>45803</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         <v>45069</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>46141</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>46141</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>45366</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>45518</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         <v>45918</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>46141</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>46141</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>45099</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>44931</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>45930</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>45930</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>45930</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>45930</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>45623</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>46147</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>45051</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>45051</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>46147</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44614</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
         <v>45224</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>45953</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>44924</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>45758</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>45974</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>45974</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>45974</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>45975</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>45974</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>45975</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>45974</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>45386</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>45985</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
         <v>45985</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>45986</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>45986</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>46160</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10547,7 +10547,7 @@
         <v>45268</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>46160</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>46160</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>44924</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>44628</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>45995</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>44844</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>45747</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>45747</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>44638</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>44706</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>45624</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>45386</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>45210</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>46044</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>46049</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>45119</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>45119</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>46178</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>44817</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>46182</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>46182</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>45152</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>46078</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>44587</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>44970</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>46083</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>46083</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>46084</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>45146</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>45386</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>45119</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>45238</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>45099</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>45099</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>45210</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>46078</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>46197</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>46198</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>45099</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>45386</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>45251</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>45152</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>46128</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>45252</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>46140</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>45918</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45670</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>45747</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>45747</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>45373</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>45634</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>46206</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>44645</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14519,7 +14519,7 @@
         <v>46252</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         <v>45281</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         <v>46051</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>44817</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>45645</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>45268</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>44931</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>45099</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>45572</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>46219</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>44547</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>46220</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>46220</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>45099</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>46219</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>46266</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>46266</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>45440</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>45477</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>46276</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>46237</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>45440</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>45000</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>46238</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>45751</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>46238</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16422,7 +16422,7 @@
         <v>45721</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16495,7 +16495,7 @@
         <v>45800</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16568,7 +16568,7 @@
         <v>45800</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>45800</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16714,7 +16714,7 @@
         <v>45805</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>45722</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16860,7 +16860,7 @@
         <v>45819</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>45833</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         <v>45839</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
         <v>44967</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>45632</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>45635</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>45736</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>44862</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45352</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>45352</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>

--- a/Översikt GÖTENE.xlsx
+++ b/Översikt GÖTENE.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44642</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45352</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45847</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>45846</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>46234</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>44827</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>44490</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>44827</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>44844</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>45763</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>45930</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>45944</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>44691</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 14296-2023</t>
+          <t>A 33478-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45011</v>
+        <v>46247</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2450,19 +2450,19 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2474,10 +2474,10 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2486,50 +2486,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Pilgrimsfalk</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 14296-2023 artfynd.xlsx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 33478-2026 artfynd.xlsx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 14296-2023 karta.png", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 33478-2026 karta.png", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 14296-2023 georefererad karta.tif", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 33478-2026 georefererad karta.tif", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 14296-2023 FSC-klagomål.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 33478-2026 FSC-klagomål.docx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 14296-2023 FSC-klagomål mail.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 33478-2026 FSC-klagomål mail.docx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 14296-2023 tillsynsbegäran.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 33478-2026 tillsynsbegäran.docx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 14296-2023 tillsynsbegäran mail.docx", "A 14296-2023")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 14296-2023 prioriterade fågelarter.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 33478-2026 tillsynsbegäran mail.docx", "A 33478-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33478-2026</t>
+          <t>A 14296-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2543,10 +2539,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46247</v>
+        <v>45011</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2559,20 +2555,20 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
@@ -2583,10 +2579,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2595,46 +2591,50 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Pilgrimsfalk</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 33478-2026 artfynd.xlsx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 14296-2023 artfynd.xlsx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 33478-2026 karta.png", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 14296-2023 karta.png", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 33478-2026 georefererad karta.tif", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 14296-2023 georefererad karta.tif", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 33478-2026 FSC-klagomål.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 14296-2023 FSC-klagomål.docx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 33478-2026 FSC-klagomål mail.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 14296-2023 FSC-klagomål mail.docx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 33478-2026 tillsynsbegäran.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 14296-2023 tillsynsbegäran.docx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 33478-2026 tillsynsbegäran mail.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 14296-2023 tillsynsbegäran mail.docx", "A 14296-2023")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 14296-2023 prioriterade fågelarter.docx", "A 14296-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 5086-2024</t>
+          <t>A 31326-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45330</v>
+        <v>46219</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2664,17 +2664,17 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
@@ -2688,7 +2688,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2697,49 +2697,53 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 5086-2024 artfynd.xlsx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 31326-2026 artfynd.xlsx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 5086-2024 karta.png", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 31326-2026 karta.png", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 5086-2024 georefererad karta.tif", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 31326-2026 georefererad karta.tif", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 5086-2024 FSC-klagomål.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 31326-2026 FSC-klagomål.docx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 5086-2024 FSC-klagomål mail.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 31326-2026 FSC-klagomål mail.docx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 5086-2024 tillsynsbegäran.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 31326-2026 tillsynsbegäran.docx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 5086-2024 tillsynsbegäran mail.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 31326-2026 tillsynsbegäran mail.docx", "A 31326-2026")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 31326-2026 prioriterade fågelarter.docx", "A 31326-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 28273-2023</t>
+          <t>A 5086-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2753,10 +2757,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45099</v>
+        <v>45330</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2769,13 +2773,13 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2802,49 +2806,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
         <v>1</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 28273-2023 artfynd.xlsx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 5086-2024 artfynd.xlsx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 28273-2023 karta.png", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 5086-2024 karta.png", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 28273-2023 georefererad karta.tif", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 5086-2024 georefererad karta.tif", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 28273-2023 FSC-klagomål.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 5086-2024 FSC-klagomål.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 28273-2023 FSC-klagomål mail.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 5086-2024 FSC-klagomål mail.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 28273-2023 tillsynsbegäran.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 5086-2024 tillsynsbegäran.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 28273-2023 tillsynsbegäran mail.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 5086-2024 tillsynsbegäran mail.docx", "A 5086-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31326-2026</t>
+          <t>A 32224-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2858,10 +2862,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46219</v>
+        <v>46237</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2874,10 +2878,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2914,46 +2918,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Backmåra</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 31326-2026 artfynd.xlsx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32224-2026 artfynd.xlsx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 31326-2026 karta.png", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32224-2026 karta.png", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 31326-2026 georefererad karta.tif", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32224-2026 georefererad karta.tif", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 31326-2026 FSC-klagomål.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32224-2026 FSC-klagomål.docx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 31326-2026 FSC-klagomål mail.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32224-2026 FSC-klagomål mail.docx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 31326-2026 tillsynsbegäran.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32224-2026 tillsynsbegäran.docx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 31326-2026 tillsynsbegäran mail.docx", "A 31326-2026")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 31326-2026 prioriterade fågelarter.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32224-2026 tillsynsbegäran mail.docx", "A 32224-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32224-2026</t>
+          <t>A 28273-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46237</v>
+        <v>45099</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2983,16 +2983,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3007,7 +3007,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3023,35 +3023,35 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Backmåra</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32224-2026 artfynd.xlsx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 28273-2023 artfynd.xlsx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32224-2026 karta.png", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 28273-2023 karta.png", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32224-2026 georefererad karta.tif", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 28273-2023 georefererad karta.tif", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32224-2026 FSC-klagomål.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 28273-2023 FSC-klagomål.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32224-2026 FSC-klagomål mail.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 28273-2023 FSC-klagomål mail.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32224-2026 tillsynsbegäran.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 28273-2023 tillsynsbegäran.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32224-2026 tillsynsbegäran mail.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 28273-2023 tillsynsbegäran mail.docx", "A 28273-2023")</f>
         <v/>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>45372</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>44490</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>44645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>44490</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>44490</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>44507</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>44614</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>44859</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>44840</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>44566</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>44684</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>44477</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>44507</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>44581</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>44761</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>44757</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>44869</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>44812</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>44848</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>44865</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>44490</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>44603</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>44475</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>44803</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>44498</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>44816</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>45634</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>45152</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>45352</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>45386</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>44931</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>45189</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>44827</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 31917-2022</t>
+          <t>A 11889-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5925,10 +5925,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44777</v>
+        <v>45376</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5984,7 +5984,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 11889-2024</t>
+          <t>A 11772-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5998,10 +5998,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45376</v>
+        <v>45373</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6057,7 +6057,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 11772-2024</t>
+          <t>A 11773-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6074,7 +6074,7 @@
         <v>45373</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6130,7 +6130,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 11773-2024</t>
+          <t>A 31917-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6144,10 +6144,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45373</v>
+        <v>44777</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>44676</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44914</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>45110</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>45446</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>45667</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>45034</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 45180-2024</t>
+          <t>A 13450-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6655,10 +6655,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45575</v>
+        <v>45736</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>14.7</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6714,7 +6714,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 14502-2023</t>
+          <t>A 45180-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6728,10 +6728,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45012</v>
+        <v>45575</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.2</v>
+        <v>14.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6787,7 +6787,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 13340-2022</t>
+          <t>A 61194-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6801,10 +6801,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44645</v>
+        <v>45645</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6816,8 +6816,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6860,7 +6865,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 13348-2022</t>
+          <t>A 14502-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6874,10 +6879,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44645</v>
+        <v>45012</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6890,7 +6895,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6933,7 +6938,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13366-2022</t>
+          <t>A 13340-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6950,7 +6955,7 @@
         <v>44645</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6963,7 +6968,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7006,7 +7011,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 9607-2024</t>
+          <t>A 13348-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7020,10 +7025,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45361</v>
+        <v>44645</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7036,7 +7041,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7079,7 +7084,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 15646-2023</t>
+          <t>A 13366-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7093,10 +7098,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45021</v>
+        <v>44645</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7109,7 +7114,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7152,7 +7157,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 30174-2022</t>
+          <t>A 45013-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7166,10 +7171,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44757</v>
+        <v>45918</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7182,7 +7187,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>5.1</v>
+        <v>1.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7225,7 +7230,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 9145-2023</t>
+          <t>A 15646-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7239,10 +7244,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44974</v>
+        <v>45021</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7255,7 +7260,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7298,7 +7303,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 61194-2024</t>
+          <t>A 1662-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7312,10 +7317,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45645</v>
+        <v>45670</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7327,13 +7332,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7376,7 +7376,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 34161-2025</t>
+          <t>A 39998-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45845</v>
+        <v>45894</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7449,7 +7449,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 39998-2025</t>
+          <t>A 9607-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7463,10 +7463,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45894</v>
+        <v>45361</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7522,7 +7522,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 13268-2024</t>
+          <t>A 30174-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7536,10 +7536,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45386</v>
+        <v>44757</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>6.7</v>
+        <v>5.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7595,7 +7595,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 10451-2024</t>
+          <t>A 34161-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7609,10 +7609,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45366</v>
+        <v>45845</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7624,13 +7624,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7673,7 +7668,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 12660-2023</t>
+          <t>A 9145-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7683,14 +7678,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45000</v>
+        <v>44974</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7703,7 +7698,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7746,7 +7741,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 25594-2025</t>
+          <t>A 45007-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7756,14 +7751,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45803</v>
+        <v>45918</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7776,7 +7771,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7819,7 +7814,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 22055-2023</t>
+          <t>A 13268-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7833,10 +7828,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45069</v>
+        <v>45386</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7849,7 +7844,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>6.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7892,7 +7887,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 20710-2026</t>
+          <t>A 47175-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7906,10 +7901,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46141</v>
+        <v>45930</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7922,7 +7917,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7965,7 +7960,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 20811-2026</t>
+          <t>A 47383-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7979,10 +7974,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46141</v>
+        <v>45930</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7995,7 +7990,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8038,7 +8033,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 10596-2024</t>
+          <t>A 47385-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8052,10 +8047,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45366</v>
+        <v>45930</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8068,7 +8063,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8111,7 +8106,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 33162-2024</t>
+          <t>A 47389-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8125,10 +8120,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45518</v>
+        <v>45930</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8141,7 +8136,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8184,7 +8179,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 45007-2025</t>
+          <t>A 25594-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8194,14 +8189,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45918</v>
+        <v>45803</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8214,7 +8209,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8257,7 +8252,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 20812-2026</t>
+          <t>A 10451-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8271,10 +8266,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46141</v>
+        <v>45366</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8286,8 +8281,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8330,7 +8330,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 20700-2026</t>
+          <t>A 20710-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8347,7 +8347,7 @@
         <v>46141</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 28268-2023</t>
+          <t>A 20811-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8417,10 +8417,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45099</v>
+        <v>46141</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8476,7 +8476,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 850-2023</t>
+          <t>A 33162-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8490,10 +8490,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44931</v>
+        <v>45518</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8549,7 +8549,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 47175-2025</t>
+          <t>A 20812-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8563,10 +8563,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45930</v>
+        <v>46141</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8622,7 +8622,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 47383-2025</t>
+          <t>A 20700-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8636,10 +8636,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45930</v>
+        <v>46141</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8695,7 +8695,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 47385-2025</t>
+          <t>A 21369-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8709,10 +8709,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45930</v>
+        <v>46147</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8768,7 +8768,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 47389-2025</t>
+          <t>A 21376-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8782,10 +8782,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45930</v>
+        <v>46147</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.5</v>
+        <v>7.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8841,7 +8841,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 55764-2024</t>
+          <t>A 12660-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8851,14 +8851,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45623</v>
+        <v>45000</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8914,7 +8914,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 21369-2026</t>
+          <t>A 22055-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8928,10 +8928,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46147</v>
+        <v>45069</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8987,7 +8987,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 19674-2023</t>
+          <t>A 10596-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9001,10 +9001,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45051</v>
+        <v>45366</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9060,7 +9060,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 19683-2023</t>
+          <t>A 52141-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9074,10 +9074,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45051</v>
+        <v>45953</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9133,7 +9133,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 21376-2026</t>
+          <t>A 22916-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9147,10 +9147,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46147</v>
+        <v>46160</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>7.2</v>
+        <v>1.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9206,7 +9206,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 8765-2022</t>
+          <t>A 22906-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9220,10 +9220,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44614</v>
+        <v>46160</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9235,13 +9235,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9284,7 +9279,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 52352-2023</t>
+          <t>A 22912-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9298,10 +9293,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45224</v>
+        <v>46160</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9314,7 +9309,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9357,7 +9352,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 52141-2025</t>
+          <t>A 28268-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9371,10 +9366,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45953</v>
+        <v>45099</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9387,7 +9382,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9430,7 +9425,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 62510-2022</t>
+          <t>A 850-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9444,10 +9439,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44924</v>
+        <v>44931</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9459,13 +9454,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9508,7 +9498,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 17876-2025</t>
+          <t>A 55764-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9522,10 +9512,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45758</v>
+        <v>45623</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9538,7 +9528,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9598,7 +9588,7 @@
         <v>45974</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9654,7 +9644,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 56347-2025</t>
+          <t>A 19674-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9668,10 +9658,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45974</v>
+        <v>45051</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9684,7 +9674,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>10.9</v>
+        <v>0.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9727,7 +9717,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 56352-2025</t>
+          <t>A 56347-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9744,7 +9734,7 @@
         <v>45974</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9757,7 +9747,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>5.9</v>
+        <v>10.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9800,7 +9790,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 56414-2025</t>
+          <t>A 56352-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9814,10 +9804,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45975</v>
+        <v>45974</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9830,7 +9820,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.3</v>
+        <v>5.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9873,7 +9863,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 56340-2025</t>
+          <t>A 56414-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9887,10 +9877,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9903,7 +9893,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9946,7 +9936,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 56417-2025</t>
+          <t>A 56340-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9960,10 +9950,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45975</v>
+        <v>45974</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9976,7 +9966,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10019,7 +10009,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 56346-2025</t>
+          <t>A 56417-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10033,10 +10023,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10049,7 +10039,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>18.8</v>
+        <v>1.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10092,7 +10082,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 13170-2024</t>
+          <t>A 56346-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10106,10 +10096,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45386</v>
+        <v>45974</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10122,7 +10112,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.7</v>
+        <v>18.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10165,7 +10155,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 58517-2025</t>
+          <t>A 19683-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10179,10 +10169,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45985</v>
+        <v>45051</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10195,7 +10185,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10238,7 +10228,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 58520-2025</t>
+          <t>A 58517-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10255,7 +10245,7 @@
         <v>45985</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10311,7 +10301,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 58766-2025</t>
+          <t>A 58520-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10325,10 +10315,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45986</v>
+        <v>45985</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10341,7 +10331,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10384,7 +10374,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 58767-2025</t>
+          <t>A 8765-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10398,10 +10388,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45986</v>
+        <v>44614</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10413,8 +10403,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10457,7 +10452,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 22916-2026</t>
+          <t>A 58766-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10471,10 +10466,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46160</v>
+        <v>45986</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10487,7 +10482,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10530,7 +10525,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 62390-2023</t>
+          <t>A 52352-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10544,10 +10539,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45268</v>
+        <v>45224</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10560,7 +10555,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10603,7 +10598,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 22906-2026</t>
+          <t>A 58767-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10617,10 +10612,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46160</v>
+        <v>45986</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10633,7 +10628,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10676,7 +10671,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 22912-2026</t>
+          <t>A 62510-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10690,10 +10685,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46160</v>
+        <v>44924</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10705,8 +10700,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10749,7 +10749,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 62499-2022</t>
+          <t>A 60559-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10763,10 +10763,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44924</v>
+        <v>45995</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10778,13 +10778,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10827,7 +10822,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 10958-2022</t>
+          <t>A 25777-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10837,14 +10832,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44628</v>
+        <v>46178</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10857,7 +10852,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10900,7 +10895,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 60559-2025</t>
+          <t>A 17876-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10914,10 +10909,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45995</v>
+        <v>45758</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10930,7 +10925,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10973,7 +10968,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 45239-2022</t>
+          <t>A 26336-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10987,10 +10982,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44844</v>
+        <v>46182</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11002,13 +10997,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11051,7 +11041,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 15426-2025</t>
+          <t>A 13170-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11065,10 +11055,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45747</v>
+        <v>45386</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11081,7 +11071,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11124,7 +11114,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 15442-2025</t>
+          <t>A 26338-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11138,10 +11128,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45747</v>
+        <v>46182</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11154,7 +11144,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11197,7 +11187,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 12450-2022</t>
+          <t>A 62390-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11211,10 +11201,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44638</v>
+        <v>45268</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11227,7 +11217,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11270,7 +11260,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 21429-2022</t>
+          <t>A 3960-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11284,10 +11274,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44706</v>
+        <v>46044</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11299,8 +11289,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11343,7 +11338,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 56169-2024</t>
+          <t>A 5044-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11357,10 +11352,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45624</v>
+        <v>46049</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11373,7 +11368,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>19.7</v>
+        <v>5.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11416,7 +11411,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 13279-2024</t>
+          <t>A 10636-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11430,10 +11425,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45386</v>
+        <v>46078</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11446,7 +11441,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11489,7 +11484,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 49256-2023</t>
+          <t>A 62499-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11503,10 +11498,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45210</v>
+        <v>44924</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11518,8 +11513,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11562,7 +11562,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 3960-2026</t>
+          <t>A 10958-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11576,10 +11576,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46044</v>
+        <v>44628</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11591,13 +11591,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11640,7 +11635,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 5044-2026</t>
+          <t>A 45239-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11654,10 +11649,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46049</v>
+        <v>44844</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11669,8 +11664,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>5.4</v>
+        <v>1.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11713,7 +11713,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 31969-2023</t>
+          <t>A 15426-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11727,10 +11727,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45119</v>
+        <v>45747</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 31978-2023</t>
+          <t>A 15442-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11800,10 +11800,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45119</v>
+        <v>45747</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11859,7 +11859,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 25777-2026</t>
+          <t>A 28467-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11869,14 +11869,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46178</v>
+        <v>46197</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11889,7 +11889,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11932,7 +11932,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 39150-2022</t>
+          <t>A 28647-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11946,10 +11946,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44817</v>
+        <v>46198</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12005,7 +12005,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 26336-2026</t>
+          <t>A 10630-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12019,10 +12019,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46182</v>
+        <v>46078</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12078,7 +12078,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 26338-2026</t>
+          <t>A 11459-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12092,10 +12092,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46182</v>
+        <v>46083</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12151,7 +12151,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 36472-2023</t>
+          <t>A 11460-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12165,10 +12165,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45152</v>
+        <v>46083</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12224,7 +12224,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 10630-2026</t>
+          <t>A 11630-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12238,10 +12238,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46078</v>
+        <v>46084</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12253,8 +12253,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12297,7 +12302,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 3932-2022</t>
+          <t>A 20507-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12311,10 +12316,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44587</v>
+        <v>46140</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12327,7 +12332,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12370,7 +12375,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 7225-2023</t>
+          <t>A 12450-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12384,10 +12389,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44970</v>
+        <v>44638</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12400,7 +12405,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12443,7 +12448,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 11459-2026</t>
+          <t>A 21429-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12457,10 +12462,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46083</v>
+        <v>44706</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12473,7 +12478,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12516,7 +12521,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 11460-2026</t>
+          <t>A 56169-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12530,10 +12535,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46083</v>
+        <v>45624</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12546,7 +12551,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.1</v>
+        <v>19.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12589,7 +12594,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 11630-2026</t>
+          <t>A 13279-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12603,10 +12608,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46084</v>
+        <v>45386</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12618,13 +12623,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12667,7 +12667,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 35408-2023</t>
+          <t>A 49256-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12681,10 +12681,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45146</v>
+        <v>45210</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12740,7 +12740,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 13280-2024</t>
+          <t>A 31969-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12754,10 +12754,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45386</v>
+        <v>45119</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12813,7 +12813,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 31981-2023</t>
+          <t>A 31978-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12830,7 +12830,7 @@
         <v>45119</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12886,7 +12886,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 55511-2023</t>
+          <t>A 39150-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12900,10 +12900,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45238</v>
+        <v>44817</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12959,7 +12959,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 28258-2023</t>
+          <t>A 18776-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12973,10 +12973,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45099</v>
+        <v>46128</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12989,7 +12989,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13032,7 +13032,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 28264-2023</t>
+          <t>A 36472-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13046,10 +13046,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45099</v>
+        <v>45152</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13105,7 +13105,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 49252-2023</t>
+          <t>A 30191-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13119,10 +13119,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45210</v>
+        <v>46206</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13134,8 +13134,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>0.4</v>
+        <v>6.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13178,7 +13183,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 10636-2026</t>
+          <t>A 3932-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13192,10 +13197,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46078</v>
+        <v>44587</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13208,7 +13213,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13251,7 +13256,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 28467-2026</t>
+          <t>A 7225-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13265,10 +13270,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46197</v>
+        <v>44970</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13281,7 +13286,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13324,7 +13329,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 28647-2026</t>
+          <t>A 34008-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13338,10 +13343,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46198</v>
+        <v>46252</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13354,7 +13359,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13397,7 +13402,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 28335-2023</t>
+          <t>A 35408-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13411,10 +13416,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45099</v>
+        <v>45146</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13427,7 +13432,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13470,7 +13475,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 13281-2024</t>
+          <t>A 13280-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13487,7 +13492,7 @@
         <v>45386</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13500,7 +13505,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13543,7 +13548,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 58650-2023</t>
+          <t>A 31981-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13557,10 +13562,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45251</v>
+        <v>45119</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13573,7 +13578,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13616,7 +13621,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 36304-2023</t>
+          <t>A 5690-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13630,10 +13635,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45152</v>
+        <v>46051</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13646,7 +13651,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13689,7 +13694,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 18776-2026</t>
+          <t>A 55511-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13703,10 +13708,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46128</v>
+        <v>45238</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13719,7 +13724,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13762,7 +13767,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 59074-2023</t>
+          <t>A 28258-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13776,10 +13781,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45252</v>
+        <v>45099</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13792,7 +13797,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.3</v>
+        <v>2.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13835,7 +13840,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 20507-2026</t>
+          <t>A 28264-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13849,10 +13854,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46140</v>
+        <v>45099</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13865,7 +13870,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13908,7 +13913,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 45013-2025</t>
+          <t>A 49252-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13922,10 +13927,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45918</v>
+        <v>45210</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13938,7 +13943,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13981,7 +13986,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 1662-2025</t>
+          <t>A 31329-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13995,10 +14000,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45670</v>
+        <v>46219</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14011,7 +14016,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.8</v>
+        <v>7.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14054,7 +14059,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 15428-2025</t>
+          <t>A 31446-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14068,10 +14073,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45747</v>
+        <v>46220</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14084,7 +14089,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.1</v>
+        <v>1.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14127,7 +14132,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 15434-2025</t>
+          <t>A 31452-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14141,10 +14146,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45747</v>
+        <v>46220</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14157,7 +14162,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.1</v>
+        <v>3.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14200,7 +14205,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 11771-2024</t>
+          <t>A 28335-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14214,10 +14219,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45373</v>
+        <v>45099</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14230,7 +14235,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14273,7 +14278,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 58417-2024</t>
+          <t>A 13281-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14287,10 +14292,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45634</v>
+        <v>45386</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14302,13 +14307,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14351,7 +14351,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 30191-2026</t>
+          <t>A 58650-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14365,10 +14365,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46206</v>
+        <v>45251</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14380,13 +14380,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14429,7 +14424,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 13345-2022</t>
+          <t>A 36304-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14443,10 +14438,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44645</v>
+        <v>45152</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14459,7 +14454,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14502,7 +14497,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 34008-2026</t>
+          <t>A 31324-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14516,10 +14511,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46252</v>
+        <v>46219</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14532,7 +14527,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14575,7 +14570,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 64712-2023</t>
+          <t>A 35869-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14589,10 +14584,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45281</v>
+        <v>46266</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14605,7 +14600,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14648,7 +14643,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 5690-2026</t>
+          <t>A 35871-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14662,10 +14657,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46051</v>
+        <v>46266</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14678,7 +14673,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14721,7 +14716,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 39081-2022</t>
+          <t>A 59074-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14735,10 +14730,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44817</v>
+        <v>45252</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14751,7 +14746,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14794,7 +14789,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 61294-2024</t>
+          <t>A 15428-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14808,10 +14803,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45645</v>
+        <v>45747</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14824,7 +14819,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14867,7 +14862,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 62402-2023</t>
+          <t>A 15434-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14881,10 +14876,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45268</v>
+        <v>45747</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14897,7 +14892,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14940,7 +14935,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 1352-2023</t>
+          <t>A 11771-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14954,10 +14949,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44931</v>
+        <v>45373</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14970,7 +14965,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15013,7 +15008,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 28332-2023</t>
+          <t>A 58417-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15027,10 +15022,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45099</v>
+        <v>45634</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15042,8 +15037,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15086,7 +15086,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 44033-2024</t>
+          <t>A 37557-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15100,10 +15100,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45572</v>
+        <v>46276</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15159,7 +15159,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 31329-2026</t>
+          <t>A 13345-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15173,10 +15173,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46219</v>
+        <v>44645</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>7.5</v>
+        <v>3.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15232,7 +15232,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 72879-2021</t>
+          <t>A 32298-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15246,10 +15246,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44547</v>
+        <v>46237</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15261,8 +15261,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15305,7 +15310,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 31446-2026</t>
+          <t>A 64712-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15319,10 +15324,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46220</v>
+        <v>45281</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15335,7 +15340,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15378,7 +15383,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 31452-2026</t>
+          <t>A 32363-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15392,10 +15397,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46220</v>
+        <v>46238</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15408,7 +15413,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15451,7 +15456,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 28267-2023</t>
+          <t>A 32364-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15465,10 +15470,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45099</v>
+        <v>46238</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15481,7 +15486,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15524,7 +15529,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 31324-2026</t>
+          <t>A 39081-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15538,10 +15543,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46219</v>
+        <v>44817</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15554,7 +15559,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15597,7 +15602,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 35869-2026</t>
+          <t>A 61294-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15611,10 +15616,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46266</v>
+        <v>45645</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15627,7 +15632,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15670,7 +15675,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 35871-2026</t>
+          <t>A 62402-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15684,10 +15689,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46266</v>
+        <v>45268</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15700,7 +15705,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15743,7 +15748,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 21285-2024</t>
+          <t>A 1352-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15757,10 +15762,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45440</v>
+        <v>44931</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15773,7 +15778,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15816,7 +15821,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 28316-2024</t>
+          <t>A 28332-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15830,10 +15835,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45477</v>
+        <v>45099</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15846,7 +15851,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15889,7 +15894,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 37557-2026</t>
+          <t>A 44033-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15903,10 +15908,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46276</v>
+        <v>45572</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15919,7 +15924,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15962,7 +15967,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 32298-2026</t>
+          <t>A 72879-2021</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15976,10 +15981,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46237</v>
+        <v>44547</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15991,13 +15996,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16040,7 +16040,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 21269-2024</t>
+          <t>A 28267-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16054,10 +16054,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45440</v>
+        <v>45099</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16113,7 +16113,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 12664-2023</t>
+          <t>A 21285-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16127,10 +16127,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45000</v>
+        <v>45440</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16186,7 +16186,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 32363-2026</t>
+          <t>A 28316-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16200,10 +16200,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46238</v>
+        <v>45477</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>6.2</v>
+        <v>3.4</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16259,7 +16259,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 16341-2025</t>
+          <t>A 21269-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16269,14 +16269,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45751</v>
+        <v>45440</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16332,7 +16332,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 32364-2026</t>
+          <t>A 12664-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16346,10 +16346,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46238</v>
+        <v>45000</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16405,7 +16405,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 10668-2025</t>
+          <t>A 16341-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16415,14 +16415,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45721</v>
+        <v>45751</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16478,7 +16478,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 25434-2025</t>
+          <t>A 10668-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16492,10 +16492,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45800</v>
+        <v>45721</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16551,7 +16551,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 25435-2025</t>
+          <t>A 25434-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16568,7 +16568,7 @@
         <v>45800</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16624,7 +16624,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 25436-2025</t>
+          <t>A 25435-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16641,7 +16641,7 @@
         <v>45800</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16697,7 +16697,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 26105-2025</t>
+          <t>A 25436-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16707,14 +16707,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45805</v>
+        <v>45800</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>5.3</v>
+        <v>1.3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16770,7 +16770,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 10703-2025</t>
+          <t>A 26105-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16780,14 +16780,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45722</v>
+        <v>45805</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16843,7 +16843,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 28390-2025</t>
+          <t>A 10703-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16857,10 +16857,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45819</v>
+        <v>45722</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16872,13 +16872,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I212" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16921,7 +16916,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 31258-2025</t>
+          <t>A 28390-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16935,10 +16930,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45833</v>
+        <v>45819</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16950,8 +16945,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I213" t="n">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16994,7 +16994,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 32967-2025</t>
+          <t>A 31258-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17008,10 +17008,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45839</v>
+        <v>45833</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17024,7 +17024,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17067,7 +17067,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 6925-2023</t>
+          <t>A 32967-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17081,10 +17081,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44967</v>
+        <v>45839</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17094,11 +17094,6 @@
       <c r="G215" t="inlineStr">
         <is>
           <t>GÖTENE</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I215" t="n">
@@ -17145,7 +17140,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 58236-2024</t>
+          <t>A 6925-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17159,10 +17154,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45632</v>
+        <v>44967</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17180,7 +17175,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17223,7 +17218,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 58691-2024</t>
+          <t>A 58236-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17237,10 +17232,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45635</v>
+        <v>45632</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17301,7 +17296,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 13450-2025</t>
+          <t>A 58691-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17315,10 +17310,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45736</v>
+        <v>45635</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17330,8 +17325,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17391,7 +17391,7 @@
         <v>44862</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45352</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>45352</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>

--- a/Översikt GÖTENE.xlsx
+++ b/Översikt GÖTENE.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44642</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45352</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45847</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>45846</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>46234</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>44827</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>44490</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41724-2022</t>
+          <t>A 5086-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44827</v>
+        <v>45330</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1815,16 +1815,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1839,7 +1839,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1848,49 +1848,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
         <v>1</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 41724-2022 artfynd.xlsx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 5086-2024 artfynd.xlsx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 41724-2022 karta.png", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 5086-2024 karta.png", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 41724-2022 georefererad karta.tif", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 5086-2024 georefererad karta.tif", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 41724-2022 FSC-klagomål.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 5086-2024 FSC-klagomål.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 41724-2022 FSC-klagomål mail.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 5086-2024 FSC-klagomål mail.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 41724-2022 tillsynsbegäran.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 5086-2024 tillsynsbegäran.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 41724-2022 tillsynsbegäran mail.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 5086-2024 tillsynsbegäran mail.docx", "A 5086-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 45211-2022</t>
+          <t>A 28273-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44844</v>
+        <v>45099</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1920,13 +1920,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1956,46 +1956,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 45211-2022 artfynd.xlsx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 28273-2023 artfynd.xlsx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 45211-2022 karta.png", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 28273-2023 karta.png", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 45211-2022 georefererad karta.tif", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 28273-2023 georefererad karta.tif", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 45211-2022 FSC-klagomål.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 28273-2023 FSC-klagomål.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 45211-2022 FSC-klagomål mail.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 28273-2023 FSC-klagomål mail.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 45211-2022 tillsynsbegäran.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 28273-2023 tillsynsbegäran.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 45211-2022 tillsynsbegäran mail.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 28273-2023 tillsynsbegäran mail.docx", "A 28273-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 18647-2025</t>
+          <t>A 47393-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45763</v>
+        <v>45930</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2024,23 +2024,18 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
@@ -2054,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2070,42 +2065,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Korallticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 18647-2025 artfynd.xlsx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 47393-2025 artfynd.xlsx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 18647-2025 karta.png", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 47393-2025 karta.png", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 18647-2025 georefererad karta.tif", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 47393-2025 georefererad karta.tif", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 18647-2025 FSC-klagomål.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 47393-2025 FSC-klagomål.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 18647-2025 FSC-klagomål mail.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 47393-2025 FSC-klagomål mail.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 18647-2025 tillsynsbegäran.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 47393-2025 tillsynsbegäran.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 18647-2025 tillsynsbegäran mail.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 47393-2025 tillsynsbegäran mail.docx", "A 47393-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 47393-2025</t>
+          <t>A 14296-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2119,10 +2114,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45930</v>
+        <v>45011</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2135,19 +2130,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2162,7 +2157,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2171,39 +2166,43 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Korallticka</t>
+          <t>Pilgrimsfalk</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 47393-2025 artfynd.xlsx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 14296-2023 artfynd.xlsx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 47393-2025 karta.png", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 14296-2023 karta.png", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 47393-2025 georefererad karta.tif", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 14296-2023 georefererad karta.tif", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 47393-2025 FSC-klagomål.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 14296-2023 FSC-klagomål.docx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 47393-2025 FSC-klagomål mail.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 14296-2023 FSC-klagomål mail.docx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 47393-2025 tillsynsbegäran.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 14296-2023 tillsynsbegäran.docx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 47393-2025 tillsynsbegäran mail.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 14296-2023 tillsynsbegäran mail.docx", "A 14296-2023")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 14296-2023 prioriterade fågelarter.docx", "A 14296-2023")</f>
         <v/>
       </c>
     </row>
@@ -2227,7 +2226,7 @@
         <v>45944</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2332,7 +2331,7 @@
         <v>44691</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2420,7 +2419,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33478-2026</t>
+          <t>A 41724-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2434,10 +2433,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46247</v>
+        <v>44827</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2450,17 +2449,17 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
@@ -2474,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2490,42 +2489,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 33478-2026 artfynd.xlsx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 41724-2022 artfynd.xlsx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 33478-2026 karta.png", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 41724-2022 karta.png", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 33478-2026 georefererad karta.tif", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 41724-2022 georefererad karta.tif", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 33478-2026 FSC-klagomål.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 41724-2022 FSC-klagomål.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 33478-2026 FSC-klagomål mail.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 41724-2022 FSC-klagomål mail.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 33478-2026 tillsynsbegäran.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 41724-2022 tillsynsbegäran.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 33478-2026 tillsynsbegäran mail.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 41724-2022 tillsynsbegäran mail.docx", "A 41724-2022")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 14296-2023</t>
+          <t>A 32909-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2539,10 +2538,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45011</v>
+        <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2555,19 +2554,19 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2582,7 +2581,7 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2591,50 +2590,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Pilgrimsfalk</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 14296-2023 artfynd.xlsx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32909-2025 artfynd.xlsx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 14296-2023 karta.png", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32909-2025 karta.png", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 14296-2023 georefererad karta.tif", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32909-2025 georefererad karta.tif", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 14296-2023 FSC-klagomål.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32909-2025 FSC-klagomål.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 14296-2023 FSC-klagomål mail.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32909-2025 FSC-klagomål mail.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 14296-2023 tillsynsbegäran.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32909-2025 tillsynsbegäran.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 14296-2023 tillsynsbegäran mail.docx", "A 14296-2023")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 14296-2023 prioriterade fågelarter.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32909-2025 tillsynsbegäran mail.docx", "A 32909-2025")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31326-2026</t>
+          <t>A 45211-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2648,10 +2643,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46219</v>
+        <v>44844</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2664,16 +2659,16 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2688,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2700,50 +2695,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 31326-2026 artfynd.xlsx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 45211-2022 artfynd.xlsx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 31326-2026 karta.png", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 45211-2022 karta.png", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 31326-2026 georefererad karta.tif", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 45211-2022 georefererad karta.tif", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 31326-2026 FSC-klagomål.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 45211-2022 FSC-klagomål.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 31326-2026 FSC-klagomål mail.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 45211-2022 FSC-klagomål mail.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 31326-2026 tillsynsbegäran.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 45211-2022 tillsynsbegäran.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 31326-2026 tillsynsbegäran mail.docx", "A 31326-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 31326-2026 prioriterade fågelarter.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 45211-2022 tillsynsbegäran mail.docx", "A 45211-2022")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 5086-2024</t>
+          <t>A 18647-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2757,10 +2748,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45330</v>
+        <v>45763</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2772,8 +2763,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2806,49 +2802,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 5086-2024 artfynd.xlsx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 18647-2025 artfynd.xlsx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 5086-2024 karta.png", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 18647-2025 karta.png", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 5086-2024 georefererad karta.tif", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 18647-2025 georefererad karta.tif", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 5086-2024 FSC-klagomål.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 18647-2025 FSC-klagomål.docx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 5086-2024 FSC-klagomål mail.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 18647-2025 FSC-klagomål mail.docx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 5086-2024 tillsynsbegäran.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 18647-2025 tillsynsbegäran.docx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 5086-2024 tillsynsbegäran mail.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 18647-2025 tillsynsbegäran mail.docx", "A 18647-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32224-2026</t>
+          <t>A 33478-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2862,10 +2858,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46237</v>
+        <v>46247</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2878,16 +2874,16 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2902,7 +2898,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2918,42 +2914,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Backmåra</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32224-2026 artfynd.xlsx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 33478-2026 artfynd.xlsx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32224-2026 karta.png", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 33478-2026 karta.png", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32224-2026 georefererad karta.tif", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 33478-2026 georefererad karta.tif", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32224-2026 FSC-klagomål.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 33478-2026 FSC-klagomål.docx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32224-2026 FSC-klagomål mail.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 33478-2026 FSC-klagomål mail.docx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32224-2026 tillsynsbegäran.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 33478-2026 tillsynsbegäran.docx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32224-2026 tillsynsbegäran mail.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 33478-2026 tillsynsbegäran mail.docx", "A 33478-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 28273-2023</t>
+          <t>A 31326-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2967,10 +2963,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45099</v>
+        <v>46219</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2983,7 +2979,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -2992,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3007,7 +3003,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3023,42 +3019,46 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 28273-2023 artfynd.xlsx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 31326-2026 artfynd.xlsx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 28273-2023 karta.png", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 31326-2026 karta.png", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 28273-2023 georefererad karta.tif", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 31326-2026 georefererad karta.tif", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 28273-2023 FSC-klagomål.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 31326-2026 FSC-klagomål.docx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 28273-2023 FSC-klagomål mail.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 31326-2026 FSC-klagomål mail.docx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 28273-2023 tillsynsbegäran.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 31326-2026 tillsynsbegäran.docx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 28273-2023 tillsynsbegäran mail.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 31326-2026 tillsynsbegäran mail.docx", "A 31326-2026")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 31326-2026 prioriterade fågelarter.docx", "A 31326-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32909-2025</t>
+          <t>A 32224-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45839</v>
+        <v>46237</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3128,35 +3128,35 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Backmåra</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32909-2025 artfynd.xlsx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32224-2026 artfynd.xlsx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32909-2025 karta.png", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32224-2026 karta.png", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32909-2025 georefererad karta.tif", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32224-2026 georefererad karta.tif", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32909-2025 FSC-klagomål.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32224-2026 FSC-klagomål.docx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32909-2025 FSC-klagomål mail.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32224-2026 FSC-klagomål mail.docx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32909-2025 tillsynsbegäran.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32224-2026 tillsynsbegäran.docx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32909-2025 tillsynsbegäran mail.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32224-2026 tillsynsbegäran mail.docx", "A 32224-2026")</f>
         <v/>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
         <v>45372</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>44490</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>44645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>44490</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>44490</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>44507</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>44614</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 48733-2022</t>
+          <t>A 44507-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44859</v>
+        <v>44840</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4076,7 +4076,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 44507-2022</t>
+          <t>A 48733-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44840</v>
+        <v>44859</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4166,7 +4166,7 @@
         <v>44566</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>44684</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>44477</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>44507</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>44581</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>44761</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>44757</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>44869</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>44812</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 46381-2022</t>
+          <t>A 11771-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44848</v>
+        <v>45373</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4840,13 +4840,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4889,7 +4884,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 49968-2022</t>
+          <t>A 36244-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4903,10 +4898,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44865</v>
+        <v>44803</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4919,7 +4914,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4962,7 +4957,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 59114-2021</t>
+          <t>A 46381-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4976,10 +4971,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44490</v>
+        <v>44848</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4991,8 +4986,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5035,7 +5035,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 6969-2022</t>
+          <t>A 49968-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44603</v>
+        <v>44865</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5108,7 +5108,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 55496-2021</t>
+          <t>A 61148-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44475</v>
+        <v>44498</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.8</v>
+        <v>0.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 36244-2022</t>
+          <t>A 38945-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5195,10 +5195,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44803</v>
+        <v>44816</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5254,7 +5254,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 61148-2021</t>
+          <t>A 59114-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44498</v>
+        <v>44490</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5327,7 +5327,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38945-2022</t>
+          <t>A 31981-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44816</v>
+        <v>45119</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5400,7 +5400,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 58418-2024</t>
+          <t>A 6969-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45634</v>
+        <v>44603</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 36381-2023</t>
+          <t>A 15646-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45152</v>
+        <v>45021</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5546,7 +5546,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8330-2024</t>
+          <t>A 55496-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5560,10 +5560,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45352</v>
+        <v>44475</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5619,7 +5619,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 13276-2024</t>
+          <t>A 9607-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5633,10 +5633,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45386</v>
+        <v>45361</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5692,7 +5692,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 849-2023</t>
+          <t>A 58650-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5706,10 +5706,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44931</v>
+        <v>45251</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5765,7 +5765,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 44608-2023</t>
+          <t>A 16341-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5775,14 +5775,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45189</v>
+        <v>45751</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5838,7 +5838,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 41721-2022</t>
+          <t>A 45239-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5852,10 +5852,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44827</v>
+        <v>44844</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5867,8 +5867,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5911,7 +5916,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 11889-2024</t>
+          <t>A 62510-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5925,10 +5930,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45376</v>
+        <v>44924</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5938,6 +5943,11 @@
       <c r="G63" t="inlineStr">
         <is>
           <t>GÖTENE</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -5984,7 +5994,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 11772-2024</t>
+          <t>A 61021-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5994,14 +6004,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45373</v>
+        <v>44914</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6014,7 +6024,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6057,7 +6067,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 11773-2024</t>
+          <t>A 10668-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6071,10 +6081,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45373</v>
+        <v>45721</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6087,7 +6097,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6130,7 +6140,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 31917-2022</t>
+          <t>A 849-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6144,10 +6154,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44777</v>
+        <v>44931</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6160,7 +6170,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6203,7 +6213,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 17010-2022</t>
+          <t>A 28264-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6217,10 +6227,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44676</v>
+        <v>45099</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6233,7 +6243,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6276,7 +6286,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 61021-2022</t>
+          <t>A 28268-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6286,14 +6296,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44914</v>
+        <v>45099</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6306,7 +6316,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6349,7 +6359,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 30205-2023</t>
+          <t>A 52352-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6363,10 +6373,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45110</v>
+        <v>45224</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6379,7 +6389,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>6.8</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6422,7 +6432,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 22278-2024</t>
+          <t>A 31969-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6436,10 +6446,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45446</v>
+        <v>45119</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6452,7 +6462,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6495,7 +6505,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 1379-2025</t>
+          <t>A 31978-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6509,10 +6519,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45667</v>
+        <v>45119</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6525,7 +6535,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6568,7 +6578,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 17069-2023</t>
+          <t>A 28258-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6582,10 +6592,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45034</v>
+        <v>45099</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6598,7 +6608,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6641,7 +6651,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13450-2025</t>
+          <t>A 61194-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6655,10 +6665,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45736</v>
+        <v>45645</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6670,8 +6680,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6714,7 +6729,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 45180-2024</t>
+          <t>A 13276-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6728,10 +6743,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45575</v>
+        <v>45386</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6744,7 +6759,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>14.7</v>
+        <v>3.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6787,7 +6802,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 61194-2024</t>
+          <t>A 22278-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6801,10 +6816,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45645</v>
+        <v>45446</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6816,13 +6831,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6865,7 +6875,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 14502-2023</t>
+          <t>A 17069-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6879,10 +6889,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45012</v>
+        <v>45034</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6895,7 +6905,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6938,7 +6948,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13340-2022</t>
+          <t>A 39998-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6952,10 +6962,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44645</v>
+        <v>45894</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6968,7 +6978,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7011,7 +7021,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 13348-2022</t>
+          <t>A 59074-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7025,10 +7035,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44645</v>
+        <v>45252</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7041,7 +7051,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7084,7 +7094,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 13366-2022</t>
+          <t>A 11772-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7098,10 +7108,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44645</v>
+        <v>45373</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7114,7 +7124,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7157,7 +7167,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 45013-2025</t>
+          <t>A 11773-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7171,10 +7181,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45918</v>
+        <v>45373</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7187,7 +7197,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7230,7 +7240,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 15646-2023</t>
+          <t>A 8765-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7244,10 +7254,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45021</v>
+        <v>44614</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7259,8 +7269,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7303,7 +7318,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 1662-2025</t>
+          <t>A 1352-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7317,10 +7332,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45670</v>
+        <v>44931</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7376,7 +7391,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 39998-2025</t>
+          <t>A 30205-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7390,10 +7405,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45894</v>
+        <v>45110</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7406,7 +7421,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7449,7 +7464,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 9607-2024</t>
+          <t>A 28267-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7463,10 +7478,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45361</v>
+        <v>45099</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7479,7 +7494,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7522,7 +7537,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 30174-2022</t>
+          <t>A 45007-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7536,10 +7551,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44757</v>
+        <v>45918</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7552,7 +7567,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7595,7 +7610,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 34161-2025</t>
+          <t>A 72879-2021</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7609,10 +7624,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45845</v>
+        <v>44547</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7625,7 +7640,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7668,7 +7683,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 9145-2023</t>
+          <t>A 25434-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7682,10 +7697,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44974</v>
+        <v>45800</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7698,7 +7713,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7741,7 +7756,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 45007-2025</t>
+          <t>A 25435-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7755,10 +7770,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45918</v>
+        <v>45800</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7771,7 +7786,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7814,7 +7829,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 13268-2024</t>
+          <t>A 25436-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7828,10 +7843,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45386</v>
+        <v>45800</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7844,7 +7859,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>6.7</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7887,7 +7902,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 47175-2025</t>
+          <t>A 26105-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7897,14 +7912,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45930</v>
+        <v>45805</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7917,7 +7932,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7960,7 +7975,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 47383-2025</t>
+          <t>A 10703-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7974,10 +7989,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45930</v>
+        <v>45722</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7990,7 +8005,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8050,7 +8065,7 @@
         <v>45930</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8106,7 +8121,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 47389-2025</t>
+          <t>A 47175-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8123,7 +8138,7 @@
         <v>45930</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8136,7 +8151,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8179,7 +8194,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 25594-2025</t>
+          <t>A 47389-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8189,14 +8204,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45803</v>
+        <v>45930</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8209,7 +8224,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8252,7 +8267,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 10451-2024</t>
+          <t>A 62499-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8266,10 +8281,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45366</v>
+        <v>44924</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8283,11 +8298,11 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8330,7 +8345,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 20710-2026</t>
+          <t>A 47383-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8344,10 +8359,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46141</v>
+        <v>45930</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8360,7 +8375,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8403,7 +8418,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 20811-2026</t>
+          <t>A 3932-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8417,10 +8432,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46141</v>
+        <v>44587</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8433,7 +8448,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8476,7 +8491,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 33162-2024</t>
+          <t>A 1379-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8490,10 +8505,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45518</v>
+        <v>45667</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8506,7 +8521,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8549,7 +8564,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 20812-2026</t>
+          <t>A 58418-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8563,10 +8578,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46141</v>
+        <v>45634</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8579,7 +8594,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8622,7 +8637,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 20700-2026</t>
+          <t>A 44608-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8636,10 +8651,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46141</v>
+        <v>45189</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8652,7 +8667,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8695,7 +8710,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 21369-2026</t>
+          <t>A 13170-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8709,10 +8724,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46147</v>
+        <v>45386</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8725,7 +8740,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8768,7 +8783,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 21376-2026</t>
+          <t>A 44033-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8782,10 +8797,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46147</v>
+        <v>45572</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8798,7 +8813,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>7.2</v>
+        <v>1.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8841,7 +8856,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 12660-2023</t>
+          <t>A 45180-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8851,14 +8866,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45000</v>
+        <v>45575</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8871,7 +8886,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.5</v>
+        <v>14.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8914,7 +8929,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 22055-2023</t>
+          <t>A 36304-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8928,10 +8943,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45069</v>
+        <v>45152</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8944,7 +8959,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8987,7 +9002,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 10596-2024</t>
+          <t>A 13366-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9001,10 +9016,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45366</v>
+        <v>44645</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9017,7 +9032,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9060,7 +9075,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 52141-2025</t>
+          <t>A 49256-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9074,10 +9089,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45953</v>
+        <v>45210</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9090,7 +9105,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9133,7 +9148,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 22916-2026</t>
+          <t>A 15428-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9147,10 +9162,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46160</v>
+        <v>45747</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9163,7 +9178,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9206,7 +9221,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 22906-2026</t>
+          <t>A 15434-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9220,10 +9235,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46160</v>
+        <v>45747</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9236,7 +9251,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9279,7 +9294,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 22912-2026</t>
+          <t>A 52141-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9293,10 +9308,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46160</v>
+        <v>45953</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9309,7 +9324,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9352,7 +9367,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 28268-2023</t>
+          <t>A 10596-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9366,10 +9381,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45099</v>
+        <v>45366</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9382,7 +9397,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9425,7 +9440,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 850-2023</t>
+          <t>A 17010-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9439,10 +9454,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44931</v>
+        <v>44676</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9455,7 +9470,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9498,7 +9513,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 55764-2024</t>
+          <t>A 21285-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9512,10 +9527,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45623</v>
+        <v>45440</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9528,7 +9543,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9571,7 +9586,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 56365-2025</t>
+          <t>A 19674-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9585,10 +9600,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45974</v>
+        <v>45051</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9601,7 +9616,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9644,7 +9659,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 19674-2023</t>
+          <t>A 13345-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9658,10 +9673,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45051</v>
+        <v>44645</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9674,7 +9689,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9717,7 +9732,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 56347-2025</t>
+          <t>A 28390-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9731,10 +9746,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45974</v>
+        <v>45819</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9746,8 +9761,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>10.9</v>
+        <v>1.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9790,7 +9810,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 56352-2025</t>
+          <t>A 41721-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9804,10 +9824,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45974</v>
+        <v>44827</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9820,7 +9840,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>5.9</v>
+        <v>4.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9863,7 +9883,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 56414-2025</t>
+          <t>A 21429-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9877,10 +9897,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45975</v>
+        <v>44706</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9893,7 +9913,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9936,7 +9956,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 56340-2025</t>
+          <t>A 56365-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9953,7 +9973,7 @@
         <v>45974</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9966,7 +9986,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10009,7 +10029,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 56417-2025</t>
+          <t>A 56347-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10023,10 +10043,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45975</v>
+        <v>45974</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10039,7 +10059,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.9</v>
+        <v>10.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10082,7 +10102,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 56346-2025</t>
+          <t>A 56352-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10099,7 +10119,7 @@
         <v>45974</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10112,7 +10132,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>18.8</v>
+        <v>5.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10155,7 +10175,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 19683-2023</t>
+          <t>A 35408-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10169,10 +10189,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45051</v>
+        <v>45146</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10185,7 +10205,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10228,7 +10248,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 58517-2025</t>
+          <t>A 56346-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10242,10 +10262,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45985</v>
+        <v>45974</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10258,7 +10278,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.1</v>
+        <v>18.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10301,7 +10321,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 58520-2025</t>
+          <t>A 56340-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10315,10 +10335,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45985</v>
+        <v>45974</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10331,7 +10351,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10374,7 +10394,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 8765-2022</t>
+          <t>A 55764-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10388,10 +10408,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44614</v>
+        <v>45623</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10403,13 +10423,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10452,7 +10467,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 58766-2025</t>
+          <t>A 56169-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10466,10 +10481,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45986</v>
+        <v>45624</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10482,7 +10497,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>19.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10525,7 +10540,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 52352-2023</t>
+          <t>A 850-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10539,10 +10554,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45224</v>
+        <v>44931</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10555,7 +10570,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10598,7 +10613,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 58767-2025</t>
+          <t>A 56417-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10612,10 +10627,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45986</v>
+        <v>45975</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10628,7 +10643,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10671,7 +10686,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 62510-2022</t>
+          <t>A 56414-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10685,10 +10700,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44924</v>
+        <v>45975</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10700,13 +10715,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10749,7 +10759,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 60559-2025</t>
+          <t>A 55511-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10763,10 +10773,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45995</v>
+        <v>45238</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10779,7 +10789,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10822,7 +10832,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 25777-2026</t>
+          <t>A 58766-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10832,14 +10842,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46178</v>
+        <v>45986</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10852,7 +10862,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10895,7 +10905,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 17876-2025</t>
+          <t>A 58767-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10909,10 +10919,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45758</v>
+        <v>45986</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10925,7 +10935,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10968,7 +10978,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 26336-2026</t>
+          <t>A 58517-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10982,10 +10992,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46182</v>
+        <v>45985</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10998,7 +11008,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11041,7 +11051,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 13170-2024</t>
+          <t>A 58520-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11055,10 +11065,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45386</v>
+        <v>45985</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11071,7 +11081,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11114,7 +11124,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 26338-2026</t>
+          <t>A 36472-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11128,10 +11138,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46182</v>
+        <v>45152</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11187,7 +11197,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 62390-2023</t>
+          <t>A 61294-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11201,10 +11211,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45268</v>
+        <v>45645</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11217,7 +11227,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11260,7 +11270,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 3960-2026</t>
+          <t>A 12660-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11270,14 +11280,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46044</v>
+        <v>45000</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11289,13 +11299,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11338,7 +11343,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 5044-2026</t>
+          <t>A 62390-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11352,10 +11357,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46049</v>
+        <v>45268</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11368,7 +11373,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>5.4</v>
+        <v>1.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11411,7 +11416,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 10636-2026</t>
+          <t>A 62402-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11425,10 +11430,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46078</v>
+        <v>45268</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11441,7 +11446,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11484,7 +11489,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 62499-2022</t>
+          <t>A 60559-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11498,10 +11503,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44924</v>
+        <v>45995</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11513,13 +11518,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11562,7 +11562,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 10958-2022</t>
+          <t>A 31258-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11576,10 +11576,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44628</v>
+        <v>45833</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.2</v>
+        <v>5.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11635,7 +11635,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 45239-2022</t>
+          <t>A 49252-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11649,10 +11649,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44844</v>
+        <v>45210</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11664,13 +11664,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11713,7 +11708,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 15426-2025</t>
+          <t>A 31917-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11727,10 +11722,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45747</v>
+        <v>44777</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11743,7 +11738,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11786,7 +11781,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 15442-2025</t>
+          <t>A 17876-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11800,10 +11795,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45747</v>
+        <v>45758</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11816,7 +11811,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.2</v>
+        <v>4.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11859,7 +11854,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 28467-2026</t>
+          <t>A 12450-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11873,10 +11868,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46197</v>
+        <v>44638</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11889,7 +11884,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11932,7 +11927,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 28647-2026</t>
+          <t>A 3960-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11946,10 +11941,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46198</v>
+        <v>46044</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11961,8 +11956,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12005,7 +12005,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 10630-2026</t>
+          <t>A 32967-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12019,10 +12019,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46078</v>
+        <v>45839</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12078,7 +12078,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 11459-2026</t>
+          <t>A 5044-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12092,10 +12092,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46083</v>
+        <v>46049</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12151,7 +12151,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 11460-2026</t>
+          <t>A 64712-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12165,10 +12165,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46083</v>
+        <v>45281</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12224,7 +12224,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 11630-2026</t>
+          <t>A 39081-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12238,10 +12238,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46084</v>
+        <v>44817</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12253,13 +12253,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12302,7 +12297,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 20507-2026</t>
+          <t>A 36381-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12316,10 +12311,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46140</v>
+        <v>45152</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12332,7 +12327,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12375,7 +12370,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 12450-2022</t>
+          <t>A 13268-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12389,10 +12384,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44638</v>
+        <v>45386</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12405,7 +12400,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.6</v>
+        <v>6.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12448,7 +12443,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 21429-2022</t>
+          <t>A 13281-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12462,10 +12457,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44706</v>
+        <v>45386</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12478,7 +12473,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12521,7 +12516,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 56169-2024</t>
+          <t>A 19683-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12535,10 +12530,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45624</v>
+        <v>45051</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12551,7 +12546,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>19.7</v>
+        <v>2.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12594,7 +12589,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 13279-2024</t>
+          <t>A 58417-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12608,10 +12603,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45386</v>
+        <v>45634</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12623,8 +12618,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12667,7 +12667,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 49256-2023</t>
+          <t>A 10630-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12681,10 +12681,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45210</v>
+        <v>46078</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12740,7 +12740,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 31969-2023</t>
+          <t>A 11459-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12754,10 +12754,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45119</v>
+        <v>46083</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12813,7 +12813,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 31978-2023</t>
+          <t>A 11460-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12827,10 +12827,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45119</v>
+        <v>46083</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12886,7 +12886,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 39150-2022</t>
+          <t>A 11630-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12900,10 +12900,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44817</v>
+        <v>46084</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12915,8 +12915,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12959,7 +12964,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 18776-2026</t>
+          <t>A 39150-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12973,10 +12978,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46128</v>
+        <v>44817</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12989,7 +12994,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13032,7 +13037,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 36472-2023</t>
+          <t>A 6925-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13046,10 +13051,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45152</v>
+        <v>44967</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13061,8 +13066,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13105,7 +13115,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 30191-2026</t>
+          <t>A 14502-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13119,10 +13129,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46206</v>
+        <v>45012</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13134,13 +13144,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13183,7 +13188,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 3932-2022</t>
+          <t>A 58236-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13197,10 +13202,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44587</v>
+        <v>45632</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13212,8 +13217,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13256,7 +13266,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 7225-2023</t>
+          <t>A 58691-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13270,10 +13280,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44970</v>
+        <v>45635</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13285,8 +13295,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13329,7 +13344,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 34008-2026</t>
+          <t>A 10958-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13343,10 +13358,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46252</v>
+        <v>44628</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13359,7 +13374,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13402,7 +13417,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 35408-2023</t>
+          <t>A 9145-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13416,10 +13431,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45146</v>
+        <v>44974</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13432,7 +13447,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13475,7 +13490,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 13280-2024</t>
+          <t>A 13450-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13489,10 +13504,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45386</v>
+        <v>45736</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13505,7 +13520,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13548,7 +13563,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 31981-2023</t>
+          <t>A 18776-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13562,10 +13577,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45119</v>
+        <v>46128</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13578,7 +13593,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13621,7 +13636,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 5690-2026</t>
+          <t>A 7225-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13635,10 +13650,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46051</v>
+        <v>44970</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13651,7 +13666,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13694,7 +13709,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 55511-2023</t>
+          <t>A 10451-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13708,10 +13723,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45238</v>
+        <v>45366</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13723,8 +13738,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13767,7 +13787,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 28258-2023</t>
+          <t>A 30174-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13781,10 +13801,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45099</v>
+        <v>44757</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13797,7 +13817,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.7</v>
+        <v>5.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13840,7 +13860,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 28264-2023</t>
+          <t>A 28332-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13857,7 +13877,7 @@
         <v>45099</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13870,7 +13890,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13913,7 +13933,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 49252-2023</t>
+          <t>A 8330-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13927,10 +13947,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45210</v>
+        <v>45352</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13943,7 +13963,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13986,7 +14006,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 31329-2026</t>
+          <t>A 13279-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14000,10 +14020,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46219</v>
+        <v>45386</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14016,7 +14036,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>7.5</v>
+        <v>1.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14059,7 +14079,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 31446-2026</t>
+          <t>A 11889-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14073,10 +14093,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46220</v>
+        <v>45376</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14089,7 +14109,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14132,7 +14152,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 31452-2026</t>
+          <t>A 15426-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14146,10 +14166,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46220</v>
+        <v>45747</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14162,7 +14182,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14205,7 +14225,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 28335-2023</t>
+          <t>A 15442-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14219,10 +14239,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45099</v>
+        <v>45747</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14235,7 +14255,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14278,7 +14298,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 13281-2024</t>
+          <t>A 13340-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14292,10 +14312,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45386</v>
+        <v>44645</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14308,7 +14328,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14351,7 +14371,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 58650-2023</t>
+          <t>A 13348-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14365,10 +14385,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45251</v>
+        <v>44645</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14381,7 +14401,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14424,7 +14444,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 36304-2023</t>
+          <t>A 22055-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14438,10 +14458,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45152</v>
+        <v>45069</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14454,7 +14474,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14497,7 +14517,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 31324-2026</t>
+          <t>A 45013-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14511,10 +14531,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46219</v>
+        <v>45918</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14527,7 +14547,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14570,7 +14590,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 35869-2026</t>
+          <t>A 34161-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14584,10 +14604,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46266</v>
+        <v>45845</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14600,7 +14620,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14643,7 +14663,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 35871-2026</t>
+          <t>A 1662-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14657,10 +14677,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46266</v>
+        <v>45670</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14673,7 +14693,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14716,7 +14736,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 59074-2023</t>
+          <t>A 20710-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14730,10 +14750,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45252</v>
+        <v>46141</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14746,7 +14766,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14789,7 +14809,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 15428-2025</t>
+          <t>A 20812-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14803,10 +14823,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45747</v>
+        <v>46141</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14819,7 +14839,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.1</v>
+        <v>2.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14862,7 +14882,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 15434-2025</t>
+          <t>A 33162-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14876,10 +14896,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45747</v>
+        <v>45518</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14892,7 +14912,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.1</v>
+        <v>2.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14935,7 +14955,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 11771-2024</t>
+          <t>A 20700-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14949,10 +14969,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45373</v>
+        <v>46141</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14965,7 +14985,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15008,7 +15028,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 58417-2024</t>
+          <t>A 13280-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15022,10 +15042,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45634</v>
+        <v>45386</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15037,13 +15057,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15086,7 +15101,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 37557-2026</t>
+          <t>A 25594-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15096,14 +15111,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46276</v>
+        <v>45803</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15116,7 +15131,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15159,7 +15174,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 13345-2022</t>
+          <t>A 20811-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15173,10 +15188,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44645</v>
+        <v>46141</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15189,7 +15204,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15232,7 +15247,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 32298-2026</t>
+          <t>A 21376-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15246,10 +15261,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46237</v>
+        <v>46147</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15261,13 +15276,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>3.8</v>
+        <v>7.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15310,7 +15320,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 64712-2023</t>
+          <t>A 28335-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15324,10 +15334,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45281</v>
+        <v>45099</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15340,7 +15350,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15383,7 +15393,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 32363-2026</t>
+          <t>A 21369-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15397,10 +15407,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46238</v>
+        <v>46147</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15413,7 +15423,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>6.2</v>
+        <v>1.3</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15456,7 +15466,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 32364-2026</t>
+          <t>A 12664-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15470,10 +15480,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46238</v>
+        <v>45000</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15486,7 +15496,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15529,7 +15539,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 39081-2022</t>
+          <t>A 21269-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15543,10 +15553,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44817</v>
+        <v>45440</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15559,7 +15569,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15602,7 +15612,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 61294-2024</t>
+          <t>A 28316-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15616,10 +15626,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45645</v>
+        <v>45477</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15632,7 +15642,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15675,7 +15685,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 62402-2023</t>
+          <t>A 22906-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15689,10 +15699,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45268</v>
+        <v>46160</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15705,7 +15715,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15748,7 +15758,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 1352-2023</t>
+          <t>A 22916-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15762,10 +15772,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44931</v>
+        <v>46160</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15821,7 +15831,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 28332-2023</t>
+          <t>A 22912-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15835,10 +15845,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45099</v>
+        <v>46160</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15851,7 +15861,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15894,7 +15904,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 44033-2024</t>
+          <t>A 25777-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15904,14 +15914,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45572</v>
+        <v>46178</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15924,7 +15934,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15967,7 +15977,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 72879-2021</t>
+          <t>A 26338-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15981,10 +15991,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44547</v>
+        <v>46182</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15997,7 +16007,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16040,7 +16050,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 28267-2023</t>
+          <t>A 26336-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16054,10 +16064,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45099</v>
+        <v>46182</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16070,7 +16080,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16113,7 +16123,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 21285-2024</t>
+          <t>A 10636-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16127,10 +16137,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45440</v>
+        <v>46078</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16143,7 +16153,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16186,7 +16196,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 28316-2024</t>
+          <t>A 28647-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16200,10 +16210,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45477</v>
+        <v>46198</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16216,7 +16226,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16259,7 +16269,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 21269-2024</t>
+          <t>A 28467-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16273,10 +16283,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45440</v>
+        <v>46197</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16289,7 +16299,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16332,7 +16342,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 12664-2023</t>
+          <t>A 20507-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16346,10 +16356,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45000</v>
+        <v>46140</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16362,7 +16372,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16405,7 +16415,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 16341-2025</t>
+          <t>A 30191-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16415,14 +16425,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45751</v>
+        <v>46206</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16434,8 +16444,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>1.4</v>
+        <v>6.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16478,7 +16493,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 10668-2025</t>
+          <t>A 34008-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16492,10 +16507,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45721</v>
+        <v>46252</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16508,7 +16523,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16551,7 +16566,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 25434-2025</t>
+          <t>A 5690-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16565,10 +16580,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45800</v>
+        <v>46051</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16581,7 +16596,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16624,7 +16639,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 25435-2025</t>
+          <t>A 31329-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16638,10 +16653,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45800</v>
+        <v>46219</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16654,7 +16669,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16697,7 +16712,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 25436-2025</t>
+          <t>A 31324-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16711,10 +16726,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45800</v>
+        <v>46219</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16727,7 +16742,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16770,7 +16785,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 26105-2025</t>
+          <t>A 35869-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16780,14 +16795,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45805</v>
+        <v>46266</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16800,7 +16815,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16843,7 +16858,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 10703-2025</t>
+          <t>A 35871-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16857,10 +16872,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45722</v>
+        <v>46266</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16873,7 +16888,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16916,7 +16931,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 28390-2025</t>
+          <t>A 31446-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16930,10 +16945,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45819</v>
+        <v>46220</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16945,13 +16960,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I213" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16994,7 +17004,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 31258-2025</t>
+          <t>A 31452-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17008,10 +17018,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45833</v>
+        <v>46220</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17024,7 +17034,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17067,7 +17077,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 32967-2025</t>
+          <t>A 37557-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17081,10 +17091,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45839</v>
+        <v>46276</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17097,7 +17107,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17140,7 +17150,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 6925-2023</t>
+          <t>A 32298-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17154,10 +17164,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44967</v>
+        <v>46237</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17171,11 +17181,11 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17218,7 +17228,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 58236-2024</t>
+          <t>A 32363-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17232,10 +17242,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45632</v>
+        <v>46238</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17247,13 +17257,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>2.3</v>
+        <v>6.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17296,7 +17301,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 58691-2024</t>
+          <t>A 32364-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17310,10 +17315,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45635</v>
+        <v>46238</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17325,13 +17330,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I218" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17391,7 +17391,7 @@
         <v>44862</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45352</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>45352</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>

--- a/Översikt GÖTENE.xlsx
+++ b/Översikt GÖTENE.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44642</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45352</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45847</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>45846</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>46234</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>44827</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>44490</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 5086-2024</t>
+          <t>A 41724-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45330</v>
+        <v>44827</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1815,17 +1815,17 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1839,7 +1839,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1848,49 +1848,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 5086-2024 artfynd.xlsx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 41724-2022 artfynd.xlsx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 5086-2024 karta.png", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 41724-2022 karta.png", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 5086-2024 georefererad karta.tif", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 41724-2022 georefererad karta.tif", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 5086-2024 FSC-klagomål.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 41724-2022 FSC-klagomål.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 5086-2024 FSC-klagomål mail.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 41724-2022 FSC-klagomål mail.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 5086-2024 tillsynsbegäran.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 41724-2022 tillsynsbegäran.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 5086-2024 tillsynsbegäran mail.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 41724-2022 tillsynsbegäran mail.docx", "A 41724-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 28273-2023</t>
+          <t>A 45211-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45099</v>
+        <v>44844</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1920,13 +1920,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>2.3</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1956,46 +1956,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 28273-2023 artfynd.xlsx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 45211-2022 artfynd.xlsx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 28273-2023 karta.png", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 45211-2022 karta.png", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 28273-2023 georefererad karta.tif", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 45211-2022 georefererad karta.tif", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 28273-2023 FSC-klagomål.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 45211-2022 FSC-klagomål.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 28273-2023 FSC-klagomål mail.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 45211-2022 FSC-klagomål mail.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 28273-2023 tillsynsbegäran.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 45211-2022 tillsynsbegäran.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 28273-2023 tillsynsbegäran mail.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 45211-2022 tillsynsbegäran mail.docx", "A 45211-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 47393-2025</t>
+          <t>A 18647-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45930</v>
+        <v>45763</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2024,17 +2024,22 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2049,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2065,42 +2070,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Korallticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 47393-2025 artfynd.xlsx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 18647-2025 artfynd.xlsx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 47393-2025 karta.png", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 18647-2025 karta.png", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 47393-2025 georefererad karta.tif", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 18647-2025 georefererad karta.tif", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 47393-2025 FSC-klagomål.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 18647-2025 FSC-klagomål.docx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 47393-2025 FSC-klagomål mail.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 18647-2025 FSC-klagomål mail.docx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 47393-2025 tillsynsbegäran.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 18647-2025 tillsynsbegäran.docx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 47393-2025 tillsynsbegäran mail.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 18647-2025 tillsynsbegäran mail.docx", "A 18647-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 14296-2023</t>
+          <t>A 47393-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2114,10 +2119,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45011</v>
+        <v>45930</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2130,19 +2135,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2157,7 +2162,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2166,43 +2171,39 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Pilgrimsfalk</t>
+          <t>Korallticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 14296-2023 artfynd.xlsx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 47393-2025 artfynd.xlsx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 14296-2023 karta.png", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 47393-2025 karta.png", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 14296-2023 georefererad karta.tif", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 47393-2025 georefererad karta.tif", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 14296-2023 FSC-klagomål.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 47393-2025 FSC-klagomål.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 14296-2023 FSC-klagomål mail.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 47393-2025 FSC-klagomål mail.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 14296-2023 tillsynsbegäran.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 47393-2025 tillsynsbegäran.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 14296-2023 tillsynsbegäran mail.docx", "A 14296-2023")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 14296-2023 prioriterade fågelarter.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 47393-2025 tillsynsbegäran mail.docx", "A 47393-2025")</f>
         <v/>
       </c>
     </row>
@@ -2226,7 +2227,7 @@
         <v>45944</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2331,7 +2332,7 @@
         <v>44691</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2419,7 +2420,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 41724-2022</t>
+          <t>A 14296-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2433,10 +2434,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44827</v>
+        <v>45011</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2449,19 +2450,19 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2476,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2485,46 +2486,50 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Pilgrimsfalk</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 41724-2022 artfynd.xlsx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 14296-2023 artfynd.xlsx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 41724-2022 karta.png", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 14296-2023 karta.png", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 41724-2022 georefererad karta.tif", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 14296-2023 georefererad karta.tif", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 41724-2022 FSC-klagomål.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 14296-2023 FSC-klagomål.docx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 41724-2022 FSC-klagomål mail.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 14296-2023 FSC-klagomål mail.docx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 41724-2022 tillsynsbegäran.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 14296-2023 tillsynsbegäran.docx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 41724-2022 tillsynsbegäran mail.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 14296-2023 tillsynsbegäran mail.docx", "A 14296-2023")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 14296-2023 prioriterade fågelarter.docx", "A 14296-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 32909-2025</t>
+          <t>A 31326-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2538,10 +2543,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45839</v>
+        <v>46219</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2554,10 +2559,10 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2594,42 +2599,46 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32909-2025 artfynd.xlsx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 31326-2026 artfynd.xlsx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32909-2025 karta.png", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 31326-2026 karta.png", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32909-2025 georefererad karta.tif", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 31326-2026 georefererad karta.tif", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32909-2025 FSC-klagomål.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 31326-2026 FSC-klagomål.docx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32909-2025 FSC-klagomål mail.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 31326-2026 FSC-klagomål mail.docx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32909-2025 tillsynsbegäran.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 31326-2026 tillsynsbegäran.docx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32909-2025 tillsynsbegäran mail.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 31326-2026 tillsynsbegäran mail.docx", "A 31326-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 31326-2026 prioriterade fågelarter.docx", "A 31326-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 45211-2022</t>
+          <t>A 5086-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2643,10 +2652,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44844</v>
+        <v>45330</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2659,7 +2668,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2692,49 +2701,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 45211-2022 artfynd.xlsx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 5086-2024 artfynd.xlsx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 45211-2022 karta.png", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 5086-2024 karta.png", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 45211-2022 georefererad karta.tif", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 5086-2024 georefererad karta.tif", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 45211-2022 FSC-klagomål.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 5086-2024 FSC-klagomål.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 45211-2022 FSC-klagomål mail.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 5086-2024 FSC-klagomål mail.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 45211-2022 tillsynsbegäran.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 5086-2024 tillsynsbegäran.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 45211-2022 tillsynsbegäran mail.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 5086-2024 tillsynsbegäran mail.docx", "A 5086-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 18647-2025</t>
+          <t>A 28273-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2748,10 +2757,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45763</v>
+        <v>45099</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2763,19 +2772,14 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2809,42 +2813,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 18647-2025 artfynd.xlsx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 28273-2023 artfynd.xlsx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 18647-2025 karta.png", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 28273-2023 karta.png", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 18647-2025 georefererad karta.tif", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 28273-2023 georefererad karta.tif", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 18647-2025 FSC-klagomål.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 28273-2023 FSC-klagomål.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 18647-2025 FSC-klagomål mail.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 28273-2023 FSC-klagomål mail.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 18647-2025 tillsynsbegäran.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 28273-2023 tillsynsbegäran.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 18647-2025 tillsynsbegäran mail.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 28273-2023 tillsynsbegäran mail.docx", "A 28273-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 33478-2026</t>
+          <t>A 32224-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2858,10 +2862,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46247</v>
+        <v>46237</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2874,17 +2878,17 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
@@ -2898,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2914,42 +2918,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Backmåra</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 33478-2026 artfynd.xlsx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32224-2026 artfynd.xlsx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 33478-2026 karta.png", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32224-2026 karta.png", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 33478-2026 georefererad karta.tif", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32224-2026 georefererad karta.tif", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 33478-2026 FSC-klagomål.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32224-2026 FSC-klagomål.docx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 33478-2026 FSC-klagomål mail.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32224-2026 FSC-klagomål mail.docx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 33478-2026 tillsynsbegäran.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32224-2026 tillsynsbegäran.docx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 33478-2026 tillsynsbegäran mail.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32224-2026 tillsynsbegäran mail.docx", "A 32224-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31326-2026</t>
+          <t>A 33478-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2963,10 +2967,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46219</v>
+        <v>46247</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2979,16 +2983,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3003,7 +3007,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3019,46 +3023,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 31326-2026 artfynd.xlsx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 33478-2026 artfynd.xlsx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 31326-2026 karta.png", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 33478-2026 karta.png", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 31326-2026 georefererad karta.tif", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 33478-2026 georefererad karta.tif", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 31326-2026 FSC-klagomål.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 33478-2026 FSC-klagomål.docx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 31326-2026 FSC-klagomål mail.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 33478-2026 FSC-klagomål mail.docx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 31326-2026 tillsynsbegäran.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 33478-2026 tillsynsbegäran.docx", "A 33478-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 31326-2026 tillsynsbegäran mail.docx", "A 31326-2026")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 31326-2026 prioriterade fågelarter.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 33478-2026 tillsynsbegäran mail.docx", "A 33478-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32224-2026</t>
+          <t>A 32909-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46237</v>
+        <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3128,35 +3128,35 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Backmåra</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32224-2026 artfynd.xlsx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32909-2025 artfynd.xlsx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32224-2026 karta.png", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32909-2025 karta.png", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32224-2026 georefererad karta.tif", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32909-2025 georefererad karta.tif", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32224-2026 FSC-klagomål.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32909-2025 FSC-klagomål.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32224-2026 FSC-klagomål mail.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32909-2025 FSC-klagomål mail.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32224-2026 tillsynsbegäran.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32909-2025 tillsynsbegäran.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32224-2026 tillsynsbegäran mail.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32909-2025 tillsynsbegäran mail.docx", "A 32909-2025")</f>
         <v/>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
         <v>45372</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>44490</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>44645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>44490</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>44490</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>44507</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>44614</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 44507-2022</t>
+          <t>A 48733-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44840</v>
+        <v>44859</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4076,7 +4076,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 48733-2022</t>
+          <t>A 44507-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44859</v>
+        <v>44840</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4166,7 +4166,7 @@
         <v>44566</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>44684</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>44477</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>44507</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>44581</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>44761</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>44757</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>44869</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>44812</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 11771-2024</t>
+          <t>A 46381-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45373</v>
+        <v>44848</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4840,8 +4840,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4884,7 +4889,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 36244-2022</t>
+          <t>A 49968-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4898,10 +4903,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44803</v>
+        <v>44865</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4914,7 +4919,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4957,7 +4962,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 46381-2022</t>
+          <t>A 59114-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4971,10 +4976,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44848</v>
+        <v>44490</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4986,13 +4991,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5035,7 +5035,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 49968-2022</t>
+          <t>A 6969-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44865</v>
+        <v>44603</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5108,7 +5108,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 61148-2021</t>
+          <t>A 55496-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44498</v>
+        <v>44475</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.3</v>
+        <v>3.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 38945-2022</t>
+          <t>A 36244-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5195,10 +5195,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44816</v>
+        <v>44803</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5254,7 +5254,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 59114-2021</t>
+          <t>A 61148-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44490</v>
+        <v>44498</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5327,7 +5327,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 31981-2023</t>
+          <t>A 38945-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45119</v>
+        <v>44816</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5400,7 +5400,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 6969-2022</t>
+          <t>A 58418-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44603</v>
+        <v>45634</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 15646-2023</t>
+          <t>A 36381-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45021</v>
+        <v>45152</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5546,7 +5546,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 55496-2021</t>
+          <t>A 8330-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5560,10 +5560,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44475</v>
+        <v>45352</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5619,7 +5619,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 9607-2024</t>
+          <t>A 13276-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5633,10 +5633,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45361</v>
+        <v>45386</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5692,7 +5692,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 58650-2023</t>
+          <t>A 849-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5706,10 +5706,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45251</v>
+        <v>44931</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5765,7 +5765,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 16341-2025</t>
+          <t>A 44608-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5775,14 +5775,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45751</v>
+        <v>45189</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5838,7 +5838,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 45239-2022</t>
+          <t>A 41721-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5852,10 +5852,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44844</v>
+        <v>44827</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5867,13 +5867,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5916,7 +5911,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 62510-2022</t>
+          <t>A 11889-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5930,10 +5925,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44924</v>
+        <v>45376</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5943,11 +5938,6 @@
       <c r="G63" t="inlineStr">
         <is>
           <t>GÖTENE</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -5994,7 +5984,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 61021-2022</t>
+          <t>A 11772-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6004,14 +5994,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44914</v>
+        <v>45373</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6024,7 +6014,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6067,7 +6057,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 10668-2025</t>
+          <t>A 11773-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6081,10 +6071,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45721</v>
+        <v>45373</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6097,7 +6087,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6140,7 +6130,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 849-2023</t>
+          <t>A 31917-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6154,10 +6144,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44931</v>
+        <v>44777</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6170,7 +6160,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6213,7 +6203,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 28264-2023</t>
+          <t>A 17010-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6227,10 +6217,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45099</v>
+        <v>44676</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6243,7 +6233,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6286,7 +6276,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 28268-2023</t>
+          <t>A 61021-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6296,14 +6286,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45099</v>
+        <v>44914</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6316,7 +6306,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6359,7 +6349,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 52352-2023</t>
+          <t>A 30205-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6373,10 +6363,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45224</v>
+        <v>45110</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6389,7 +6379,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.7</v>
+        <v>6.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6432,7 +6422,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 31969-2023</t>
+          <t>A 22278-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6446,10 +6436,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45119</v>
+        <v>45446</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6462,7 +6452,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6505,7 +6495,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31978-2023</t>
+          <t>A 1379-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6519,10 +6509,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45119</v>
+        <v>45667</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6535,7 +6525,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6578,7 +6568,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 28258-2023</t>
+          <t>A 17069-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6592,10 +6582,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45099</v>
+        <v>45034</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6608,7 +6598,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6651,7 +6641,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61194-2024</t>
+          <t>A 13450-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6665,10 +6655,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45645</v>
+        <v>45736</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6680,13 +6670,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6729,7 +6714,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 13276-2024</t>
+          <t>A 45180-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6743,10 +6728,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45386</v>
+        <v>45575</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6759,7 +6744,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.6</v>
+        <v>14.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6802,7 +6787,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 22278-2024</t>
+          <t>A 61194-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6816,10 +6801,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45446</v>
+        <v>45645</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6831,8 +6816,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6875,7 +6865,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 17069-2023</t>
+          <t>A 14502-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6889,10 +6879,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45034</v>
+        <v>45012</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6905,7 +6895,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6948,7 +6938,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 39998-2025</t>
+          <t>A 13340-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6962,10 +6952,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45894</v>
+        <v>44645</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6978,7 +6968,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7021,7 +7011,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 59074-2023</t>
+          <t>A 13348-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7035,10 +7025,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45252</v>
+        <v>44645</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7051,7 +7041,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7094,7 +7084,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 11772-2024</t>
+          <t>A 13366-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7108,10 +7098,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45373</v>
+        <v>44645</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7124,7 +7114,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7167,7 +7157,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 11773-2024</t>
+          <t>A 45013-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7181,10 +7171,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45373</v>
+        <v>45918</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7197,7 +7187,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7240,7 +7230,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 8765-2022</t>
+          <t>A 15646-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7254,10 +7244,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44614</v>
+        <v>45021</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7269,13 +7259,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7318,7 +7303,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 1352-2023</t>
+          <t>A 1662-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7332,10 +7317,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44931</v>
+        <v>45670</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7391,7 +7376,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 30205-2023</t>
+          <t>A 39998-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7405,10 +7390,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45110</v>
+        <v>45894</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7421,7 +7406,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7464,7 +7449,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 28267-2023</t>
+          <t>A 9607-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7478,10 +7463,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45099</v>
+        <v>45361</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7494,7 +7479,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7537,7 +7522,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 45007-2025</t>
+          <t>A 30174-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7551,10 +7536,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45918</v>
+        <v>44757</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7567,7 +7552,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7610,7 +7595,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 72879-2021</t>
+          <t>A 9145-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7624,10 +7609,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44547</v>
+        <v>44974</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7640,7 +7625,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7683,7 +7668,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 25434-2025</t>
+          <t>A 45007-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7697,10 +7682,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45800</v>
+        <v>45918</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7713,7 +7698,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7756,7 +7741,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 25435-2025</t>
+          <t>A 13268-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7770,10 +7755,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45800</v>
+        <v>45386</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7786,7 +7771,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3</v>
+        <v>6.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7829,7 +7814,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 25436-2025</t>
+          <t>A 10451-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7843,10 +7828,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45800</v>
+        <v>45366</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7858,8 +7843,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7902,7 +7892,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 26105-2025</t>
+          <t>A 47175-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7912,14 +7902,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45805</v>
+        <v>45930</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7932,7 +7922,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7975,7 +7965,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 10703-2025</t>
+          <t>A 47383-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7989,10 +7979,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45722</v>
+        <v>45930</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8005,7 +7995,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8065,7 +8055,7 @@
         <v>45930</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8121,7 +8111,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 47175-2025</t>
+          <t>A 34161-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8135,10 +8125,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45930</v>
+        <v>45845</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8151,7 +8141,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8211,7 +8201,7 @@
         <v>45930</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8267,7 +8257,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 62499-2022</t>
+          <t>A 12660-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8277,14 +8267,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44924</v>
+        <v>45000</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8296,13 +8286,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8345,7 +8330,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 47383-2025</t>
+          <t>A 22055-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8359,10 +8344,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45930</v>
+        <v>45069</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8375,7 +8360,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8418,7 +8403,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 3932-2022</t>
+          <t>A 10596-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8432,10 +8417,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44587</v>
+        <v>45366</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8448,7 +8433,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8491,7 +8476,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 1379-2025</t>
+          <t>A 52141-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8505,10 +8490,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45667</v>
+        <v>45953</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8521,7 +8506,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8564,7 +8549,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 58418-2024</t>
+          <t>A 28268-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8578,10 +8563,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45634</v>
+        <v>45099</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8594,7 +8579,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8637,7 +8622,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 44608-2023</t>
+          <t>A 850-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8651,10 +8636,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45189</v>
+        <v>44931</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8667,7 +8652,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8710,7 +8695,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 13170-2024</t>
+          <t>A 55764-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8724,10 +8709,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45386</v>
+        <v>45623</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8783,7 +8768,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 44033-2024</t>
+          <t>A 19674-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8797,10 +8782,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45572</v>
+        <v>45051</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8813,7 +8798,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8856,7 +8841,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 45180-2024</t>
+          <t>A 25594-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8866,14 +8851,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45575</v>
+        <v>45803</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8886,7 +8871,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>14.7</v>
+        <v>3.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8929,7 +8914,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 36304-2023</t>
+          <t>A 20710-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8943,10 +8928,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45152</v>
+        <v>46141</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9002,7 +8987,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 13366-2022</t>
+          <t>A 19683-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9016,10 +9001,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44645</v>
+        <v>45051</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9032,7 +9017,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9075,7 +9060,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 49256-2023</t>
+          <t>A 56365-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9089,10 +9074,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45210</v>
+        <v>45974</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9105,7 +9090,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9148,7 +9133,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 15428-2025</t>
+          <t>A 56347-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9162,10 +9147,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45747</v>
+        <v>45974</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9178,7 +9163,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.1</v>
+        <v>10.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9221,7 +9206,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 15434-2025</t>
+          <t>A 56352-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9235,10 +9220,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45747</v>
+        <v>45974</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9251,7 +9236,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.1</v>
+        <v>5.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9294,7 +9279,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 52141-2025</t>
+          <t>A 56414-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9308,10 +9293,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45953</v>
+        <v>45975</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9324,7 +9309,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9367,7 +9352,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 10596-2024</t>
+          <t>A 56340-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9381,10 +9366,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45366</v>
+        <v>45974</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9397,7 +9382,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9440,7 +9425,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 17010-2022</t>
+          <t>A 56417-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9454,10 +9439,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44676</v>
+        <v>45975</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9470,7 +9455,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9513,7 +9498,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 21285-2024</t>
+          <t>A 20811-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9527,10 +9512,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45440</v>
+        <v>46141</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9543,7 +9528,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9586,7 +9571,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 19674-2023</t>
+          <t>A 56346-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9600,10 +9585,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45051</v>
+        <v>45974</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9616,7 +9601,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.7</v>
+        <v>18.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9659,7 +9644,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 13345-2022</t>
+          <t>A 33162-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9673,10 +9658,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44645</v>
+        <v>45518</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9689,7 +9674,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9732,7 +9717,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 28390-2025</t>
+          <t>A 8765-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9746,10 +9731,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45819</v>
+        <v>44614</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9763,11 +9748,11 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9810,7 +9795,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 41721-2022</t>
+          <t>A 52352-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9824,10 +9809,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44827</v>
+        <v>45224</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9840,7 +9825,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9883,7 +9868,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 21429-2022</t>
+          <t>A 20812-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9897,10 +9882,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44706</v>
+        <v>46141</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9913,7 +9898,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9956,7 +9941,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 56365-2025</t>
+          <t>A 58517-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9970,10 +9955,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45974</v>
+        <v>45985</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9986,7 +9971,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10029,7 +10014,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 56347-2025</t>
+          <t>A 58520-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10043,10 +10028,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45974</v>
+        <v>45985</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10059,7 +10044,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>10.9</v>
+        <v>1.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10102,7 +10087,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 56352-2025</t>
+          <t>A 62510-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10116,10 +10101,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45974</v>
+        <v>44924</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10131,8 +10116,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>5.9</v>
+        <v>0.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10175,7 +10165,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 35408-2023</t>
+          <t>A 20700-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10189,10 +10179,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45146</v>
+        <v>46141</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10205,7 +10195,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10248,7 +10238,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 56346-2025</t>
+          <t>A 58766-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10262,10 +10252,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45974</v>
+        <v>45986</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10278,7 +10268,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>18.8</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10321,7 +10311,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 56340-2025</t>
+          <t>A 58767-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10335,10 +10325,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45974</v>
+        <v>45986</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10351,7 +10341,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10394,7 +10384,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 55764-2024</t>
+          <t>A 21369-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10408,10 +10398,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45623</v>
+        <v>46147</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10424,7 +10414,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10467,7 +10457,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 56169-2024</t>
+          <t>A 21376-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10481,10 +10471,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45624</v>
+        <v>46147</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10497,7 +10487,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>19.7</v>
+        <v>7.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10540,7 +10530,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 850-2023</t>
+          <t>A 60559-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10554,10 +10544,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44931</v>
+        <v>45995</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10570,7 +10560,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10613,7 +10603,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 56417-2025</t>
+          <t>A 17876-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10627,10 +10617,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45975</v>
+        <v>45758</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10643,7 +10633,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10686,7 +10676,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 56414-2025</t>
+          <t>A 22916-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10700,10 +10690,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45975</v>
+        <v>46160</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10716,7 +10706,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10759,7 +10749,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 55511-2023</t>
+          <t>A 13170-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10773,10 +10763,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45238</v>
+        <v>45386</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10789,7 +10779,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10832,7 +10822,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 58766-2025</t>
+          <t>A 22906-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10846,10 +10836,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45986</v>
+        <v>46160</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10862,7 +10852,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10905,7 +10895,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 58767-2025</t>
+          <t>A 22912-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10919,10 +10909,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45986</v>
+        <v>46160</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10935,7 +10925,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10978,7 +10968,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 58517-2025</t>
+          <t>A 62390-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10992,10 +10982,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45985</v>
+        <v>45268</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11008,7 +10998,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11051,7 +11041,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 58520-2025</t>
+          <t>A 62499-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11065,10 +11055,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45985</v>
+        <v>44924</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11080,8 +11070,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11124,7 +11119,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 36472-2023</t>
+          <t>A 3960-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11138,10 +11133,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45152</v>
+        <v>46044</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11153,8 +11148,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11197,7 +11197,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 61294-2024</t>
+          <t>A 10958-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11211,10 +11211,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45645</v>
+        <v>44628</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11270,7 +11270,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 12660-2023</t>
+          <t>A 45239-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11280,14 +11280,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45000</v>
+        <v>44844</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11299,8 +11299,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11343,7 +11348,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 62390-2023</t>
+          <t>A 15426-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11357,10 +11362,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45268</v>
+        <v>45747</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11373,7 +11378,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11416,7 +11421,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 62402-2023</t>
+          <t>A 15442-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11430,10 +11435,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45268</v>
+        <v>45747</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11446,7 +11451,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11489,7 +11494,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 60559-2025</t>
+          <t>A 5044-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11503,10 +11508,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45995</v>
+        <v>46049</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11519,7 +11524,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.5</v>
+        <v>5.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11562,7 +11567,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 31258-2025</t>
+          <t>A 10630-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11576,10 +11581,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45833</v>
+        <v>46078</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11592,7 +11597,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>5.2</v>
+        <v>0.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11635,7 +11640,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 49252-2023</t>
+          <t>A 12450-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11649,10 +11654,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45210</v>
+        <v>44638</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11665,7 +11670,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11708,7 +11713,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 31917-2022</t>
+          <t>A 11459-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11722,10 +11727,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44777</v>
+        <v>46083</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11738,7 +11743,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11781,7 +11786,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 17876-2025</t>
+          <t>A 21429-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11795,10 +11800,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45758</v>
+        <v>44706</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11811,7 +11816,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11854,7 +11859,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 12450-2022</t>
+          <t>A 11460-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11868,10 +11873,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44638</v>
+        <v>46083</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11884,7 +11889,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11927,7 +11932,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 3960-2026</t>
+          <t>A 11630-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11941,10 +11946,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46044</v>
+        <v>46084</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11962,7 +11967,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12005,7 +12010,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 32967-2025</t>
+          <t>A 56169-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12019,10 +12024,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45839</v>
+        <v>45624</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12035,7 +12040,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.9</v>
+        <v>19.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12078,7 +12083,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 5044-2026</t>
+          <t>A 25777-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12088,14 +12093,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46049</v>
+        <v>46178</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12108,7 +12113,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12151,7 +12156,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 64712-2023</t>
+          <t>A 13279-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12165,10 +12170,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45281</v>
+        <v>45386</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12181,7 +12186,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12224,7 +12229,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 39081-2022</t>
+          <t>A 49256-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12238,10 +12243,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44817</v>
+        <v>45210</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12254,7 +12259,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12297,7 +12302,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 36381-2023</t>
+          <t>A 26336-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12311,10 +12316,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45152</v>
+        <v>46182</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12327,7 +12332,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12370,7 +12375,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 13268-2024</t>
+          <t>A 26338-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12384,10 +12389,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45386</v>
+        <v>46182</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12400,7 +12405,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>6.7</v>
+        <v>1.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12443,7 +12448,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 13281-2024</t>
+          <t>A 31969-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12457,10 +12462,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45386</v>
+        <v>45119</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12516,7 +12521,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 19683-2023</t>
+          <t>A 31978-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12530,10 +12535,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45051</v>
+        <v>45119</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12546,7 +12551,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12589,7 +12594,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 58417-2024</t>
+          <t>A 39150-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12603,10 +12608,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45634</v>
+        <v>44817</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12618,13 +12623,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12667,7 +12667,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 10630-2026</t>
+          <t>A 36472-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12681,10 +12681,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46078</v>
+        <v>45152</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12740,7 +12740,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 11459-2026</t>
+          <t>A 18776-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12754,10 +12754,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46083</v>
+        <v>46128</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12813,7 +12813,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 11460-2026</t>
+          <t>A 10636-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12827,10 +12827,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46083</v>
+        <v>46078</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12886,7 +12886,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 11630-2026</t>
+          <t>A 3932-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12900,10 +12900,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46084</v>
+        <v>44587</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12913,11 +12913,6 @@
       <c r="G158" t="inlineStr">
         <is>
           <t>GÖTENE</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I158" t="n">
@@ -12964,7 +12959,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 39150-2022</t>
+          <t>A 7225-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12978,10 +12973,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44817</v>
+        <v>44970</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12994,7 +12989,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13037,7 +13032,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 6925-2023</t>
+          <t>A 35408-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13051,10 +13046,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44967</v>
+        <v>45146</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13066,13 +13061,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13115,7 +13105,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 14502-2023</t>
+          <t>A 13280-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13129,10 +13119,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45012</v>
+        <v>45386</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13145,7 +13135,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13188,7 +13178,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 58236-2024</t>
+          <t>A 31981-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13202,10 +13192,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45632</v>
+        <v>45119</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13217,13 +13207,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13266,7 +13251,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 58691-2024</t>
+          <t>A 28467-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13280,10 +13265,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45635</v>
+        <v>46197</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13295,13 +13280,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13344,7 +13324,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 10958-2022</t>
+          <t>A 55511-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13358,10 +13338,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44628</v>
+        <v>45238</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13374,7 +13354,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13417,7 +13397,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 9145-2023</t>
+          <t>A 28647-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13431,10 +13411,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44974</v>
+        <v>46198</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13447,7 +13427,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13490,7 +13470,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 13450-2025</t>
+          <t>A 28258-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13504,10 +13484,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45736</v>
+        <v>45099</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13520,7 +13500,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13563,7 +13543,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 18776-2026</t>
+          <t>A 28264-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13577,10 +13557,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46128</v>
+        <v>45099</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13593,7 +13573,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13636,7 +13616,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 7225-2023</t>
+          <t>A 49252-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13650,10 +13630,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44970</v>
+        <v>45210</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13666,7 +13646,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13709,7 +13689,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 10451-2024</t>
+          <t>A 20507-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13723,10 +13703,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45366</v>
+        <v>46140</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13738,13 +13718,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13787,7 +13762,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 30174-2022</t>
+          <t>A 30191-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13801,10 +13776,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44757</v>
+        <v>46206</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13816,8 +13791,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>5.1</v>
+        <v>6.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13860,7 +13840,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 28332-2023</t>
+          <t>A 28335-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13877,7 +13857,7 @@
         <v>45099</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13890,7 +13870,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13933,7 +13913,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 8330-2024</t>
+          <t>A 34008-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13947,10 +13927,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45352</v>
+        <v>46252</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13963,7 +13943,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14006,7 +13986,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 13279-2024</t>
+          <t>A 13281-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14023,7 +14003,7 @@
         <v>45386</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14036,7 +14016,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14079,7 +14059,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 11889-2024</t>
+          <t>A 58650-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14093,10 +14073,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45376</v>
+        <v>45251</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14109,7 +14089,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14152,7 +14132,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 15426-2025</t>
+          <t>A 36304-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14166,10 +14146,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45747</v>
+        <v>45152</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14182,7 +14162,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14225,7 +14205,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 15442-2025</t>
+          <t>A 5690-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14239,10 +14219,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45747</v>
+        <v>46051</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14255,7 +14235,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14298,7 +14278,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 13340-2022</t>
+          <t>A 59074-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14312,10 +14292,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44645</v>
+        <v>45252</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14328,7 +14308,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.9</v>
+        <v>0.3</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14371,7 +14351,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 13348-2022</t>
+          <t>A 15428-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14385,10 +14365,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44645</v>
+        <v>45747</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14401,7 +14381,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14444,7 +14424,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 22055-2023</t>
+          <t>A 15434-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14458,10 +14438,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45069</v>
+        <v>45747</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14474,7 +14454,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14517,7 +14497,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 45013-2025</t>
+          <t>A 31329-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14531,10 +14511,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45918</v>
+        <v>46219</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14547,7 +14527,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.3</v>
+        <v>7.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14590,7 +14570,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 34161-2025</t>
+          <t>A 31446-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14604,10 +14584,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45845</v>
+        <v>46220</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14620,7 +14600,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14663,7 +14643,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 1662-2025</t>
+          <t>A 31452-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14677,10 +14657,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45670</v>
+        <v>46220</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14693,7 +14673,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14736,7 +14716,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 20710-2026</t>
+          <t>A 11771-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14750,10 +14730,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46141</v>
+        <v>45373</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14766,7 +14746,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14809,7 +14789,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 20812-2026</t>
+          <t>A 58417-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14823,10 +14803,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46141</v>
+        <v>45634</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14838,8 +14818,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14882,7 +14867,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 33162-2024</t>
+          <t>A 13345-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14896,10 +14881,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45518</v>
+        <v>44645</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14912,7 +14897,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14955,7 +14940,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 20700-2026</t>
+          <t>A 31324-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14969,10 +14954,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46141</v>
+        <v>46219</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14985,7 +14970,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15028,7 +15013,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 13280-2024</t>
+          <t>A 35869-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15042,10 +15027,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45386</v>
+        <v>46266</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15058,7 +15043,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15101,7 +15086,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 25594-2025</t>
+          <t>A 35871-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15111,14 +15096,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45803</v>
+        <v>46266</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15131,7 +15116,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15174,7 +15159,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 20811-2026</t>
+          <t>A 64712-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15188,10 +15173,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46141</v>
+        <v>45281</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15204,7 +15189,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15247,7 +15232,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 21376-2026</t>
+          <t>A 39081-2022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15261,10 +15246,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46147</v>
+        <v>44817</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15277,7 +15262,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>7.2</v>
+        <v>1.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15320,7 +15305,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 28335-2023</t>
+          <t>A 61294-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15334,10 +15319,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45099</v>
+        <v>45645</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15350,7 +15335,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15393,7 +15378,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 21369-2026</t>
+          <t>A 62402-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15407,10 +15392,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46147</v>
+        <v>45268</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15423,7 +15408,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15466,7 +15451,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 12664-2023</t>
+          <t>A 1352-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15480,10 +15465,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45000</v>
+        <v>44931</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15496,7 +15481,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15539,7 +15524,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 21269-2024</t>
+          <t>A 28332-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15553,10 +15538,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45440</v>
+        <v>45099</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15569,7 +15554,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15612,7 +15597,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 28316-2024</t>
+          <t>A 44033-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15626,10 +15611,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45477</v>
+        <v>45572</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15642,7 +15627,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15685,7 +15670,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 22906-2026</t>
+          <t>A 37557-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15699,10 +15684,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46160</v>
+        <v>46276</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15715,7 +15700,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15758,7 +15743,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 22916-2026</t>
+          <t>A 32298-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15772,10 +15757,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46160</v>
+        <v>46237</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15787,8 +15772,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15831,7 +15821,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 22912-2026</t>
+          <t>A 72879-2021</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15845,10 +15835,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46160</v>
+        <v>44547</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15861,7 +15851,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15904,7 +15894,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 25777-2026</t>
+          <t>A 28267-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15914,14 +15904,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46178</v>
+        <v>45099</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15934,7 +15924,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15977,7 +15967,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 26338-2026</t>
+          <t>A 32363-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15991,10 +15981,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46182</v>
+        <v>46238</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16007,7 +15997,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.5</v>
+        <v>6.2</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16050,7 +16040,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 26336-2026</t>
+          <t>A 32364-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16064,10 +16054,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46182</v>
+        <v>46238</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16080,7 +16070,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16123,7 +16113,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 10636-2026</t>
+          <t>A 21285-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16137,10 +16127,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46078</v>
+        <v>45440</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16153,7 +16143,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16196,7 +16186,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 28647-2026</t>
+          <t>A 28316-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16210,10 +16200,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46198</v>
+        <v>45477</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16226,7 +16216,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16269,7 +16259,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 28467-2026</t>
+          <t>A 21269-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16283,10 +16273,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46197</v>
+        <v>45440</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16299,7 +16289,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16342,7 +16332,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 20507-2026</t>
+          <t>A 12664-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16356,10 +16346,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46140</v>
+        <v>45000</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16372,7 +16362,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16415,7 +16405,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 30191-2026</t>
+          <t>A 16341-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16425,14 +16415,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46206</v>
+        <v>45751</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16444,13 +16434,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>6.5</v>
+        <v>1.4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16493,7 +16478,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 34008-2026</t>
+          <t>A 10668-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16507,10 +16492,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46252</v>
+        <v>45721</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16523,7 +16508,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16566,7 +16551,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 5690-2026</t>
+          <t>A 25434-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16580,10 +16565,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46051</v>
+        <v>45800</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16596,7 +16581,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16639,7 +16624,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 31329-2026</t>
+          <t>A 25435-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16653,10 +16638,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46219</v>
+        <v>45800</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16669,7 +16654,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16712,7 +16697,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 31324-2026</t>
+          <t>A 25436-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16726,10 +16711,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46219</v>
+        <v>45800</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16742,7 +16727,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16785,7 +16770,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 35869-2026</t>
+          <t>A 26105-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16795,14 +16780,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46266</v>
+        <v>45805</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16815,7 +16800,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16858,7 +16843,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 35871-2026</t>
+          <t>A 10703-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16872,10 +16857,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46266</v>
+        <v>45722</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16888,7 +16873,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16931,7 +16916,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 31446-2026</t>
+          <t>A 28390-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16945,10 +16930,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46220</v>
+        <v>45819</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16960,8 +16945,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I213" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17004,7 +16994,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 31452-2026</t>
+          <t>A 31258-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17018,10 +17008,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46220</v>
+        <v>45833</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17034,7 +17024,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17077,7 +17067,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 37557-2026</t>
+          <t>A 32967-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17091,10 +17081,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46276</v>
+        <v>45839</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17107,7 +17097,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17150,7 +17140,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 32298-2026</t>
+          <t>A 6925-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17164,10 +17154,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46237</v>
+        <v>44967</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17181,11 +17171,11 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I216" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17228,7 +17218,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 32363-2026</t>
+          <t>A 58236-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17242,10 +17232,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46238</v>
+        <v>45632</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17257,8 +17247,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>6.2</v>
+        <v>2.3</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17301,7 +17296,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 32364-2026</t>
+          <t>A 58691-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17315,10 +17310,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46238</v>
+        <v>45635</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17330,8 +17325,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17391,7 +17391,7 @@
         <v>44862</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45352</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>45352</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>

--- a/Översikt GÖTENE.xlsx
+++ b/Översikt GÖTENE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE221"/>
+  <dimension ref="A1:AE227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44642</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45352</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1257,430 +1257,437 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
+          <t>A 39835-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>GÖTENE</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Fransig jordstjärna
+Kamjordstjärna
+Kragjordstjärna</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 39835-2026 artfynd.xlsx", "A 39835-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 39835-2026 karta.png", "A 39835-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 39835-2026 georefererad karta.tif", "A 39835-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 39835-2026 FSC-klagomål.docx", "A 39835-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 39835-2026 FSC-klagomål mail.docx", "A 39835-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 39835-2026 tillsynsbegäran.docx", "A 39835-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 39835-2026 tillsynsbegäran mail.docx", "A 39835-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>A 34562-2025</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>45847</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>GÖTENE</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E9" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>GÖTENE</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>11.1</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>2</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>2</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Rävticka
 Strimspindling</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 34562-2025 artfynd.xlsx", "A 34562-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 34562-2025 karta.png", "A 34562-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 34562-2025 georefererad karta.tif", "A 34562-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 34562-2025 FSC-klagomål.docx", "A 34562-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 34562-2025 FSC-klagomål mail.docx", "A 34562-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 34562-2025 tillsynsbegäran.docx", "A 34562-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 34562-2025 tillsynsbegäran mail.docx", "A 34562-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 34395-2025</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>45846</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>GÖTENE</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E10" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>GÖTENE</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>11.1</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>2</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>2</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>2</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Rävticka
 Strimspindling</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 34395-2025 artfynd.xlsx", "A 34395-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 34395-2025 karta.png", "A 34395-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 34395-2025 georefererad karta.tif", "A 34395-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 34395-2025 FSC-klagomål.docx", "A 34395-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 34395-2025 FSC-klagomål mail.docx", "A 34395-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 34395-2025 tillsynsbegäran.docx", "A 34395-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 34395-2025 tillsynsbegäran mail.docx", "A 34395-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 32140-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>46234</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>GÖTENE</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>GÖTENE</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>2</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>2</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Guldlockmossa
 Rostfläck</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32140-2026 artfynd.xlsx", "A 32140-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32140-2026 karta.png", "A 32140-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32140-2026 georefererad karta.tif", "A 32140-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32140-2026 FSC-klagomål.docx", "A 32140-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32140-2026 FSC-klagomål mail.docx", "A 32140-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32140-2026 tillsynsbegäran.docx", "A 32140-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32140-2026 tillsynsbegäran mail.docx", "A 32140-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 41722-2022</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44827</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>GÖTENE</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Svinrot</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 41722-2022 artfynd.xlsx", "A 41722-2022")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 41722-2022 karta.png", "A 41722-2022")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 41722-2022 georefererad karta.tif", "A 41722-2022")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 41722-2022 FSC-klagomål.docx", "A 41722-2022")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 41722-2022 FSC-klagomål mail.docx", "A 41722-2022")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 41722-2022 tillsynsbegäran.docx", "A 41722-2022")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 41722-2022 tillsynsbegäran mail.docx", "A 41722-2022")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 59103-2021</t>
+          <t>A 39839-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1694,10 +1701,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44490</v>
+        <v>46290</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1709,14 +1716,19 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1740,52 +1752,53 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Ängskovall</t>
+          <t>Fransig jordstjärna
+Kragjordstjärna</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 59103-2021 artfynd.xlsx", "A 59103-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 39839-2026 artfynd.xlsx", "A 39839-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 59103-2021 karta.png", "A 59103-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 39839-2026 karta.png", "A 39839-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 59103-2021 georefererad karta.tif", "A 59103-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 39839-2026 georefererad karta.tif", "A 39839-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 59103-2021 FSC-klagomål.docx", "A 59103-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 39839-2026 FSC-klagomål.docx", "A 39839-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 59103-2021 FSC-klagomål mail.docx", "A 59103-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 39839-2026 FSC-klagomål mail.docx", "A 39839-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 59103-2021 tillsynsbegäran.docx", "A 59103-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 39839-2026 tillsynsbegäran.docx", "A 39839-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 59103-2021 tillsynsbegäran mail.docx", "A 59103-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 39839-2026 tillsynsbegäran mail.docx", "A 39839-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41724-2022</t>
+          <t>A 41722-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1802,7 +1815,7 @@
         <v>44827</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1815,7 +1828,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1859,38 +1872,38 @@
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 41724-2022 artfynd.xlsx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 41722-2022 artfynd.xlsx", "A 41722-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 41724-2022 karta.png", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 41722-2022 karta.png", "A 41722-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 41724-2022 georefererad karta.tif", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 41722-2022 georefererad karta.tif", "A 41722-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 41724-2022 FSC-klagomål.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 41722-2022 FSC-klagomål.docx", "A 41722-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 41724-2022 FSC-klagomål mail.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 41722-2022 FSC-klagomål mail.docx", "A 41722-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 41724-2022 tillsynsbegäran.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 41722-2022 tillsynsbegäran.docx", "A 41722-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 41724-2022 tillsynsbegäran mail.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 41722-2022 tillsynsbegäran mail.docx", "A 41722-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 45211-2022</t>
+          <t>A 59103-2021</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1904,10 +1917,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44844</v>
+        <v>44490</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1920,13 +1933,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1960,42 +1973,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Ängskovall</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 45211-2022 artfynd.xlsx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 59103-2021 artfynd.xlsx", "A 59103-2021")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 45211-2022 karta.png", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 59103-2021 karta.png", "A 59103-2021")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 45211-2022 georefererad karta.tif", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 59103-2021 georefererad karta.tif", "A 59103-2021")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 45211-2022 FSC-klagomål.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 59103-2021 FSC-klagomål.docx", "A 59103-2021")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 45211-2022 FSC-klagomål mail.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 59103-2021 FSC-klagomål mail.docx", "A 59103-2021")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 45211-2022 tillsynsbegäran.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 59103-2021 tillsynsbegäran.docx", "A 59103-2021")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 45211-2022 tillsynsbegäran mail.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 59103-2021 tillsynsbegäran mail.docx", "A 59103-2021")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 18647-2025</t>
+          <t>A 5086-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2009,10 +2022,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45763</v>
+        <v>45330</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2024,13 +2037,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2063,49 +2071,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
         <v>1</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 18647-2025 artfynd.xlsx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 5086-2024 artfynd.xlsx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 18647-2025 karta.png", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 5086-2024 karta.png", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 18647-2025 georefererad karta.tif", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 5086-2024 georefererad karta.tif", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 18647-2025 FSC-klagomål.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 5086-2024 FSC-klagomål.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 18647-2025 FSC-klagomål mail.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 5086-2024 FSC-klagomål mail.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 18647-2025 tillsynsbegäran.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 5086-2024 tillsynsbegäran.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 18647-2025 tillsynsbegäran mail.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 5086-2024 tillsynsbegäran mail.docx", "A 5086-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 47393-2025</t>
+          <t>A 28273-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2119,10 +2127,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45930</v>
+        <v>45099</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2135,16 +2143,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2159,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2175,42 +2183,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Korallticka</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 47393-2025 artfynd.xlsx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 28273-2023 artfynd.xlsx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 47393-2025 karta.png", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 28273-2023 karta.png", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 47393-2025 georefererad karta.tif", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 28273-2023 georefererad karta.tif", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 47393-2025 FSC-klagomål.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 28273-2023 FSC-klagomål.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 47393-2025 FSC-klagomål mail.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 28273-2023 FSC-klagomål mail.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 47393-2025 tillsynsbegäran.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 28273-2023 tillsynsbegäran.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 47393-2025 tillsynsbegäran mail.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 28273-2023 tillsynsbegäran mail.docx", "A 28273-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 50366-2025</t>
+          <t>A 47393-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2224,10 +2232,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45944</v>
+        <v>45930</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2284,38 +2292,38 @@
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 50366-2025 artfynd.xlsx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 47393-2025 artfynd.xlsx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 50366-2025 karta.png", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 47393-2025 karta.png", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 50366-2025 georefererad karta.tif", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 47393-2025 georefererad karta.tif", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 50366-2025 FSC-klagomål.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 47393-2025 FSC-klagomål.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 50366-2025 FSC-klagomål mail.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 47393-2025 FSC-klagomål mail.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 50366-2025 tillsynsbegäran.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 47393-2025 tillsynsbegäran.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 50366-2025 tillsynsbegäran mail.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 47393-2025 tillsynsbegäran mail.docx", "A 47393-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 19083-2022</t>
+          <t>A 50366-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2329,10 +2337,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44691</v>
+        <v>45944</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2345,19 +2353,19 @@
         </is>
       </c>
       <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2372,7 +2380,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2381,46 +2389,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Läderbagge</t>
+          <t>Korallticka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 19083-2022 artfynd.xlsx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 50366-2025 artfynd.xlsx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 19083-2022 karta.png", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 50366-2025 karta.png", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 19083-2022 georefererad karta.tif", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 50366-2025 georefererad karta.tif", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 19083-2022 FSC-klagomål.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 50366-2025 FSC-klagomål.docx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 19083-2022 FSC-klagomål mail.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 50366-2025 FSC-klagomål mail.docx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 19083-2022 tillsynsbegäran.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 50366-2025 tillsynsbegäran.docx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 19083-2022 tillsynsbegäran mail.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 50366-2025 tillsynsbegäran mail.docx", "A 50366-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 14296-2023</t>
+          <t>A 41724-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2434,10 +2442,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45011</v>
+        <v>44827</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2450,19 +2458,19 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2477,7 +2485,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2486,50 +2494,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Pilgrimsfalk</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 14296-2023 artfynd.xlsx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 41724-2022 artfynd.xlsx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 14296-2023 karta.png", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 41724-2022 karta.png", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 14296-2023 georefererad karta.tif", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 41724-2022 georefererad karta.tif", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 14296-2023 FSC-klagomål.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 41724-2022 FSC-klagomål.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 14296-2023 FSC-klagomål mail.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 41724-2022 FSC-klagomål mail.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 14296-2023 tillsynsbegäran.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 41724-2022 tillsynsbegäran.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 14296-2023 tillsynsbegäran mail.docx", "A 14296-2023")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 14296-2023 prioriterade fågelarter.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 41724-2022 tillsynsbegäran mail.docx", "A 41724-2022")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 31326-2026</t>
+          <t>A 18647-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2543,10 +2547,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46219</v>
+        <v>45763</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2558,17 +2562,22 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2583,7 +2592,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2599,46 +2608,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 31326-2026 artfynd.xlsx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 18647-2025 artfynd.xlsx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 31326-2026 karta.png", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 18647-2025 karta.png", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 31326-2026 georefererad karta.tif", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 18647-2025 georefererad karta.tif", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 31326-2026 FSC-klagomål.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 18647-2025 FSC-klagomål.docx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 31326-2026 FSC-klagomål mail.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 18647-2025 FSC-klagomål mail.docx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 31326-2026 tillsynsbegäran.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 18647-2025 tillsynsbegäran.docx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 31326-2026 tillsynsbegäran mail.docx", "A 31326-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 31326-2026 prioriterade fågelarter.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 18647-2025 tillsynsbegäran mail.docx", "A 18647-2025")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 5086-2024</t>
+          <t>A 32909-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2652,10 +2657,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45330</v>
+        <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2668,17 +2673,17 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
@@ -2692,7 +2697,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2701,49 +2706,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 5086-2024 artfynd.xlsx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32909-2025 artfynd.xlsx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 5086-2024 karta.png", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32909-2025 karta.png", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 5086-2024 georefererad karta.tif", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32909-2025 georefererad karta.tif", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 5086-2024 FSC-klagomål.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32909-2025 FSC-klagomål.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 5086-2024 FSC-klagomål mail.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32909-2025 FSC-klagomål mail.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 5086-2024 tillsynsbegäran.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32909-2025 tillsynsbegäran.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 5086-2024 tillsynsbegäran mail.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32909-2025 tillsynsbegäran mail.docx", "A 32909-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 28273-2023</t>
+          <t>A 14296-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2757,10 +2762,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45099</v>
+        <v>45011</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2773,7 +2778,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5.1</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2785,7 +2790,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2797,10 +2802,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2809,46 +2814,50 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Pilgrimsfalk</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 28273-2023 artfynd.xlsx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 14296-2023 artfynd.xlsx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 28273-2023 karta.png", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 14296-2023 karta.png", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 28273-2023 georefererad karta.tif", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 14296-2023 georefererad karta.tif", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 28273-2023 FSC-klagomål.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 14296-2023 FSC-klagomål.docx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 28273-2023 FSC-klagomål mail.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 14296-2023 FSC-klagomål mail.docx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 28273-2023 tillsynsbegäran.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 14296-2023 tillsynsbegäran.docx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 28273-2023 tillsynsbegäran mail.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 14296-2023 tillsynsbegäran mail.docx", "A 14296-2023")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 14296-2023 prioriterade fågelarter.docx", "A 14296-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32224-2026</t>
+          <t>A 19083-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2862,10 +2871,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46237</v>
+        <v>44691</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2878,19 +2887,19 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2905,7 +2914,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2914,46 +2923,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Backmåra</t>
+          <t>Läderbagge</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32224-2026 artfynd.xlsx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 19083-2022 artfynd.xlsx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32224-2026 karta.png", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 19083-2022 karta.png", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32224-2026 georefererad karta.tif", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 19083-2022 georefererad karta.tif", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32224-2026 FSC-klagomål.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 19083-2022 FSC-klagomål.docx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32224-2026 FSC-klagomål mail.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 19083-2022 FSC-klagomål mail.docx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32224-2026 tillsynsbegäran.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 19083-2022 tillsynsbegäran.docx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32224-2026 tillsynsbegäran mail.docx", "A 32224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 19083-2022 tillsynsbegäran mail.docx", "A 19083-2022")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 33478-2026</t>
+          <t>A 31326-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2967,10 +2976,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46247</v>
+        <v>46219</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2983,17 +2992,17 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3007,7 +3016,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3023,42 +3032,46 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 33478-2026 artfynd.xlsx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 31326-2026 artfynd.xlsx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 33478-2026 karta.png", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 31326-2026 karta.png", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 33478-2026 georefererad karta.tif", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 31326-2026 georefererad karta.tif", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 33478-2026 FSC-klagomål.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 31326-2026 FSC-klagomål.docx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 33478-2026 FSC-klagomål mail.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 31326-2026 FSC-klagomål mail.docx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 33478-2026 tillsynsbegäran.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 31326-2026 tillsynsbegäran.docx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 33478-2026 tillsynsbegäran mail.docx", "A 33478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 31326-2026 tillsynsbegäran mail.docx", "A 31326-2026")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 31326-2026 prioriterade fågelarter.docx", "A 31326-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32909-2025</t>
+          <t>A 45211-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3072,10 +3085,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45839</v>
+        <v>44844</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3088,16 +3101,16 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3112,7 +3125,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3124,63 +3137,63 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32909-2025 artfynd.xlsx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 45211-2022 artfynd.xlsx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32909-2025 karta.png", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 45211-2022 karta.png", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32909-2025 georefererad karta.tif", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 45211-2022 georefererad karta.tif", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32909-2025 FSC-klagomål.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 45211-2022 FSC-klagomål.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32909-2025 FSC-klagomål mail.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 45211-2022 FSC-klagomål mail.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32909-2025 tillsynsbegäran.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 45211-2022 tillsynsbegäran.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32909-2025 tillsynsbegäran mail.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 45211-2022 tillsynsbegäran mail.docx", "A 45211-2022")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S 840-2024</t>
+          <t>A 32224-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45372</v>
+        <v>46237</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3193,7 +3206,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>55.4</v>
+        <v>1.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3229,46 +3242,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Backmåra</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/S 840-2024 artfynd.xlsx", "S 840-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32224-2026 artfynd.xlsx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/S 840-2024 karta.png", "S 840-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32224-2026 karta.png", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/S 840-2024 georefererad karta.tif", "S 840-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32224-2026 georefererad karta.tif", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/S 840-2024 FSC-klagomål.docx", "S 840-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32224-2026 FSC-klagomål.docx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/S 840-2024 FSC-klagomål mail.docx", "S 840-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32224-2026 FSC-klagomål mail.docx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/S 840-2024 tillsynsbegäran.docx", "S 840-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32224-2026 tillsynsbegäran.docx", "A 32224-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/S 840-2024 tillsynsbegäran mail.docx", "S 840-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32224-2026 tillsynsbegäran mail.docx", "A 32224-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 562-2022</t>
+          <t>A 33478-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3282,10 +3295,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44566</v>
+        <v>46247</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3298,13 +3311,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3328,37 +3341,69 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
-      <c r="V27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Rödbrun jordstjärna</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 33478-2026 artfynd.xlsx", "A 33478-2026")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 33478-2026 karta.png", "A 33478-2026")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 33478-2026 georefererad karta.tif", "A 33478-2026")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 33478-2026 FSC-klagomål.docx", "A 33478-2026")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 33478-2026 FSC-klagomål mail.docx", "A 33478-2026")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 33478-2026 tillsynsbegäran.docx", "A 33478-2026")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 33478-2026 tillsynsbegäran mail.docx", "A 33478-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 59086-2021</t>
+          <t>S 840-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44490</v>
+        <v>45372</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3371,7 +3416,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>55.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3380,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3395,26 +3440,58 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Kandelabersvamp</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/S 840-2024 artfynd.xlsx", "S 840-2024")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/S 840-2024 karta.png", "S 840-2024")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/S 840-2024 georefererad karta.tif", "S 840-2024")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/S 840-2024 FSC-klagomål.docx", "S 840-2024")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/S 840-2024 FSC-klagomål mail.docx", "S 840-2024")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/S 840-2024 tillsynsbegäran.docx", "S 840-2024")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/S 840-2024 tillsynsbegäran mail.docx", "S 840-2024")</f>
+        <v/>
+      </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 13357-2022</t>
+          <t>A 562-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3428,10 +3505,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44645</v>
+        <v>44566</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3444,7 +3521,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3487,7 +3564,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13342-2022</t>
+          <t>A 59086-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3501,10 +3578,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44645</v>
+        <v>44490</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3517,7 +3594,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3560,7 +3637,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 59088-2021</t>
+          <t>A 13357-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3574,10 +3651,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44490</v>
+        <v>44645</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3590,7 +3667,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3633,7 +3710,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 59108-2021</t>
+          <t>A 13342-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3647,10 +3724,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44490</v>
+        <v>44645</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3663,7 +3740,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3706,7 +3783,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 3708-2022</t>
+          <t>A 59088-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3720,10 +3797,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44586</v>
+        <v>44490</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3779,7 +3856,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 63200-2021</t>
+          <t>A 59108-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3793,10 +3870,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44507</v>
+        <v>44490</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3809,7 +3886,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3852,7 +3929,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 8786-2022</t>
+          <t>A 3708-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3866,10 +3943,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44614</v>
+        <v>44586</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3881,13 +3958,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>8.1</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3930,7 +4002,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 16742-2022</t>
+          <t>A 63200-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3944,10 +4016,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44673</v>
+        <v>44507</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3960,7 +4032,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4003,7 +4075,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 48733-2022</t>
+          <t>A 8786-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4017,10 +4089,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44859</v>
+        <v>44614</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4032,8 +4104,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>8.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4076,7 +4153,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 44507-2022</t>
+          <t>A 16742-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4090,10 +4167,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44840</v>
+        <v>44673</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4106,7 +4183,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4149,7 +4226,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 561-2022</t>
+          <t>A 48733-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4163,10 +4240,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44566</v>
+        <v>44859</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4179,7 +4256,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4222,7 +4299,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 18124-2022</t>
+          <t>A 44507-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4236,10 +4313,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44684</v>
+        <v>44840</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4252,7 +4329,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4295,7 +4372,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 56157-2021</t>
+          <t>A 561-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4309,10 +4386,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44477</v>
+        <v>44566</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4325,7 +4402,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4368,7 +4445,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 63198-2021</t>
+          <t>A 18124-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4382,10 +4459,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44507</v>
+        <v>44684</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4398,7 +4475,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4441,7 +4518,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 2984-2022</t>
+          <t>A 56157-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4455,10 +4532,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44581</v>
+        <v>44477</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4471,7 +4548,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4514,7 +4591,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30432-2022</t>
+          <t>A 63198-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4528,10 +4605,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44761</v>
+        <v>44507</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4544,7 +4621,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4587,7 +4664,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30128-2022</t>
+          <t>A 2984-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4601,10 +4678,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44757</v>
+        <v>44581</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4617,7 +4694,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4660,7 +4737,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 51451-2022</t>
+          <t>A 30432-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4674,10 +4751,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44869</v>
+        <v>44761</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4690,7 +4767,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4733,7 +4810,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 38195-2022</t>
+          <t>A 30128-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4747,10 +4824,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44812</v>
+        <v>44757</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4762,13 +4839,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4811,7 +4883,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 46381-2022</t>
+          <t>A 51451-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4825,10 +4897,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44848</v>
+        <v>44869</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4840,13 +4912,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4889,7 +4956,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 49968-2022</t>
+          <t>A 38195-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4903,10 +4970,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44865</v>
+        <v>44812</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4918,8 +4985,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4962,7 +5034,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 59114-2021</t>
+          <t>A 46381-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4976,10 +5048,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44490</v>
+        <v>44848</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4991,8 +5063,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5035,7 +5112,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 6969-2022</t>
+          <t>A 49968-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5049,10 +5126,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44603</v>
+        <v>44865</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5065,7 +5142,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5108,7 +5185,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 55496-2021</t>
+          <t>A 59114-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5122,10 +5199,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44475</v>
+        <v>44490</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5138,7 +5215,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.8</v>
+        <v>0.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5181,7 +5258,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 36244-2022</t>
+          <t>A 6969-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5195,10 +5272,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44803</v>
+        <v>44603</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5211,7 +5288,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5254,7 +5331,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 61148-2021</t>
+          <t>A 55496-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5268,10 +5345,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44498</v>
+        <v>44475</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5284,7 +5361,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.3</v>
+        <v>3.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5327,7 +5404,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38945-2022</t>
+          <t>A 36244-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5341,10 +5418,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44816</v>
+        <v>44803</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5357,7 +5434,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5400,7 +5477,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 58418-2024</t>
+          <t>A 38945-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5414,10 +5491,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45634</v>
+        <v>44816</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5430,7 +5507,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5473,7 +5550,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 36381-2023</t>
+          <t>A 61148-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5487,10 +5564,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45152</v>
+        <v>44498</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5503,7 +5580,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5546,7 +5623,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8330-2024</t>
+          <t>A 9607-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5560,10 +5637,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45352</v>
+        <v>45361</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5576,7 +5653,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5619,7 +5696,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 13276-2024</t>
+          <t>A 58650-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5633,10 +5710,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45386</v>
+        <v>45251</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5649,7 +5726,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5692,7 +5769,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 849-2023</t>
+          <t>A 45239-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5706,10 +5783,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44931</v>
+        <v>44844</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5721,8 +5798,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5765,7 +5847,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 44608-2023</t>
+          <t>A 52352-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5779,10 +5861,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45189</v>
+        <v>45224</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5795,7 +5877,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5838,7 +5920,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 41721-2022</t>
+          <t>A 28264-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5852,10 +5934,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44827</v>
+        <v>45099</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5868,7 +5950,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5911,7 +5993,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 11889-2024</t>
+          <t>A 28268-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5925,10 +6007,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45376</v>
+        <v>45099</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5941,7 +6023,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5984,7 +6066,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 11772-2024</t>
+          <t>A 13276-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5998,10 +6080,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45373</v>
+        <v>45386</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6014,7 +6096,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6057,7 +6139,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 11773-2024</t>
+          <t>A 61194-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6071,10 +6153,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45373</v>
+        <v>45645</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6086,8 +6168,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6130,7 +6217,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 31917-2022</t>
+          <t>A 1352-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6144,10 +6231,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44777</v>
+        <v>44931</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6160,7 +6247,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6203,7 +6290,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 17010-2022</t>
+          <t>A 28267-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6217,10 +6304,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44676</v>
+        <v>45099</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6233,7 +6320,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6276,7 +6363,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 61021-2022</t>
+          <t>A 39998-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6286,14 +6373,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44914</v>
+        <v>45894</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6306,7 +6393,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6349,7 +6436,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 30205-2023</t>
+          <t>A 3960-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6363,10 +6450,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45110</v>
+        <v>46044</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6378,8 +6465,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>6.8</v>
+        <v>3.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6422,7 +6514,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 22278-2024</t>
+          <t>A 72879-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6436,10 +6528,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45446</v>
+        <v>44547</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6452,7 +6544,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6495,7 +6587,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 1379-2025</t>
+          <t>A 5044-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6509,10 +6601,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45667</v>
+        <v>46049</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6525,7 +6617,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>5.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6568,7 +6660,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 17069-2023</t>
+          <t>A 62499-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6582,10 +6674,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45034</v>
+        <v>44924</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6597,8 +6689,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6641,7 +6738,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13450-2025</t>
+          <t>A 45007-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6655,10 +6752,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45736</v>
+        <v>45918</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6671,7 +6768,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6714,7 +6811,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 45180-2024</t>
+          <t>A 3932-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6728,10 +6825,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45575</v>
+        <v>44587</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6744,7 +6841,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>14.7</v>
+        <v>1.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6787,7 +6884,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 61194-2024</t>
+          <t>A 25434-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6801,10 +6898,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45645</v>
+        <v>45800</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6816,13 +6913,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6865,7 +6957,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 14502-2023</t>
+          <t>A 25435-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6879,10 +6971,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45012</v>
+        <v>45800</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6895,7 +6987,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6938,7 +7030,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13340-2022</t>
+          <t>A 25436-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6952,10 +7044,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44645</v>
+        <v>45800</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6968,7 +7060,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7011,7 +7103,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 13348-2022</t>
+          <t>A 47385-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7025,10 +7117,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44645</v>
+        <v>45930</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7041,7 +7133,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7084,7 +7176,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 13366-2022</t>
+          <t>A 10630-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7098,10 +7190,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44645</v>
+        <v>46078</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7114,7 +7206,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7157,7 +7249,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 45013-2025</t>
+          <t>A 47175-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7171,10 +7263,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45918</v>
+        <v>45930</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7187,7 +7279,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7230,7 +7322,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 15646-2023</t>
+          <t>A 47389-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7244,10 +7336,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45021</v>
+        <v>45930</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7352,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7303,7 +7395,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 1662-2025</t>
+          <t>A 47383-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7317,10 +7409,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45670</v>
+        <v>45930</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7333,7 +7425,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7376,7 +7468,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 39998-2025</t>
+          <t>A 11459-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7390,10 +7482,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45894</v>
+        <v>46083</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7406,7 +7498,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7449,7 +7541,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 9607-2024</t>
+          <t>A 26105-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7459,14 +7551,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45361</v>
+        <v>45805</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7479,7 +7571,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7522,7 +7614,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 30174-2022</t>
+          <t>A 11460-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7536,10 +7628,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44757</v>
+        <v>46083</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7552,7 +7644,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7595,7 +7687,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 9145-2023</t>
+          <t>A 11630-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7609,10 +7701,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44974</v>
+        <v>46084</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7622,6 +7714,11 @@
       <c r="G86" t="inlineStr">
         <is>
           <t>GÖTENE</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I86" t="n">
@@ -7668,7 +7765,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 45007-2025</t>
+          <t>A 10703-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7682,10 +7779,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45918</v>
+        <v>45722</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7698,7 +7795,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7741,7 +7838,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 13268-2024</t>
+          <t>A 58418-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7755,10 +7852,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45386</v>
+        <v>45634</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7771,7 +7868,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>6.7</v>
+        <v>0.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7814,7 +7911,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 10451-2024</t>
+          <t>A 13170-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7828,10 +7925,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45366</v>
+        <v>45386</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7843,13 +7940,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7892,7 +7984,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 47175-2025</t>
+          <t>A 45180-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7906,10 +7998,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45930</v>
+        <v>45575</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7922,7 +8014,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.9</v>
+        <v>14.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7965,7 +8057,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 47383-2025</t>
+          <t>A 36304-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7979,10 +8071,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45930</v>
+        <v>45152</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7995,7 +8087,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8038,7 +8130,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 47385-2025</t>
+          <t>A 49256-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8052,10 +8144,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45930</v>
+        <v>45210</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8068,7 +8160,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8111,7 +8203,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 34161-2025</t>
+          <t>A 10596-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8125,10 +8217,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45845</v>
+        <v>45366</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8141,7 +8233,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.7</v>
+        <v>0.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8184,7 +8276,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 47389-2025</t>
+          <t>A 21285-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8198,10 +8290,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45930</v>
+        <v>45440</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8214,7 +8306,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8257,7 +8349,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 12660-2023</t>
+          <t>A 52141-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8267,14 +8359,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45000</v>
+        <v>45953</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8287,7 +8379,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8330,7 +8422,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 22055-2023</t>
+          <t>A 41721-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8344,10 +8436,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45069</v>
+        <v>44827</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8360,7 +8452,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8403,7 +8495,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 10596-2024</t>
+          <t>A 55764-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8417,10 +8509,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45366</v>
+        <v>45623</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8433,7 +8525,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8476,7 +8568,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 52141-2025</t>
+          <t>A 56169-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8490,10 +8582,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45953</v>
+        <v>45624</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8506,7 +8598,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.1</v>
+        <v>19.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8549,7 +8641,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 28268-2023</t>
+          <t>A 850-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8563,10 +8655,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45099</v>
+        <v>44931</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8579,7 +8671,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8622,7 +8714,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 850-2023</t>
+          <t>A 56365-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8636,10 +8728,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44931</v>
+        <v>45974</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8652,7 +8744,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8695,7 +8787,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 55764-2024</t>
+          <t>A 56347-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8709,10 +8801,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45623</v>
+        <v>45974</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8725,7 +8817,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.7</v>
+        <v>10.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8768,7 +8860,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 19674-2023</t>
+          <t>A 56352-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8782,10 +8874,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45051</v>
+        <v>45974</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8798,7 +8890,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.7</v>
+        <v>5.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8841,7 +8933,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 25594-2025</t>
+          <t>A 56346-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8851,14 +8943,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45803</v>
+        <v>45974</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8871,7 +8963,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.2</v>
+        <v>18.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8914,7 +9006,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 20710-2026</t>
+          <t>A 56340-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8928,10 +9020,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46141</v>
+        <v>45974</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8944,7 +9036,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8987,7 +9079,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 19683-2023</t>
+          <t>A 56417-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9001,10 +9093,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45051</v>
+        <v>45975</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9017,7 +9109,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9060,7 +9152,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 56365-2025</t>
+          <t>A 18776-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9074,10 +9166,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45974</v>
+        <v>46128</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9090,7 +9182,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9133,7 +9225,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 56347-2025</t>
+          <t>A 61294-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9147,10 +9239,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45974</v>
+        <v>45645</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9163,7 +9255,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>10.9</v>
+        <v>0.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9206,7 +9298,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 56352-2025</t>
+          <t>A 56414-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9220,10 +9312,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9236,7 +9328,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>5.9</v>
+        <v>3.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9279,7 +9371,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 56414-2025</t>
+          <t>A 12660-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9289,14 +9381,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45975</v>
+        <v>45000</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9309,7 +9401,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9352,7 +9444,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 56340-2025</t>
+          <t>A 58766-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9366,10 +9458,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45974</v>
+        <v>45986</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9382,7 +9474,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9425,7 +9517,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 56417-2025</t>
+          <t>A 58767-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9439,10 +9531,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45975</v>
+        <v>45986</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9455,7 +9547,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9498,7 +9590,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 20811-2026</t>
+          <t>A 58517-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9512,10 +9604,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46141</v>
+        <v>45985</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9528,7 +9620,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9571,7 +9663,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 56346-2025</t>
+          <t>A 58520-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9585,10 +9677,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45974</v>
+        <v>45985</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9601,7 +9693,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>18.8</v>
+        <v>1.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9644,7 +9736,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 33162-2024</t>
+          <t>A 62390-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9658,10 +9750,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45518</v>
+        <v>45268</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9674,7 +9766,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9717,7 +9809,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 8765-2022</t>
+          <t>A 62402-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9731,10 +9823,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44614</v>
+        <v>45268</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9746,13 +9838,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9795,7 +9882,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 52352-2023</t>
+          <t>A 11771-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9809,10 +9896,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45224</v>
+        <v>45373</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9825,7 +9912,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9868,7 +9955,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 20812-2026</t>
+          <t>A 31981-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9882,10 +9969,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46141</v>
+        <v>45119</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9898,7 +9985,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9941,7 +10028,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 58517-2025</t>
+          <t>A 60559-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9955,10 +10042,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45985</v>
+        <v>45995</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9971,7 +10058,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10014,7 +10101,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 58520-2025</t>
+          <t>A 30174-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10028,10 +10115,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45985</v>
+        <v>44757</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10044,7 +10131,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10087,7 +10174,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 62510-2022</t>
+          <t>A 15646-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10101,10 +10188,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44924</v>
+        <v>45021</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10116,13 +10203,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10165,7 +10247,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 20700-2026</t>
+          <t>A 28390-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10179,10 +10261,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46141</v>
+        <v>45819</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10194,8 +10276,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10238,7 +10325,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 58766-2025</t>
+          <t>A 45013-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10252,10 +10339,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45986</v>
+        <v>45918</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10268,7 +10355,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10311,7 +10398,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 58767-2025</t>
+          <t>A 34161-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10325,10 +10412,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45986</v>
+        <v>45845</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10341,7 +10428,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10384,7 +10471,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 21369-2026</t>
+          <t>A 1662-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10398,10 +10485,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46147</v>
+        <v>45670</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10414,7 +10501,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10457,7 +10544,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 21376-2026</t>
+          <t>A 20710-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10471,10 +10558,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46147</v>
+        <v>46141</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10487,7 +10574,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>7.2</v>
+        <v>1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10530,7 +10617,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 60559-2025</t>
+          <t>A 20812-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10544,10 +10631,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45995</v>
+        <v>46141</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10560,7 +10647,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10603,7 +10690,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 17876-2025</t>
+          <t>A 33162-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10617,10 +10704,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45758</v>
+        <v>45518</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10633,7 +10720,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10676,7 +10763,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 22916-2026</t>
+          <t>A 20700-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10690,10 +10777,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46160</v>
+        <v>46141</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10706,7 +10793,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10749,7 +10836,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 13170-2024</t>
+          <t>A 62510-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10763,10 +10850,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45386</v>
+        <v>44924</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10778,8 +10865,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10822,7 +10914,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 22906-2026</t>
+          <t>A 61021-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10832,14 +10924,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46160</v>
+        <v>44914</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10852,7 +10944,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10895,7 +10987,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 22912-2026</t>
+          <t>A 25594-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10905,14 +10997,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46160</v>
+        <v>45803</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10925,7 +11017,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10968,7 +11060,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 62390-2023</t>
+          <t>A 849-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10982,10 +11074,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45268</v>
+        <v>44931</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10998,7 +11090,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11041,7 +11133,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 62499-2022</t>
+          <t>A 20811-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11055,10 +11147,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44924</v>
+        <v>46141</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11070,13 +11162,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11119,7 +11206,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 3960-2026</t>
+          <t>A 21376-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11133,10 +11220,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46044</v>
+        <v>46147</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11148,13 +11235,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>3.7</v>
+        <v>7.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11197,7 +11279,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 10958-2022</t>
+          <t>A 21369-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11211,10 +11293,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44628</v>
+        <v>46147</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11227,7 +11309,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11270,7 +11352,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 45239-2022</t>
+          <t>A 31969-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11284,10 +11366,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44844</v>
+        <v>45119</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11299,13 +11381,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11348,7 +11425,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 15426-2025</t>
+          <t>A 31978-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11362,10 +11439,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45747</v>
+        <v>45119</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11378,7 +11455,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11421,7 +11498,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 15442-2025</t>
+          <t>A 31258-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11435,10 +11512,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45747</v>
+        <v>45833</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11451,7 +11528,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.2</v>
+        <v>5.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11494,7 +11571,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 5044-2026</t>
+          <t>A 28258-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11508,10 +11585,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46049</v>
+        <v>45099</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11524,7 +11601,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11567,7 +11644,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 10630-2026</t>
+          <t>A 22906-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11581,10 +11658,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46078</v>
+        <v>46160</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11597,7 +11674,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11640,7 +11717,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 12450-2022</t>
+          <t>A 22916-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11654,10 +11731,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44638</v>
+        <v>46160</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11670,7 +11747,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11713,7 +11790,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 11459-2026</t>
+          <t>A 22912-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11727,10 +11804,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46083</v>
+        <v>46160</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11743,7 +11820,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11786,7 +11863,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 21429-2022</t>
+          <t>A 22278-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11800,10 +11877,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44706</v>
+        <v>45446</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11816,7 +11893,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11859,7 +11936,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 11460-2026</t>
+          <t>A 32967-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11873,10 +11950,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46083</v>
+        <v>45839</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11889,7 +11966,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11932,7 +12009,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 11630-2026</t>
+          <t>A 17069-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11946,10 +12023,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46084</v>
+        <v>45034</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11961,13 +12038,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12010,7 +12082,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 56169-2024</t>
+          <t>A 59074-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12024,10 +12096,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45624</v>
+        <v>45252</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12040,7 +12112,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>19.7</v>
+        <v>0.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12083,7 +12155,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 25777-2026</t>
+          <t>A 6925-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12093,14 +12165,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46178</v>
+        <v>44967</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12112,8 +12184,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12156,7 +12233,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 13279-2024</t>
+          <t>A 58236-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12170,10 +12247,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45386</v>
+        <v>45632</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12185,8 +12262,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12229,7 +12311,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 49256-2023</t>
+          <t>A 58691-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12243,10 +12325,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45210</v>
+        <v>45635</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12258,8 +12340,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12302,7 +12389,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 26336-2026</t>
+          <t>A 11772-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12316,10 +12403,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46182</v>
+        <v>45373</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12332,7 +12419,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12375,7 +12462,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 26338-2026</t>
+          <t>A 11773-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12389,10 +12476,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46182</v>
+        <v>45373</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12405,7 +12492,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12448,7 +12535,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 31969-2023</t>
+          <t>A 8765-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12462,10 +12549,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45119</v>
+        <v>44614</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12477,8 +12564,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12521,7 +12613,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 31978-2023</t>
+          <t>A 30205-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12535,10 +12627,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45119</v>
+        <v>45110</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12551,7 +12643,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.2</v>
+        <v>6.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12594,7 +12686,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 39150-2022</t>
+          <t>A 25777-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12604,14 +12696,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44817</v>
+        <v>46178</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12624,7 +12716,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12667,7 +12759,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 36472-2023</t>
+          <t>A 26338-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12681,10 +12773,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45152</v>
+        <v>46182</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12740,7 +12832,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 18776-2026</t>
+          <t>A 13450-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12754,10 +12846,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46128</v>
+        <v>45736</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12770,7 +12862,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12830,7 +12922,7 @@
         <v>46078</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12886,7 +12978,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 3932-2022</t>
+          <t>A 1379-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12900,10 +12992,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44587</v>
+        <v>45667</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12916,7 +13008,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12959,7 +13051,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 7225-2023</t>
+          <t>A 28647-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12973,10 +13065,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44970</v>
+        <v>46198</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12989,7 +13081,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13032,7 +13124,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 35408-2023</t>
+          <t>A 28467-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13046,10 +13138,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45146</v>
+        <v>46197</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13062,7 +13154,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13105,7 +13197,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 13280-2024</t>
+          <t>A 44608-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13119,10 +13211,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45386</v>
+        <v>45189</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13135,7 +13227,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13178,7 +13270,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 31981-2023</t>
+          <t>A 44033-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13192,10 +13284,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45119</v>
+        <v>45572</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13208,7 +13300,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13251,7 +13343,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 28467-2026</t>
+          <t>A 13366-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13265,10 +13357,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46197</v>
+        <v>44645</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13281,7 +13373,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13324,7 +13416,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 55511-2023</t>
+          <t>A 15428-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13338,10 +13430,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45238</v>
+        <v>45747</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13354,7 +13446,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3.6</v>
+        <v>0.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13397,7 +13489,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 28647-2026</t>
+          <t>A 15434-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13411,10 +13503,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46198</v>
+        <v>45747</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13427,7 +13519,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13470,7 +13562,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 28258-2023</t>
+          <t>A 20507-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13484,10 +13576,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45099</v>
+        <v>46140</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13500,7 +13592,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13543,7 +13635,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 28264-2023</t>
+          <t>A 17010-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13557,10 +13649,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45099</v>
+        <v>44676</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13573,7 +13665,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13616,7 +13708,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 49252-2023</t>
+          <t>A 30191-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13630,10 +13722,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45210</v>
+        <v>46206</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13645,8 +13737,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>0.4</v>
+        <v>6.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13689,7 +13786,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 20507-2026</t>
+          <t>A 34008-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13703,10 +13800,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46140</v>
+        <v>46252</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13719,7 +13816,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13762,7 +13859,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 30191-2026</t>
+          <t>A 19674-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13776,10 +13873,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46206</v>
+        <v>45051</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13791,13 +13888,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>6.5</v>
+        <v>0.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13840,7 +13932,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 28335-2023</t>
+          <t>A 5690-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13854,10 +13946,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45099</v>
+        <v>46051</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13870,7 +13962,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13913,7 +14005,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 34008-2026</t>
+          <t>A 13345-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13927,10 +14019,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46252</v>
+        <v>44645</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13943,7 +14035,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13986,7 +14078,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 13281-2024</t>
+          <t>A 21429-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14000,10 +14092,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45386</v>
+        <v>44706</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14016,7 +14108,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14059,7 +14151,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 58650-2023</t>
+          <t>A 35408-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14073,10 +14165,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45251</v>
+        <v>45146</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14089,7 +14181,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14132,7 +14224,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 36304-2023</t>
+          <t>A 55511-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14146,10 +14238,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45152</v>
+        <v>45238</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14162,7 +14254,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14205,7 +14297,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 5690-2026</t>
+          <t>A 31329-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14219,10 +14311,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46051</v>
+        <v>46219</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14235,7 +14327,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.8</v>
+        <v>7.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14278,7 +14370,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 59074-2023</t>
+          <t>A 36472-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14292,10 +14384,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45252</v>
+        <v>45152</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14308,7 +14400,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14351,7 +14443,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 15428-2025</t>
+          <t>A 31324-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14365,10 +14457,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45747</v>
+        <v>46219</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14381,7 +14473,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.1</v>
+        <v>2.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14424,7 +14516,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 15434-2025</t>
+          <t>A 35869-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14438,10 +14530,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45747</v>
+        <v>46266</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14454,7 +14546,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.1</v>
+        <v>1.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14497,7 +14589,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 31329-2026</t>
+          <t>A 35871-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14511,10 +14603,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46219</v>
+        <v>46266</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14527,7 +14619,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>7.5</v>
+        <v>2.9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14587,7 +14679,7 @@
         <v>46220</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14660,7 +14752,7 @@
         <v>46220</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14716,7 +14808,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 11771-2024</t>
+          <t>A 49252-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14730,10 +14822,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45373</v>
+        <v>45210</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14746,7 +14838,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14789,7 +14881,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 58417-2024</t>
+          <t>A 31917-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14803,10 +14895,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45634</v>
+        <v>44777</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14818,13 +14910,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14867,7 +14954,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 13345-2022</t>
+          <t>A 17876-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14881,10 +14968,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44645</v>
+        <v>45758</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14897,7 +14984,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14940,7 +15027,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 31324-2026</t>
+          <t>A 12450-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14954,10 +15041,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46219</v>
+        <v>44638</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14970,7 +15057,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15013,7 +15100,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 35869-2026</t>
+          <t>A 64712-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15027,10 +15114,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46266</v>
+        <v>45281</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15043,7 +15130,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15086,7 +15173,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 35871-2026</t>
+          <t>A 37557-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15100,10 +15187,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46266</v>
+        <v>46276</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15116,7 +15203,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15159,7 +15246,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 64712-2023</t>
+          <t>A 39081-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15173,10 +15260,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45281</v>
+        <v>44817</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15189,7 +15276,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15232,7 +15319,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 39081-2022</t>
+          <t>A 36381-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15246,10 +15333,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44817</v>
+        <v>45152</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15262,7 +15349,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15305,7 +15392,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 61294-2024</t>
+          <t>A 32298-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15319,10 +15406,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45645</v>
+        <v>46237</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15334,8 +15421,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>0.3</v>
+        <v>3.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15378,7 +15470,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 62402-2023</t>
+          <t>A 32363-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15392,10 +15484,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45268</v>
+        <v>46238</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15408,7 +15500,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.5</v>
+        <v>6.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15451,7 +15543,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 1352-2023</t>
+          <t>A 32364-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15465,10 +15557,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44931</v>
+        <v>46238</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15481,7 +15573,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15524,7 +15616,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 28332-2023</t>
+          <t>A 13268-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15538,10 +15630,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45099</v>
+        <v>45386</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15554,7 +15646,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.8</v>
+        <v>6.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15597,7 +15689,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 44033-2024</t>
+          <t>A 13281-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15611,10 +15703,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45572</v>
+        <v>45386</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15627,7 +15719,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15670,7 +15762,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 37557-2026</t>
+          <t>A 19683-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15684,10 +15776,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46276</v>
+        <v>45051</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15700,7 +15792,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15743,7 +15835,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 32298-2026</t>
+          <t>A 58417-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15757,10 +15849,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46237</v>
+        <v>45634</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15774,11 +15866,11 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I197" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15821,7 +15913,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 72879-2021</t>
+          <t>A 39150-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15835,10 +15927,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44547</v>
+        <v>44817</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15851,7 +15943,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15894,7 +15986,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 28267-2023</t>
+          <t>A 26336-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15908,10 +16000,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45099</v>
+        <v>46182</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15924,7 +16016,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15967,7 +16059,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 32363-2026</t>
+          <t>A 39846-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15981,10 +16073,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46238</v>
+        <v>46290</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15996,8 +16088,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>6.2</v>
+        <v>2.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16040,7 +16137,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 32364-2026</t>
+          <t>A 39848-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16054,10 +16151,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46238</v>
+        <v>46290</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16069,8 +16166,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I201" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16113,7 +16215,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 21285-2024</t>
+          <t>A 39837-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16127,10 +16229,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45440</v>
+        <v>46290</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16142,8 +16244,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16186,7 +16293,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 28316-2024</t>
+          <t>A 14502-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16200,10 +16307,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45477</v>
+        <v>45012</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16216,7 +16323,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16259,7 +16366,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 21269-2024</t>
+          <t>A 39842-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16273,10 +16380,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45440</v>
+        <v>46290</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16288,8 +16395,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16332,7 +16444,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 12664-2023</t>
+          <t>A 10958-2022</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16346,10 +16458,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45000</v>
+        <v>44628</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16362,7 +16474,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16405,7 +16517,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 16341-2025</t>
+          <t>A 9145-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16415,14 +16527,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45751</v>
+        <v>44974</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16435,7 +16547,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16478,7 +16590,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 10668-2025</t>
+          <t>A 7225-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16492,10 +16604,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45721</v>
+        <v>44970</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16508,7 +16620,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16551,7 +16663,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 25434-2025</t>
+          <t>A 10451-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16565,10 +16677,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45800</v>
+        <v>45366</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16580,8 +16692,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16624,7 +16741,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 25435-2025</t>
+          <t>A 28332-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16638,10 +16755,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45800</v>
+        <v>45099</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16654,7 +16771,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16697,7 +16814,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 25436-2025</t>
+          <t>A 8330-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16711,10 +16828,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45800</v>
+        <v>45352</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16727,7 +16844,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16770,7 +16887,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 26105-2025</t>
+          <t>A 13279-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16780,14 +16897,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45805</v>
+        <v>45386</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16800,7 +16917,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>5.3</v>
+        <v>1.3</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16843,7 +16960,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 10703-2025</t>
+          <t>A 11889-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16857,10 +16974,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45722</v>
+        <v>45376</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16873,7 +16990,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16916,7 +17033,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 28390-2025</t>
+          <t>A 15426-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16930,10 +17047,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45819</v>
+        <v>45747</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16943,11 +17060,6 @@
       <c r="G213" t="inlineStr">
         <is>
           <t>GÖTENE</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I213" t="n">
@@ -16994,7 +17106,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 31258-2025</t>
+          <t>A 15442-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17008,10 +17120,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45833</v>
+        <v>45747</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17024,7 +17136,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>5.2</v>
+        <v>0.2</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17067,7 +17179,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 32967-2025</t>
+          <t>A 13340-2022</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17081,10 +17193,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45839</v>
+        <v>44645</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17097,7 +17209,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17140,7 +17252,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 6925-2023</t>
+          <t>A 13348-2022</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17154,10 +17266,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44967</v>
+        <v>44645</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17169,13 +17281,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17218,7 +17325,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 58236-2024</t>
+          <t>A 22055-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17232,10 +17339,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45632</v>
+        <v>45069</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17247,13 +17354,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17296,7 +17398,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 58691-2024</t>
+          <t>A 13280-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17310,10 +17412,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45635</v>
+        <v>45386</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17325,13 +17427,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I218" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17374,24 +17471,24 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>S 6120-2022</t>
+          <t>A 28335-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44862</v>
+        <v>45099</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17404,7 +17501,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17447,148 +17544,586 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
+          <t>A 12664-2023</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D220" s="1" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E220" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>GÖTENE</t>
+        </is>
+      </c>
+      <c r="I220" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" t="n">
+        <v>0</v>
+      </c>
+      <c r="L220" t="n">
+        <v>0</v>
+      </c>
+      <c r="M220" t="n">
+        <v>0</v>
+      </c>
+      <c r="N220" t="n">
+        <v>0</v>
+      </c>
+      <c r="O220" t="n">
+        <v>0</v>
+      </c>
+      <c r="P220" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>0</v>
+      </c>
+      <c r="R220" t="n">
+        <v>0</v>
+      </c>
+      <c r="S220" t="n">
+        <v>0</v>
+      </c>
+      <c r="T220" t="n">
+        <v>0</v>
+      </c>
+      <c r="U220" t="n">
+        <v>0</v>
+      </c>
+      <c r="V220" s="2" t="inlineStr"/>
+    </row>
+    <row r="221" ht="15" customHeight="1">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>A 21269-2024</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D221" s="1" t="n">
+        <v>45440</v>
+      </c>
+      <c r="E221" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>GÖTENE</t>
+        </is>
+      </c>
+      <c r="I221" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" t="n">
+        <v>0</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0</v>
+      </c>
+      <c r="M221" t="n">
+        <v>0</v>
+      </c>
+      <c r="N221" t="n">
+        <v>0</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
+      <c r="P221" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>0</v>
+      </c>
+      <c r="R221" t="n">
+        <v>0</v>
+      </c>
+      <c r="S221" t="n">
+        <v>0</v>
+      </c>
+      <c r="T221" t="n">
+        <v>0</v>
+      </c>
+      <c r="U221" t="n">
+        <v>0</v>
+      </c>
+      <c r="V221" s="2" t="inlineStr"/>
+    </row>
+    <row r="222" ht="15" customHeight="1">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>A 28316-2024</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D222" s="1" t="n">
+        <v>45477</v>
+      </c>
+      <c r="E222" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>GÖTENE</t>
+        </is>
+      </c>
+      <c r="I222" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" t="n">
+        <v>0</v>
+      </c>
+      <c r="L222" t="n">
+        <v>0</v>
+      </c>
+      <c r="M222" t="n">
+        <v>0</v>
+      </c>
+      <c r="N222" t="n">
+        <v>0</v>
+      </c>
+      <c r="O222" t="n">
+        <v>0</v>
+      </c>
+      <c r="P222" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>0</v>
+      </c>
+      <c r="R222" t="n">
+        <v>0</v>
+      </c>
+      <c r="S222" t="n">
+        <v>0</v>
+      </c>
+      <c r="T222" t="n">
+        <v>0</v>
+      </c>
+      <c r="U222" t="n">
+        <v>0</v>
+      </c>
+      <c r="V222" s="2" t="inlineStr"/>
+    </row>
+    <row r="223" ht="15" customHeight="1">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>A 16341-2025</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D223" s="1" t="n">
+        <v>45751</v>
+      </c>
+      <c r="E223" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>GÖTENE</t>
+        </is>
+      </c>
+      <c r="I223" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J223" t="n">
+        <v>0</v>
+      </c>
+      <c r="K223" t="n">
+        <v>0</v>
+      </c>
+      <c r="L223" t="n">
+        <v>0</v>
+      </c>
+      <c r="M223" t="n">
+        <v>0</v>
+      </c>
+      <c r="N223" t="n">
+        <v>0</v>
+      </c>
+      <c r="O223" t="n">
+        <v>0</v>
+      </c>
+      <c r="P223" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>0</v>
+      </c>
+      <c r="R223" t="n">
+        <v>0</v>
+      </c>
+      <c r="S223" t="n">
+        <v>0</v>
+      </c>
+      <c r="T223" t="n">
+        <v>0</v>
+      </c>
+      <c r="U223" t="n">
+        <v>0</v>
+      </c>
+      <c r="V223" s="2" t="inlineStr"/>
+    </row>
+    <row r="224" ht="15" customHeight="1">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>A 10668-2025</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D224" s="1" t="n">
+        <v>45721</v>
+      </c>
+      <c r="E224" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>GÖTENE</t>
+        </is>
+      </c>
+      <c r="I224" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J224" t="n">
+        <v>0</v>
+      </c>
+      <c r="K224" t="n">
+        <v>0</v>
+      </c>
+      <c r="L224" t="n">
+        <v>0</v>
+      </c>
+      <c r="M224" t="n">
+        <v>0</v>
+      </c>
+      <c r="N224" t="n">
+        <v>0</v>
+      </c>
+      <c r="O224" t="n">
+        <v>0</v>
+      </c>
+      <c r="P224" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>0</v>
+      </c>
+      <c r="R224" t="n">
+        <v>0</v>
+      </c>
+      <c r="S224" t="n">
+        <v>0</v>
+      </c>
+      <c r="T224" t="n">
+        <v>0</v>
+      </c>
+      <c r="U224" t="n">
+        <v>0</v>
+      </c>
+      <c r="V224" s="2" t="inlineStr"/>
+    </row>
+    <row r="225" ht="15" customHeight="1">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>S 6120-2022</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D225" s="1" t="n">
+        <v>44862</v>
+      </c>
+      <c r="E225" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>GÖTENE</t>
+        </is>
+      </c>
+      <c r="I225" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" t="n">
+        <v>0</v>
+      </c>
+      <c r="L225" t="n">
+        <v>0</v>
+      </c>
+      <c r="M225" t="n">
+        <v>0</v>
+      </c>
+      <c r="N225" t="n">
+        <v>0</v>
+      </c>
+      <c r="O225" t="n">
+        <v>0</v>
+      </c>
+      <c r="P225" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>0</v>
+      </c>
+      <c r="R225" t="n">
+        <v>0</v>
+      </c>
+      <c r="S225" t="n">
+        <v>0</v>
+      </c>
+      <c r="T225" t="n">
+        <v>0</v>
+      </c>
+      <c r="U225" t="n">
+        <v>0</v>
+      </c>
+      <c r="V225" s="2" t="inlineStr"/>
+    </row>
+    <row r="226" ht="15" customHeight="1">
+      <c r="A226" t="inlineStr">
+        <is>
           <t>S 615-2024</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
+      <c r="B226" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr">
+      <c r="C226" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D220" s="1" t="n">
+      <c r="D226" s="1" t="n">
         <v>45352</v>
       </c>
-      <c r="E220" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>GÖTENE</t>
-        </is>
-      </c>
-      <c r="I220" t="n">
+      <c r="E226" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>GÖTENE</t>
+        </is>
+      </c>
+      <c r="I226" t="n">
         <v>19.1</v>
       </c>
-      <c r="J220" t="n">
-        <v>0</v>
-      </c>
-      <c r="K220" t="n">
-        <v>0</v>
-      </c>
-      <c r="L220" t="n">
-        <v>0</v>
-      </c>
-      <c r="M220" t="n">
-        <v>0</v>
-      </c>
-      <c r="N220" t="n">
-        <v>0</v>
-      </c>
-      <c r="O220" t="n">
-        <v>0</v>
-      </c>
-      <c r="P220" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
-      <c r="R220" t="n">
-        <v>0</v>
-      </c>
-      <c r="S220" t="n">
-        <v>0</v>
-      </c>
-      <c r="T220" t="n">
-        <v>0</v>
-      </c>
-      <c r="U220" t="n">
-        <v>0</v>
-      </c>
-      <c r="V220" s="2" t="inlineStr"/>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
+      <c r="J226" t="n">
+        <v>0</v>
+      </c>
+      <c r="K226" t="n">
+        <v>0</v>
+      </c>
+      <c r="L226" t="n">
+        <v>0</v>
+      </c>
+      <c r="M226" t="n">
+        <v>0</v>
+      </c>
+      <c r="N226" t="n">
+        <v>0</v>
+      </c>
+      <c r="O226" t="n">
+        <v>0</v>
+      </c>
+      <c r="P226" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>0</v>
+      </c>
+      <c r="R226" t="n">
+        <v>0</v>
+      </c>
+      <c r="S226" t="n">
+        <v>0</v>
+      </c>
+      <c r="T226" t="n">
+        <v>0</v>
+      </c>
+      <c r="U226" t="n">
+        <v>0</v>
+      </c>
+      <c r="V226" s="2" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
         <is>
           <t>S 614-2024</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="B227" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
+      <c r="C227" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D221" s="1" t="n">
+      <c r="D227" s="1" t="n">
         <v>45352</v>
       </c>
-      <c r="E221" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>GÖTENE</t>
-        </is>
-      </c>
-      <c r="I221" t="n">
+      <c r="E227" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>GÖTENE</t>
+        </is>
+      </c>
+      <c r="I227" t="n">
         <v>11.4</v>
       </c>
-      <c r="J221" t="n">
-        <v>0</v>
-      </c>
-      <c r="K221" t="n">
-        <v>0</v>
-      </c>
-      <c r="L221" t="n">
-        <v>0</v>
-      </c>
-      <c r="M221" t="n">
-        <v>0</v>
-      </c>
-      <c r="N221" t="n">
-        <v>0</v>
-      </c>
-      <c r="O221" t="n">
-        <v>0</v>
-      </c>
-      <c r="P221" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
-      <c r="R221" t="n">
-        <v>0</v>
-      </c>
-      <c r="S221" t="n">
-        <v>0</v>
-      </c>
-      <c r="T221" t="n">
-        <v>0</v>
-      </c>
-      <c r="U221" t="n">
-        <v>0</v>
-      </c>
-      <c r="V221" s="2" t="inlineStr"/>
+      <c r="J227" t="n">
+        <v>0</v>
+      </c>
+      <c r="K227" t="n">
+        <v>0</v>
+      </c>
+      <c r="L227" t="n">
+        <v>0</v>
+      </c>
+      <c r="M227" t="n">
+        <v>0</v>
+      </c>
+      <c r="N227" t="n">
+        <v>0</v>
+      </c>
+      <c r="O227" t="n">
+        <v>0</v>
+      </c>
+      <c r="P227" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>0</v>
+      </c>
+      <c r="R227" t="n">
+        <v>0</v>
+      </c>
+      <c r="S227" t="n">
+        <v>0</v>
+      </c>
+      <c r="T227" t="n">
+        <v>0</v>
+      </c>
+      <c r="U227" t="n">
+        <v>0</v>
+      </c>
+      <c r="V227" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt GÖTENE.xlsx
+++ b/Översikt GÖTENE.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44642</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45352</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>46290</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>45847</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>45846</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>46234</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>46290</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>44827</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>44490</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>45330</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>45099</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45930</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>45944</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>44827</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45763</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>45011</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>44691</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>46219</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>44844</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>46237</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>46247</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>45372</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>44566</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>44490</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>44645</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>44645</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>44490</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>44490</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>44586</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>44507</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>44614</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>44673</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44859</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>44840</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>44566</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>44684</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>44477</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>44507</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>44581</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44761</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>44757</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>44869</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44812</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>44848</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>44865</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>44490</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>44603</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>44475</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>44803</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>44816</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>44498</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>45361</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>45251</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>44844</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>45224</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>45099</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>45099</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>45386</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>45645</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>44931</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>45099</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>45894</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>46044</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>44547</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>46049</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>44924</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>45918</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>44587</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>45800</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>45800</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>45800</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>45930</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>46078</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>45930</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>45930</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>45930</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>46083</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>45805</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>46083</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>46084</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>45722</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>45634</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>45386</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>45575</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         <v>45152</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>45210</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>45366</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>45440</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>45953</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>44827</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>45623</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>45624</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>44931</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>45974</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>45974</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>45974</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>45974</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>45974</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>45975</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>46128</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>45645</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>45975</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>45000</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>45986</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>45986</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>45985</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>45985</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>45268</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>45268</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>45373</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>45119</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>45995</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>44757</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>45021</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         <v>45819</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>45918</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>45845</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>45670</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>46141</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>46141</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>45518</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>46141</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>44924</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>44914</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>45803</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>44931</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>46141</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>46147</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>46147</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>45119</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>45119</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>45833</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>45099</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>46160</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>46160</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>46160</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>45446</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>45839</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>45034</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>45252</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>44967</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>45632</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>45635</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>45373</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>45373</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>44614</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>45110</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         <v>46178</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>46182</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>45736</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>46078</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>45667</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
         <v>46198</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>46197</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>45189</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>45572</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44645</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>45747</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>45747</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>46140</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>44676</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>46206</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>46252</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>45051</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>46051</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>44645</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>44706</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>45146</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>45238</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14314,7 +14314,7 @@
         <v>46219</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>45152</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>46219</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>46266</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>46266</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>46220</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>46220</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>45210</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>44777</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>45758</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>44638</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>45281</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>46276</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>44817</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>45152</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>46237</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>46238</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
         <v>46238</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>45386</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>45386</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>45051</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15852,7 +15852,7 @@
         <v>45634</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>44817</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>46182</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>46290</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16154,7 +16154,7 @@
         <v>46290</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>46290</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>45012</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>46290</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>44628</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>44974</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>44970</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>45366</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>45099</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>45352</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>45386</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>45376</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>45747</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>45747</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>44645</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>44645</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>45069</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>45386</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>45099</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>45000</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>45440</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>45477</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>45751</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>45721</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         <v>44862</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>45352</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>45352</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>

--- a/Översikt GÖTENE.xlsx
+++ b/Översikt GÖTENE.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44642</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45352</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>46290</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>45847</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>45846</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>46234</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>46290</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>44827</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>44490</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>45330</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>45099</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45930</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>45944</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>44827</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45763</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>45011</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>44691</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>46219</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>44844</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>46237</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>46247</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>45372</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>44566</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>44490</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>44645</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>44645</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>44490</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>44490</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>44586</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>44507</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>44614</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>44673</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44859</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>44840</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>44566</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>44684</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>44477</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>44507</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>44581</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44761</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>44757</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>44869</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44812</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>44848</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>44865</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>44490</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>44603</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>44475</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>44803</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>44816</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>44498</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>45361</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>45251</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>44844</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>45224</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>45099</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>45099</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>45386</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>45645</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>44931</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>45099</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>45894</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>46044</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>44547</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>46049</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>44924</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>45918</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>44587</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>45800</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>45800</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>45800</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>45930</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>46078</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>45930</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>45930</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>45930</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>46083</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>45805</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>46083</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>46084</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>45722</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>45634</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>45386</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>45575</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         <v>45152</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>45210</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>45366</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>45440</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>45953</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>44827</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>45623</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>45624</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>44931</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>45974</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>45974</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>45974</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>45974</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>45974</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>45975</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>46128</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>45645</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>45975</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>45000</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>45986</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>45986</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>45985</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>45985</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>45268</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>45268</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>45373</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>45119</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>45995</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>44757</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>45021</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         <v>45819</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>45918</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>45845</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>45670</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>46141</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>46141</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>45518</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>46141</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>44924</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>44914</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>45803</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>44931</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>46141</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>46147</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>46147</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>45119</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>45119</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>45833</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>45099</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>46160</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>46160</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>46160</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>45446</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>45839</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>45034</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>45252</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>44967</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>45632</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>45635</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>45373</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>45373</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>44614</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>45110</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         <v>46178</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>46182</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>45736</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>46078</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>45667</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
         <v>46198</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>46197</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>45189</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>45572</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44645</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>45747</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>45747</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>46140</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>44676</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>46206</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>46252</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>45051</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>46051</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>44645</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>44706</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>45146</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>45238</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14314,7 +14314,7 @@
         <v>46219</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>45152</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>46219</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>46266</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>46266</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>46220</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>46220</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>45210</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>44777</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>45758</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>44638</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>45281</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>46276</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>44817</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>45152</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>46237</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>46238</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
         <v>46238</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>45386</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>45386</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>45051</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15852,7 +15852,7 @@
         <v>45634</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>44817</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>46182</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>46290</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16154,7 +16154,7 @@
         <v>46290</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>46290</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>45012</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>46290</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>44628</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>44974</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>44970</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>45366</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>45099</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>45352</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>45386</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>45376</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>45747</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>45747</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>44645</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>44645</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>45069</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>45386</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>45099</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>45000</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>45440</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>45477</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>45751</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>45721</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         <v>44862</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>45352</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>45352</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>

--- a/Översikt GÖTENE.xlsx
+++ b/Översikt GÖTENE.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44642</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45352</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>46290</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>45847</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>45846</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>46234</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>46290</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>44827</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>44490</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 5086-2024</t>
+          <t>A 41724-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45330</v>
+        <v>44827</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2038,17 +2038,17 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
@@ -2062,7 +2062,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2071,49 +2071,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 5086-2024 artfynd.xlsx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 41724-2022 artfynd.xlsx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 5086-2024 karta.png", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 41724-2022 karta.png", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 5086-2024 georefererad karta.tif", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 41724-2022 georefererad karta.tif", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 5086-2024 FSC-klagomål.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 41724-2022 FSC-klagomål.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 5086-2024 FSC-klagomål mail.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 41724-2022 FSC-klagomål mail.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 5086-2024 tillsynsbegäran.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 41724-2022 tillsynsbegäran.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 5086-2024 tillsynsbegäran mail.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 41724-2022 tillsynsbegäran mail.docx", "A 41724-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28273-2023</t>
+          <t>A 47393-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45099</v>
+        <v>45930</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2143,17 +2143,17 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2183,42 +2183,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Korallticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 28273-2023 artfynd.xlsx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 47393-2025 artfynd.xlsx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 28273-2023 karta.png", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 47393-2025 karta.png", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 28273-2023 georefererad karta.tif", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 47393-2025 georefererad karta.tif", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 28273-2023 FSC-klagomål.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 47393-2025 FSC-klagomål.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 28273-2023 FSC-klagomål mail.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 47393-2025 FSC-klagomål mail.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 28273-2023 tillsynsbegäran.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 47393-2025 tillsynsbegäran.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 28273-2023 tillsynsbegäran mail.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 47393-2025 tillsynsbegäran mail.docx", "A 47393-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 47393-2025</t>
+          <t>A 32909-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2232,10 +2232,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45930</v>
+        <v>45839</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2288,35 +2288,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Korallticka</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 47393-2025 artfynd.xlsx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32909-2025 artfynd.xlsx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 47393-2025 karta.png", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32909-2025 karta.png", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 47393-2025 georefererad karta.tif", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32909-2025 georefererad karta.tif", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 47393-2025 FSC-klagomål.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32909-2025 FSC-klagomål.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 47393-2025 FSC-klagomål mail.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32909-2025 FSC-klagomål mail.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 47393-2025 tillsynsbegäran.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32909-2025 tillsynsbegäran.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 47393-2025 tillsynsbegäran mail.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32909-2025 tillsynsbegäran mail.docx", "A 32909-2025")</f>
         <v/>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
         <v>45944</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 41724-2022</t>
+          <t>A 45211-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44827</v>
+        <v>44844</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2458,16 +2458,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2482,7 +2482,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2494,39 +2494,39 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 41724-2022 artfynd.xlsx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 45211-2022 artfynd.xlsx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 41724-2022 karta.png", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 45211-2022 karta.png", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 41724-2022 georefererad karta.tif", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 45211-2022 georefererad karta.tif", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 41724-2022 FSC-klagomål.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 45211-2022 FSC-klagomål.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 41724-2022 FSC-klagomål mail.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 45211-2022 FSC-klagomål mail.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 41724-2022 tillsynsbegäran.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 45211-2022 tillsynsbegäran.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 41724-2022 tillsynsbegäran mail.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 45211-2022 tillsynsbegäran mail.docx", "A 45211-2022")</f>
         <v/>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
         <v>45763</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 32909-2025</t>
+          <t>A 19083-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45839</v>
+        <v>44691</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,19 +2673,19 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2700,7 +2700,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2709,39 +2709,39 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Läderbagge</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32909-2025 artfynd.xlsx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 19083-2022 artfynd.xlsx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32909-2025 karta.png", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 19083-2022 karta.png", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32909-2025 georefererad karta.tif", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 19083-2022 georefererad karta.tif", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32909-2025 FSC-klagomål.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 19083-2022 FSC-klagomål.docx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32909-2025 FSC-klagomål mail.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 19083-2022 FSC-klagomål mail.docx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32909-2025 tillsynsbegäran.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 19083-2022 tillsynsbegäran.docx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32909-2025 tillsynsbegäran mail.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 19083-2022 tillsynsbegäran mail.docx", "A 19083-2022")</f>
         <v/>
       </c>
     </row>
@@ -2765,7 +2765,7 @@
         <v>45011</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 19083-2022</t>
+          <t>A 5086-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44691</v>
+        <v>45330</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="I23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>1</v>
       </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2911,51 +2911,51 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
         <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Läderbagge</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 19083-2022 artfynd.xlsx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 5086-2024 artfynd.xlsx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 19083-2022 karta.png", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 5086-2024 karta.png", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 19083-2022 georefererad karta.tif", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 5086-2024 georefererad karta.tif", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 19083-2022 FSC-klagomål.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 5086-2024 FSC-klagomål.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 19083-2022 FSC-klagomål mail.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 5086-2024 FSC-klagomål mail.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 19083-2022 tillsynsbegäran.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 5086-2024 tillsynsbegäran.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 19083-2022 tillsynsbegäran mail.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 5086-2024 tillsynsbegäran mail.docx", "A 5086-2024")</f>
         <v/>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
         <v>46219</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 45211-2022</t>
+          <t>A 28273-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44844</v>
+        <v>45099</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3101,13 +3101,13 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3137,39 +3137,39 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 45211-2022 artfynd.xlsx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 28273-2023 artfynd.xlsx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 45211-2022 karta.png", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 28273-2023 karta.png", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 45211-2022 georefererad karta.tif", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 28273-2023 georefererad karta.tif", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 45211-2022 FSC-klagomål.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 28273-2023 FSC-klagomål.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 45211-2022 FSC-klagomål mail.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 28273-2023 FSC-klagomål mail.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 45211-2022 tillsynsbegäran.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 28273-2023 tillsynsbegäran.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 45211-2022 tillsynsbegäran mail.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 28273-2023 tillsynsbegäran mail.docx", "A 28273-2023")</f>
         <v/>
       </c>
     </row>
@@ -3193,7 +3193,7 @@
         <v>46237</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>46247</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>45372</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>44566</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>44490</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>44645</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>44645</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>44490</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>44490</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>44586</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 63200-2021</t>
+          <t>A 8786-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4016,10 +4016,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44507</v>
+        <v>44614</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4031,8 +4031,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>8.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4075,7 +4080,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8786-2022</t>
+          <t>A 63200-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4089,10 +4094,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44614</v>
+        <v>44507</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4104,13 +4109,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>8.1</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4170,7 +4170,7 @@
         <v>44673</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 48733-2022</t>
+          <t>A 44507-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4240,10 +4240,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44859</v>
+        <v>44840</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 44507-2022</t>
+          <t>A 48733-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4313,10 +4313,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44840</v>
+        <v>44859</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4389,7 +4389,7 @@
         <v>44566</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>44684</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>44477</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>44507</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>44581</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44761</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>44757</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>44869</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44812</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>44848</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>44865</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>44490</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>44603</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>44475</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>44803</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 38945-2022</t>
+          <t>A 61148-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44816</v>
+        <v>44498</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5550,7 +5550,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 61148-2021</t>
+          <t>A 38945-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5564,10 +5564,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44498</v>
+        <v>44816</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5623,7 +5623,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 9607-2024</t>
+          <t>A 58418-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5637,10 +5637,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45361</v>
+        <v>45634</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5696,7 +5696,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 58650-2023</t>
+          <t>A 36381-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5710,10 +5710,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45251</v>
+        <v>45152</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5769,7 +5769,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 45239-2022</t>
+          <t>A 8330-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44844</v>
+        <v>45352</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5798,13 +5798,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5847,7 +5842,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 52352-2023</t>
+          <t>A 16341-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5857,14 +5852,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45224</v>
+        <v>45751</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5877,7 +5872,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5920,7 +5915,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28264-2023</t>
+          <t>A 10668-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5934,10 +5929,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45099</v>
+        <v>45721</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5950,7 +5945,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5993,7 +5988,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 28268-2023</t>
+          <t>A 13276-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6007,10 +6002,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45099</v>
+        <v>45386</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6023,7 +6018,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6066,7 +6061,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 13276-2024</t>
+          <t>A 61194-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6080,10 +6075,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45386</v>
+        <v>45645</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6095,8 +6090,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6139,7 +6139,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 61194-2024</t>
+          <t>A 849-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6153,10 +6153,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45645</v>
+        <v>44931</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6168,13 +6168,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6217,7 +6212,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 1352-2023</t>
+          <t>A 39998-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6231,10 +6226,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44931</v>
+        <v>45894</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6247,7 +6242,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6290,7 +6285,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 28267-2023</t>
+          <t>A 25434-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6304,10 +6299,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45099</v>
+        <v>45800</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6320,7 +6315,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6363,7 +6358,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 39998-2025</t>
+          <t>A 25435-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6377,10 +6372,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45894</v>
+        <v>45800</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6393,7 +6388,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6436,7 +6431,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3960-2026</t>
+          <t>A 25436-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6450,10 +6445,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46044</v>
+        <v>45800</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6465,13 +6460,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6514,7 +6504,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 72879-2021</t>
+          <t>A 44608-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6528,10 +6518,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44547</v>
+        <v>45189</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6544,7 +6534,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6587,7 +6577,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 5044-2026</t>
+          <t>A 26105-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6597,14 +6587,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46049</v>
+        <v>45805</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6617,7 +6607,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6660,7 +6650,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 62499-2022</t>
+          <t>A 10703-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6674,10 +6664,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44924</v>
+        <v>45722</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6689,13 +6679,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6738,7 +6723,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 45007-2025</t>
+          <t>A 41721-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6752,10 +6737,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45918</v>
+        <v>44827</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6768,7 +6753,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6811,7 +6796,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 3932-2022</t>
+          <t>A 31917-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6825,10 +6810,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44587</v>
+        <v>44777</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6841,7 +6826,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6884,7 +6869,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 25434-2025</t>
+          <t>A 11889-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6898,10 +6883,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45800</v>
+        <v>45376</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6914,7 +6899,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6957,7 +6942,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 25435-2025</t>
+          <t>A 11772-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6971,10 +6956,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45800</v>
+        <v>45373</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6987,7 +6972,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7030,7 +7015,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 25436-2025</t>
+          <t>A 11773-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7044,10 +7029,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45800</v>
+        <v>45373</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7060,7 +7045,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7103,7 +7088,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 47385-2025</t>
+          <t>A 28390-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7117,10 +7102,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45930</v>
+        <v>45819</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7132,8 +7117,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7176,7 +7166,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 10630-2026</t>
+          <t>A 45007-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7190,10 +7180,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46078</v>
+        <v>45918</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7206,7 +7196,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7266,7 +7256,7 @@
         <v>45930</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7322,7 +7312,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 47389-2025</t>
+          <t>A 47383-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7339,7 +7329,7 @@
         <v>45930</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7352,7 +7342,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7395,7 +7385,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 47383-2025</t>
+          <t>A 31258-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7409,10 +7399,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45930</v>
+        <v>45833</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7425,7 +7415,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.4</v>
+        <v>5.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7468,7 +7458,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 11459-2026</t>
+          <t>A 47385-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7482,10 +7472,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46083</v>
+        <v>45930</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7498,7 +7488,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7541,7 +7531,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 26105-2025</t>
+          <t>A 47389-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7551,14 +7541,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45805</v>
+        <v>45930</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7571,7 +7561,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5.3</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7614,7 +7604,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 11460-2026</t>
+          <t>A 17010-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7628,10 +7618,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46083</v>
+        <v>44676</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7644,7 +7634,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7687,7 +7677,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 11630-2026</t>
+          <t>A 32967-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7701,10 +7691,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46084</v>
+        <v>45839</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7716,13 +7706,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7765,7 +7750,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 10703-2025</t>
+          <t>A 61021-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7775,14 +7760,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45722</v>
+        <v>44914</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7795,7 +7780,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7838,7 +7823,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 58418-2024</t>
+          <t>A 30205-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7852,10 +7837,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45634</v>
+        <v>45110</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7868,7 +7853,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.4</v>
+        <v>6.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7911,7 +7896,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 13170-2024</t>
+          <t>A 6925-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7925,10 +7910,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45386</v>
+        <v>44967</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7940,8 +7925,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7984,7 +7974,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 45180-2024</t>
+          <t>A 58236-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7998,10 +7988,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45575</v>
+        <v>45632</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8013,8 +8003,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>14.7</v>
+        <v>2.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8057,7 +8052,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 36304-2023</t>
+          <t>A 58691-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8071,10 +8066,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45152</v>
+        <v>45635</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8086,8 +8081,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8130,7 +8130,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 49256-2023</t>
+          <t>A 52141-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8144,10 +8144,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45210</v>
+        <v>45953</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8203,7 +8203,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 10596-2024</t>
+          <t>A 22278-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8217,10 +8217,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45366</v>
+        <v>45446</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8276,7 +8276,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 21285-2024</t>
+          <t>A 13450-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8290,10 +8290,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45440</v>
+        <v>45736</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8349,7 +8349,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 52141-2025</t>
+          <t>A 17069-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8363,10 +8363,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45953</v>
+        <v>45034</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8422,7 +8422,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 41721-2022</t>
+          <t>A 1379-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8436,10 +8436,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44827</v>
+        <v>45667</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8495,7 +8495,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 55764-2024</t>
+          <t>A 56365-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45623</v>
+        <v>45974</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8568,7 +8568,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 56169-2024</t>
+          <t>A 56347-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8582,10 +8582,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45624</v>
+        <v>45974</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>19.7</v>
+        <v>10.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8641,7 +8641,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 850-2023</t>
+          <t>A 56352-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8655,10 +8655,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44931</v>
+        <v>45974</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.4</v>
+        <v>5.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8714,7 +8714,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 56365-2025</t>
+          <t>A 56414-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8728,10 +8728,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8787,7 +8787,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 56347-2025</t>
+          <t>A 56340-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8804,7 +8804,7 @@
         <v>45974</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>10.9</v>
+        <v>4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8860,7 +8860,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 56352-2025</t>
+          <t>A 56417-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8874,10 +8874,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5.9</v>
+        <v>1.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8950,7 +8950,7 @@
         <v>45974</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 56340-2025</t>
+          <t>A 58517-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9020,10 +9020,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45974</v>
+        <v>45985</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9079,7 +9079,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 56417-2025</t>
+          <t>A 58520-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9093,10 +9093,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45975</v>
+        <v>45985</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9152,7 +9152,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 18776-2026</t>
+          <t>A 3960-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9166,10 +9166,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46128</v>
+        <v>46044</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9181,8 +9181,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9225,7 +9230,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 61294-2024</t>
+          <t>A 58766-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9239,10 +9244,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45645</v>
+        <v>45986</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9255,7 +9260,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9298,7 +9303,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 56414-2025</t>
+          <t>A 58767-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9312,10 +9317,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45975</v>
+        <v>45986</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9328,7 +9333,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9371,7 +9376,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 12660-2023</t>
+          <t>A 45180-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9381,14 +9386,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45000</v>
+        <v>45575</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9401,7 +9406,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.5</v>
+        <v>14.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9444,7 +9449,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 58766-2025</t>
+          <t>A 5044-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9458,10 +9463,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45986</v>
+        <v>46049</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9474,7 +9479,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>5.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9517,7 +9522,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 58767-2025</t>
+          <t>A 14502-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9531,10 +9536,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45986</v>
+        <v>45012</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9547,7 +9552,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9590,7 +9595,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 58517-2025</t>
+          <t>A 13340-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9604,10 +9609,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45985</v>
+        <v>44645</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9620,7 +9625,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9663,7 +9668,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 58520-2025</t>
+          <t>A 13348-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9677,10 +9682,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45985</v>
+        <v>44645</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9693,7 +9698,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9736,7 +9741,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 62390-2023</t>
+          <t>A 13366-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9750,10 +9755,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45268</v>
+        <v>44645</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9766,7 +9771,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9809,7 +9814,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 62402-2023</t>
+          <t>A 15646-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9823,10 +9828,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45268</v>
+        <v>45021</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9839,7 +9844,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9882,7 +9887,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 11771-2024</t>
+          <t>A 9607-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9896,10 +9901,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45373</v>
+        <v>45361</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9912,7 +9917,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9955,7 +9960,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 31981-2023</t>
+          <t>A 60559-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9969,10 +9974,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45119</v>
+        <v>45995</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9985,7 +9990,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10028,7 +10033,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 60559-2025</t>
+          <t>A 9145-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10042,10 +10047,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45995</v>
+        <v>44974</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10058,7 +10063,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10101,7 +10106,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 30174-2022</t>
+          <t>A 10630-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10115,10 +10120,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44757</v>
+        <v>46078</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10131,7 +10136,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>5.1</v>
+        <v>0.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10174,7 +10179,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 15646-2023</t>
+          <t>A 13268-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10188,10 +10193,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45021</v>
+        <v>45386</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10204,7 +10209,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3</v>
+        <v>6.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10247,7 +10252,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 28390-2025</t>
+          <t>A 10451-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10261,10 +10266,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45819</v>
+        <v>45366</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10278,11 +10283,11 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10325,7 +10330,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 45013-2025</t>
+          <t>A 11459-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10339,10 +10344,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45918</v>
+        <v>46083</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10355,7 +10360,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10398,7 +10403,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 34161-2025</t>
+          <t>A 11460-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10412,10 +10417,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45845</v>
+        <v>46083</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10428,7 +10433,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10471,7 +10476,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 1662-2025</t>
+          <t>A 11630-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10485,10 +10490,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45670</v>
+        <v>46084</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10500,8 +10505,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10544,7 +10554,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 20710-2026</t>
+          <t>A 12660-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10554,14 +10564,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46141</v>
+        <v>45000</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10574,7 +10584,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10617,7 +10627,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 20812-2026</t>
+          <t>A 22055-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10631,10 +10641,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46141</v>
+        <v>45069</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10647,7 +10657,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10690,7 +10700,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 33162-2024</t>
+          <t>A 10596-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10704,10 +10714,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45518</v>
+        <v>45366</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10720,7 +10730,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10763,7 +10773,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 20700-2026</t>
+          <t>A 28268-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10777,10 +10787,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46141</v>
+        <v>45099</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10793,7 +10803,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10836,7 +10846,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 62510-2022</t>
+          <t>A 850-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10850,10 +10860,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44924</v>
+        <v>44931</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10865,13 +10875,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10914,7 +10919,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 61021-2022</t>
+          <t>A 55764-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10924,14 +10929,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44914</v>
+        <v>45623</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10944,7 +10949,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10987,7 +10992,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 25594-2025</t>
+          <t>A 19674-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10997,14 +11002,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45803</v>
+        <v>45051</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11017,7 +11022,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11060,7 +11065,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 849-2023</t>
+          <t>A 19683-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11074,10 +11079,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44931</v>
+        <v>45051</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11090,7 +11095,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11133,7 +11138,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 20811-2026</t>
+          <t>A 8765-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11147,10 +11152,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46141</v>
+        <v>44614</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11162,8 +11167,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11206,7 +11216,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 21376-2026</t>
+          <t>A 52352-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11220,10 +11230,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46147</v>
+        <v>45224</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11236,7 +11246,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>7.2</v>
+        <v>0.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11279,7 +11289,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 21369-2026</t>
+          <t>A 18776-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11293,10 +11303,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46147</v>
+        <v>46128</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11352,7 +11362,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 31969-2023</t>
+          <t>A 62510-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11366,10 +11376,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45119</v>
+        <v>44924</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11381,8 +11391,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11425,7 +11440,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 31978-2023</t>
+          <t>A 45013-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11439,10 +11454,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45119</v>
+        <v>45918</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11455,7 +11470,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11498,7 +11513,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 31258-2025</t>
+          <t>A 1662-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11512,10 +11527,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45833</v>
+        <v>45670</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11528,7 +11543,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>5.2</v>
+        <v>1.8</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11571,7 +11586,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 28258-2023</t>
+          <t>A 30174-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11585,10 +11600,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45099</v>
+        <v>44757</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11601,7 +11616,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.7</v>
+        <v>5.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11644,7 +11659,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 22906-2026</t>
+          <t>A 17876-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11658,10 +11673,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46160</v>
+        <v>45758</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11674,7 +11689,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11717,7 +11732,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 22916-2026</t>
+          <t>A 34161-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11731,10 +11746,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46160</v>
+        <v>45845</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11747,7 +11762,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.8</v>
+        <v>4.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11790,7 +11805,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 22912-2026</t>
+          <t>A 13170-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11804,10 +11819,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46160</v>
+        <v>45386</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11820,7 +11835,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11863,7 +11878,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 22278-2024</t>
+          <t>A 25594-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11873,14 +11888,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45446</v>
+        <v>45803</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11893,7 +11908,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11936,7 +11951,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 32967-2025</t>
+          <t>A 62390-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11950,10 +11965,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45839</v>
+        <v>45268</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11966,7 +11981,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12009,7 +12024,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 17069-2023</t>
+          <t>A 20710-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12023,10 +12038,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45034</v>
+        <v>46141</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12039,7 +12054,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12082,7 +12097,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 59074-2023</t>
+          <t>A 20811-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12096,10 +12111,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45252</v>
+        <v>46141</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12112,7 +12127,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12155,7 +12170,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 6925-2023</t>
+          <t>A 33162-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12169,10 +12184,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44967</v>
+        <v>45518</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12184,13 +12199,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12233,7 +12243,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 58236-2024</t>
+          <t>A 20812-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12247,10 +12257,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45632</v>
+        <v>46141</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12262,13 +12272,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12311,7 +12316,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 58691-2024</t>
+          <t>A 20700-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12325,10 +12330,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45635</v>
+        <v>46141</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12340,13 +12345,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12389,7 +12389,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 11772-2024</t>
+          <t>A 62499-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12403,10 +12403,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45373</v>
+        <v>44924</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12418,8 +12418,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12462,7 +12467,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 11773-2024</t>
+          <t>A 21369-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12476,10 +12481,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45373</v>
+        <v>46147</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12492,7 +12497,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12535,7 +12540,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 8765-2022</t>
+          <t>A 10958-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12549,10 +12554,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44614</v>
+        <v>44628</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12564,13 +12569,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12613,7 +12613,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 30205-2023</t>
+          <t>A 45239-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12627,10 +12627,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45110</v>
+        <v>44844</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12642,8 +12642,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>6.8</v>
+        <v>1.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12686,7 +12691,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 25777-2026</t>
+          <t>A 21376-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12696,14 +12701,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46178</v>
+        <v>46147</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12716,7 +12721,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12759,7 +12764,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 26338-2026</t>
+          <t>A 15426-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12773,10 +12778,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46182</v>
+        <v>45747</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12789,7 +12794,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12832,7 +12837,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 13450-2025</t>
+          <t>A 15442-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12846,10 +12851,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45736</v>
+        <v>45747</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12862,7 +12867,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12905,7 +12910,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 10636-2026</t>
+          <t>A 22916-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12919,10 +12924,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46078</v>
+        <v>46160</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12935,7 +12940,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12978,7 +12983,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 1379-2025</t>
+          <t>A 22906-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12992,10 +12997,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45667</v>
+        <v>46160</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13008,7 +13013,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13051,7 +13056,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 28647-2026</t>
+          <t>A 22912-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13065,10 +13070,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46198</v>
+        <v>46160</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13081,7 +13086,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13124,7 +13129,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 28467-2026</t>
+          <t>A 12450-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13138,10 +13143,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46197</v>
+        <v>44638</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13154,7 +13159,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13197,7 +13202,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 44608-2023</t>
+          <t>A 21429-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13211,10 +13216,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45189</v>
+        <v>44706</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13227,7 +13232,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13270,7 +13275,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 44033-2024</t>
+          <t>A 56169-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13284,10 +13289,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45572</v>
+        <v>45624</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13300,7 +13305,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.2</v>
+        <v>19.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13343,7 +13348,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 13366-2022</t>
+          <t>A 13279-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13357,10 +13362,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44645</v>
+        <v>45386</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13373,7 +13378,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13416,7 +13421,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 15428-2025</t>
+          <t>A 49256-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13430,10 +13435,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45747</v>
+        <v>45210</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13446,7 +13451,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.1</v>
+        <v>4.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13489,7 +13494,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 15434-2025</t>
+          <t>A 31969-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13503,10 +13508,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45747</v>
+        <v>45119</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13519,7 +13524,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13562,7 +13567,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 20507-2026</t>
+          <t>A 31978-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13576,10 +13581,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46140</v>
+        <v>45119</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13592,7 +13597,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13635,7 +13640,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 17010-2022</t>
+          <t>A 39150-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13649,10 +13654,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44676</v>
+        <v>44817</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13665,7 +13670,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13708,7 +13713,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 30191-2026</t>
+          <t>A 25777-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13718,14 +13723,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46206</v>
+        <v>46178</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13737,13 +13742,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13786,7 +13786,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 34008-2026</t>
+          <t>A 36472-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13800,10 +13800,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46252</v>
+        <v>45152</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13859,7 +13859,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 19674-2023</t>
+          <t>A 26338-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13873,10 +13873,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45051</v>
+        <v>46182</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13932,7 +13932,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 5690-2026</t>
+          <t>A 3932-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13946,10 +13946,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46051</v>
+        <v>44587</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14005,7 +14005,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 13345-2022</t>
+          <t>A 7225-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14019,10 +14019,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44645</v>
+        <v>44970</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14078,7 +14078,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 21429-2022</t>
+          <t>A 35408-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14092,10 +14092,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44706</v>
+        <v>45146</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14151,7 +14151,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 35408-2023</t>
+          <t>A 13280-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14165,10 +14165,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45146</v>
+        <v>45386</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14224,7 +14224,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 55511-2023</t>
+          <t>A 31981-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14238,10 +14238,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45238</v>
+        <v>45119</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14297,7 +14297,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 31329-2026</t>
+          <t>A 55511-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14311,10 +14311,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46219</v>
+        <v>45238</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>7.5</v>
+        <v>3.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14370,7 +14370,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 36472-2023</t>
+          <t>A 28258-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14384,10 +14384,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45152</v>
+        <v>45099</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14443,7 +14443,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 31324-2026</t>
+          <t>A 28264-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14457,10 +14457,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46219</v>
+        <v>45099</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14516,7 +14516,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 35869-2026</t>
+          <t>A 10636-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14530,10 +14530,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46266</v>
+        <v>46078</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14589,7 +14589,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 35871-2026</t>
+          <t>A 49252-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14603,10 +14603,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46266</v>
+        <v>45210</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14662,7 +14662,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 31446-2026</t>
+          <t>A 28467-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14676,10 +14676,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46220</v>
+        <v>46197</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14735,7 +14735,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 31452-2026</t>
+          <t>A 28647-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14749,10 +14749,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46220</v>
+        <v>46198</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14808,7 +14808,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 49252-2023</t>
+          <t>A 20507-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14822,10 +14822,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45210</v>
+        <v>46140</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14881,7 +14881,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 31917-2022</t>
+          <t>A 28335-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14895,10 +14895,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44777</v>
+        <v>45099</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14954,7 +14954,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 17876-2025</t>
+          <t>A 13281-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14968,10 +14968,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45758</v>
+        <v>45386</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15027,7 +15027,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 12450-2022</t>
+          <t>A 58650-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15041,10 +15041,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44638</v>
+        <v>45251</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15100,7 +15100,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 64712-2023</t>
+          <t>A 36304-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15114,10 +15114,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45281</v>
+        <v>45152</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15130,7 +15130,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15173,7 +15173,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 37557-2026</t>
+          <t>A 30191-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15187,10 +15187,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46276</v>
+        <v>46206</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15202,8 +15202,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15246,7 +15251,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 39081-2022</t>
+          <t>A 59074-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15260,10 +15265,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44817</v>
+        <v>45252</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15276,7 +15281,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15319,7 +15324,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 36381-2023</t>
+          <t>A 34008-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15333,10 +15338,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45152</v>
+        <v>46252</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15349,7 +15354,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15392,7 +15397,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 32298-2026</t>
+          <t>A 5690-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15406,10 +15411,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46237</v>
+        <v>46051</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15421,13 +15426,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 32363-2026</t>
+          <t>A 15428-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15484,10 +15484,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46238</v>
+        <v>45747</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>6.2</v>
+        <v>0.1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15543,7 +15543,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 32364-2026</t>
+          <t>A 15434-2025</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15557,10 +15557,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46238</v>
+        <v>45747</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15573,7 +15573,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15616,7 +15616,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 13268-2024</t>
+          <t>A 11771-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15630,10 +15630,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45386</v>
+        <v>45373</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>6.7</v>
+        <v>3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15689,7 +15689,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 13281-2024</t>
+          <t>A 58417-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45386</v>
+        <v>45634</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15718,8 +15718,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15762,7 +15767,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 19683-2023</t>
+          <t>A 13345-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15776,10 +15781,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45051</v>
+        <v>44645</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15792,7 +15797,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15835,7 +15840,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 58417-2024</t>
+          <t>A 31329-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15849,10 +15854,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45634</v>
+        <v>46219</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15864,13 +15869,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>0.5</v>
+        <v>7.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15913,7 +15913,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 39150-2022</t>
+          <t>A 31446-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15927,10 +15927,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44817</v>
+        <v>46220</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15986,7 +15986,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 26336-2026</t>
+          <t>A 31452-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16000,10 +16000,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46182</v>
+        <v>46220</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16059,7 +16059,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 39846-2026</t>
+          <t>A 64712-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16073,10 +16073,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46290</v>
+        <v>45281</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16088,13 +16088,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16137,7 +16132,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 39848-2026</t>
+          <t>A 31324-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16151,10 +16146,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46290</v>
+        <v>46219</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16166,13 +16161,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16215,7 +16205,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 39837-2026</t>
+          <t>A 39081-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16229,10 +16219,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46290</v>
+        <v>44817</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16244,13 +16234,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16293,7 +16278,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 14502-2023</t>
+          <t>A 61294-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16307,10 +16292,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45012</v>
+        <v>45645</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16323,7 +16308,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>3.2</v>
+        <v>0.3</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16366,7 +16351,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 39842-2026</t>
+          <t>A 35869-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16380,10 +16365,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46290</v>
+        <v>46266</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16395,13 +16380,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I204" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16444,7 +16424,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 10958-2022</t>
+          <t>A 35871-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16458,10 +16438,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44628</v>
+        <v>46266</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16474,7 +16454,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16517,7 +16497,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 9145-2023</t>
+          <t>A 62402-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16531,10 +16511,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44974</v>
+        <v>45268</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16547,7 +16527,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16590,7 +16570,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 7225-2023</t>
+          <t>A 1352-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16604,10 +16584,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44970</v>
+        <v>44931</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16620,7 +16600,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16663,7 +16643,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 10451-2024</t>
+          <t>A 28332-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16677,10 +16657,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45366</v>
+        <v>45099</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16692,13 +16672,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I208" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16741,7 +16716,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 28332-2023</t>
+          <t>A 44033-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16755,10 +16730,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45099</v>
+        <v>45572</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16771,7 +16746,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16814,7 +16789,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 8330-2024</t>
+          <t>A 72879-2021</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16828,10 +16803,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45352</v>
+        <v>44547</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16844,7 +16819,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16887,7 +16862,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 13279-2024</t>
+          <t>A 28267-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16901,10 +16876,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45386</v>
+        <v>45099</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16917,7 +16892,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16960,7 +16935,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 11889-2024</t>
+          <t>A 37557-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16974,10 +16949,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45376</v>
+        <v>46276</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16990,7 +16965,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17033,7 +17008,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 15426-2025</t>
+          <t>A 32298-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17047,10 +17022,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45747</v>
+        <v>46237</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17062,8 +17037,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I213" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17106,7 +17086,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 15442-2025</t>
+          <t>A 21285-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17120,10 +17100,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45747</v>
+        <v>45440</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17136,7 +17116,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17179,7 +17159,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 13340-2022</t>
+          <t>A 32363-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17193,10 +17173,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44645</v>
+        <v>46238</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17209,7 +17189,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17252,7 +17232,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 13348-2022</t>
+          <t>A 32364-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17266,10 +17246,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44645</v>
+        <v>46238</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17282,7 +17262,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17325,7 +17305,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 22055-2023</t>
+          <t>A 28316-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17339,10 +17319,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45069</v>
+        <v>45477</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17355,7 +17335,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17398,7 +17378,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 13280-2024</t>
+          <t>A 21269-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17412,10 +17392,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45386</v>
+        <v>45440</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17428,7 +17408,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17471,7 +17451,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 28335-2023</t>
+          <t>A 12664-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17485,10 +17465,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45099</v>
+        <v>45000</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17501,7 +17481,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17544,7 +17524,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 12664-2023</t>
+          <t>A 39842-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17558,10 +17538,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45000</v>
+        <v>46290</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17573,8 +17553,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I220" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17617,7 +17602,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 21269-2024</t>
+          <t>A 26336-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17631,10 +17616,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45440</v>
+        <v>46182</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17690,7 +17675,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 28316-2024</t>
+          <t>A 39848-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17704,10 +17689,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45477</v>
+        <v>46290</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17719,8 +17704,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I222" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17763,7 +17753,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 16341-2025</t>
+          <t>A 39846-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17773,14 +17763,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45751</v>
+        <v>46290</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17792,8 +17782,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I223" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17836,7 +17831,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 10668-2025</t>
+          <t>A 39837-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17850,10 +17845,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45721</v>
+        <v>46290</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17865,8 +17860,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17926,7 +17926,7 @@
         <v>44862</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>45352</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>45352</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>

--- a/Översikt GÖTENE.xlsx
+++ b/Översikt GÖTENE.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44642</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45352</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>46290</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>45847</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>45846</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>46234</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>46290</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>44827</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>44490</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 41724-2022</t>
+          <t>A 5086-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44827</v>
+        <v>45330</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2038,16 +2038,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2062,7 +2062,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2071,49 +2071,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
         <v>1</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 41724-2022 artfynd.xlsx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 5086-2024 artfynd.xlsx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 41724-2022 karta.png", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 5086-2024 karta.png", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 41724-2022 georefererad karta.tif", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 5086-2024 georefererad karta.tif", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 41724-2022 FSC-klagomål.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 5086-2024 FSC-klagomål.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 41724-2022 FSC-klagomål mail.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 5086-2024 FSC-klagomål mail.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 41724-2022 tillsynsbegäran.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 5086-2024 tillsynsbegäran.docx", "A 5086-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 41724-2022 tillsynsbegäran mail.docx", "A 41724-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 5086-2024 tillsynsbegäran mail.docx", "A 5086-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 47393-2025</t>
+          <t>A 28273-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45930</v>
+        <v>45099</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2143,16 +2143,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2183,42 +2183,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Korallticka</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 47393-2025 artfynd.xlsx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 28273-2023 artfynd.xlsx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 47393-2025 karta.png", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 28273-2023 karta.png", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 47393-2025 georefererad karta.tif", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 28273-2023 georefererad karta.tif", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 47393-2025 FSC-klagomål.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 28273-2023 FSC-klagomål.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 47393-2025 FSC-klagomål mail.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 28273-2023 FSC-klagomål mail.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 47393-2025 tillsynsbegäran.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 28273-2023 tillsynsbegäran.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 47393-2025 tillsynsbegäran mail.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 28273-2023 tillsynsbegäran mail.docx", "A 28273-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 32909-2025</t>
+          <t>A 47393-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2232,10 +2232,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45839</v>
+        <v>45930</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2288,42 +2288,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Korallticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32909-2025 artfynd.xlsx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 47393-2025 artfynd.xlsx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32909-2025 karta.png", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 47393-2025 karta.png", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32909-2025 georefererad karta.tif", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 47393-2025 georefererad karta.tif", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32909-2025 FSC-klagomål.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 47393-2025 FSC-klagomål.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32909-2025 FSC-klagomål mail.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 47393-2025 FSC-klagomål mail.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32909-2025 tillsynsbegäran.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 47393-2025 tillsynsbegäran.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32909-2025 tillsynsbegäran mail.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 47393-2025 tillsynsbegäran mail.docx", "A 47393-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 50366-2025</t>
+          <t>A 32909-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45944</v>
+        <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2393,42 +2393,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Korallticka</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 50366-2025 artfynd.xlsx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32909-2025 artfynd.xlsx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 50366-2025 karta.png", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32909-2025 karta.png", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 50366-2025 georefererad karta.tif", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32909-2025 georefererad karta.tif", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 50366-2025 FSC-klagomål.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32909-2025 FSC-klagomål.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 50366-2025 FSC-klagomål mail.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32909-2025 FSC-klagomål mail.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 50366-2025 tillsynsbegäran.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32909-2025 tillsynsbegäran.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 50366-2025 tillsynsbegäran mail.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32909-2025 tillsynsbegäran mail.docx", "A 32909-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 45211-2022</t>
+          <t>A 50366-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44844</v>
+        <v>45944</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2458,17 +2458,17 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
@@ -2482,7 +2482,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2494,46 +2494,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Korallticka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 45211-2022 artfynd.xlsx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 50366-2025 artfynd.xlsx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 45211-2022 karta.png", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 50366-2025 karta.png", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 45211-2022 georefererad karta.tif", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 50366-2025 georefererad karta.tif", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 45211-2022 FSC-klagomål.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 50366-2025 FSC-klagomål.docx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 45211-2022 FSC-klagomål mail.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 50366-2025 FSC-klagomål mail.docx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 45211-2022 tillsynsbegäran.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 50366-2025 tillsynsbegäran.docx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 45211-2022 tillsynsbegäran mail.docx", "A 45211-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 50366-2025 tillsynsbegäran mail.docx", "A 50366-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 18647-2025</t>
+          <t>A 41724-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45763</v>
+        <v>44827</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2562,23 +2562,18 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
@@ -2592,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2608,42 +2603,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 18647-2025 artfynd.xlsx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 41724-2022 artfynd.xlsx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 18647-2025 karta.png", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 41724-2022 karta.png", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 18647-2025 georefererad karta.tif", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 41724-2022 georefererad karta.tif", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 18647-2025 FSC-klagomål.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 41724-2022 FSC-klagomål.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 18647-2025 FSC-klagomål mail.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 41724-2022 FSC-klagomål mail.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 18647-2025 tillsynsbegäran.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 41724-2022 tillsynsbegäran.docx", "A 41724-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 18647-2025 tillsynsbegäran mail.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 41724-2022 tillsynsbegäran mail.docx", "A 41724-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 19083-2022</t>
+          <t>A 18647-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2657,10 +2652,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44691</v>
+        <v>45763</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2672,20 +2667,25 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2697,10 +2697,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2709,39 +2709,39 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Läderbagge</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 19083-2022 artfynd.xlsx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 18647-2025 artfynd.xlsx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 19083-2022 karta.png", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 18647-2025 karta.png", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 19083-2022 georefererad karta.tif", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 18647-2025 georefererad karta.tif", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 19083-2022 FSC-klagomål.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 18647-2025 FSC-klagomål.docx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 19083-2022 FSC-klagomål mail.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 18647-2025 FSC-klagomål mail.docx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 19083-2022 tillsynsbegäran.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 18647-2025 tillsynsbegäran.docx", "A 18647-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 19083-2022 tillsynsbegäran mail.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 18647-2025 tillsynsbegäran mail.docx", "A 18647-2025")</f>
         <v/>
       </c>
     </row>
@@ -2765,7 +2765,7 @@
         <v>45011</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 5086-2024</t>
+          <t>A 19083-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45330</v>
+        <v>44691</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2887,20 +2887,20 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
@@ -2911,58 +2911,58 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
         <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Läderbagge</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 5086-2024 artfynd.xlsx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 19083-2022 artfynd.xlsx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 5086-2024 karta.png", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 19083-2022 karta.png", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 5086-2024 georefererad karta.tif", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 19083-2022 georefererad karta.tif", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 5086-2024 FSC-klagomål.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 19083-2022 FSC-klagomål.docx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 5086-2024 FSC-klagomål mail.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 19083-2022 FSC-klagomål mail.docx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 5086-2024 tillsynsbegäran.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 19083-2022 tillsynsbegäran.docx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 5086-2024 tillsynsbegäran mail.docx", "A 5086-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 19083-2022 tillsynsbegäran mail.docx", "A 19083-2022")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31326-2026</t>
+          <t>A 45211-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46219</v>
+        <v>44844</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2992,16 +2992,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3016,7 +3016,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3028,50 +3028,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 31326-2026 artfynd.xlsx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 45211-2022 artfynd.xlsx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 31326-2026 karta.png", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 45211-2022 karta.png", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 31326-2026 georefererad karta.tif", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 45211-2022 georefererad karta.tif", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 31326-2026 FSC-klagomål.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 45211-2022 FSC-klagomål.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 31326-2026 FSC-klagomål mail.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 45211-2022 FSC-klagomål mail.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 31326-2026 tillsynsbegäran.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 45211-2022 tillsynsbegäran.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 31326-2026 tillsynsbegäran mail.docx", "A 31326-2026")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 31326-2026 prioriterade fågelarter.docx", "A 31326-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 45211-2022 tillsynsbegäran mail.docx", "A 45211-2022")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 28273-2023</t>
+          <t>A 31326-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3085,10 +3081,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45099</v>
+        <v>46219</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3101,7 +3097,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3110,7 +3106,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3125,7 +3121,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3141,35 +3137,39 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 28273-2023 artfynd.xlsx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 31326-2026 artfynd.xlsx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 28273-2023 karta.png", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 31326-2026 karta.png", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 28273-2023 georefererad karta.tif", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 31326-2026 georefererad karta.tif", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 28273-2023 FSC-klagomål.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 31326-2026 FSC-klagomål.docx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 28273-2023 FSC-klagomål mail.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 31326-2026 FSC-klagomål mail.docx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 28273-2023 tillsynsbegäran.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 31326-2026 tillsynsbegäran.docx", "A 31326-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 28273-2023 tillsynsbegäran mail.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 31326-2026 tillsynsbegäran mail.docx", "A 31326-2026")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 31326-2026 prioriterade fågelarter.docx", "A 31326-2026")</f>
         <v/>
       </c>
     </row>
@@ -3193,7 +3193,7 @@
         <v>46237</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>46247</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>45372</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>44566</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>44490</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>44645</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>44645</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>44490</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>44490</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>44586</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 8786-2022</t>
+          <t>A 63200-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4016,10 +4016,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44614</v>
+        <v>44507</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4031,13 +4031,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>8.1</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4080,7 +4075,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 63200-2021</t>
+          <t>A 8786-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4094,10 +4089,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44507</v>
+        <v>44614</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4109,8 +4104,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>8.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4170,7 +4170,7 @@
         <v>44673</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44840</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>44859</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>44566</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>44684</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>44477</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>44507</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>44581</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44761</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>44757</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>44869</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44812</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>44848</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>44865</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>44490</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>44603</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>44475</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>44803</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>44498</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>44816</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 58418-2024</t>
+          <t>A 9607-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5637,10 +5637,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45634</v>
+        <v>45361</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5696,7 +5696,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 36381-2023</t>
+          <t>A 58650-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5710,10 +5710,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45152</v>
+        <v>45251</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5769,7 +5769,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8330-2024</t>
+          <t>A 45239-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45352</v>
+        <v>44844</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5798,8 +5798,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5842,7 +5847,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 16341-2025</t>
+          <t>A 28264-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5852,14 +5857,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45751</v>
+        <v>45099</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5872,7 +5877,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5915,7 +5920,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 10668-2025</t>
+          <t>A 28268-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5929,10 +5934,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45721</v>
+        <v>45099</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5945,7 +5950,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5988,7 +5993,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 13276-2024</t>
+          <t>A 52352-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6002,10 +6007,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45386</v>
+        <v>45224</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6018,7 +6023,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6061,7 +6066,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 61194-2024</t>
+          <t>A 16341-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6071,14 +6076,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45645</v>
+        <v>45751</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6090,13 +6095,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6139,7 +6139,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 849-2023</t>
+          <t>A 13276-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6153,10 +6153,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44931</v>
+        <v>45386</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6212,7 +6212,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 39998-2025</t>
+          <t>A 10668-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6226,10 +6226,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45894</v>
+        <v>45721</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 25434-2025</t>
+          <t>A 61194-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6299,10 +6299,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45800</v>
+        <v>45645</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6314,8 +6314,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6358,7 +6363,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 25435-2025</t>
+          <t>A 39998-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6372,10 +6377,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45800</v>
+        <v>45894</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6388,7 +6393,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6431,7 +6436,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 25436-2025</t>
+          <t>A 1352-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6445,10 +6450,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45800</v>
+        <v>44931</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6461,7 +6466,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6504,7 +6509,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 44608-2023</t>
+          <t>A 25434-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6518,10 +6523,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45189</v>
+        <v>45800</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6534,7 +6539,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6577,7 +6582,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 26105-2025</t>
+          <t>A 28267-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6587,14 +6592,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45805</v>
+        <v>45099</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6607,7 +6612,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5.3</v>
+        <v>0.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6650,7 +6655,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 10703-2025</t>
+          <t>A 25435-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6664,10 +6669,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45722</v>
+        <v>45800</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6680,7 +6685,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6723,7 +6728,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 41721-2022</t>
+          <t>A 25436-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6737,10 +6742,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44827</v>
+        <v>45800</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6753,7 +6758,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6796,7 +6801,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 31917-2022</t>
+          <t>A 26105-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6806,14 +6811,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44777</v>
+        <v>45805</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6826,7 +6831,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.9</v>
+        <v>5.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6869,7 +6874,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 11889-2024</t>
+          <t>A 72879-2021</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6883,10 +6888,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45376</v>
+        <v>44547</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6899,7 +6904,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6942,7 +6947,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 11772-2024</t>
+          <t>A 10703-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6956,10 +6961,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45373</v>
+        <v>45722</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6972,7 +6977,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7015,7 +7020,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 11773-2024</t>
+          <t>A 62499-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7029,10 +7034,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45373</v>
+        <v>44924</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7044,8 +7049,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7105,7 +7115,7 @@
         <v>45819</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7166,7 +7176,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 45007-2025</t>
+          <t>A 3932-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7180,10 +7190,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45918</v>
+        <v>44587</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7196,7 +7206,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7239,7 +7249,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 47175-2025</t>
+          <t>A 45007-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7253,10 +7263,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45930</v>
+        <v>45918</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7269,7 +7279,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7312,7 +7322,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 47383-2025</t>
+          <t>A 31258-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7326,10 +7336,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45930</v>
+        <v>45833</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7342,7 +7352,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>5.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7385,7 +7395,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 31258-2025</t>
+          <t>A 3960-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7399,10 +7409,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45833</v>
+        <v>46044</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7414,8 +7424,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7475,7 +7490,7 @@
         <v>45930</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7531,7 +7546,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 47389-2025</t>
+          <t>A 47175-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7548,7 +7563,7 @@
         <v>45930</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7561,7 +7576,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7604,7 +7619,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 17010-2022</t>
+          <t>A 47389-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7618,10 +7633,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44676</v>
+        <v>45930</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7634,7 +7649,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7677,7 +7692,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 32967-2025</t>
+          <t>A 47383-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7691,10 +7706,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45839</v>
+        <v>45930</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7707,7 +7722,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7750,7 +7765,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 61021-2022</t>
+          <t>A 58418-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7760,14 +7775,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44914</v>
+        <v>45634</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7780,7 +7795,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7823,7 +7838,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 30205-2023</t>
+          <t>A 32967-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7837,10 +7852,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45110</v>
+        <v>45839</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7853,7 +7868,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>6.8</v>
+        <v>0.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7896,7 +7911,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 6925-2023</t>
+          <t>A 13170-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7910,10 +7925,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44967</v>
+        <v>45386</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7925,13 +7940,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7974,7 +7984,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 58236-2024</t>
+          <t>A 45180-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7988,10 +7998,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45632</v>
+        <v>45575</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8003,13 +8013,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>2.3</v>
+        <v>14.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8052,7 +8057,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 58691-2024</t>
+          <t>A 36304-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8066,10 +8071,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45635</v>
+        <v>45152</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8081,13 +8086,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8130,7 +8130,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 52141-2025</t>
+          <t>A 49256-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8144,10 +8144,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45953</v>
+        <v>45210</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8203,7 +8203,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 22278-2024</t>
+          <t>A 6925-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8217,10 +8217,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45446</v>
+        <v>44967</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8232,8 +8232,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8276,7 +8281,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 13450-2025</t>
+          <t>A 58236-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8290,10 +8295,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45736</v>
+        <v>45632</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8305,8 +8310,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8349,7 +8359,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 17069-2023</t>
+          <t>A 58691-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8363,10 +8373,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45034</v>
+        <v>45635</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8378,8 +8388,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8422,7 +8437,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 1379-2025</t>
+          <t>A 10596-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8436,10 +8451,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45667</v>
+        <v>45366</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8452,7 +8467,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8495,7 +8510,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 56365-2025</t>
+          <t>A 21285-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8509,10 +8524,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45974</v>
+        <v>45440</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8525,7 +8540,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8568,7 +8583,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 56347-2025</t>
+          <t>A 5044-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8582,10 +8597,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45974</v>
+        <v>46049</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8598,7 +8613,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>10.9</v>
+        <v>5.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8641,7 +8656,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 56352-2025</t>
+          <t>A 13450-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8655,10 +8670,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45974</v>
+        <v>45736</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8671,7 +8686,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5.9</v>
+        <v>1.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8714,7 +8729,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 56414-2025</t>
+          <t>A 52141-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8728,10 +8743,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45975</v>
+        <v>45953</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8744,7 +8759,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8787,7 +8802,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 56340-2025</t>
+          <t>A 41721-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8801,10 +8816,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45974</v>
+        <v>44827</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8817,7 +8832,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8860,7 +8875,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 56417-2025</t>
+          <t>A 55764-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8874,10 +8889,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45975</v>
+        <v>45623</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8890,7 +8905,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8933,7 +8948,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 56346-2025</t>
+          <t>A 56169-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8947,10 +8962,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45974</v>
+        <v>45624</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8963,7 +8978,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>18.8</v>
+        <v>19.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9006,7 +9021,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 58517-2025</t>
+          <t>A 850-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9020,10 +9035,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45985</v>
+        <v>44931</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9036,7 +9051,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9079,7 +9094,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 58520-2025</t>
+          <t>A 56365-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9093,10 +9108,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45985</v>
+        <v>45974</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9109,7 +9124,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9152,7 +9167,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 3960-2026</t>
+          <t>A 56347-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9166,10 +9181,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46044</v>
+        <v>45974</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9181,13 +9196,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>3.7</v>
+        <v>10.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9230,7 +9240,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 58766-2025</t>
+          <t>A 56352-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9244,10 +9254,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45986</v>
+        <v>45974</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9260,7 +9270,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>5.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9303,7 +9313,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 58767-2025</t>
+          <t>A 56346-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9317,10 +9327,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45986</v>
+        <v>45974</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9333,7 +9343,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.7</v>
+        <v>18.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9376,7 +9386,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 45180-2024</t>
+          <t>A 56340-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9390,10 +9400,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45575</v>
+        <v>45974</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9406,7 +9416,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>14.7</v>
+        <v>4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9449,7 +9459,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 5044-2026</t>
+          <t>A 56417-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9463,10 +9473,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46049</v>
+        <v>45975</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9479,7 +9489,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>5.4</v>
+        <v>1.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9522,7 +9532,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 14502-2023</t>
+          <t>A 56414-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9536,10 +9546,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45012</v>
+        <v>45975</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9552,7 +9562,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9595,7 +9605,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 13340-2022</t>
+          <t>A 61294-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9609,10 +9619,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44645</v>
+        <v>45645</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9625,7 +9635,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.9</v>
+        <v>0.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9668,7 +9678,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 13348-2022</t>
+          <t>A 12660-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9678,14 +9688,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44645</v>
+        <v>45000</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9698,7 +9708,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9741,7 +9751,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 13366-2022</t>
+          <t>A 58766-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9755,10 +9765,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44645</v>
+        <v>45986</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9771,7 +9781,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9814,7 +9824,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 15646-2023</t>
+          <t>A 58767-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9828,10 +9838,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45021</v>
+        <v>45986</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9844,7 +9854,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9887,7 +9897,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 9607-2024</t>
+          <t>A 58517-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9901,10 +9911,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45361</v>
+        <v>45985</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9917,7 +9927,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9960,7 +9970,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 60559-2025</t>
+          <t>A 58520-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9974,10 +9984,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45995</v>
+        <v>45985</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9990,7 +10000,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10033,7 +10043,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 9145-2023</t>
+          <t>A 62390-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10047,10 +10057,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44974</v>
+        <v>45268</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10063,7 +10073,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10106,7 +10116,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 10630-2026</t>
+          <t>A 62402-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10120,10 +10130,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46078</v>
+        <v>45268</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10179,7 +10189,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 13268-2024</t>
+          <t>A 11771-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10193,10 +10203,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45386</v>
+        <v>45373</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10209,7 +10219,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>6.7</v>
+        <v>3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10252,7 +10262,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 10451-2024</t>
+          <t>A 10630-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10266,10 +10276,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45366</v>
+        <v>46078</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10281,13 +10291,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10330,7 +10335,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 11459-2026</t>
+          <t>A 31981-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10344,10 +10349,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46083</v>
+        <v>45119</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10360,7 +10365,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10403,7 +10408,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 11460-2026</t>
+          <t>A 11459-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10420,7 +10425,7 @@
         <v>46083</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10433,7 +10438,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10476,7 +10481,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 11630-2026</t>
+          <t>A 11460-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10490,10 +10495,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10505,13 +10510,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10554,7 +10554,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 12660-2023</t>
+          <t>A 60559-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10564,14 +10564,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45000</v>
+        <v>45995</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10627,7 +10627,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 22055-2023</t>
+          <t>A 11630-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10641,10 +10641,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45069</v>
+        <v>46084</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10656,8 +10656,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10700,7 +10705,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 10596-2024</t>
+          <t>A 15646-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10714,10 +10719,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45366</v>
+        <v>45021</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10730,7 +10735,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10773,7 +10778,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 28268-2023</t>
+          <t>A 62510-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10787,10 +10792,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45099</v>
+        <v>44924</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10802,8 +10807,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10846,7 +10856,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 850-2023</t>
+          <t>A 61021-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10856,14 +10866,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44931</v>
+        <v>44914</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10876,7 +10886,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10919,7 +10929,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 55764-2024</t>
+          <t>A 849-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10933,10 +10943,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45623</v>
+        <v>44931</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10949,7 +10959,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10992,7 +11002,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 19674-2023</t>
+          <t>A 31969-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11006,10 +11016,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45051</v>
+        <v>45119</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11022,7 +11032,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11065,7 +11075,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 19683-2023</t>
+          <t>A 31978-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11079,10 +11089,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45051</v>
+        <v>45119</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11095,7 +11105,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11138,7 +11148,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 8765-2022</t>
+          <t>A 18776-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11152,10 +11162,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44614</v>
+        <v>46128</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11167,13 +11177,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11216,7 +11221,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 52352-2023</t>
+          <t>A 28258-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11230,10 +11235,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45224</v>
+        <v>45099</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11246,7 +11251,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11289,7 +11294,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 18776-2026</t>
+          <t>A 22278-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11303,10 +11308,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46128</v>
+        <v>45446</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11319,7 +11324,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11362,7 +11367,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 62510-2022</t>
+          <t>A 17069-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11376,10 +11381,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44924</v>
+        <v>45034</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11391,13 +11396,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11440,7 +11440,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 45013-2025</t>
+          <t>A 59074-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11454,10 +11454,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45918</v>
+        <v>45252</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11513,7 +11513,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 1662-2025</t>
+          <t>A 11772-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11527,10 +11527,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45670</v>
+        <v>45373</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11586,7 +11586,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 30174-2022</t>
+          <t>A 11773-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11600,10 +11600,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44757</v>
+        <v>45373</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11659,7 +11659,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 17876-2025</t>
+          <t>A 30174-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11673,10 +11673,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45758</v>
+        <v>44757</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11732,7 +11732,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 34161-2025</t>
+          <t>A 8765-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11746,10 +11746,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45845</v>
+        <v>44614</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11761,8 +11761,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11805,7 +11810,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 13170-2024</t>
+          <t>A 30205-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11819,10 +11824,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45386</v>
+        <v>45110</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11835,7 +11840,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.7</v>
+        <v>6.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11878,7 +11883,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 25594-2025</t>
+          <t>A 45013-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11888,14 +11893,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45803</v>
+        <v>45918</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11908,7 +11913,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11951,7 +11956,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 62390-2023</t>
+          <t>A 34161-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11965,10 +11970,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45268</v>
+        <v>45845</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11981,7 +11986,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.8</v>
+        <v>4.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12024,7 +12029,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 20710-2026</t>
+          <t>A 1662-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12038,10 +12043,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46141</v>
+        <v>45670</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12054,7 +12059,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12097,7 +12102,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 20811-2026</t>
+          <t>A 20710-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12114,7 +12119,7 @@
         <v>46141</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12127,7 +12132,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12170,7 +12175,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 33162-2024</t>
+          <t>A 20812-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12184,10 +12189,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45518</v>
+        <v>46141</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12243,7 +12248,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 20812-2026</t>
+          <t>A 33162-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12257,10 +12262,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46141</v>
+        <v>45518</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12333,7 +12338,7 @@
         <v>46141</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12389,7 +12394,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 62499-2022</t>
+          <t>A 25594-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12399,14 +12404,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44924</v>
+        <v>45803</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12418,13 +12423,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12467,7 +12467,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 21369-2026</t>
+          <t>A 1379-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12481,10 +12481,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46147</v>
+        <v>45667</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12540,7 +12540,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 10958-2022</t>
+          <t>A 20811-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12554,10 +12554,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44628</v>
+        <v>46141</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12570,7 +12570,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12613,7 +12613,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 45239-2022</t>
+          <t>A 21376-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12627,10 +12627,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44844</v>
+        <v>46147</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12642,13 +12642,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>1.7</v>
+        <v>7.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12691,7 +12686,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 21376-2026</t>
+          <t>A 21369-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12708,7 +12703,7 @@
         <v>46147</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12721,7 +12716,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>7.2</v>
+        <v>1.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12764,7 +12759,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 15426-2025</t>
+          <t>A 44608-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12778,10 +12773,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45747</v>
+        <v>45189</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12837,7 +12832,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 15442-2025</t>
+          <t>A 44033-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12851,10 +12846,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45747</v>
+        <v>45572</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12867,7 +12862,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12910,7 +12905,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 22916-2026</t>
+          <t>A 13366-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12924,10 +12919,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46160</v>
+        <v>44645</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12940,7 +12935,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12983,7 +12978,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 22906-2026</t>
+          <t>A 15428-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12997,10 +12992,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46160</v>
+        <v>45747</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13013,7 +13008,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13056,7 +13051,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 22912-2026</t>
+          <t>A 15434-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13070,10 +13065,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46160</v>
+        <v>45747</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13086,7 +13081,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13129,7 +13124,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 12450-2022</t>
+          <t>A 17010-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13143,10 +13138,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44638</v>
+        <v>44676</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13159,7 +13154,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13202,7 +13197,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 21429-2022</t>
+          <t>A 22906-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13216,10 +13211,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44706</v>
+        <v>46160</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13232,7 +13227,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13275,7 +13270,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 56169-2024</t>
+          <t>A 19674-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13289,10 +13284,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45624</v>
+        <v>45051</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13305,7 +13300,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>19.7</v>
+        <v>0.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13348,7 +13343,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 13279-2024</t>
+          <t>A 13345-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13362,10 +13357,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45386</v>
+        <v>44645</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13378,7 +13373,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13421,7 +13416,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 49256-2023</t>
+          <t>A 22916-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13435,10 +13430,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45210</v>
+        <v>46160</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13451,7 +13446,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13494,7 +13489,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 31969-2023</t>
+          <t>A 22912-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13508,10 +13503,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45119</v>
+        <v>46160</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13524,7 +13519,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13567,7 +13562,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 31978-2023</t>
+          <t>A 21429-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13581,10 +13576,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45119</v>
+        <v>44706</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13597,7 +13592,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13640,7 +13635,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 39150-2022</t>
+          <t>A 35408-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13654,10 +13649,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44817</v>
+        <v>45146</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13670,7 +13665,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13713,7 +13708,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 25777-2026</t>
+          <t>A 55511-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13723,14 +13718,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46178</v>
+        <v>45238</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13743,7 +13738,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13803,7 +13798,7 @@
         <v>45152</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13859,7 +13854,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 26338-2026</t>
+          <t>A 25777-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13869,14 +13864,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13889,7 +13884,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13932,7 +13927,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 3932-2022</t>
+          <t>A 49252-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13946,10 +13941,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44587</v>
+        <v>45210</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13962,7 +13957,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14005,7 +14000,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 7225-2023</t>
+          <t>A 31917-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14019,10 +14014,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44970</v>
+        <v>44777</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14035,7 +14030,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14078,7 +14073,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 35408-2023</t>
+          <t>A 17876-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14092,10 +14087,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45146</v>
+        <v>45758</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14108,7 +14103,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14151,7 +14146,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 13280-2024</t>
+          <t>A 26338-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14165,10 +14160,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45386</v>
+        <v>46182</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14181,7 +14176,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14224,7 +14219,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 31981-2023</t>
+          <t>A 12450-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14238,10 +14233,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45119</v>
+        <v>44638</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14254,7 +14249,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14297,7 +14292,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 55511-2023</t>
+          <t>A 64712-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14311,10 +14306,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45238</v>
+        <v>45281</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14327,7 +14322,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14370,7 +14365,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 28258-2023</t>
+          <t>A 10636-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14384,10 +14379,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45099</v>
+        <v>46078</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14400,7 +14395,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14443,7 +14438,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 28264-2023</t>
+          <t>A 39081-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14457,10 +14452,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45099</v>
+        <v>44817</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14473,7 +14468,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14516,7 +14511,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 10636-2026</t>
+          <t>A 36381-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14530,10 +14525,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46078</v>
+        <v>45152</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14546,7 +14541,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14589,7 +14584,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 49252-2023</t>
+          <t>A 28647-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14603,10 +14598,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45210</v>
+        <v>46198</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14619,7 +14614,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14679,7 +14674,7 @@
         <v>46197</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14735,7 +14730,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 28647-2026</t>
+          <t>A 13268-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14749,10 +14744,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46198</v>
+        <v>45386</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14765,7 +14760,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.6</v>
+        <v>6.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14808,7 +14803,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 20507-2026</t>
+          <t>A 13281-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14822,10 +14817,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46140</v>
+        <v>45386</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14838,7 +14833,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14881,7 +14876,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 28335-2023</t>
+          <t>A 19683-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14895,10 +14890,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45099</v>
+        <v>45051</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14911,7 +14906,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14954,7 +14949,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 13281-2024</t>
+          <t>A 58417-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14968,10 +14963,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45386</v>
+        <v>45634</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14983,8 +14978,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15027,7 +15027,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 58650-2023</t>
+          <t>A 20507-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15041,10 +15041,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45251</v>
+        <v>46140</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15100,7 +15100,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 36304-2023</t>
+          <t>A 39150-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15114,10 +15114,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45152</v>
+        <v>44817</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15130,7 +15130,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15190,7 +15190,7 @@
         <v>46206</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 59074-2023</t>
+          <t>A 5690-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15265,10 +15265,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45252</v>
+        <v>46051</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15324,7 +15324,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 34008-2026</t>
+          <t>A 14502-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15338,10 +15338,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46252</v>
+        <v>45012</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15397,7 +15397,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 5690-2026</t>
+          <t>A 10958-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15411,10 +15411,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46051</v>
+        <v>44628</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 15428-2025</t>
+          <t>A 31329-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15484,10 +15484,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45747</v>
+        <v>46219</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.1</v>
+        <v>7.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15543,7 +15543,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 15434-2025</t>
+          <t>A 9145-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15557,10 +15557,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45747</v>
+        <v>44974</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15573,7 +15573,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.1</v>
+        <v>1.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15616,7 +15616,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 11771-2024</t>
+          <t>A 31324-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15630,10 +15630,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45373</v>
+        <v>46219</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15689,7 +15689,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 58417-2024</t>
+          <t>A 35871-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45634</v>
+        <v>46266</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15718,13 +15718,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15767,7 +15762,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 13345-2022</t>
+          <t>A 31446-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15781,10 +15776,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44645</v>
+        <v>46220</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15797,7 +15792,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15840,7 +15835,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 31329-2026</t>
+          <t>A 31452-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15854,10 +15849,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15870,7 +15865,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>7.5</v>
+        <v>3.6</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15913,7 +15908,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 31446-2026</t>
+          <t>A 7225-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15927,10 +15922,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46220</v>
+        <v>44970</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15943,7 +15938,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15986,7 +15981,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 31452-2026</t>
+          <t>A 10451-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16000,10 +15995,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46220</v>
+        <v>45366</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16015,8 +16010,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16059,7 +16059,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 64712-2023</t>
+          <t>A 37557-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16073,10 +16073,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45281</v>
+        <v>46276</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16132,7 +16132,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 31324-2026</t>
+          <t>A 28332-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16146,10 +16146,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46219</v>
+        <v>45099</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16205,7 +16205,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 39081-2022</t>
+          <t>A 8330-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16219,10 +16219,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44817</v>
+        <v>45352</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16278,7 +16278,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 61294-2024</t>
+          <t>A 32298-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16292,10 +16292,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45645</v>
+        <v>46237</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16307,8 +16307,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>0.3</v>
+        <v>3.8</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16351,7 +16356,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 35869-2026</t>
+          <t>A 13279-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16365,10 +16370,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46266</v>
+        <v>45386</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16381,7 +16386,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16424,7 +16429,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 35871-2026</t>
+          <t>A 32363-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16438,10 +16443,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46266</v>
+        <v>46238</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16454,7 +16459,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2.9</v>
+        <v>6.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16497,7 +16502,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 62402-2023</t>
+          <t>A 32364-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16511,10 +16516,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45268</v>
+        <v>46238</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16527,7 +16532,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16570,7 +16575,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 1352-2023</t>
+          <t>A 11889-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16584,10 +16589,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44931</v>
+        <v>45376</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16600,7 +16605,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16643,7 +16648,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 28332-2023</t>
+          <t>A 15426-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16657,10 +16662,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45099</v>
+        <v>45747</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16673,7 +16678,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16716,7 +16721,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 44033-2024</t>
+          <t>A 15442-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16730,10 +16735,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45572</v>
+        <v>45747</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16746,7 +16751,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16789,7 +16794,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 72879-2021</t>
+          <t>A 13340-2022</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16803,10 +16808,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44547</v>
+        <v>44645</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16819,7 +16824,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16862,7 +16867,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 28267-2023</t>
+          <t>A 13348-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16876,10 +16881,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45099</v>
+        <v>44645</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16892,7 +16897,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16935,7 +16940,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 37557-2026</t>
+          <t>A 22055-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16949,10 +16954,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46276</v>
+        <v>45069</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16965,7 +16970,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17008,7 +17013,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 32298-2026</t>
+          <t>A 13280-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17022,10 +17027,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46237</v>
+        <v>45386</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17037,13 +17042,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I213" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17086,7 +17086,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 21285-2024</t>
+          <t>A 28335-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17100,10 +17100,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45440</v>
+        <v>45099</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17159,7 +17159,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 32363-2026</t>
+          <t>A 26336-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17173,10 +17173,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46238</v>
+        <v>46182</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>6.2</v>
+        <v>1.3</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17232,7 +17232,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 32364-2026</t>
+          <t>A 39846-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17246,10 +17246,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46238</v>
+        <v>46290</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17261,8 +17261,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I216" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17305,7 +17310,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 28316-2024</t>
+          <t>A 39848-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17319,10 +17324,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45477</v>
+        <v>46290</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17334,8 +17339,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17378,7 +17388,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 21269-2024</t>
+          <t>A 12664-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17392,10 +17402,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45440</v>
+        <v>45000</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17408,7 +17418,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17451,7 +17461,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 12664-2023</t>
+          <t>A 21269-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17465,10 +17475,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45000</v>
+        <v>45440</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17481,7 +17491,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17524,7 +17534,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 39842-2026</t>
+          <t>A 28316-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17538,10 +17548,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46290</v>
+        <v>45477</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17553,13 +17563,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I220" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17602,7 +17607,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 26336-2026</t>
+          <t>A 39837-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17616,10 +17621,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46182</v>
+        <v>46290</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17631,8 +17636,13 @@
           <t>GÖTENE</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I221" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17675,7 +17685,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 39848-2026</t>
+          <t>A 39842-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17692,7 +17702,7 @@
         <v>46290</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17710,7 +17720,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17753,7 +17763,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 39846-2026</t>
+          <t>A 35869-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17767,10 +17777,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46290</v>
+        <v>46266</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17782,13 +17792,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I223" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17831,7 +17836,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 39837-2026</t>
+          <t>A 34008-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17845,10 +17850,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46290</v>
+        <v>46252</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17860,13 +17865,8 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17926,7 +17926,7 @@
         <v>44862</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>45352</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>45352</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>

--- a/Översikt GÖTENE.xlsx
+++ b/Översikt GÖTENE.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44642</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45352</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>46290</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>45847</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>45846</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>46234</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>46290</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>44827</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>44490</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>45330</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28273-2023</t>
+          <t>A 19083-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45099</v>
+        <v>44691</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.1</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2155,7 +2155,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2167,10 +2167,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2179,46 +2179,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Läderbagge</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 28273-2023 artfynd.xlsx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 19083-2022 artfynd.xlsx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 28273-2023 karta.png", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 19083-2022 karta.png", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 28273-2023 georefererad karta.tif", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 19083-2022 georefererad karta.tif", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 28273-2023 FSC-klagomål.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 19083-2022 FSC-klagomål.docx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 28273-2023 FSC-klagomål mail.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 19083-2022 FSC-klagomål mail.docx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 28273-2023 tillsynsbegäran.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 19083-2022 tillsynsbegäran.docx", "A 19083-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 28273-2023 tillsynsbegäran mail.docx", "A 28273-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 19083-2022 tillsynsbegäran mail.docx", "A 19083-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 47393-2025</t>
+          <t>A 45211-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2232,10 +2232,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45930</v>
+        <v>44844</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2272,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2284,46 +2284,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Korallticka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 47393-2025 artfynd.xlsx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 45211-2022 artfynd.xlsx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 47393-2025 karta.png", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 45211-2022 karta.png", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 47393-2025 georefererad karta.tif", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 45211-2022 georefererad karta.tif", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 47393-2025 FSC-klagomål.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 45211-2022 FSC-klagomål.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 47393-2025 FSC-klagomål mail.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 45211-2022 FSC-klagomål mail.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 47393-2025 tillsynsbegäran.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 45211-2022 tillsynsbegäran.docx", "A 45211-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 47393-2025 tillsynsbegäran mail.docx", "A 47393-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 45211-2022 tillsynsbegäran mail.docx", "A 45211-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 32909-2025</t>
+          <t>A 28273-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45839</v>
+        <v>45099</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2353,16 +2353,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2377,7 +2377,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2393,42 +2393,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32909-2025 artfynd.xlsx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 28273-2023 artfynd.xlsx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32909-2025 karta.png", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 28273-2023 karta.png", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32909-2025 georefererad karta.tif", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 28273-2023 georefererad karta.tif", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32909-2025 FSC-klagomål.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 28273-2023 FSC-klagomål.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32909-2025 FSC-klagomål mail.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 28273-2023 FSC-klagomål mail.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32909-2025 tillsynsbegäran.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 28273-2023 tillsynsbegäran.docx", "A 28273-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32909-2025 tillsynsbegäran mail.docx", "A 32909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 28273-2023 tillsynsbegäran mail.docx", "A 28273-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 50366-2025</t>
+          <t>A 14296-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45944</v>
+        <v>45011</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2458,19 +2458,19 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2485,7 +2485,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2494,39 +2494,43 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Korallticka</t>
+          <t>Pilgrimsfalk</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 50366-2025 artfynd.xlsx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 14296-2023 artfynd.xlsx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 50366-2025 karta.png", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 14296-2023 karta.png", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 50366-2025 georefererad karta.tif", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 14296-2023 georefererad karta.tif", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 50366-2025 FSC-klagomål.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 14296-2023 FSC-klagomål.docx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 50366-2025 FSC-klagomål mail.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 14296-2023 FSC-klagomål mail.docx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 50366-2025 tillsynsbegäran.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 14296-2023 tillsynsbegäran.docx", "A 14296-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 50366-2025 tillsynsbegäran mail.docx", "A 50366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 14296-2023 tillsynsbegäran mail.docx", "A 14296-2023")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 14296-2023 prioriterade fågelarter.docx", "A 14296-2023")</f>
         <v/>
       </c>
     </row>
@@ -2550,7 +2554,7 @@
         <v>44827</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2638,7 +2642,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 18647-2025</t>
+          <t>A 32909-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2652,10 +2656,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45763</v>
+        <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2667,23 +2671,18 @@
           <t>GÖTENE</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
@@ -2697,7 +2696,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2713,42 +2712,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 18647-2025 artfynd.xlsx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 32909-2025 artfynd.xlsx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 18647-2025 karta.png", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 32909-2025 karta.png", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 18647-2025 georefererad karta.tif", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 32909-2025 georefererad karta.tif", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 18647-2025 FSC-klagomål.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 32909-2025 FSC-klagomål.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 18647-2025 FSC-klagomål mail.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 32909-2025 FSC-klagomål mail.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 18647-2025 tillsynsbegäran.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 32909-2025 tillsynsbegäran.docx", "A 32909-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 18647-2025 tillsynsbegäran mail.docx", "A 18647-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 32909-2025 tillsynsbegäran mail.docx", "A 32909-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 14296-2023</t>
+          <t>A 50366-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2762,10 +2761,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45011</v>
+        <v>45944</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2778,19 +2777,19 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2805,7 +2804,7 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2814,50 +2813,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Pilgrimsfalk</t>
+          <t>Korallticka</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 14296-2023 artfynd.xlsx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 50366-2025 artfynd.xlsx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 14296-2023 karta.png", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 50366-2025 karta.png", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 14296-2023 georefererad karta.tif", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 50366-2025 georefererad karta.tif", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 14296-2023 FSC-klagomål.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 50366-2025 FSC-klagomål.docx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 14296-2023 FSC-klagomål mail.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 50366-2025 FSC-klagomål mail.docx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 14296-2023 tillsynsbegäran.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 50366-2025 tillsynsbegäran.docx", "A 50366-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 14296-2023 tillsynsbegäran mail.docx", "A 14296-2023")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/fåglar/A 14296-2023 prioriterade fågelarter.docx", "A 14296-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsynsmail/A 50366-2025 tillsynsbegäran mail.docx", "A 50366-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 19083-2022</t>
+          <t>A 47393-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2871,10 +2866,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44691</v>
+        <v>45930</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2887,19 +2882,19 @@
         </is>
       </c>
       <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2914,7 +2909,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2923,46 +2918,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Läderbagge</t>
+          <t>Korallticka</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 19083-2022 artfynd.xlsx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/artfynd/A 47393-2025 artfynd.xlsx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 19083-2022 karta.png", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor/A 47393-2025 karta.png", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 19083-2022 georefererad karta.tif", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/kartor_geotiff/A 47393-2025 georefererad karta.tif", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 19083-2022 FSC-klagomål.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomål/A 47393-2025 FSC-klagomål.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 19083-2022 FSC-klagomål mail.docx", "A 19083-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1471/klagomålsmail/A 47393-2025 FSC-klagomål mail.docx", "A 47393-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1471/tillsyn/A 19083-2022 tillsynsbegäran.docx", "A 19083-2022")</f>
+        <f>HYPERL